--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -1492,10 +1492,10 @@
     <t>RemoteCheckoutAction</t>
   </si>
   <si>
-    <t>만들고 전환</t>
-  </si>
-  <si>
-    <t>Create and switch</t>
+    <t>체크아웃</t>
+  </si>
+  <si>
+    <t>Checkout</t>
   </si>
   <si>
     <t>RemoteCheckoutDescription</t>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D342"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -7296,6 +7296,426 @@
       <c r="D321" t="inlineStr">
         <is>
           <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322">
+        <v>2906</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteLocalBranch</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>로컬 브랜치 삭제...</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Delete local branch...</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323">
+        <v>2907</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteRemoteBranch</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>원격 브랜치 삭제...</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Delete remote branch...</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324">
+        <v>2908</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteLocalBranchTitle</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>로컬 브랜치 삭제</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Delete local branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325">
+        <v>2909</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteRemoteBranchTitle</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>원격 브랜치 삭제</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Delete remote branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326">
+        <v>2910</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteLocalBranchConfirm</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>{0} 브랜치를 삭제하시겠습니까? 병합되지 않은 커밋이 있으면 삭제하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Delete local branch {0}? Git will keep it if it contains unmerged commits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327">
+        <v>2911</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteRemoteBranchConfirm</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>원격 브랜치 {0}을(를) 서버에서 삭제하시겠습니까? 다른 사용자에게도 영향을 주며 앱에서 되돌릴 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Delete remote branch {0} from the server? This affects other users and cannot be undone from the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328">
+        <v>2912</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ReferenceDeleteBranchAction</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>브랜치 삭제</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Delete branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329">
+        <v>2913</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ReferenceDeletingBranch</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>{0} 브랜치 삭제 중...</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Deleting branch {0}...</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330">
+        <v>2914</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleted</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>{0} 로컬 브랜치를 삭제했습니다.</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Deleted local branch {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331">
+        <v>2915</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleted</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>{0} 원격 브랜치를 삭제했습니다.</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Deleted remote branch {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332">
+        <v>2916</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ReferenceBranchDeleteRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>{0} 참조 목록 새로고침 실패: {1}</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>{0} Could not refresh references: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333">
+        <v>2917</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleteCurrent</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>현재 체크아웃된 {0} 브랜치는 삭제할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Cannot delete the checked-out branch {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334">
+        <v>2918</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleteMissing</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>{0} 로컬 브랜치를 찾을 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Local branch {0} no longer exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335">
+        <v>2919</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleteChanged</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>{0} 브랜치가 확인 이후 변경되었습니다. 새로고친 뒤 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Branch {0} changed after confirmation. Refresh and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336">
+        <v>2920</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleteFailed</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>{0} 로컬 브랜치를 삭제하지 못했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Could not delete local branch {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337">
+        <v>2921</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ReferenceLocalBranchDeleteFailedWithoutOutput</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>{0} 로컬 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Could not delete local branch {0} (exit code {1}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338">
+        <v>2922</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleteDefault</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>{0}은(는) 원격의 기본 브랜치라 삭제할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Cannot delete {0} because it is the remote's default branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339">
+        <v>2923</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleteMissing</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>{0} 원격 브랜치를 찾을 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Remote branch {0} no longer exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340">
+        <v>2924</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleteChanged</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>{0} 원격 브랜치가 확인 이후 변경되었습니다. Fetch한 뒤 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Remote branch {0} changed after confirmation. Fetch and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341">
+        <v>2925</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleteFailed</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>{0} 원격 브랜치를 삭제하지 못했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Could not delete remote branch {0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342">
+        <v>2926</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ReferenceRemoteBranchDeleteFailedWithoutOutput</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>{0} 원격 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Could not delete remote branch {0} (exit code {1}).</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D342"/>
+  <dimension ref="A1:D397"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -4574,11 +4574,15 @@
       <c r="B172" t="s">
         <v>455</v>
       </c>
-      <c r="C172" t="s">
-        <v>456</v>
-      </c>
-      <c r="D172" t="s">
-        <v>457</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>추적 파일 {0}개의 스테이징되지 않은 변경을 버립니다. 이름 변경 {1}개는 원래 경로로 되돌립니다. 이미 스테이징한 변경은 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Discard unstaged changes in {0} tracked files. Restore {1} renames to their original paths. Staged changes remain intact.</t>
+        </is>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -7716,6 +7720,1106 @@
       <c r="D342" t="inlineStr">
         <is>
           <t>Could not delete remote branch {0} (exit code {1}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343">
+        <v>2927</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ConflictBatchCurrentFileLabel</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>현재 파일의 남은 충돌 구간 {0}개</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>{0} unresolved sections remaining in this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344">
+        <v>2928</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ConflictBatchTooltip</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>이미 선택한 구간은 유지합니다. 최종 파일 미리보기만 바뀌며 저장·스테이징은 별도로 해야 합니다.</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Previous choices stay unchanged. This updates only the final-file preview; save and stage separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345">
+        <v>2929</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ConflictBatchReplaceEditsTitle</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>직접 편집한 내용 바꾸기</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Replace manual edits</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346">
+        <v>2930</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ConflictBatchReplaceEditsMessage</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>최종 파일을 직접 편집했습니다. 남은 구간에 일괄 선택을 적용하면 직접 편집한 내용이 사라집니다. 계속할까요?</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>You edited the final file. Applying one choice to the remaining sections will replace those manual edits. Continue?</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347">
+        <v>2931</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ConflictBatchApplyButton</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>일괄 적용</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Apply to remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348">
+        <v>2932</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>RebaseTargetChange</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>리베이스 대상 · 적용된 커밋</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Rebase target · applied commits</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349">
+        <v>2933</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>RebaseReplayChange</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>다시 적용 중인 내 커밋</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>My commit being replayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350">
+        <v>2934</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>RebaseUseTarget</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>리베이스 대상 사용</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Use rebase target</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351">
+        <v>2935</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>RebaseUseReplay</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>내 커밋 사용</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Use my commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352">
+        <v>2936</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RebaseTargetSource</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>리베이스 대상 HEAD</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Rebase target HEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353">
+        <v>2937</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RebaseReplaySource</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>내 커밋 REBASE_HEAD</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>My commit REBASE_HEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354">
+        <v>2938</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>RebaseBothOrderTip</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>둘 다 사용하면 리베이스 대상 내용을 먼저, 다시 적용 중인 내 커밋 내용을 뒤에 둡니다.</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Use both places the rebase target content first, followed by my replayed commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355">
+        <v>2939</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>RebaseProgressLabel</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>리베이스 진행 중</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Rebase in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356">
+        <v>2940</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>RebaseResolveBeforeContinue</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>남은 충돌 {0}건을 해결·스테이징하면 계속할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Resolve and stage {0} remaining conflicts to continue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357">
+        <v>2941</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>RebaseReadyToContinue</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>모든 충돌을 스테이징했습니다. 계속을 눌러 리베이스를 진행하세요.</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>All conflicts are staged. Select Continue rebase to proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358">
+        <v>2942</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>RebaseContinueAction</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>리베이스 계속</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Continue rebase</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359">
+        <v>2943</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>RebaseNoLongerInProgress</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>리베이스가 더 이상 진행 중이지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>The rebase is no longer in progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360">
+        <v>2944</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>RebaseUnresolvedConflicts</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>미해결 충돌 {0}건이 있어 리베이스를 계속할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Cannot continue the rebase while {0} conflicts remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361">
+        <v>2945</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>RebaseContinueFailed</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>리베이스 계속에 실패했습니다(종료 코드 {0}). {1}</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Could not continue the rebase (exit code {0}). {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362">
+        <v>2946</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>RebaseNextConflicts</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>리베이스에서 새 충돌 {0}건이 발생했습니다. 해결·스테이징한 뒤 계속하세요.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>The rebase has {0} new conflicts. Resolve and stage them, then continue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363">
+        <v>2947</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>RebaseContinueCompleted</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>리베이스를 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Rebase completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364">
+        <v>2948</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>RebaseContinueStillInProgress</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>리베이스가 아직 진행 중입니다. Git 상태를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>The rebase is still in progress. Check the Git state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365">
+        <v>2949</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>RebaseRepositoryChanged</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>저장소 루트가 바뀌어 리베이스를 계속하지 않았습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>The repository root changed, so the rebase was not continued: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366">
+        <v>2950</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>RebaseCheckingConflicts</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>충돌 상태를 확인하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Checking the conflict state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367">
+        <v>2951</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>DefaultPullStrategyHeading</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Bough 기본 Pull 방식</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Bough default Pull strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368">
+        <v>2952</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>DefaultPullStrategyDescription</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>모든 저장소에서 Bough의 기본 Pull 동작에 적용됩니다. Git CLI의 pull.rebase 및 pull.ff 설정은 변경하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Applies to Bough's default Pull action for every repository. Git CLI pull.rebase and pull.ff settings are not changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369">
+        <v>2953</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>PullStrategyFastForwardOnly</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>빠른 전진만</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Fast-forward only</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370">
+        <v>2954</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>PullStrategyMerge</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371">
+        <v>2955</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>PullStrategyRebase</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>리베이스</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Rebase</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372">
+        <v>2956</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>DefaultPullStrategySaved</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Bough 기본 Pull 방식 저장: {0}</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Bough default Pull strategy saved: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373">
+        <v>2957</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>RemotePullConfiguredDefaultTip</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>기본 Pull: {0}. upstream이 없으면 받을 원격 브랜치를 선택합니다.</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Default Pull: {0}. Choose a remote branch if there is no upstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374">
+        <v>2958</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>RemotePullConfiguredDefaultAutomation</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Pull (기본 방식: {0})</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Pull (default: {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375">
+        <v>2959</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>RemotePullStrategyMenuTip</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>이번 Pull에 사용할 방식 또는 받을 브랜치를 선택합니다. 기본 방식: {0}</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Choose a strategy or source branch for this Pull. Default: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376">
+        <v>2960</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>RemotePullChooseBranchDefaultTip</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>받을 원격 브랜치를 고른 뒤 기본 방식({0})으로 Pull을 실행합니다.</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Choose a remote branch, then Pull with the default strategy ({0}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377">
+        <v>2961</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>RemotePullFastForwardAction</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>빠른 전진만으로 받기</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Pull fast-forward only</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378">
+        <v>2962</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>RemotePullDefaultSuffix</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (기본)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (default)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379">
+        <v>2963</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>RemotePullStrategyMenuAutomation</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Pull 방식 메뉴 (기본: {0})</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Pull strategy menu (default: {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380">
+        <v>2964</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>RemotePullFastForwardTip</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>현재 upstream에서 빠른 전진만으로 한 번 Pull합니다. upstream이 없으면 받을 원격 브랜치를 선택합니다.</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Pull once from the current upstream using fast-forward only. If there is no upstream, choose a remote branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381">
+        <v>2965</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>DiscardTrackedSelectionCount</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>선택한 추적 파일 {0}개의 변경 버리기</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Discard changes in {0} selected tracked files</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382">
+        <v>2966</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>DeleteUntrackedSelectionCount</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>선택한 미추적 파일 {0}개 삭제</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Delete {0} selected untracked files</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383">
+        <v>2967</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>DiscardMixedSelectionCount</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>변경 버리기 {0}개 · 미추적 파일 삭제 {1}개</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Discard changes in {0} tracked files · delete {1} untracked files</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384">
+        <v>2968</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>DiscardTrackedTitle</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>추적 파일 변경 버리기</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Discard tracked file changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385">
+        <v>2969</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>DeleteUntrackedTitle</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>미추적 파일 삭제</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Delete untracked files</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386">
+        <v>2970</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>DiscardMixedTitle</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>변경 버리기 및 미추적 파일 삭제</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Discard changes and delete untracked files</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387">
+        <v>2971</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>DeleteUntrackedImpact</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>미추적 파일 {0}개를 디스크에서 영구 삭제합니다.</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Permanently delete {0} untracked files from disk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388">
+        <v>2972</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DiscardConfirmMixed</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>변경 버리기 및 파일 삭제</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Discard changes and delete files</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389">
+        <v>2973</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>StopTrackingSelectionCount</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>선택한 추적 파일 {0}개 추적 중지</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Stop tracking {0} selected files</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390">
+        <v>2974</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>StopTrackingTitle</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>파일 추적 중지</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Stop tracking files</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391">
+        <v>2975</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>StopTrackingDescription</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>추적 파일 {0}개를 Git 인덱스에서만 제거합니다. 작업 파일은 삭제하지 않으며, 파일 삭제가 스테이징된 변경으로 표시됩니다. 계속 추적하지 않으려면 작업 후 별도로 무시 규칙을 추가하세요.</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Remove {0} tracked files from the Git index only. Working files are kept, and their deletion is staged. Add ignore rules separately afterward if they should remain untracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392">
+        <v>2976</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>StopTrackingConfirm</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>추적 중지</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Stop tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393">
+        <v>2977</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>LocalStopTrackingRequiresConfirmation</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>추적 중지를 확인할 창을 열 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>The stop-tracking confirmation window is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394">
+        <v>2978</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DiscardTrackedContextMenu</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>변경 버리기</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Discard changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395">
+        <v>2979</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DeleteUntrackedContextMenu</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>파일 삭제</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Delete files</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396">
+        <v>2980</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>DiscardMixedContextMenu</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>변경 버리기 및 파일 삭제</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Discard changes and delete files</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397">
+        <v>2981</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>StopTrackingContextMenu</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>추적 중지</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Stop tracking</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D397"/>
+  <dimension ref="A1:D424"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -8820,6 +8820,546 @@
       <c r="D397" t="inlineStr">
         <is>
           <t>Stop tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398">
+        <v>2982</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>CloneAction</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>복제</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Clone</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399">
+        <v>2983</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>CloneTitle</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>저장소 복제</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Clone repository</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400">
+        <v>2984</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>CloneUrlLabel</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>원격 URL 또는 로컬 경로</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Remote URL or local path</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401">
+        <v>2985</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>CloneParentLabel</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>저장할 상위 폴더</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Parent folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402">
+        <v>2986</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>CloneFolderLabel</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>새 폴더 이름</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>New folder name</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403">
+        <v>2987</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>CloneBrowseParent</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>찾아보기</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Browse</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404">
+        <v>2988</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ClonePickParentTitle</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>복제할 위치 선택</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Choose clone location</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405">
+        <v>2989</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>CloneDestinationPreview</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>생성 위치: {0}</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Destination: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406">
+        <v>2990</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>CloneUrlRequired</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>원격 주소를 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Enter a remote address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407">
+        <v>2991</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>CloneUrlInvalid</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>지원하지 않는 원격 주소입니다.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>The remote address is not supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408">
+        <v>2992</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>CloneUrlContainsCredentials</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>주소에 사용자 이름이나 토큰을 포함할 수 없습니다. Git 인증 도우미를 사용하세요.</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Remove credentials from the address and use the Git credential helper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409">
+        <v>2993</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>CloneParentRequired</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>상위 폴더를 선택하세요.</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Choose a parent folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410">
+        <v>2994</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>CloneParentMissing</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>상위 폴더가 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>The parent folder does not exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411">
+        <v>2995</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>CloneFolderRequired</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>새 폴더 이름을 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Enter a new folder name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412">
+        <v>2996</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>CloneFolderInvalid</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>사용할 수 없는 폴더 이름입니다.</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>The folder name is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413">
+        <v>2997</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>CloneDestinationOccupied</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>생성 위치가 이미 존재합니다: {0}</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>The destination already exists: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414">
+        <v>2998</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>CloneQueued</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>복제 대기 중입니다.</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Waiting to clone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415">
+        <v>2999</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>CloneProgress</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Git 진행 단계: {0}%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Git progress step: {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416">
+        <v>3000</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>CloneRunning</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>저장소를 복제하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Cloning the repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417">
+        <v>3001</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>CloneSucceeded</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>복제가 완료됐습니다.</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Clone completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418">
+        <v>3002</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>CloneCancelled</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>복제가 취소됐습니다.</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Clone canceled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419">
+        <v>3003</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>CloneGitFailed</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Git 복제 명령이 종료 코드 {0}으로 실패했습니다.</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Git clone failed with exit code {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420">
+        <v>3004</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>CloneDestinationPreserved</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>생성 위치에 파일이 남아 있습니다: {0}. 수동으로 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Files remain at {0}. Review them before reuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421">
+        <v>3005</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>CloneDestinationAbsent</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>생성 위치에 폴더가 만들어지지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>No destination folder was created.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422">
+        <v>3006</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>CloneOpenFailed</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>복제는 완료됐지만 저장소를 열지 못했습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Clone completed, but the repository could not be opened: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423">
+        <v>3007</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>CloneStop</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>중단</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424">
+        <v>3008</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>CloneClose</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>닫기</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Close</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D424"/>
+  <dimension ref="A1:D438"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -9360,6 +9360,286 @@
       <c r="D424" t="inlineStr">
         <is>
           <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425">
+        <v>3009</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>CloneDestinationLabel</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>복제할 폴더</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Destination folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426">
+        <v>3010</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>CloneDestinationHint</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>선택한 폴더에 바로 복제합니다. 새 폴더 경로를 직접 입력할 수도 있습니다.</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Clone into the selected folder, or enter a path for a new folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427">
+        <v>3011</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>CloneBrowseDestination</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>찾아보기</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Browse</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428">
+        <v>3012</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ClonePickDestinationTitle</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>복제할 폴더 선택</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Choose destination folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429">
+        <v>3013</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>CloneDestinationRequired</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>복제할 폴더 경로를 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Enter a destination folder path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430">
+        <v>3014</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>CloneDestinationInvalid</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>복제할 폴더 경로가 올바르지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>The destination folder path is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431">
+        <v>3015</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>CloneDestinationAbsoluteRequired</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>복제할 폴더의 절대 경로를 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Enter an absolute path for the destination folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432">
+        <v>3016</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>CloneDestinationRootForbidden</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>드라이브 또는 파일 시스템 루트에는 복제할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Cannot clone into a drive or file system root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433">
+        <v>3017</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>CloneDestinationParentMissing</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>복제할 폴더의 상위 폴더가 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>The destination folder's parent does not exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434">
+        <v>3018</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>CloneDestinationFileExists</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>복제 위치에 파일이 이미 있습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>A file already exists at the destination: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435">
+        <v>3019</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>CloneDestinationNotEmpty</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>복제할 폴더가 비어 있지 않습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>The destination folder is not empty: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436">
+        <v>3020</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>RepositoryActionsButtonText</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>+ 저장소</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>+ Repository</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437">
+        <v>3021</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>RepositoryActionsTooltip</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>저장소 추가 또는 복제</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Add or clone a repository</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438">
+        <v>3022</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>RepositoryAddExistingAction</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>기존 저장소 추가</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Add existing repository</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9274,12 +9274,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>생성 위치에 파일이 남아 있습니다: {0}. 수동으로 확인하세요.</t>
+          <t>복제 위치가 남아 있습니다: {0}. 기존 폴더일 수도 있으므로 내용을 확인하세요.</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Files remain at {0}. Review them before reuse.</t>
+          <t>The destination still exists at {0}. It may have existed before cloning; review it before reuse.</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>생성 위치에 폴더가 만들어지지 않았습니다.</t>
+          <t>복제 위치에 폴더가 없습니다.</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>No destination folder was created.</t>
+          <t>No destination folder exists.</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Destination folder</t>
+          <t>Clone destination folder</t>
         </is>
       </c>
     </row>
@@ -9394,12 +9394,12 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>선택한 폴더에 바로 복제합니다. 새 폴더 경로를 직접 입력할 수도 있습니다.</t>
+          <t>기존 빈 폴더 또는 새 폴더의 절대 경로를 입력하세요.</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Clone into the selected folder, or enter a path for a new folder.</t>
+          <t>Enter an absolute path to an existing empty folder or a new folder.</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Choose destination folder</t>
+          <t>Choose a destination folder</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Enter an absolute path for the destination folder.</t>
+          <t>Enter an absolute destination folder path.</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>드라이브 또는 파일 시스템 루트에는 복제할 수 없습니다.</t>
+          <t>드라이브 또는 파일 시스템의 루트 폴더에는 복제할 수 없습니다.</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>The destination folder's parent does not exist.</t>
+          <t>The parent folder of the destination does not exist.</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>복제 위치에 파일이 이미 있습니다: {0}</t>
+          <t>복제할 위치에 파일이 이미 존재합니다: {0}</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>저장소 추가 또는 복제</t>
+          <t>기존 저장소를 추가하거나 새 저장소를 복제합니다.</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Add or clone a repository</t>
+          <t>Add an existing repository or clone a new one.</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D438"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -9640,6 +9640,26 @@
       <c r="D438" t="inlineStr">
         <is>
           <t>Add existing repository</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439">
+        <v>2404</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MainOpenIn</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>열기</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -9660,6 +9660,1034 @@
       <c r="D439" t="inlineStr">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440">
+        <v>3023</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalMenu</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 삭제</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441">
+        <v>3024</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteMenu</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 태그 삭제</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete remote tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442">
+        <v>3025</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalTitle</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 삭제</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete local tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443">
+        <v>3026</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalConfirm</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 '{0}'을 삭제합니다.
+태그 객체: {1}
+로컬 태그 참조만 삭제합니다. 원격 태그, 같은 이름의 브랜치, 작업 파일과 커밋은 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete local tag '{0}'.
+Tag object: {1}
+Only the local tag reference is deleted. Remote tags, branches with the same name, working files and commits are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444">
+        <v>3027</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteTitle</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 태그 삭제</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete remote tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445">
+        <v>3028</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteConfirm</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제합니다.
+태그 객체: {2}
+서버의 태그를 삭제하며 다른 사용자에게 영향을 줍니다. 로컬 태그와 같은 이름의 브랜치는 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete tag '{1}' from remote '{0}'.
+Tag object: {2}
+This deletes the tag on the server and affects other users. The local tag and branches with the same name are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446">
+        <v>3029</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteAction</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447">
+        <v>3030</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteSelectRemoteTitle</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그를 삭제할 원격 선택</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Select remote for tag deletion</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448">
+        <v>3031</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemotePrompt</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 '{0}'을 조회할 등록된 원격을 선택하세요. 다음 확인 창에서 서버 삭제 대상을 확인합니다.</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Select a registered remote to inspect tag '{0}'. Confirm the server deletion target in the next dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449">
+        <v>3032</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteInspectRemoteAction</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상 확인</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect target</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450">
+        <v>3033</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalSucceeded</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 '{0}'을 삭제했습니다.</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deleted local tag '{0}'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451">
+        <v>3034</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteSucceeded</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제했습니다. 로컬 태그는 유지했습니다.</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deleted tag '{1}' from remote '{0}'. The local tag was preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452">
+        <v>3035</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} 참조 갱신에 실패했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} Reference refresh failed: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453">
+        <v>3036</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteInvalidName</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제할 태그 이름이 유효하지 않습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tag name is not valid for deletion: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454">
+        <v>3037</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteInvalidObjectId</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 참조 목록을 새로 고친 뒤 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The confirmed object OID for tag '{0}' is invalid. Refresh references and confirm again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455">
+        <v>3038</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalMissing</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 '{0}'이 더 이상 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local tag '{0}' no longer exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456">
+        <v>3039</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalChanged</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 이후 로컬 태그 '{0}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local tag '{0}' changed after confirmation and was not deleted. Confirm again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457">
+        <v>3040</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteLocalFailed</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 '{0}'을 삭제하지 못했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not delete local tag '{0}': {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458">
+        <v>3041</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteRequired</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 태그를 삭제하려면 등록된 원격이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A registered remote is required to delete a remote tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459">
+        <v>3042</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteUnavailable</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 Push 주소를 확인할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not resolve the push URL for remote '{0}'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460">
+        <v>3043</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteMultiplePushUrls</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'에 Push 주소가 여러 개라 태그 삭제를 지원하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag deletion is not supported for remote '{0}' because it has multiple push URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461">
+        <v>3044</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteTagMissing</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'에 태그 '{1}'이 없습니다.</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remote '{0}' has no tag '{1}'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462">
+        <v>3045</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteLookupFailed</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하지 못했습니다: {2}</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not inspect tag '{1}' on remote '{0}': {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463">
+        <v>3046</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteChanged</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 이후 원격 '{0}'의 태그 '{1}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag '{1}' on remote '{0}' changed after confirmation and was not deleted. Confirm again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464">
+        <v>3047</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteUrlChanged</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 이후 원격 '{0}'의 Push 주소가 변경되어 삭제하지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The push URL for remote '{0}' changed after confirmation. Nothing was deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465">
+        <v>3048</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRemoteFailed</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제하지 못했습니다: {2}</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not delete tag '{1}' on remote '{0}': {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466">
+        <v>3049</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteRepositoryChanged</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 삭제를 확인한 저장소와 요청한 저장소가 다릅니다.</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The requested repository differs from the repository confirmed for tag deletion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467">
+        <v>3050</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameBranchMenu</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">브랜치 이름 변경</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rename branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468">
+        <v>3051</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameTagMenu</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 이름 변경</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rename tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469">
+        <v>3052</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameOriginalName</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 이름</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current name</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470">
+        <v>3053</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameNewName</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 이름</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New name</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471">
+        <v>3054</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameLocalOnly</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 참조만 변경합니다. 원격 브랜치와 태그는 변경하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the local reference is renamed. Remote branches and tags are not changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472">
+        <v>3055</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameTagObjectsHint</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 참조 이름만 변경합니다. 객체 내부의 기존 이름·주석·서명은 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the tag reference name changes. The original name, annotation and signature inside the tag object are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473">
+        <v>3056</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameAction</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 변경</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rename</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474">
+        <v>3057</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameBranchSucceeded</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 브랜치 '{0}'의 이름을 '{1}'로 변경했습니다.</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renamed local branch '{0}' to '{1}'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475">
+        <v>3058</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameTagSucceeded</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그 '{0}'의 참조 이름을 '{1}'로 변경했습니다. 태그 객체는 유지했습니다.</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renamed local tag reference '{0}' to '{1}'. The tag object was preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476">
+        <v>3059</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameUnchanged</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{0}'은 기존 이름과 같아 변경하지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{0}' is the current name. Nothing was changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477">
+        <v>3060</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameRepositoryChanged</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 변경을 확인한 저장소와 실행할 저장소가 다릅니다.</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The execution repository differs from the repository confirmed for renaming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478">
+        <v>3061</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameSourceInvalid</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 변경 대상 로컬 참조가 유효하지 않습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The local reference to rename is invalid: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479">
+        <v>3062</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameSourceMissing</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 변경 대상 참조 '{0}'이 더 이상 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference '{0}' no longer exists and cannot be renamed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480">
+        <v>3063</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameSourceChanged</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 이후 참조 '{0}'이 변경되어 이름을 바꾸지 않았습니다. 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference '{0}' changed after confirmation and was not renamed. Confirm again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481">
+        <v>3064</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameInvalidObjectId</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">참조 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 목록을 새로 고친 뒤 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The confirmed object OID for reference '{0}' is invalid. Refresh references and confirm again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482">
+        <v>3065</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameNameRequired</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 이름을 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enter a new name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483">
+        <v>3066</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameNameInvalid</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 이름이 유효하지 않습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The new name is invalid: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484">
+        <v>3067</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameDestinationExists</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목적지 참조 '{0}'이 이미 존재합니다. 덮어쓰지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destination reference '{0}' already exists. It will not be overwritten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485">
+        <v>3068</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameLookupFailed</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">참조 '{0}'을 확인하지 못했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not inspect reference '{0}': {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486">
+        <v>3069</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameFailed</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">참조 '{0}'을 '{1}'로 변경하지 못했습니다: {2}</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not rename reference '{0}' to '{1}': {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487">
+        <v>3070</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} 상태 갱신에 실패했습니다: {1}</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} State refresh failed: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488">
+        <v>3071</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameStateReadFailed</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{0}'에서 '{1}'로 이름 변경은 반영되었지만 저장소 상태를 읽지 못했습니다. 새로 고침하세요.</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The rename from '{0}' to '{1}' was applied, but repository state could not be read. Refresh the repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489">
+        <v>3072</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameQueueProgress</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{0}'으로 이름 변경 중 · 대기 {1}건</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renaming to '{0}' · {1} queued</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490">
+        <v>3073</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReferenceRenameQueueClosing</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{0}'으로 이름 변경 결과를 기다린 뒤 닫습니다.</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting for rename to '{0}' to finish before closing.</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D497"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -10688,6 +10688,146 @@
       <c r="D490" t="inlineStr">
         <is>
           <t xml:space="preserve">Waiting for rename to '{0}' to finish before closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491">
+        <v>3074</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogLocalScope</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 태그</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492">
+        <v>3075</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogRemoteScope</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 태그</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remote tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493">
+        <v>3076</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogRemoteHint</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택한 원격 서버의 태그만 삭제합니다. 다른 사용자에게 영향을 주며 로컬 태그와 브랜치는 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the tag on the selected remote server is deleted. This affects other users. Local tags and branches are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494">
+        <v>3077</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogLoading</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspecting tag '{1}' on remote '{0}'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495">
+        <v>3078</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogConfirmRemote</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 서버에서 삭제하는 영향을 확인했습니다.</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I confirm the impact of deleting tag '{1}' from remote '{0}' on the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496">
+        <v>3079</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogDeleting</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태그 삭제 결과를 기다리는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting for the tag deletion result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497">
+        <v>3080</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TagDeleteDialogReload</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상 다시 조회</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reload target</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9634,12 +9634,12 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>기존 저장소 추가</t>
+          <t>저장소 열기</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Add existing repository</t>
+          <t>Open repository</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D497"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -10828,6 +10828,266 @@
       <c r="D497" t="inlineStr">
         <is>
           <t xml:space="preserve">Reload target</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498">
+        <v>3081</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureAuthentication</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 인증에 실패했습니다(종료 코드 {0}). 로그인 상태와 인증 도우미 또는 SSH 키를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git authentication failed (exit code {0}). Check your sign-in, credential helper, or SSH key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499">
+        <v>3082</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureRemoteAccessDenied</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 저장소 접근이 거부되었습니다(종료 코드 {0}). 계정의 저장소 접근 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access to the remote repository was denied (exit code {0}). Check the account permissions for this repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500">
+        <v>3083</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureRepositoryUnavailable</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장소를 찾거나 읽을 수 없습니다(종료 코드 {0}). 주소 또는 경로, 저장소 존재 여부와 접근 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The repository could not be found or read (exit code {0}). Check the address or path, repository existence, and access permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501">
+        <v>3084</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureConnection</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 연결에 실패했습니다(종료 코드 {0}). 네트워크, DNS, 프록시와 서버 인증서를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The remote connection failed (exit code {0}). Check the network, DNS, proxy, and server certificate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502">
+        <v>3085</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureDiskFull</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Git이 저장 공간 또는 할당량 부족을 보고했습니다(종료 코드 {0}). 로컬 또는 원격의 저장 공간을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Git reported insufficient storage space or quota (exit code {0}). Check local or remote storage space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503">
+        <v>3086</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureFileAccess</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 파일을 만들거나 쓸 수 없습니다(종료 코드 {0}). 목적지 폴더의 쓰기 권한과 파일 잠금을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local files could not be created or written (exit code {0}). Check destination write permissions and file locks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504">
+        <v>3087</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureDestinationConflict</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실행 시 목적지에 이미 내용이 있어 복제할 수 없습니다(종료 코드 {0}). 비어 있는 폴더 또는 새 경로를 선택하세요.</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The destination already contained data when cloning ran (exit code {0}). Choose an empty folder or a new path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505">
+        <v>3088</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureUnknown</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 복제에 실패했습니다(종료 코드 {0}). 주소, 인증, 연결과 목적지 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git clone failed (exit code {0}). Check the address, authentication, connection, and destination permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506">
+        <v>3089</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneFailureUnexpected</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">복제 요청을 처리하지 못했습니다. 주소, 인증, 연결과 목적지 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The clone request could not be completed. Check the address, authentication, connection, and destination permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507">
+        <v>3090</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneDestinationMissingAfterAttempt</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목적지 폴더가 없습니다: {0}. 같은 경로로 다시 시도할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The destination folder does not exist: {0}. You can retry using this path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508">
+        <v>3091</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneDestinationEmptyAfterAttempt</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">복제할 폴더가 비어 있습니다: {0}. 실패 원인을 해결한 뒤 다시 시도할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The destination folder is empty: {0}. You can retry after resolving the clone error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509">
+        <v>3092</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneDestinationContentsAfterAttempt</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">복제 위치에 내용이 남아 있습니다: {0}. 다시 시도하기 전에 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Files remain at the destination: {0}. Review them before trying again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510">
+        <v>3093</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CloneDestinationInspectionFailed</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">복제 위치의 상태를 확인할 수 없습니다: {0}. 폴더와 접근 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not read the destination state: {0}. Check the folder and access permissions.</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R0619a3bb29304a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="Rd36796b387094c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Re0da5ecb44f9448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="R06822bbf18404f6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -600,15 +600,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Final file</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FinalFileHint</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">선택 결과가 즉시 반영되며 직접 편집할 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Choices update the final file instantly. You can edit it directly.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SaveAndStage</x:t>
@@ -3227,17 +3218,17 @@
       </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="A90">
+      <x:c r="A90" t="n">
         <x:v>1088</x:v>
       </x:c>
-      <x:c r="B90" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="C90" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D90" t="s">
-        <x:v>199</x:v>
+      <x:c r="B90" t="str">
+        <x:v>FinalFileHint</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>선택 결과를 확인·편집한 뒤 저장 및 스테이징을 눌러 완료하세요.</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>Review or edit the result, then save and stage to finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3245,13 +3236,13 @@
         <x:v>1089</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D91" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3259,13 +3250,13 @@
         <x:v>1090</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D92" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -3273,13 +3264,13 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>206</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>207</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D93" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -3287,13 +3278,13 @@
         <x:v>1092</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D94" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -3301,13 +3292,13 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D95" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -3315,13 +3306,13 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D96" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -3329,13 +3320,13 @@
         <x:v>1095</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D97" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -3343,13 +3334,13 @@
         <x:v>1096</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>221</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>222</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D98" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -3357,13 +3348,13 @@
         <x:v>1097</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>224</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C99" t="s">
-        <x:v>225</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D99" t="s">
-        <x:v>226</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -3371,13 +3362,13 @@
         <x:v>1098</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>227</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C100" t="s">
-        <x:v>228</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D100" t="s">
-        <x:v>229</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -3385,13 +3376,13 @@
         <x:v>1099</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>230</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C101" t="s">
-        <x:v>231</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D101" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -3399,13 +3390,13 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>233</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C102" t="s">
-        <x:v>234</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D102" t="s">
-        <x:v>235</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -3413,13 +3404,13 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>236</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>237</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D103" t="s">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -3427,13 +3418,13 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>239</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>240</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D104" t="s">
-        <x:v>241</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -3441,13 +3432,13 @@
         <x:v>1103</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D105" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -3455,13 +3446,13 @@
         <x:v>1104</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>245</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>246</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D106" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -3469,13 +3460,13 @@
         <x:v>1105</x:v>
       </x:c>
       <x:c r="B107" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C107" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D107" t="s">
-        <x:v>250</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -3483,13 +3474,13 @@
         <x:v>1106</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>251</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C108" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D108" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -3497,13 +3488,13 @@
         <x:v>1107</x:v>
       </x:c>
       <x:c r="B109" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C109" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D109" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -3511,13 +3502,13 @@
         <x:v>1108</x:v>
       </x:c>
       <x:c r="B110" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C110" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D110" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -3525,13 +3516,13 @@
         <x:v>1109</x:v>
       </x:c>
       <x:c r="B111" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C111" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D111" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -3539,13 +3530,13 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B112" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C112" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D112" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -3553,13 +3544,13 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B113" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C113" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D113" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -3567,13 +3558,13 @@
         <x:v>1112</x:v>
       </x:c>
       <x:c r="B114" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C114" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D114" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -3581,13 +3572,13 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B115" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C115" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D115" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -3595,13 +3586,13 @@
         <x:v>1114</x:v>
       </x:c>
       <x:c r="B116" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C116" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D116" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -3609,13 +3600,13 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B117" t="s">
-        <x:v>278</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C117" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D117" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -3623,13 +3614,13 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B118" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C118" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D118" t="s">
-        <x:v>283</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -3637,13 +3628,13 @@
         <x:v>1117</x:v>
       </x:c>
       <x:c r="B119" t="s">
-        <x:v>284</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C119" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D119" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -3651,13 +3642,13 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B120" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D120" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -3665,13 +3656,13 @@
         <x:v>1119</x:v>
       </x:c>
       <x:c r="B121" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D121" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -3679,13 +3670,13 @@
         <x:v>1120</x:v>
       </x:c>
       <x:c r="B122" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D122" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3693,13 +3684,13 @@
         <x:v>1121</x:v>
       </x:c>
       <x:c r="B123" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D123" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3707,13 +3698,13 @@
         <x:v>1122</x:v>
       </x:c>
       <x:c r="B124" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D124" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3721,13 +3712,13 @@
         <x:v>1123</x:v>
       </x:c>
       <x:c r="B125" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C125" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D125" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3735,13 +3726,13 @@
         <x:v>1124</x:v>
       </x:c>
       <x:c r="B126" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="D126" t="s">
-        <x:v>305</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3749,13 +3740,13 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B127" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C127" t="s">
-        <x:v>307</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="D127" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3763,13 +3754,13 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B128" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C128" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D128" t="s">
-        <x:v>311</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3777,13 +3768,13 @@
         <x:v>1127</x:v>
       </x:c>
       <x:c r="B129" t="s">
-        <x:v>312</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C129" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D129" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3791,13 +3782,13 @@
         <x:v>1128</x:v>
       </x:c>
       <x:c r="B130" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C130" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D130" t="s">
-        <x:v>317</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3805,13 +3796,13 @@
         <x:v>1129</x:v>
       </x:c>
       <x:c r="B131" t="s">
-        <x:v>318</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C131" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D131" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3819,13 +3810,13 @@
         <x:v>1130</x:v>
       </x:c>
       <x:c r="B132" t="s">
-        <x:v>320</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C132" t="s">
-        <x:v>321</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D132" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3833,13 +3824,13 @@
         <x:v>1131</x:v>
       </x:c>
       <x:c r="B133" t="s">
-        <x:v>323</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C133" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D133" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3847,13 +3838,13 @@
         <x:v>1132</x:v>
       </x:c>
       <x:c r="B134" t="s">
-        <x:v>326</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>327</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="D134" t="s">
-        <x:v>328</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3861,13 +3852,13 @@
         <x:v>1133</x:v>
       </x:c>
       <x:c r="B135" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C135" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D135" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3875,7 +3866,7 @@
         <x:v>1134</x:v>
       </x:c>
       <x:c r="B136" t="s">
-        <x:v>332</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C136" t="s">
         <x:v>69</x:v>
@@ -3889,13 +3880,13 @@
         <x:v>1135</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>334</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D137" t="s">
-        <x:v>335</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3903,13 +3894,13 @@
         <x:v>1136</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>336</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>337</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="D138" t="s">
-        <x:v>338</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3917,13 +3908,13 @@
         <x:v>1137</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>339</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>340</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="D139" t="s">
-        <x:v>341</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3931,13 +3922,13 @@
         <x:v>1138</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>342</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D140" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3945,13 +3936,13 @@
         <x:v>1139</x:v>
       </x:c>
       <x:c r="B141" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C141" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="D141" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3959,13 +3950,13 @@
         <x:v>1140</x:v>
       </x:c>
       <x:c r="B142" t="s">
-        <x:v>348</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C142" t="s">
-        <x:v>349</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="D142" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3973,13 +3964,13 @@
         <x:v>1141</x:v>
       </x:c>
       <x:c r="B143" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C143" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="D143" t="s">
-        <x:v>353</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3987,13 +3978,13 @@
         <x:v>1142</x:v>
       </x:c>
       <x:c r="B144" t="s">
-        <x:v>354</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C144" t="s">
-        <x:v>355</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="D144" t="s">
-        <x:v>356</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -4001,13 +3992,13 @@
         <x:v>1143</x:v>
       </x:c>
       <x:c r="B145" t="s">
-        <x:v>357</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C145" t="s">
-        <x:v>358</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="D145" t="s">
-        <x:v>359</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -4015,13 +4006,13 @@
         <x:v>1144</x:v>
       </x:c>
       <x:c r="B146" t="s">
-        <x:v>360</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C146" t="s">
-        <x:v>361</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="D146" t="s">
-        <x:v>362</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -4029,13 +4020,13 @@
         <x:v>1145</x:v>
       </x:c>
       <x:c r="B147" t="s">
-        <x:v>363</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C147" t="s">
-        <x:v>364</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="D147" t="s">
-        <x:v>365</x:v>
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -4043,13 +4034,13 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B148" t="s">
-        <x:v>366</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C148" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D148" t="s">
-        <x:v>368</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -4057,13 +4048,13 @@
         <x:v>1147</x:v>
       </x:c>
       <x:c r="B149" t="s">
-        <x:v>369</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C149" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D149" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -4071,13 +4062,13 @@
         <x:v>1148</x:v>
       </x:c>
       <x:c r="B150" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C150" t="s">
-        <x:v>373</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="D150" t="s">
-        <x:v>374</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -4085,13 +4076,13 @@
         <x:v>1149</x:v>
       </x:c>
       <x:c r="B151" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C151" t="s">
-        <x:v>376</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="D151" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -4099,13 +4090,13 @@
         <x:v>1150</x:v>
       </x:c>
       <x:c r="B152" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C152" t="s">
-        <x:v>379</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D152" t="s">
-        <x:v>380</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -4113,13 +4104,13 @@
         <x:v>1151</x:v>
       </x:c>
       <x:c r="B153" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C153" t="s">
-        <x:v>382</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D153" t="s">
-        <x:v>383</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -4127,13 +4118,13 @@
         <x:v>1152</x:v>
       </x:c>
       <x:c r="B154" t="s">
-        <x:v>384</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C154" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D154" t="s">
-        <x:v>386</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -4141,13 +4132,13 @@
         <x:v>1153</x:v>
       </x:c>
       <x:c r="B155" t="s">
-        <x:v>387</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="C155" t="s">
-        <x:v>388</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D155" t="s">
-        <x:v>389</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -4155,13 +4146,13 @@
         <x:v>1154</x:v>
       </x:c>
       <x:c r="B156" t="s">
-        <x:v>390</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C156" t="s">
-        <x:v>391</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="D156" t="s">
-        <x:v>392</x:v>
+        <x:v>389</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -4169,13 +4160,13 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c r="B157" t="s">
-        <x:v>393</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C157" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D157" t="s">
-        <x:v>395</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -4183,13 +4174,13 @@
         <x:v>1156</x:v>
       </x:c>
       <x:c r="B158" t="s">
-        <x:v>396</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C158" t="s">
-        <x:v>397</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D158" t="s">
-        <x:v>398</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -4197,13 +4188,13 @@
         <x:v>1157</x:v>
       </x:c>
       <x:c r="B159" t="s">
-        <x:v>399</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C159" t="s">
-        <x:v>400</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D159" t="s">
-        <x:v>401</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -4211,13 +4202,13 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B160" t="s">
-        <x:v>402</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C160" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D160" t="s">
-        <x:v>404</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -4225,13 +4216,13 @@
         <x:v>1159</x:v>
       </x:c>
       <x:c r="B161" t="s">
-        <x:v>405</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C161" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="D161" t="s">
-        <x:v>407</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -4239,13 +4230,13 @@
         <x:v>1160</x:v>
       </x:c>
       <x:c r="B162" t="s">
-        <x:v>408</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C162" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D162" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -4253,13 +4244,13 @@
         <x:v>1161</x:v>
       </x:c>
       <x:c r="B163" t="s">
-        <x:v>411</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C163" t="s">
-        <x:v>412</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="D163" t="s">
-        <x:v>413</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -4267,13 +4258,13 @@
         <x:v>1162</x:v>
       </x:c>
       <x:c r="B164" t="s">
-        <x:v>414</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C164" t="s">
-        <x:v>415</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D164" t="s">
-        <x:v>416</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -4281,7 +4272,7 @@
         <x:v>1163</x:v>
       </x:c>
       <x:c r="B165" t="s">
-        <x:v>417</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C165" t="s">
         <x:v>69</x:v>
@@ -4295,13 +4286,13 @@
         <x:v>1164</x:v>
       </x:c>
       <x:c r="B166" t="s">
-        <x:v>418</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C166" t="s">
-        <x:v>419</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="D166" t="s">
-        <x:v>420</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -4309,13 +4300,13 @@
         <x:v>1165</x:v>
       </x:c>
       <x:c r="B167" t="s">
-        <x:v>421</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C167" t="s">
-        <x:v>422</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D167" t="s">
-        <x:v>423</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -4323,13 +4314,13 @@
         <x:v>1166</x:v>
       </x:c>
       <x:c r="B168" t="s">
-        <x:v>424</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C168" t="s">
-        <x:v>425</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="D168" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -4337,13 +4328,13 @@
         <x:v>1167</x:v>
       </x:c>
       <x:c r="B169" t="s">
-        <x:v>427</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C169" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="D169" t="s">
-        <x:v>429</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -4351,13 +4342,13 @@
         <x:v>1168</x:v>
       </x:c>
       <x:c r="B170" t="s">
-        <x:v>430</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C170" t="s">
-        <x:v>431</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="D170" t="s">
-        <x:v>432</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -4365,13 +4356,13 @@
         <x:v>1169</x:v>
       </x:c>
       <x:c r="B171" t="s">
-        <x:v>433</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C171" t="s">
-        <x:v>434</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D171" t="s">
-        <x:v>435</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -4379,7 +4370,7 @@
         <x:v>1170</x:v>
       </x:c>
       <x:c r="B172" t="s">
-        <x:v>436</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C172" t="inlineStr">
         <x:is>
@@ -4397,13 +4388,13 @@
         <x:v>1171</x:v>
       </x:c>
       <x:c r="B173" t="s">
-        <x:v>437</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C173" t="s">
-        <x:v>438</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="D173" t="s">
-        <x:v>439</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4411,13 +4402,13 @@
         <x:v>1172</x:v>
       </x:c>
       <x:c r="B174" t="s">
-        <x:v>440</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C174" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D174" t="s">
-        <x:v>442</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4425,13 +4416,13 @@
         <x:v>1173</x:v>
       </x:c>
       <x:c r="B175" t="s">
-        <x:v>443</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C175" t="s">
-        <x:v>444</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D175" t="s">
-        <x:v>445</x:v>
+        <x:v>442</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4439,13 +4430,13 @@
         <x:v>1174</x:v>
       </x:c>
       <x:c r="B176" t="s">
-        <x:v>446</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C176" t="s">
-        <x:v>447</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D176" t="s">
-        <x:v>448</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4453,13 +4444,13 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B177" t="s">
-        <x:v>449</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C177" t="s">
-        <x:v>450</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D177" t="s">
-        <x:v>451</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4467,13 +4458,13 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B178" t="s">
-        <x:v>452</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C178" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D178" t="s">
-        <x:v>454</x:v>
+        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -4481,13 +4472,13 @@
         <x:v>1177</x:v>
       </x:c>
       <x:c r="B179" t="s">
-        <x:v>455</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C179" t="s">
-        <x:v>456</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D179" t="s">
-        <x:v>457</x:v>
+        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -4495,13 +4486,13 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B180" t="s">
-        <x:v>458</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C180" t="s">
-        <x:v>459</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D180" t="s">
-        <x:v>460</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -4509,13 +4500,13 @@
         <x:v>1179</x:v>
       </x:c>
       <x:c r="B181" t="s">
-        <x:v>461</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="C181" t="s">
-        <x:v>462</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="D181" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -4523,13 +4514,13 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B182" t="s">
-        <x:v>464</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C182" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="D182" t="s">
-        <x:v>466</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -4537,13 +4528,13 @@
         <x:v>1181</x:v>
       </x:c>
       <x:c r="B183" t="s">
-        <x:v>467</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C183" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D183" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -4551,13 +4542,13 @@
         <x:v>1182</x:v>
       </x:c>
       <x:c r="B184" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C184" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D184" t="s">
-        <x:v>472</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -4565,13 +4556,13 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B185" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C185" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="D185" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -4579,13 +4570,13 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B186" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C186" t="s">
-        <x:v>477</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D186" t="s">
-        <x:v>478</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -4593,13 +4584,13 @@
         <x:v>1185</x:v>
       </x:c>
       <x:c r="B187" t="s">
-        <x:v>479</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="C187" t="s">
-        <x:v>480</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="D187" t="s">
-        <x:v>481</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -4607,13 +4598,13 @@
         <x:v>1186</x:v>
       </x:c>
       <x:c r="B188" t="s">
-        <x:v>482</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C188" t="s">
-        <x:v>483</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D188" t="s">
-        <x:v>484</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -4621,13 +4612,13 @@
         <x:v>1187</x:v>
       </x:c>
       <x:c r="B189" t="s">
-        <x:v>485</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C189" t="s">
-        <x:v>486</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D189" t="s">
-        <x:v>487</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -4635,13 +4626,13 @@
         <x:v>1188</x:v>
       </x:c>
       <x:c r="B190" t="s">
-        <x:v>488</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C190" t="s">
-        <x:v>489</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D190" t="s">
-        <x:v>490</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -4649,13 +4640,13 @@
         <x:v>1189</x:v>
       </x:c>
       <x:c r="B191" t="s">
-        <x:v>491</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C191" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D191" t="s">
-        <x:v>493</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -4663,13 +4654,13 @@
         <x:v>1190</x:v>
       </x:c>
       <x:c r="B192" t="s">
-        <x:v>494</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C192" t="s">
-        <x:v>495</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D192" t="s">
-        <x:v>496</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -4677,13 +4668,13 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B193" t="s">
-        <x:v>497</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="C193" t="s">
-        <x:v>498</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D193" t="s">
-        <x:v>499</x:v>
+        <x:v>496</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -4691,13 +4682,13 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B194" t="s">
-        <x:v>500</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C194" t="s">
-        <x:v>501</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D194" t="s">
-        <x:v>502</x:v>
+        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -4705,13 +4696,13 @@
         <x:v>1193</x:v>
       </x:c>
       <x:c r="B195" t="s">
-        <x:v>503</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C195" t="s">
-        <x:v>504</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D195" t="s">
-        <x:v>505</x:v>
+        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -4719,13 +4710,13 @@
         <x:v>1194</x:v>
       </x:c>
       <x:c r="B196" t="s">
-        <x:v>506</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C196" t="s">
-        <x:v>507</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D196" t="s">
-        <x:v>508</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -4733,13 +4724,13 @@
         <x:v>1195</x:v>
       </x:c>
       <x:c r="B197" t="s">
-        <x:v>509</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C197" t="s">
-        <x:v>510</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D197" t="s">
-        <x:v>511</x:v>
+        <x:v>508</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -4747,13 +4738,13 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B198" t="s">
-        <x:v>512</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="C198" t="s">
-        <x:v>513</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="D198" t="s">
-        <x:v>514</x:v>
+        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -4761,13 +4752,13 @@
         <x:v>1197</x:v>
       </x:c>
       <x:c r="B199" t="s">
-        <x:v>515</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C199" t="s">
-        <x:v>516</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D199" t="s">
-        <x:v>517</x:v>
+        <x:v>514</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -4775,13 +4766,13 @@
         <x:v>1198</x:v>
       </x:c>
       <x:c r="B200" t="s">
-        <x:v>518</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C200" t="s">
-        <x:v>519</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D200" t="s">
-        <x:v>520</x:v>
+        <x:v>517</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -4789,13 +4780,13 @@
         <x:v>1199</x:v>
       </x:c>
       <x:c r="B201" t="s">
-        <x:v>521</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="C201" t="s">
-        <x:v>522</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D201" t="s">
-        <x:v>523</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -4803,13 +4794,13 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="B202" t="s">
-        <x:v>524</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C202" t="s">
-        <x:v>525</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D202" t="s">
-        <x:v>526</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -4817,13 +4808,13 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B203" t="s">
-        <x:v>527</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C203" t="s">
-        <x:v>528</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="D203" t="s">
-        <x:v>529</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -4831,13 +4822,13 @@
         <x:v>1202</x:v>
       </x:c>
       <x:c r="B204" t="s">
-        <x:v>530</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="C204" t="s">
-        <x:v>531</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D204" t="s">
-        <x:v>532</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -4845,13 +4836,13 @@
         <x:v>1203</x:v>
       </x:c>
       <x:c r="B205" t="s">
-        <x:v>533</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C205" t="s">
-        <x:v>534</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D205" t="s">
-        <x:v>535</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -4859,13 +4850,13 @@
         <x:v>1204</x:v>
       </x:c>
       <x:c r="B206" t="s">
-        <x:v>536</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="C206" t="s">
-        <x:v>537</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="D206" t="s">
-        <x:v>538</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -4873,13 +4864,13 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B207" t="s">
-        <x:v>539</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="C207" t="s">
-        <x:v>540</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D207" t="s">
-        <x:v>541</x:v>
+        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -4887,13 +4878,13 @@
         <x:v>1206</x:v>
       </x:c>
       <x:c r="B208" t="s">
-        <x:v>542</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C208" t="s">
-        <x:v>543</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D208" t="s">
-        <x:v>544</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -4901,13 +4892,13 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B209" t="s">
-        <x:v>545</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="C209" t="s">
-        <x:v>546</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D209" t="s">
-        <x:v>547</x:v>
+        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -4915,13 +4906,13 @@
         <x:v>1208</x:v>
       </x:c>
       <x:c r="B210" t="s">
-        <x:v>548</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C210" t="s">
-        <x:v>549</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D210" t="s">
-        <x:v>550</x:v>
+        <x:v>547</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -4929,13 +4920,13 @@
         <x:v>1209</x:v>
       </x:c>
       <x:c r="B211" t="s">
-        <x:v>551</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C211" t="s">
-        <x:v>552</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D211" t="s">
-        <x:v>553</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -4943,13 +4934,13 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B212" t="s">
-        <x:v>554</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C212" t="s">
-        <x:v>555</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="D212" t="s">
-        <x:v>556</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -4957,13 +4948,13 @@
         <x:v>1211</x:v>
       </x:c>
       <x:c r="B213" t="s">
-        <x:v>557</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C213" t="s">
-        <x:v>558</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D213" t="s">
-        <x:v>559</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -4971,13 +4962,13 @@
         <x:v>1212</x:v>
       </x:c>
       <x:c r="B214" t="s">
-        <x:v>560</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C214" t="s">
-        <x:v>561</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D214" t="s">
-        <x:v>562</x:v>
+        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -4985,13 +4976,13 @@
         <x:v>1213</x:v>
       </x:c>
       <x:c r="B215" t="s">
-        <x:v>563</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C215" t="s">
-        <x:v>564</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D215" t="s">
-        <x:v>565</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -4999,13 +4990,13 @@
         <x:v>1214</x:v>
       </x:c>
       <x:c r="B216" t="s">
-        <x:v>566</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="C216" t="s">
-        <x:v>567</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="D216" t="s">
-        <x:v>568</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -5013,13 +5004,13 @@
         <x:v>1215</x:v>
       </x:c>
       <x:c r="B217" t="s">
-        <x:v>569</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C217" t="s">
-        <x:v>570</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D217" t="s">
-        <x:v>571</x:v>
+        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -7531,23 +7522,17 @@
       </x:c>
     </x:row>
     <x:row r="343">
-      <x:c r="A343">
+      <x:c r="A343" t="n">
         <x:v>2927</x:v>
       </x:c>
-      <x:c r="B343" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ConflictBatchCurrentFileLabel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C343" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">현재 파일의 남은 충돌 구간 {0}개</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D343" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{0} unresolved sections remaining in this file</x:t>
-        </x:is>
+      <x:c r="B343" t="str">
+        <x:v>ConflictBatchCurrentFileLabel</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>이 파일의 미해결 구간 {0}개</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>{0} unresolved sections in this file</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -7611,23 +7596,17 @@
       </x:c>
     </x:row>
     <x:row r="347">
-      <x:c r="A347">
+      <x:c r="A347" t="n">
         <x:v>2931</x:v>
       </x:c>
-      <x:c r="B347" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ConflictBatchApplyButton</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C347" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">일괄 적용</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D347" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Apply to remaining</x:t>
-        </x:is>
+      <x:c r="B347" t="str">
+        <x:v>ConflictBatchApplyButton</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>남은 구간 일괄 선택</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>Choose remaining sections</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -8451,83 +8430,59 @@
       </x:c>
     </x:row>
     <x:row r="389">
-      <x:c r="A389">
+      <x:c r="A389" t="n">
         <x:v>2973</x:v>
       </x:c>
-      <x:c r="B389" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StopTrackingSelectionCount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C389" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">선택한 추적 파일 {0}개 추적 중지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D389" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stop tracking {0} selected files</x:t>
-        </x:is>
+      <x:c r="B389" t="str">
+        <x:v>StopTrackingSelectionCount</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>선택한 추적 파일 {0}개 추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>Stop tracking and ignore {0} selected files</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
-      <x:c r="A390">
+      <x:c r="A390" t="n">
         <x:v>2974</x:v>
       </x:c>
-      <x:c r="B390" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StopTrackingTitle</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C390" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">파일 추적 중지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D390" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stop tracking files</x:t>
-        </x:is>
+      <x:c r="B390" t="str">
+        <x:v>StopTrackingTitle</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>파일 추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>Stop tracking and ignore files</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
-      <x:c r="A391">
+      <x:c r="A391" t="n">
         <x:v>2975</x:v>
       </x:c>
-      <x:c r="B391" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StopTrackingDescription</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C391" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">추적 파일 {0}개를 Git 인덱스에서만 제거합니다. 작업 파일은 삭제하지 않으며, 파일 삭제가 스테이징된 변경으로 표시됩니다. 계속 추적하지 않으려면 작업 후 별도로 무시 규칙을 추가하세요.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D391" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Remove {0} tracked files from the Git index only. Working files are kept, and their deletion is staged. Add ignore rules separately afterward if they should remain untracked.</x:t>
-        </x:is>
+      <x:c r="B391" t="str">
+        <x:v>StopTrackingDescription</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>선택한 추적 파일 {0}개의 경로를 저장소 루트의 .gitignore에 추가하고 Git 인덱스에서 제거합니다. 작업 파일은 남겨두며 삭제가 스테이징됩니다. .gitignore 변경은 자동으로 스테이징하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>Add the paths of {0} selected tracked files to the repository root .gitignore and remove them from the Git index. Working files are kept, and their deletion is staged. The .gitignore change is not staged automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
-      <x:c r="A392">
+      <x:c r="A392" t="n">
         <x:v>2976</x:v>
       </x:c>
-      <x:c r="B392" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StopTrackingConfirm</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C392" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">추적 중지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D392" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stop tracking</x:t>
-        </x:is>
+      <x:c r="B392" t="str">
+        <x:v>StopTrackingConfirm</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>Stop tracking and ignore</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -8611,23 +8566,17 @@
       </x:c>
     </x:row>
     <x:row r="397">
-      <x:c r="A397">
+      <x:c r="A397" t="n">
         <x:v>2981</x:v>
       </x:c>
-      <x:c r="B397" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StopTrackingContextMenu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C397" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">추적 중지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D397" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stop tracking</x:t>
-        </x:is>
+      <x:c r="B397" t="str">
+        <x:v>StopTrackingContextMenu</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>추적 중지 및 무시…</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>Stop tracking and ignore…</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -10966,6 +10915,136 @@
       </x:c>
       <x:c r="D515" t="str">
         <x:v>Language changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" t="n">
+        <x:v>3099</x:v>
+      </x:c>
+      <x:c r="B516" t="str">
+        <x:v>WorkingStopTrackingPartialFailure</x:v>
+      </x:c>
+      <x:c r="C516" t="str">
+        <x:v>.gitignore에 무시 규칙을 추가했지만 추적 중지 중 오류가 발생했습니다. 스테이징 상태를 확인하세요.
+{0}</x:v>
+      </x:c>
+      <x:c r="D516" t="str">
+        <x:v>Ignore rules were added to .gitignore, but stopping tracking encountered an error. Review the staged changes.
+{0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="B517" t="str">
+        <x:v>RemotePullFastForwardUnavailable</x:v>
+      </x:c>
+      <x:c r="C517" t="str">
+        <x:v>빠른 전진으로 통합할 수 없습니다. Pull 메뉴에서 병합 또는 재배치를 선택하세요.</x:v>
+      </x:c>
+      <x:c r="D517" t="str">
+        <x:v>Fast-forward is not possible. Choose merge or rebase from the Pull menu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" t="n">
+        <x:v>3101</x:v>
+      </x:c>
+      <x:c r="B518" t="str">
+        <x:v>RemotePullFetchFailedSummary</x:v>
+      </x:c>
+      <x:c r="C518" t="str">
+        <x:v>원격 변경을 가져오지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D518" t="str">
+        <x:v>Could not fetch remote changes. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" t="n">
+        <x:v>3102</x:v>
+      </x:c>
+      <x:c r="B519" t="str">
+        <x:v>RemotePullApplyFailedSummary</x:v>
+      </x:c>
+      <x:c r="C519" t="str">
+        <x:v>가져온 변경을 현재 브랜치에 반영하지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D519" t="str">
+        <x:v>Could not apply incoming changes to the current branch. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="B520" t="str">
+        <x:v>RemotePushFailedSummary</x:v>
+      </x:c>
+      <x:c r="C520" t="str">
+        <x:v>원격에 변경을 보내지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D520" t="str">
+        <x:v>Could not push changes. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" t="n">
+        <x:v>3104</x:v>
+      </x:c>
+      <x:c r="B521" t="str">
+        <x:v>RemoteFetchFailedSummary</x:v>
+      </x:c>
+      <x:c r="C521" t="str">
+        <x:v>{0} 가져오기에 실패했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D521" t="str">
+        <x:v>Fetch failed for {0}. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" t="n">
+        <x:v>3105</x:v>
+      </x:c>
+      <x:c r="B522" t="str">
+        <x:v>RemoteOperationDetails</x:v>
+      </x:c>
+      <x:c r="C522" t="str">
+        <x:v>자세히</x:v>
+      </x:c>
+      <x:c r="D522" t="str">
+        <x:v>Details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" t="n">
+        <x:v>3106</x:v>
+      </x:c>
+      <x:c r="B523" t="str">
+        <x:v>ConflictSelectionSummary</x:v>
+      </x:c>
+      <x:c r="C523" t="str">
+        <x:v>{0}/{1}개 구간 선택</x:v>
+      </x:c>
+      <x:c r="D523" t="str">
+        <x:v>{0}/{1} sections chosen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" t="n">
+        <x:v>3107</x:v>
+      </x:c>
+      <x:c r="B524" t="str">
+        <x:v>WorkingMergeMessageReadFailed</x:v>
+      </x:c>
+      <x:c r="C524" t="str">
+        <x:v>병합 커밋 메시지를 읽지 못했습니다: {0}
+{1}</x:v>
+      </x:c>
+      <x:c r="D524" t="str">
+        <x:v>Could not read the merge commit message: {0}
+{1}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10985,10 +11064,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -11002,7 +11081,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>571</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -11016,7 +11095,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -11030,7 +11109,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11044,7 +11123,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -1962,31 +1962,9194 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?><x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><x:sheetFormatPr defaultRowHeight="16.5" /><x:cols><x:col min="2" max="2" width="20.125" customWidth="1" /><x:col min="3" max="3" width="22.625" customWidth="1" /><x:col min="4" max="4" width="42.75" customWidth="1" /></x:cols><x:sheetData><x:row r="1"><x:c r="A1" s="1" t="s"><x:v>0</x:v></x:c><x:c r="B1" s="1" t="s"><x:v>1</x:v></x:c><x:c r="C1" s="1" t="s"><x:v>2</x:v></x:c><x:c r="D1" s="1" t="s"><x:v>3</x:v></x:c></x:row><x:row r="2"><x:c r="A2"><x:v>1000</x:v></x:c><x:c r="B2"><x:v>1000</x:v></x:c><x:c r="C2" t="s"><x:v>4</x:v></x:c><x:c r="D2" t="s"><x:v>5</x:v></x:c></x:row><x:row r="3"><x:c r="A3"><x:v>1001</x:v></x:c><x:c r="B3"><x:v>1001</x:v></x:c><x:c r="C3" t="s"><x:v>6</x:v></x:c><x:c r="D3" t="s"><x:v>7</x:v></x:c></x:row><x:row r="4"><x:c r="A4"><x:v>1002</x:v></x:c><x:c r="B4"><x:v>1002</x:v></x:c><x:c r="C4" t="s"><x:v>8</x:v></x:c><x:c r="D4" t="s"><x:v>9</x:v></x:c></x:row><x:row r="5"><x:c r="A5"><x:v>1003</x:v></x:c><x:c r="B5"><x:v>1003</x:v></x:c><x:c r="C5" t="s"><x:v>10</x:v></x:c><x:c r="D5" t="s"><x:v>11</x:v></x:c></x:row><x:row r="6"><x:c r="A6"><x:v>1004</x:v></x:c><x:c r="B6"><x:v>1004</x:v></x:c><x:c r="C6" t="s"><x:v>12</x:v></x:c><x:c r="D6" t="s"><x:v>13</x:v></x:c></x:row><x:row r="7"><x:c r="A7"><x:v>1005</x:v></x:c><x:c r="B7"><x:v>1005</x:v></x:c><x:c r="C7" t="s"><x:v>14</x:v></x:c><x:c r="D7" t="s"><x:v>15</x:v></x:c></x:row><x:row r="8"><x:c r="A8"><x:v>1006</x:v></x:c><x:c r="B8"><x:v>1006</x:v></x:c><x:c r="C8" t="s"><x:v>16</x:v></x:c><x:c r="D8" t="s"><x:v>17</x:v></x:c></x:row><x:row r="9"><x:c r="A9"><x:v>1007</x:v></x:c><x:c r="B9"><x:v>1007</x:v></x:c><x:c r="C9" t="s"><x:v>18</x:v></x:c><x:c r="D9" t="s"><x:v>19</x:v></x:c></x:row><x:row r="10"><x:c r="A10"><x:v>1008</x:v></x:c><x:c r="B10"><x:v>1008</x:v></x:c><x:c r="C10" t="s"><x:v>20</x:v></x:c><x:c r="D10" t="s"><x:v>21</x:v></x:c></x:row><x:row r="11"><x:c r="A11"><x:v>1009</x:v></x:c><x:c r="B11"><x:v>1009</x:v></x:c><x:c r="C11" t="s"><x:v>22</x:v></x:c><x:c r="D11" t="s"><x:v>23</x:v></x:c></x:row><x:row r="12"><x:c r="A12"><x:v>1010</x:v></x:c><x:c r="B12"><x:v>1010</x:v></x:c><x:c r="C12" t="s"><x:v>24</x:v></x:c><x:c r="D12" t="s"><x:v>25</x:v></x:c></x:row><x:row r="13"><x:c r="A13"><x:v>1011</x:v></x:c><x:c r="B13"><x:v>1011</x:v></x:c><x:c r="C13" t="s"><x:v>26</x:v></x:c><x:c r="D13" t="s"><x:v>27</x:v></x:c></x:row><x:row r="14"><x:c r="A14"><x:v>1012</x:v></x:c><x:c r="B14"><x:v>1012</x:v></x:c><x:c r="C14" t="s"><x:v>28</x:v></x:c><x:c r="D14" t="s"><x:v>29</x:v></x:c></x:row><x:row r="15"><x:c r="A15"><x:v>1013</x:v></x:c><x:c r="B15"><x:v>1013</x:v></x:c><x:c r="C15" t="s"><x:v>30</x:v></x:c><x:c r="D15" t="s"><x:v>31</x:v></x:c></x:row><x:row r="16"><x:c r="A16"><x:v>1014</x:v></x:c><x:c r="B16"><x:v>1014</x:v></x:c><x:c r="C16" t="s"><x:v>32</x:v></x:c><x:c r="D16" t="s"><x:v>33</x:v></x:c></x:row><x:row r="17"><x:c r="A17"><x:v>1015</x:v></x:c><x:c r="B17"><x:v>1015</x:v></x:c><x:c r="C17" t="s"><x:v>34</x:v></x:c><x:c r="D17" t="s"><x:v>35</x:v></x:c></x:row><x:row r="18"><x:c r="A18"><x:v>1016</x:v></x:c><x:c r="B18"><x:v>1016</x:v></x:c><x:c r="C18" t="s"><x:v>36</x:v></x:c><x:c r="D18" t="s"><x:v>36</x:v></x:c></x:row><x:row r="19"><x:c r="A19"><x:v>1017</x:v></x:c><x:c r="B19"><x:v>1017</x:v></x:c><x:c r="C19" t="s"><x:v>37</x:v></x:c><x:c r="D19" t="s"><x:v>38</x:v></x:c></x:row><x:row r="20"><x:c r="A20"><x:v>1018</x:v></x:c><x:c r="B20"><x:v>1018</x:v></x:c><x:c r="C20" t="s"><x:v>39</x:v></x:c><x:c r="D20" t="s"><x:v>40</x:v></x:c></x:row><x:row r="21"><x:c r="A21"><x:v>1019</x:v></x:c><x:c r="B21"><x:v>1019</x:v></x:c><x:c r="C21" t="s"><x:v>41</x:v></x:c><x:c r="D21" t="s"><x:v>42</x:v></x:c></x:row><x:row r="22"><x:c r="A22"><x:v>1020</x:v></x:c><x:c r="B22"><x:v>1020</x:v></x:c><x:c r="C22" t="s"><x:v>43</x:v></x:c><x:c r="D22" t="s"><x:v>44</x:v></x:c></x:row><x:row r="23"><x:c r="A23"><x:v>1021</x:v></x:c><x:c r="B23"><x:v>1021</x:v></x:c><x:c r="C23" t="s"><x:v>45</x:v></x:c><x:c r="D23" t="s"><x:v>46</x:v></x:c></x:row><x:row r="24"><x:c r="A24"><x:v>1022</x:v></x:c><x:c r="B24"><x:v>1022</x:v></x:c><x:c r="C24" t="s"><x:v>47</x:v></x:c><x:c r="D24" t="s"><x:v>48</x:v></x:c></x:row><x:row r="25"><x:c r="A25"><x:v>1023</x:v></x:c><x:c r="B25"><x:v>1023</x:v></x:c><x:c r="C25" t="s"><x:v>49</x:v></x:c><x:c r="D25" t="s"><x:v>50</x:v></x:c></x:row><x:row r="26"><x:c r="A26"><x:v>1024</x:v></x:c><x:c r="B26"><x:v>1024</x:v></x:c><x:c r="C26" t="s"><x:v>51</x:v></x:c><x:c r="D26" t="s"><x:v>52</x:v></x:c></x:row><x:row r="27"><x:c r="A27"><x:v>1025</x:v></x:c><x:c r="B27"><x:v>1025</x:v></x:c><x:c r="C27" t="s"><x:v>53</x:v></x:c><x:c r="D27" t="s"><x:v>54</x:v></x:c></x:row><x:row r="28"><x:c r="A28"><x:v>1026</x:v></x:c><x:c r="B28"><x:v>1026</x:v></x:c><x:c r="C28" t="s"><x:v>55</x:v></x:c><x:c r="D28" t="s"><x:v>56</x:v></x:c></x:row><x:row r="29"><x:c r="A29"><x:v>1027</x:v></x:c><x:c r="B29"><x:v>1027</x:v></x:c><x:c r="C29" t="s"><x:v>57</x:v></x:c><x:c r="D29" t="s"><x:v>58</x:v></x:c></x:row><x:row r="30"><x:c r="A30"><x:v>1028</x:v></x:c><x:c r="B30" t="s"><x:v>59</x:v></x:c><x:c r="C30" t="s"><x:v>60</x:v></x:c><x:c r="D30" t="s"><x:v>59</x:v></x:c></x:row><x:row r="31"><x:c r="A31"><x:v>1029</x:v></x:c><x:c r="B31" t="s"><x:v>61</x:v></x:c><x:c r="C31" t="s"><x:v>62</x:v></x:c><x:c r="D31" t="s"><x:v>61</x:v></x:c></x:row><x:row r="32"><x:c r="A32"><x:v>1030</x:v></x:c><x:c r="B32" t="s"><x:v>63</x:v></x:c><x:c r="C32" t="s"><x:v>64</x:v></x:c><x:c r="D32" t="s"><x:v>65</x:v></x:c></x:row><x:row r="33"><x:c r="A33"><x:v>1031</x:v></x:c><x:c r="B33" t="s"><x:v>66</x:v></x:c><x:c r="C33" t="s"><x:v>67</x:v></x:c><x:c r="D33" t="s"><x:v>68</x:v></x:c></x:row><x:row r="34"><x:c r="A34"><x:v>1032</x:v></x:c><x:c r="B34"><x:v>1032</x:v></x:c><x:c r="C34" t="s"><x:v>69</x:v></x:c><x:c r="D34" t="s"><x:v>70</x:v></x:c></x:row><x:row r="35"><x:c r="A35"><x:v>1033</x:v></x:c><x:c r="B35"><x:v>1033</x:v></x:c><x:c r="C35" t="s"><x:v>71</x:v></x:c><x:c r="D35" t="s"><x:v>72</x:v></x:c></x:row><x:row r="36"><x:c r="A36"><x:v>1034</x:v></x:c><x:c r="B36"><x:v>1034</x:v></x:c><x:c r="C36" t="s"><x:v>73</x:v></x:c><x:c r="D36" t="s"><x:v>74</x:v></x:c></x:row><x:row r="37"><x:c r="A37"><x:v>1035</x:v></x:c><x:c r="B37"><x:v>1035</x:v></x:c><x:c r="C37" t="s"><x:v>75</x:v></x:c><x:c r="D37" t="s"><x:v>76</x:v></x:c></x:row><x:row r="38"><x:c r="A38"><x:v>1036</x:v></x:c><x:c r="B38"><x:v>1036</x:v></x:c><x:c r="C38" t="s"><x:v>77</x:v></x:c><x:c r="D38" t="s"><x:v>78</x:v></x:c></x:row><x:row r="39"><x:c r="A39"><x:v>1037</x:v></x:c><x:c r="B39"><x:v>1037</x:v></x:c><x:c r="C39" t="s"><x:v>79</x:v></x:c><x:c r="D39" t="s"><x:v>80</x:v></x:c></x:row><x:row r="40"><x:c r="A40"><x:v>1038</x:v></x:c><x:c r="B40"><x:v>1038</x:v></x:c><x:c r="C40" t="s"><x:v>81</x:v></x:c><x:c r="D40" t="s"><x:v>82</x:v></x:c></x:row><x:row r="41"><x:c r="A41"><x:v>1039</x:v></x:c><x:c r="B41"><x:v>1039</x:v></x:c><x:c r="C41" t="s"><x:v>83</x:v></x:c><x:c r="D41" t="s"><x:v>84</x:v></x:c></x:row><x:row r="42"><x:c r="A42"><x:v>1040</x:v></x:c><x:c r="B42"><x:v>1040</x:v></x:c><x:c r="C42" t="s"><x:v>85</x:v></x:c><x:c r="D42" t="s"><x:v>86</x:v></x:c></x:row><x:row r="43"><x:c r="A43"><x:v>1041</x:v></x:c><x:c r="B43"><x:v>1041</x:v></x:c><x:c r="C43" t="s"><x:v>87</x:v></x:c><x:c r="D43" t="s"><x:v>88</x:v></x:c></x:row><x:row r="44"><x:c r="A44"><x:v>1042</x:v></x:c><x:c r="B44"><x:v>1042</x:v></x:c><x:c r="C44" t="s"><x:v>89</x:v></x:c><x:c r="D44" t="s"><x:v>90</x:v></x:c></x:row><x:row r="45"><x:c r="A45"><x:v>1043</x:v></x:c><x:c r="B45"><x:v>1043</x:v></x:c><x:c r="C45" t="s"><x:v>91</x:v></x:c><x:c r="D45" t="s"><x:v>92</x:v></x:c></x:row><x:row r="46"><x:c r="A46"><x:v>1044</x:v></x:c><x:c r="B46"><x:v>1044</x:v></x:c><x:c r="C46" t="s"><x:v>93</x:v></x:c><x:c r="D46" t="s"><x:v>94</x:v></x:c></x:row><x:row r="47"><x:c r="A47"><x:v>1045</x:v></x:c><x:c r="B47"><x:v>1045</x:v></x:c><x:c r="C47" t="s"><x:v>95</x:v></x:c><x:c r="D47" t="s"><x:v>96</x:v></x:c></x:row><x:row r="48"><x:c r="A48"><x:v>1046</x:v></x:c><x:c r="B48"><x:v>1046</x:v></x:c><x:c r="C48" t="s"><x:v>97</x:v></x:c><x:c r="D48" t="s"><x:v>98</x:v></x:c></x:row><x:row r="49"><x:c r="A49"><x:v>1047</x:v></x:c><x:c r="B49"><x:v>1047</x:v></x:c><x:c r="C49" t="s"><x:v>99</x:v></x:c><x:c r="D49" t="s"><x:v>100</x:v></x:c></x:row><x:row r="50"><x:c r="A50"><x:v>1048</x:v></x:c><x:c r="B50"><x:v>1048</x:v></x:c><x:c r="C50" t="s"><x:v>101</x:v></x:c><x:c r="D50" t="s"><x:v>102</x:v></x:c></x:row><x:row r="51"><x:c r="A51"><x:v>1049</x:v></x:c><x:c r="B51"><x:v>1049</x:v></x:c><x:c r="C51" t="s"><x:v>103</x:v></x:c><x:c r="D51" t="s"><x:v>104</x:v></x:c></x:row><x:row r="52"><x:c r="A52"><x:v>1050</x:v></x:c><x:c r="B52"><x:v>1050</x:v></x:c><x:c r="C52" t="s"><x:v>105</x:v></x:c><x:c r="D52" t="s"><x:v>106</x:v></x:c></x:row><x:row r="53"><x:c r="A53"><x:v>1051</x:v></x:c><x:c r="B53"><x:v>1051</x:v></x:c><x:c r="C53" t="s"><x:v>107</x:v></x:c><x:c r="D53" t="s"><x:v>108</x:v></x:c></x:row><x:row r="54"><x:c r="A54"><x:v>1052</x:v></x:c><x:c r="B54"><x:v>1052</x:v></x:c><x:c r="C54" t="s"><x:v>109</x:v></x:c><x:c r="D54" t="s"><x:v>110</x:v></x:c></x:row><x:row r="55"><x:c r="A55"><x:v>1053</x:v></x:c><x:c r="B55"><x:v>1053</x:v></x:c><x:c r="C55" t="s"><x:v>111</x:v></x:c><x:c r="D55" t="s"><x:v>112</x:v></x:c></x:row><x:row r="56" ht="17.450000762939453" customHeight="1"><x:c r="A56"><x:v>1054</x:v></x:c><x:c r="B56"><x:v>1054</x:v></x:c><x:c r="C56" t="s"><x:v>113</x:v></x:c><x:c r="D56" t="s"><x:v>114</x:v></x:c></x:row><x:row r="57"><x:c r="A57"><x:v>1055</x:v></x:c><x:c r="B57"><x:v>1055</x:v></x:c><x:c r="C57" t="s"><x:v>81</x:v></x:c><x:c r="D57" t="s"><x:v>82</x:v></x:c></x:row><x:row r="58"><x:c r="A58"><x:v>1056</x:v></x:c><x:c r="B58"><x:v>1056</x:v></x:c><x:c r="C58" t="s"><x:v>115</x:v></x:c><x:c r="D58" t="s"><x:v>116</x:v></x:c></x:row><x:row r="59"><x:c r="A59"><x:v>1057</x:v></x:c><x:c r="B59"><x:v>1057</x:v></x:c><x:c r="C59" t="s"><x:v>117</x:v></x:c><x:c r="D59" t="s"><x:v>117</x:v></x:c></x:row><x:row r="60"><x:c r="A60"><x:v>1058</x:v></x:c><x:c r="B60"><x:v>1058</x:v></x:c><x:c r="C60" t="s"><x:v>118</x:v></x:c><x:c r="D60" t="s"><x:v>119</x:v></x:c></x:row><x:row r="61"><x:c r="A61"><x:v>1059</x:v></x:c><x:c r="B61"><x:v>1059</x:v></x:c><x:c r="C61" t="s"><x:v>120</x:v></x:c><x:c r="D61" t="s"><x:v>121</x:v></x:c></x:row><x:row r="62"><x:c r="A62"><x:v>1060</x:v></x:c><x:c r="B62"><x:v>1060</x:v></x:c><x:c r="C62" t="s"><x:v>122</x:v></x:c><x:c r="D62" t="s"><x:v>123</x:v></x:c></x:row><x:row r="63"><x:c r="A63"><x:v>1061</x:v></x:c><x:c r="B63"><x:v>1061</x:v></x:c><x:c r="C63" t="s"><x:v>124</x:v></x:c><x:c r="D63" t="s"><x:v>125</x:v></x:c></x:row><x:row r="64"><x:c r="A64"><x:v>1062</x:v></x:c><x:c r="B64"><x:v>1062</x:v></x:c><x:c r="C64" t="s"><x:v>126</x:v></x:c><x:c r="D64" t="s"><x:v>127</x:v></x:c></x:row><x:row r="65"><x:c r="A65"><x:v>1063</x:v></x:c><x:c r="B65"><x:v>1063</x:v></x:c><x:c r="C65" t="s"><x:v>128</x:v></x:c><x:c r="D65" t="s"><x:v>129</x:v></x:c></x:row><x:row r="66"><x:c r="A66"><x:v>1064</x:v></x:c><x:c r="B66"><x:v>1064</x:v></x:c><x:c r="C66" t="s"><x:v>130</x:v></x:c><x:c r="D66" t="s"><x:v>131</x:v></x:c></x:row><x:row r="67"><x:c r="A67"><x:v>1065</x:v></x:c><x:c r="B67"><x:v>1065</x:v></x:c><x:c r="C67" t="s"><x:v>132</x:v></x:c><x:c r="D67" t="s"><x:v>133</x:v></x:c></x:row><x:row r="68"><x:c r="A68"><x:v>1066</x:v></x:c><x:c r="B68"><x:v>1066</x:v></x:c><x:c r="C68" t="s"><x:v>134</x:v></x:c><x:c r="D68" t="s"><x:v>135</x:v></x:c></x:row><x:row r="69"><x:c r="A69"><x:v>1067</x:v></x:c><x:c r="B69" t="s"><x:v>136</x:v></x:c><x:c r="C69" t="s"><x:v>137</x:v></x:c><x:c r="D69" t="s"><x:v>138</x:v></x:c></x:row><x:row r="70"><x:c r="A70"><x:v>1068</x:v></x:c><x:c r="B70" t="s"><x:v>139</x:v></x:c><x:c r="C70" t="s"><x:v>140</x:v></x:c><x:c r="D70" t="s"><x:v>141</x:v></x:c></x:row><x:row r="71"><x:c r="A71"><x:v>1069</x:v></x:c><x:c r="B71" t="s"><x:v>142</x:v></x:c><x:c r="C71" t="s"><x:v>143</x:v></x:c><x:c r="D71" t="s"><x:v>144</x:v></x:c></x:row><x:row r="72"><x:c r="A72"><x:v>1070</x:v></x:c><x:c r="B72" t="s"><x:v>145</x:v></x:c><x:c r="C72" t="s"><x:v>146</x:v></x:c><x:c r="D72" t="s"><x:v>147</x:v></x:c></x:row><x:row r="73"><x:c r="A73"><x:v>1071</x:v></x:c><x:c r="B73" t="s"><x:v>148</x:v></x:c><x:c r="C73" t="s"><x:v>149</x:v></x:c><x:c r="D73" t="s"><x:v>150</x:v></x:c></x:row><x:row r="74"><x:c r="A74"><x:v>1072</x:v></x:c><x:c r="B74" t="s"><x:v>151</x:v></x:c><x:c r="C74" t="s"><x:v>152</x:v></x:c><x:c r="D74" t="s"><x:v>153</x:v></x:c></x:row><x:row r="75"><x:c r="A75"><x:v>1073</x:v></x:c><x:c r="B75" t="s"><x:v>154</x:v></x:c><x:c r="C75" t="s"><x:v>155</x:v></x:c><x:c r="D75" t="s"><x:v>156</x:v></x:c></x:row><x:row r="76"><x:c r="A76"><x:v>1074</x:v></x:c><x:c r="B76" t="s"><x:v>157</x:v></x:c><x:c r="C76" t="s"><x:v>158</x:v></x:c><x:c r="D76" t="s"><x:v>159</x:v></x:c></x:row><x:row r="77"><x:c r="A77"><x:v>1075</x:v></x:c><x:c r="B77" t="s"><x:v>160</x:v></x:c><x:c r="C77" t="s"><x:v>161</x:v></x:c><x:c r="D77" t="s"><x:v>162</x:v></x:c></x:row><x:row r="78"><x:c r="A78"><x:v>1076</x:v></x:c><x:c r="B78" t="s"><x:v>163</x:v></x:c><x:c r="C78" t="s"><x:v>164</x:v></x:c><x:c r="D78" t="s"><x:v>165</x:v></x:c></x:row><x:row r="79"><x:c r="A79"><x:v>1077</x:v></x:c><x:c r="B79" t="s"><x:v>166</x:v></x:c><x:c r="C79" t="s"><x:v>167</x:v></x:c><x:c r="D79" t="s"><x:v>168</x:v></x:c></x:row><x:row r="80"><x:c r="A80"><x:v>1078</x:v></x:c><x:c r="B80" t="s"><x:v>169</x:v></x:c><x:c r="C80" t="s"><x:v>170</x:v></x:c><x:c r="D80" t="s"><x:v>171</x:v></x:c></x:row><x:row r="81"><x:c r="A81"><x:v>1079</x:v></x:c><x:c r="B81" t="s"><x:v>172</x:v></x:c><x:c r="C81" t="s"><x:v>113</x:v></x:c><x:c r="D81" t="s"><x:v>114</x:v></x:c></x:row><x:row r="82"><x:c r="A82"><x:v>1080</x:v></x:c><x:c r="B82" t="s"><x:v>173</x:v></x:c><x:c r="C82" t="s"><x:v>174</x:v></x:c><x:c r="D82" t="s"><x:v>175</x:v></x:c></x:row><x:row r="83"><x:c r="A83"><x:v>1081</x:v></x:c><x:c r="B83" t="s"><x:v>176</x:v></x:c><x:c r="C83" t="s"><x:v>177</x:v></x:c><x:c r="D83" t="s"><x:v>178</x:v></x:c></x:row><x:row r="84"><x:c r="A84"><x:v>1082</x:v></x:c><x:c r="B84" t="s"><x:v>179</x:v></x:c><x:c r="C84" t="s"><x:v>180</x:v></x:c><x:c r="D84" t="s"><x:v>181</x:v></x:c></x:row><x:row r="85"><x:c r="A85"><x:v>1083</x:v></x:c><x:c r="B85" t="s"><x:v>182</x:v></x:c><x:c r="C85" t="s"><x:v>183</x:v></x:c><x:c r="D85" t="s"><x:v>184</x:v></x:c></x:row><x:row r="86"><x:c r="A86"><x:v>1084</x:v></x:c><x:c r="B86" t="s"><x:v>185</x:v></x:c><x:c r="C86" t="s"><x:v>186</x:v></x:c><x:c r="D86" t="s"><x:v>187</x:v></x:c></x:row><x:row r="87"><x:c r="A87"><x:v>1085</x:v></x:c><x:c r="B87" t="s"><x:v>188</x:v></x:c><x:c r="C87" t="s"><x:v>189</x:v></x:c><x:c r="D87" t="s"><x:v>190</x:v></x:c></x:row><x:row r="88"><x:c r="A88"><x:v>1086</x:v></x:c><x:c r="B88" t="s"><x:v>191</x:v></x:c><x:c r="C88" t="s"><x:v>192</x:v></x:c><x:c r="D88" t="s"><x:v>193</x:v></x:c></x:row><x:row r="89"><x:c r="A89"><x:v>1087</x:v></x:c><x:c r="B89" t="s"><x:v>194</x:v></x:c><x:c r="C89" t="s"><x:v>195</x:v></x:c><x:c r="D89" t="s"><x:v>196</x:v></x:c></x:row><x:row r="90"><x:c r="A90" t="n"><x:v>1088</x:v></x:c><x:c r="B90" t="str"><x:v>FinalFileHint</x:v></x:c><x:c r="C90" t="str"><x:v>선택 결과를 확인·편집한 뒤 저장 및 스테이징을 눌러 완료하세요.</x:v></x:c><x:c r="D90" t="str"><x:v>Review or edit the result, then save and stage to finish.</x:v></x:c></x:row><x:row r="91"><x:c r="A91"><x:v>1089</x:v></x:c><x:c r="B91" t="s"><x:v>197</x:v></x:c><x:c r="C91" t="s"><x:v>198</x:v></x:c><x:c r="D91" t="s"><x:v>199</x:v></x:c></x:row><x:row r="92"><x:c r="A92"><x:v>1090</x:v></x:c><x:c r="B92" t="s"><x:v>200</x:v></x:c><x:c r="C92" t="s"><x:v>201</x:v></x:c><x:c r="D92" t="s"><x:v>202</x:v></x:c></x:row><x:row r="93"><x:c r="A93"><x:v>1091</x:v></x:c><x:c r="B93" t="s"><x:v>203</x:v></x:c><x:c r="C93" t="s"><x:v>204</x:v></x:c><x:c r="D93" t="s"><x:v>205</x:v></x:c></x:row><x:row r="94"><x:c r="A94"><x:v>1092</x:v></x:c><x:c r="B94" t="s"><x:v>206</x:v></x:c><x:c r="C94" t="s"><x:v>207</x:v></x:c><x:c r="D94" t="s"><x:v>208</x:v></x:c></x:row><x:row r="95"><x:c r="A95"><x:v>1093</x:v></x:c><x:c r="B95" t="s"><x:v>209</x:v></x:c><x:c r="C95" t="s"><x:v>210</x:v></x:c><x:c r="D95" t="s"><x:v>211</x:v></x:c></x:row><x:row r="96"><x:c r="A96"><x:v>1094</x:v></x:c><x:c r="B96" t="s"><x:v>212</x:v></x:c><x:c r="C96" t="s"><x:v>213</x:v></x:c><x:c r="D96" t="s"><x:v>214</x:v></x:c></x:row><x:row r="97"><x:c r="A97"><x:v>1095</x:v></x:c><x:c r="B97" t="s"><x:v>215</x:v></x:c><x:c r="C97" t="s"><x:v>216</x:v></x:c><x:c r="D97" t="s"><x:v>217</x:v></x:c></x:row><x:row r="98"><x:c r="A98"><x:v>1096</x:v></x:c><x:c r="B98" t="s"><x:v>218</x:v></x:c><x:c r="C98" t="s"><x:v>219</x:v></x:c><x:c r="D98" t="s"><x:v>220</x:v></x:c></x:row><x:row r="99"><x:c r="A99"><x:v>1097</x:v></x:c><x:c r="B99" t="s"><x:v>221</x:v></x:c><x:c r="C99" t="s"><x:v>222</x:v></x:c><x:c r="D99" t="s"><x:v>223</x:v></x:c></x:row><x:row r="100"><x:c r="A100"><x:v>1098</x:v></x:c><x:c r="B100" t="s"><x:v>224</x:v></x:c><x:c r="C100" t="s"><x:v>225</x:v></x:c><x:c r="D100" t="s"><x:v>226</x:v></x:c></x:row><x:row r="101"><x:c r="A101"><x:v>1099</x:v></x:c><x:c r="B101" t="s"><x:v>227</x:v></x:c><x:c r="C101" t="s"><x:v>228</x:v></x:c><x:c r="D101" t="s"><x:v>229</x:v></x:c></x:row><x:row r="102"><x:c r="A102"><x:v>1100</x:v></x:c><x:c r="B102" t="s"><x:v>230</x:v></x:c><x:c r="C102" t="s"><x:v>231</x:v></x:c><x:c r="D102" t="s"><x:v>232</x:v></x:c></x:row><x:row r="103"><x:c r="A103"><x:v>1101</x:v></x:c><x:c r="B103" t="s"><x:v>233</x:v></x:c><x:c r="C103" t="s"><x:v>234</x:v></x:c><x:c r="D103" t="s"><x:v>235</x:v></x:c></x:row><x:row r="104"><x:c r="A104"><x:v>1102</x:v></x:c><x:c r="B104" t="s"><x:v>236</x:v></x:c><x:c r="C104" t="s"><x:v>237</x:v></x:c><x:c r="D104" t="s"><x:v>238</x:v></x:c></x:row><x:row r="105"><x:c r="A105"><x:v>1103</x:v></x:c><x:c r="B105" t="s"><x:v>239</x:v></x:c><x:c r="C105" t="s"><x:v>240</x:v></x:c><x:c r="D105" t="s"><x:v>241</x:v></x:c></x:row><x:row r="106"><x:c r="A106"><x:v>1104</x:v></x:c><x:c r="B106" t="s"><x:v>242</x:v></x:c><x:c r="C106" t="s"><x:v>243</x:v></x:c><x:c r="D106" t="s"><x:v>244</x:v></x:c></x:row><x:row r="107"><x:c r="A107"><x:v>1105</x:v></x:c><x:c r="B107" t="s"><x:v>245</x:v></x:c><x:c r="C107" t="s"><x:v>246</x:v></x:c><x:c r="D107" t="s"><x:v>247</x:v></x:c></x:row><x:row r="108"><x:c r="A108"><x:v>1106</x:v></x:c><x:c r="B108" t="s"><x:v>248</x:v></x:c><x:c r="C108" t="s"><x:v>249</x:v></x:c><x:c r="D108" t="s"><x:v>250</x:v></x:c></x:row><x:row r="109"><x:c r="A109"><x:v>1107</x:v></x:c><x:c r="B109" t="s"><x:v>251</x:v></x:c><x:c r="C109" t="s"><x:v>252</x:v></x:c><x:c r="D109" t="s"><x:v>253</x:v></x:c></x:row><x:row r="110"><x:c r="A110"><x:v>1108</x:v></x:c><x:c r="B110" t="s"><x:v>254</x:v></x:c><x:c r="C110" t="s"><x:v>255</x:v></x:c><x:c r="D110" t="s"><x:v>256</x:v></x:c></x:row><x:row r="111"><x:c r="A111"><x:v>1109</x:v></x:c><x:c r="B111" t="s"><x:v>257</x:v></x:c><x:c r="C111" t="s"><x:v>258</x:v></x:c><x:c r="D111" t="s"><x:v>259</x:v></x:c></x:row><x:row r="112"><x:c r="A112"><x:v>1110</x:v></x:c><x:c r="B112" t="s"><x:v>260</x:v></x:c><x:c r="C112" t="s"><x:v>261</x:v></x:c><x:c r="D112" t="s"><x:v>262</x:v></x:c></x:row><x:row r="113"><x:c r="A113"><x:v>1111</x:v></x:c><x:c r="B113" t="s"><x:v>263</x:v></x:c><x:c r="C113" t="s"><x:v>264</x:v></x:c><x:c r="D113" t="s"><x:v>265</x:v></x:c></x:row><x:row r="114"><x:c r="A114"><x:v>1112</x:v></x:c><x:c r="B114" t="s"><x:v>266</x:v></x:c><x:c r="C114" t="s"><x:v>267</x:v></x:c><x:c r="D114" t="s"><x:v>268</x:v></x:c></x:row><x:row r="115"><x:c r="A115"><x:v>1113</x:v></x:c><x:c r="B115" t="s"><x:v>269</x:v></x:c><x:c r="C115" t="s"><x:v>270</x:v></x:c><x:c r="D115" t="s"><x:v>271</x:v></x:c></x:row><x:row r="116"><x:c r="A116"><x:v>1114</x:v></x:c><x:c r="B116" t="s"><x:v>272</x:v></x:c><x:c r="C116" t="s"><x:v>273</x:v></x:c><x:c r="D116" t="s"><x:v>274</x:v></x:c></x:row><x:row r="117"><x:c r="A117"><x:v>1115</x:v></x:c><x:c r="B117" t="s"><x:v>275</x:v></x:c><x:c r="C117" t="s"><x:v>276</x:v></x:c><x:c r="D117" t="s"><x:v>277</x:v></x:c></x:row><x:row r="118"><x:c r="A118"><x:v>1116</x:v></x:c><x:c r="B118" t="s"><x:v>278</x:v></x:c><x:c r="C118" t="s"><x:v>279</x:v></x:c><x:c r="D118" t="s"><x:v>280</x:v></x:c></x:row><x:row r="119"><x:c r="A119"><x:v>1117</x:v></x:c><x:c r="B119" t="s"><x:v>281</x:v></x:c><x:c r="C119" t="s"><x:v>282</x:v></x:c><x:c r="D119" t="s"><x:v>283</x:v></x:c></x:row><x:row r="120"><x:c r="A120"><x:v>1118</x:v></x:c><x:c r="B120" t="s"><x:v>284</x:v></x:c><x:c r="C120" t="s"><x:v>285</x:v></x:c><x:c r="D120" t="s"><x:v>286</x:v></x:c></x:row><x:row r="121"><x:c r="A121"><x:v>1119</x:v></x:c><x:c r="B121" t="s"><x:v>287</x:v></x:c><x:c r="C121" t="s"><x:v>273</x:v></x:c><x:c r="D121" t="s"><x:v>274</x:v></x:c></x:row><x:row r="122"><x:c r="A122"><x:v>1120</x:v></x:c><x:c r="B122" t="s"><x:v>288</x:v></x:c><x:c r="C122" t="s"><x:v>289</x:v></x:c><x:c r="D122" t="s"><x:v>290</x:v></x:c></x:row><x:row r="123"><x:c r="A123"><x:v>1121</x:v></x:c><x:c r="B123" t="s"><x:v>291</x:v></x:c><x:c r="C123" t="s"><x:v>292</x:v></x:c><x:c r="D123" t="s"><x:v>293</x:v></x:c></x:row><x:row r="124"><x:c r="A124"><x:v>1122</x:v></x:c><x:c r="B124" t="s"><x:v>294</x:v></x:c><x:c r="C124" t="s"><x:v>295</x:v></x:c><x:c r="D124" t="s"><x:v>296</x:v></x:c></x:row><x:row r="125"><x:c r="A125"><x:v>1123</x:v></x:c><x:c r="B125" t="s"><x:v>297</x:v></x:c><x:c r="C125" t="s"><x:v>298</x:v></x:c><x:c r="D125" t="s"><x:v>299</x:v></x:c></x:row><x:row r="126"><x:c r="A126"><x:v>1124</x:v></x:c><x:c r="B126" t="s"><x:v>300</x:v></x:c><x:c r="C126" t="s"><x:v>301</x:v></x:c><x:c r="D126" t="s"><x:v>302</x:v></x:c></x:row><x:row r="127"><x:c r="A127"><x:v>1125</x:v></x:c><x:c r="B127" t="s"><x:v>303</x:v></x:c><x:c r="C127" t="s"><x:v>304</x:v></x:c><x:c r="D127" t="s"><x:v>305</x:v></x:c></x:row><x:row r="128"><x:c r="A128"><x:v>1126</x:v></x:c><x:c r="B128" t="s"><x:v>306</x:v></x:c><x:c r="C128" t="s"><x:v>307</x:v></x:c><x:c r="D128" t="s"><x:v>308</x:v></x:c></x:row><x:row r="129"><x:c r="A129"><x:v>1127</x:v></x:c><x:c r="B129" t="s"><x:v>309</x:v></x:c><x:c r="C129" t="s"><x:v>310</x:v></x:c><x:c r="D129" t="s"><x:v>311</x:v></x:c></x:row><x:row r="130"><x:c r="A130"><x:v>1128</x:v></x:c><x:c r="B130" t="s"><x:v>312</x:v></x:c><x:c r="C130" t="s"><x:v>313</x:v></x:c><x:c r="D130" t="s"><x:v>314</x:v></x:c></x:row><x:row r="131"><x:c r="A131"><x:v>1129</x:v></x:c><x:c r="B131" t="s"><x:v>315</x:v></x:c><x:c r="C131" t="s"><x:v>307</x:v></x:c><x:c r="D131" t="s"><x:v>316</x:v></x:c></x:row><x:row r="132"><x:c r="A132"><x:v>1130</x:v></x:c><x:c r="B132" t="s"><x:v>317</x:v></x:c><x:c r="C132" t="s"><x:v>318</x:v></x:c><x:c r="D132" t="s"><x:v>319</x:v></x:c></x:row><x:row r="133"><x:c r="A133"><x:v>1131</x:v></x:c><x:c r="B133" t="s"><x:v>320</x:v></x:c><x:c r="C133" t="s"><x:v>321</x:v></x:c><x:c r="D133" t="s"><x:v>322</x:v></x:c></x:row><x:row r="134"><x:c r="A134"><x:v>1132</x:v></x:c><x:c r="B134" t="s"><x:v>323</x:v></x:c><x:c r="C134" t="s"><x:v>324</x:v></x:c><x:c r="D134" t="s"><x:v>325</x:v></x:c></x:row><x:row r="135"><x:c r="A135"><x:v>1133</x:v></x:c><x:c r="B135" t="s"><x:v>326</x:v></x:c><x:c r="C135" t="s"><x:v>327</x:v></x:c><x:c r="D135" t="s"><x:v>328</x:v></x:c></x:row><x:row r="136"><x:c r="A136"><x:v>1134</x:v></x:c><x:c r="B136" t="s"><x:v>329</x:v></x:c><x:c r="C136" t="s"><x:v>69</x:v></x:c><x:c r="D136" t="s"><x:v>70</x:v></x:c></x:row><x:row r="137"><x:c r="A137"><x:v>1135</x:v></x:c><x:c r="B137" t="s"><x:v>330</x:v></x:c><x:c r="C137" t="s"><x:v>331</x:v></x:c><x:c r="D137" t="s"><x:v>332</x:v></x:c></x:row><x:row r="138"><x:c r="A138"><x:v>1136</x:v></x:c><x:c r="B138" t="s"><x:v>333</x:v></x:c><x:c r="C138" t="s"><x:v>334</x:v></x:c><x:c r="D138" t="s"><x:v>335</x:v></x:c></x:row><x:row r="139"><x:c r="A139"><x:v>1137</x:v></x:c><x:c r="B139" t="s"><x:v>336</x:v></x:c><x:c r="C139" t="s"><x:v>337</x:v></x:c><x:c r="D139" t="s"><x:v>338</x:v></x:c></x:row><x:row r="140"><x:c r="A140"><x:v>1138</x:v></x:c><x:c r="B140" t="s"><x:v>339</x:v></x:c><x:c r="C140" t="s"><x:v>340</x:v></x:c><x:c r="D140" t="s"><x:v>341</x:v></x:c></x:row><x:row r="141"><x:c r="A141"><x:v>1139</x:v></x:c><x:c r="B141" t="s"><x:v>342</x:v></x:c><x:c r="C141" t="s"><x:v>343</x:v></x:c><x:c r="D141" t="s"><x:v>344</x:v></x:c></x:row><x:row r="142"><x:c r="A142"><x:v>1140</x:v></x:c><x:c r="B142" t="s"><x:v>345</x:v></x:c><x:c r="C142" t="s"><x:v>346</x:v></x:c><x:c r="D142" t="s"><x:v>347</x:v></x:c></x:row><x:row r="143"><x:c r="A143"><x:v>1141</x:v></x:c><x:c r="B143" t="s"><x:v>348</x:v></x:c><x:c r="C143" t="s"><x:v>349</x:v></x:c><x:c r="D143" t="s"><x:v>350</x:v></x:c></x:row><x:row r="144"><x:c r="A144"><x:v>1142</x:v></x:c><x:c r="B144" t="s"><x:v>351</x:v></x:c><x:c r="C144" t="s"><x:v>352</x:v></x:c><x:c r="D144" t="s"><x:v>353</x:v></x:c></x:row><x:row r="145"><x:c r="A145"><x:v>1143</x:v></x:c><x:c r="B145" t="s"><x:v>354</x:v></x:c><x:c r="C145" t="s"><x:v>355</x:v></x:c><x:c r="D145" t="s"><x:v>356</x:v></x:c></x:row><x:row r="146"><x:c r="A146"><x:v>1144</x:v></x:c><x:c r="B146" t="s"><x:v>357</x:v></x:c><x:c r="C146" t="s"><x:v>358</x:v></x:c><x:c r="D146" t="s"><x:v>359</x:v></x:c></x:row><x:row r="147"><x:c r="A147"><x:v>1145</x:v></x:c><x:c r="B147" t="s"><x:v>360</x:v></x:c><x:c r="C147" t="s"><x:v>361</x:v></x:c><x:c r="D147" t="s"><x:v>362</x:v></x:c></x:row><x:row r="148"><x:c r="A148"><x:v>1146</x:v></x:c><x:c r="B148" t="s"><x:v>363</x:v></x:c><x:c r="C148" t="s"><x:v>364</x:v></x:c><x:c r="D148" t="s"><x:v>365</x:v></x:c></x:row><x:row r="149"><x:c r="A149"><x:v>1147</x:v></x:c><x:c r="B149" t="s"><x:v>366</x:v></x:c><x:c r="C149" t="s"><x:v>367</x:v></x:c><x:c r="D149" t="s"><x:v>368</x:v></x:c></x:row><x:row r="150"><x:c r="A150"><x:v>1148</x:v></x:c><x:c r="B150" t="s"><x:v>369</x:v></x:c><x:c r="C150" t="s"><x:v>370</x:v></x:c><x:c r="D150" t="s"><x:v>371</x:v></x:c></x:row><x:row r="151"><x:c r="A151"><x:v>1149</x:v></x:c><x:c r="B151" t="s"><x:v>372</x:v></x:c><x:c r="C151" t="s"><x:v>373</x:v></x:c><x:c r="D151" t="s"><x:v>374</x:v></x:c></x:row><x:row r="152"><x:c r="A152"><x:v>1150</x:v></x:c><x:c r="B152" t="s"><x:v>375</x:v></x:c><x:c r="C152" t="s"><x:v>376</x:v></x:c><x:c r="D152" t="s"><x:v>377</x:v></x:c></x:row><x:row r="153"><x:c r="A153"><x:v>1151</x:v></x:c><x:c r="B153" t="s"><x:v>378</x:v></x:c><x:c r="C153" t="s"><x:v>379</x:v></x:c><x:c r="D153" t="s"><x:v>380</x:v></x:c></x:row><x:row r="154"><x:c r="A154"><x:v>1152</x:v></x:c><x:c r="B154" t="s"><x:v>381</x:v></x:c><x:c r="C154" t="s"><x:v>382</x:v></x:c><x:c r="D154" t="s"><x:v>383</x:v></x:c></x:row><x:row r="155"><x:c r="A155"><x:v>1153</x:v></x:c><x:c r="B155" t="s"><x:v>384</x:v></x:c><x:c r="C155" t="s"><x:v>385</x:v></x:c><x:c r="D155" t="s"><x:v>386</x:v></x:c></x:row><x:row r="156"><x:c r="A156"><x:v>1154</x:v></x:c><x:c r="B156" t="s"><x:v>387</x:v></x:c><x:c r="C156" t="s"><x:v>388</x:v></x:c><x:c r="D156" t="s"><x:v>389</x:v></x:c></x:row><x:row r="157"><x:c r="A157"><x:v>1155</x:v></x:c><x:c r="B157" t="s"><x:v>390</x:v></x:c><x:c r="C157" t="s"><x:v>391</x:v></x:c><x:c r="D157" t="s"><x:v>392</x:v></x:c></x:row><x:row r="158"><x:c r="A158"><x:v>1156</x:v></x:c><x:c r="B158" t="s"><x:v>393</x:v></x:c><x:c r="C158" t="s"><x:v>394</x:v></x:c><x:c r="D158" t="s"><x:v>395</x:v></x:c></x:row><x:row r="159"><x:c r="A159"><x:v>1157</x:v></x:c><x:c r="B159" t="s"><x:v>396</x:v></x:c><x:c r="C159" t="s"><x:v>397</x:v></x:c><x:c r="D159" t="s"><x:v>398</x:v></x:c></x:row><x:row r="160"><x:c r="A160"><x:v>1158</x:v></x:c><x:c r="B160" t="s"><x:v>399</x:v></x:c><x:c r="C160" t="s"><x:v>400</x:v></x:c><x:c r="D160" t="s"><x:v>401</x:v></x:c></x:row><x:row r="161"><x:c r="A161"><x:v>1159</x:v></x:c><x:c r="B161" t="s"><x:v>402</x:v></x:c><x:c r="C161" t="s"><x:v>403</x:v></x:c><x:c r="D161" t="s"><x:v>404</x:v></x:c></x:row><x:row r="162"><x:c r="A162"><x:v>1160</x:v></x:c><x:c r="B162" t="s"><x:v>405</x:v></x:c><x:c r="C162" t="s"><x:v>406</x:v></x:c><x:c r="D162" t="s"><x:v>407</x:v></x:c></x:row><x:row r="163"><x:c r="A163"><x:v>1161</x:v></x:c><x:c r="B163" t="s"><x:v>408</x:v></x:c><x:c r="C163" t="s"><x:v>409</x:v></x:c><x:c r="D163" t="s"><x:v>410</x:v></x:c></x:row><x:row r="164"><x:c r="A164"><x:v>1162</x:v></x:c><x:c r="B164" t="s"><x:v>411</x:v></x:c><x:c r="C164" t="s"><x:v>412</x:v></x:c><x:c r="D164" t="s"><x:v>413</x:v></x:c></x:row><x:row r="165"><x:c r="A165"><x:v>1163</x:v></x:c><x:c r="B165" t="s"><x:v>414</x:v></x:c><x:c r="C165" t="s"><x:v>69</x:v></x:c><x:c r="D165" t="s"><x:v>70</x:v></x:c></x:row><x:row r="166"><x:c r="A166"><x:v>1164</x:v></x:c><x:c r="B166" t="s"><x:v>415</x:v></x:c><x:c r="C166" t="s"><x:v>416</x:v></x:c><x:c r="D166" t="s"><x:v>417</x:v></x:c></x:row><x:row r="167"><x:c r="A167"><x:v>1165</x:v></x:c><x:c r="B167" t="s"><x:v>418</x:v></x:c><x:c r="C167" t="s"><x:v>419</x:v></x:c><x:c r="D167" t="s"><x:v>420</x:v></x:c></x:row><x:row r="168"><x:c r="A168"><x:v>1166</x:v></x:c><x:c r="B168" t="s"><x:v>421</x:v></x:c><x:c r="C168" t="s"><x:v>422</x:v></x:c><x:c r="D168" t="s"><x:v>423</x:v></x:c></x:row><x:row r="169"><x:c r="A169"><x:v>1167</x:v></x:c><x:c r="B169" t="s"><x:v>424</x:v></x:c><x:c r="C169" t="s"><x:v>425</x:v></x:c><x:c r="D169" t="s"><x:v>426</x:v></x:c></x:row><x:row r="170"><x:c r="A170"><x:v>1168</x:v></x:c><x:c r="B170" t="s"><x:v>427</x:v></x:c><x:c r="C170" t="s"><x:v>428</x:v></x:c><x:c r="D170" t="s"><x:v>429</x:v></x:c></x:row><x:row r="171"><x:c r="A171"><x:v>1169</x:v></x:c><x:c r="B171" t="s"><x:v>430</x:v></x:c><x:c r="C171" t="s"><x:v>431</x:v></x:c><x:c r="D171" t="s"><x:v>432</x:v></x:c></x:row><x:row r="172"><x:c r="A172"><x:v>1170</x:v></x:c><x:c r="B172" t="s"><x:v>433</x:v></x:c><x:c r="C172" t="inlineStr"><x:is><x:t xml:space="preserve">추적 파일 {0}개의 스테이징되지 않은 변경을 버립니다. 이름 변경 {1}개는 원래 경로로 되돌립니다. 이미 스테이징한 변경은 유지됩니다.</x:t></x:is></x:c><x:c r="D172" t="inlineStr"><x:is><x:t xml:space="preserve">Discard unstaged changes in {0} tracked files. Restore {1} renames to their original paths. Staged changes remain intact.</x:t></x:is></x:c></x:row><x:row r="173"><x:c r="A173"><x:v>1171</x:v></x:c><x:c r="B173" t="s"><x:v>434</x:v></x:c><x:c r="C173" t="s"><x:v>435</x:v></x:c><x:c r="D173" t="s"><x:v>436</x:v></x:c></x:row><x:row r="174"><x:c r="A174"><x:v>1172</x:v></x:c><x:c r="B174" t="s"><x:v>437</x:v></x:c><x:c r="C174" t="s"><x:v>438</x:v></x:c><x:c r="D174" t="s"><x:v>439</x:v></x:c></x:row><x:row r="175"><x:c r="A175"><x:v>1173</x:v></x:c><x:c r="B175" t="s"><x:v>440</x:v></x:c><x:c r="C175" t="s"><x:v>441</x:v></x:c><x:c r="D175" t="s"><x:v>442</x:v></x:c></x:row><x:row r="176"><x:c r="A176"><x:v>1174</x:v></x:c><x:c r="B176" t="s"><x:v>443</x:v></x:c><x:c r="C176" t="s"><x:v>444</x:v></x:c><x:c r="D176" t="s"><x:v>445</x:v></x:c></x:row><x:row r="177"><x:c r="A177"><x:v>1175</x:v></x:c><x:c r="B177" t="s"><x:v>446</x:v></x:c><x:c r="C177" t="s"><x:v>447</x:v></x:c><x:c r="D177" t="s"><x:v>448</x:v></x:c></x:row><x:row r="178"><x:c r="A178"><x:v>1176</x:v></x:c><x:c r="B178" t="s"><x:v>449</x:v></x:c><x:c r="C178" t="s"><x:v>450</x:v></x:c><x:c r="D178" t="s"><x:v>451</x:v></x:c></x:row><x:row r="179"><x:c r="A179"><x:v>1177</x:v></x:c><x:c r="B179" t="s"><x:v>452</x:v></x:c><x:c r="C179" t="s"><x:v>453</x:v></x:c><x:c r="D179" t="s"><x:v>454</x:v></x:c></x:row><x:row r="180"><x:c r="A180"><x:v>1178</x:v></x:c><x:c r="B180" t="s"><x:v>455</x:v></x:c><x:c r="C180" t="s"><x:v>456</x:v></x:c><x:c r="D180" t="s"><x:v>457</x:v></x:c></x:row><x:row r="181"><x:c r="A181"><x:v>1179</x:v></x:c><x:c r="B181" t="s"><x:v>458</x:v></x:c><x:c r="C181" t="s"><x:v>459</x:v></x:c><x:c r="D181" t="s"><x:v>460</x:v></x:c></x:row><x:row r="182"><x:c r="A182"><x:v>1180</x:v></x:c><x:c r="B182" t="s"><x:v>461</x:v></x:c><x:c r="C182" t="s"><x:v>462</x:v></x:c><x:c r="D182" t="s"><x:v>463</x:v></x:c></x:row><x:row r="183"><x:c r="A183"><x:v>1181</x:v></x:c><x:c r="B183" t="s"><x:v>464</x:v></x:c><x:c r="C183" t="s"><x:v>465</x:v></x:c><x:c r="D183" t="s"><x:v>466</x:v></x:c></x:row><x:row r="184"><x:c r="A184"><x:v>1182</x:v></x:c><x:c r="B184" t="s"><x:v>467</x:v></x:c><x:c r="C184" t="s"><x:v>468</x:v></x:c><x:c r="D184" t="s"><x:v>469</x:v></x:c></x:row><x:row r="185"><x:c r="A185"><x:v>1183</x:v></x:c><x:c r="B185" t="s"><x:v>470</x:v></x:c><x:c r="C185" t="s"><x:v>471</x:v></x:c><x:c r="D185" t="s"><x:v>472</x:v></x:c></x:row><x:row r="186"><x:c r="A186"><x:v>1184</x:v></x:c><x:c r="B186" t="s"><x:v>473</x:v></x:c><x:c r="C186" t="s"><x:v>474</x:v></x:c><x:c r="D186" t="s"><x:v>475</x:v></x:c></x:row><x:row r="187"><x:c r="A187"><x:v>1185</x:v></x:c><x:c r="B187" t="s"><x:v>476</x:v></x:c><x:c r="C187" t="s"><x:v>477</x:v></x:c><x:c r="D187" t="s"><x:v>478</x:v></x:c></x:row><x:row r="188"><x:c r="A188"><x:v>1186</x:v></x:c><x:c r="B188" t="s"><x:v>479</x:v></x:c><x:c r="C188" t="s"><x:v>480</x:v></x:c><x:c r="D188" t="s"><x:v>481</x:v></x:c></x:row><x:row r="189"><x:c r="A189"><x:v>1187</x:v></x:c><x:c r="B189" t="s"><x:v>482</x:v></x:c><x:c r="C189" t="s"><x:v>483</x:v></x:c><x:c r="D189" t="s"><x:v>484</x:v></x:c></x:row><x:row r="190"><x:c r="A190"><x:v>1188</x:v></x:c><x:c r="B190" t="s"><x:v>485</x:v></x:c><x:c r="C190" t="s"><x:v>486</x:v></x:c><x:c r="D190" t="s"><x:v>487</x:v></x:c></x:row><x:row r="191"><x:c r="A191"><x:v>1189</x:v></x:c><x:c r="B191" t="s"><x:v>488</x:v></x:c><x:c r="C191" t="s"><x:v>489</x:v></x:c><x:c r="D191" t="s"><x:v>490</x:v></x:c></x:row><x:row r="192"><x:c r="A192"><x:v>1190</x:v></x:c><x:c r="B192" t="s"><x:v>491</x:v></x:c><x:c r="C192" t="s"><x:v>492</x:v></x:c><x:c r="D192" t="s"><x:v>493</x:v></x:c></x:row><x:row r="193"><x:c r="A193"><x:v>1191</x:v></x:c><x:c r="B193" t="s"><x:v>494</x:v></x:c><x:c r="C193" t="s"><x:v>495</x:v></x:c><x:c r="D193" t="s"><x:v>496</x:v></x:c></x:row><x:row r="194"><x:c r="A194"><x:v>1192</x:v></x:c><x:c r="B194" t="s"><x:v>497</x:v></x:c><x:c r="C194" t="s"><x:v>498</x:v></x:c><x:c r="D194" t="s"><x:v>499</x:v></x:c></x:row><x:row r="195"><x:c r="A195"><x:v>1193</x:v></x:c><x:c r="B195" t="s"><x:v>500</x:v></x:c><x:c r="C195" t="s"><x:v>501</x:v></x:c><x:c r="D195" t="s"><x:v>502</x:v></x:c></x:row><x:row r="196"><x:c r="A196"><x:v>1194</x:v></x:c><x:c r="B196" t="s"><x:v>503</x:v></x:c><x:c r="C196" t="s"><x:v>504</x:v></x:c><x:c r="D196" t="s"><x:v>505</x:v></x:c></x:row><x:row r="197"><x:c r="A197"><x:v>1195</x:v></x:c><x:c r="B197" t="s"><x:v>506</x:v></x:c><x:c r="C197" t="s"><x:v>507</x:v></x:c><x:c r="D197" t="s"><x:v>508</x:v></x:c></x:row><x:row r="198"><x:c r="A198"><x:v>1196</x:v></x:c><x:c r="B198" t="s"><x:v>509</x:v></x:c><x:c r="C198" t="s"><x:v>510</x:v></x:c><x:c r="D198" t="s"><x:v>511</x:v></x:c></x:row><x:row r="199"><x:c r="A199"><x:v>1197</x:v></x:c><x:c r="B199" t="s"><x:v>512</x:v></x:c><x:c r="C199" t="s"><x:v>513</x:v></x:c><x:c r="D199" t="s"><x:v>514</x:v></x:c></x:row><x:row r="200"><x:c r="A200"><x:v>1198</x:v></x:c><x:c r="B200" t="s"><x:v>515</x:v></x:c><x:c r="C200" t="s"><x:v>516</x:v></x:c><x:c r="D200" t="s"><x:v>517</x:v></x:c></x:row><x:row r="201"><x:c r="A201"><x:v>1199</x:v></x:c><x:c r="B201" t="s"><x:v>518</x:v></x:c><x:c r="C201" t="s"><x:v>519</x:v></x:c><x:c r="D201" t="s"><x:v>520</x:v></x:c></x:row><x:row r="202"><x:c r="A202"><x:v>1200</x:v></x:c><x:c r="B202" t="s"><x:v>521</x:v></x:c><x:c r="C202" t="s"><x:v>522</x:v></x:c><x:c r="D202" t="s"><x:v>523</x:v></x:c></x:row><x:row r="203"><x:c r="A203"><x:v>1201</x:v></x:c><x:c r="B203" t="s"><x:v>524</x:v></x:c><x:c r="C203" t="s"><x:v>525</x:v></x:c><x:c r="D203" t="s"><x:v>526</x:v></x:c></x:row><x:row r="204"><x:c r="A204"><x:v>1202</x:v></x:c><x:c r="B204" t="s"><x:v>527</x:v></x:c><x:c r="C204" t="s"><x:v>528</x:v></x:c><x:c r="D204" t="s"><x:v>529</x:v></x:c></x:row><x:row r="205"><x:c r="A205"><x:v>1203</x:v></x:c><x:c r="B205" t="s"><x:v>530</x:v></x:c><x:c r="C205" t="s"><x:v>531</x:v></x:c><x:c r="D205" t="s"><x:v>532</x:v></x:c></x:row><x:row r="206"><x:c r="A206"><x:v>1204</x:v></x:c><x:c r="B206" t="s"><x:v>533</x:v></x:c><x:c r="C206" t="s"><x:v>534</x:v></x:c><x:c r="D206" t="s"><x:v>535</x:v></x:c></x:row><x:row r="207"><x:c r="A207"><x:v>1205</x:v></x:c><x:c r="B207" t="s"><x:v>536</x:v></x:c><x:c r="C207" t="s"><x:v>537</x:v></x:c><x:c r="D207" t="s"><x:v>538</x:v></x:c></x:row><x:row r="208"><x:c r="A208"><x:v>1206</x:v></x:c><x:c r="B208" t="s"><x:v>539</x:v></x:c><x:c r="C208" t="s"><x:v>540</x:v></x:c><x:c r="D208" t="s"><x:v>541</x:v></x:c></x:row><x:row r="209"><x:c r="A209"><x:v>1207</x:v></x:c><x:c r="B209" t="s"><x:v>542</x:v></x:c><x:c r="C209" t="s"><x:v>543</x:v></x:c><x:c r="D209" t="s"><x:v>544</x:v></x:c></x:row><x:row r="210"><x:c r="A210"><x:v>1208</x:v></x:c><x:c r="B210" t="s"><x:v>545</x:v></x:c><x:c r="C210" t="s"><x:v>546</x:v></x:c><x:c r="D210" t="s"><x:v>547</x:v></x:c></x:row><x:row r="211"><x:c r="A211"><x:v>1209</x:v></x:c><x:c r="B211" t="s"><x:v>548</x:v></x:c><x:c r="C211" t="s"><x:v>549</x:v></x:c><x:c r="D211" t="s"><x:v>550</x:v></x:c></x:row><x:row r="212"><x:c r="A212"><x:v>1210</x:v></x:c><x:c r="B212" t="s"><x:v>551</x:v></x:c><x:c r="C212" t="s"><x:v>552</x:v></x:c><x:c r="D212" t="s"><x:v>553</x:v></x:c></x:row><x:row r="213"><x:c r="A213"><x:v>1211</x:v></x:c><x:c r="B213" t="s"><x:v>554</x:v></x:c><x:c r="C213" t="s"><x:v>555</x:v></x:c><x:c r="D213" t="s"><x:v>556</x:v></x:c></x:row><x:row r="214"><x:c r="A214"><x:v>1212</x:v></x:c><x:c r="B214" t="s"><x:v>557</x:v></x:c><x:c r="C214" t="s"><x:v>558</x:v></x:c><x:c r="D214" t="s"><x:v>559</x:v></x:c></x:row><x:row r="215"><x:c r="A215"><x:v>1213</x:v></x:c><x:c r="B215" t="s"><x:v>560</x:v></x:c><x:c r="C215" t="s"><x:v>561</x:v></x:c><x:c r="D215" t="s"><x:v>562</x:v></x:c></x:row><x:row r="216"><x:c r="A216"><x:v>1214</x:v></x:c><x:c r="B216" t="s"><x:v>563</x:v></x:c><x:c r="C216" t="s"><x:v>564</x:v></x:c><x:c r="D216" t="s"><x:v>565</x:v></x:c></x:row><x:row r="217"><x:c r="A217"><x:v>1215</x:v></x:c><x:c r="B217" t="s"><x:v>566</x:v></x:c><x:c r="C217" t="s"><x:v>567</x:v></x:c><x:c r="D217" t="s"><x:v>568</x:v></x:c></x:row><x:row r="218"><x:c r="A218"><x:v>1400</x:v></x:c><x:c r="B218" t="inlineStr"><x:is><x:t xml:space="preserve">LocalSelectedFileUnavailable</x:t></x:is></x:c><x:c r="C218" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 파일 {0}을(를) 현재 작업에 사용할 수 없습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D218" t="inlineStr"><x:is><x:t xml:space="preserve">The selected file is no longer available for this operation: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="219"><x:c r="A219"><x:v>1401</x:v></x:c><x:c r="B219" t="inlineStr"><x:is><x:t xml:space="preserve">LocalResolveBeforeDiscard</x:t></x:is></x:c><x:c r="C219" t="inlineStr"><x:is><x:t xml:space="preserve">{0}의 충돌을 해결한 뒤 변경을 폐기하세요.</x:t></x:is></x:c><x:c r="D219" t="inlineStr"><x:is><x:t xml:space="preserve">Resolve the conflict in {0} before discarding changes.</x:t></x:is></x:c></x:row><x:row r="220"><x:c r="A220"><x:v>1402</x:v></x:c><x:c r="B220" t="inlineStr"><x:is><x:t xml:space="preserve">LocalDiscardRequiresConfirmation</x:t></x:is></x:c><x:c r="C220" t="inlineStr"><x:is><x:t xml:space="preserve">변경을 폐기하려면 확인이 필요합니다.</x:t></x:is></x:c><x:c r="D220" t="inlineStr"><x:is><x:t xml:space="preserve">Discarding changes requires confirmation.</x:t></x:is></x:c></x:row><x:row r="221"><x:c r="A221"><x:v>1403</x:v></x:c><x:c r="B221" t="inlineStr"><x:is><x:t xml:space="preserve">LocalIgnoreRequiresConfirmation</x:t></x:is></x:c><x:c r="C221" t="inlineStr"><x:is><x:t xml:space="preserve">파일을 무시하려면 확인이 필요합니다.</x:t></x:is></x:c><x:c r="D221" t="inlineStr"><x:is><x:t xml:space="preserve">Ignoring files requires confirmation.</x:t></x:is></x:c></x:row><x:row r="222"><x:c r="A222"><x:v>1404</x:v></x:c><x:c r="B222" t="inlineStr"><x:is><x:t xml:space="preserve">LocalLargeStageRequiresConfirmation</x:t></x:is></x:c><x:c r="C222" t="inlineStr"><x:is><x:t xml:space="preserve">새 큰 파일을 스테이징하려면 확인이 필요합니다.</x:t></x:is></x:c><x:c r="D222" t="inlineStr"><x:is><x:t xml:space="preserve">Staging large new files requires confirmation.</x:t></x:is></x:c></x:row><x:row r="223"><x:c r="A223"><x:v>1405</x:v></x:c><x:c r="B223" t="inlineStr"><x:is><x:t xml:space="preserve">LocalSelectionSetChanged</x:t></x:is></x:c><x:c r="C223" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 파일 목록이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D223" t="inlineStr"><x:is><x:t xml:space="preserve">The selected file set changed before the operation started. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="224"><x:c r="A224"><x:v>1406</x:v></x:c><x:c r="B224" t="inlineStr"><x:is><x:t xml:space="preserve">LocalSelectedFileChanged</x:t></x:is></x:c><x:c r="C224" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D224" t="inlineStr"><x:is><x:t xml:space="preserve">The selected file changed before the operation started: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="225"><x:c r="A225"><x:v>1407</x:v></x:c><x:c r="B225" t="inlineStr"><x:is><x:t xml:space="preserve">LocalIndexChanged</x:t></x:is></x:c><x:c r="C225" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일의 인덱스 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D225" t="inlineStr"><x:is><x:t xml:space="preserve">The index state changed before the operation started: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="226"><x:c r="A226"><x:v>1408</x:v></x:c><x:c r="B226" t="inlineStr"><x:is><x:t xml:space="preserve">LocalWorkingFileChanged</x:t></x:is></x:c><x:c r="C226" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일의 작업 트리 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D226" t="inlineStr"><x:is><x:t xml:space="preserve">The working-tree state changed before the operation started: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="227"><x:c r="A227"><x:v>1409</x:v></x:c><x:c r="B227" t="inlineStr"><x:is><x:t xml:space="preserve">StashTargetsUnavailable</x:t></x:is></x:c><x:c r="C227" t="inlineStr"><x:is><x:t xml:space="preserve">Stash에 보관할 변경 목록이 없습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D227" t="inlineStr"><x:is><x:t xml:space="preserve">The stash targets are no longer available. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="228"><x:c r="A228"><x:v>1410</x:v></x:c><x:c r="B228" t="inlineStr"><x:is><x:t xml:space="preserve">StashTargetsChanged</x:t></x:is></x:c><x:c r="C228" t="inlineStr"><x:is><x:t xml:space="preserve">Stash 보관 대상이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D228" t="inlineStr"><x:is><x:t xml:space="preserve">The stash targets changed before the operation started. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="229"><x:c r="A229"><x:v>1411</x:v></x:c><x:c r="B229" t="inlineStr"><x:is><x:t xml:space="preserve">StashTargetChanged</x:t></x:is></x:c><x:c r="C229" t="inlineStr"><x:is><x:t xml:space="preserve">Stash 보관 대상 {0}이(가) 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D229" t="inlineStr"><x:is><x:t xml:space="preserve">The stash target changed before the operation started: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="230"><x:c r="A230"><x:v>1412</x:v></x:c><x:c r="B230" t="inlineStr"><x:is><x:t xml:space="preserve">StashTargetIndexChanged</x:t></x:is></x:c><x:c r="C230" t="inlineStr"><x:is><x:t xml:space="preserve">Stash 보관 대상 {0}의 인덱스 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D230" t="inlineStr"><x:is><x:t xml:space="preserve">The stash target index changed before the operation started: {0}. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="231"><x:c r="A231"><x:v>1300</x:v></x:c><x:c r="B231" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictStageUnavailable</x:t></x:is></x:c><x:c r="C231" t="inlineStr"><x:is><x:t xml:space="preserve">충돌 파일 저장을 완료할 화면 연결이 없습니다.</x:t></x:is></x:c><x:c r="D231" t="inlineStr"><x:is><x:t xml:space="preserve">The conflict save cannot be completed because its screen connection is unavailable.</x:t></x:is></x:c></x:row><x:row r="232"><x:c r="A232"><x:v>1301</x:v></x:c><x:c r="B232" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictStageCanceled</x:t></x:is></x:c><x:c r="C232" t="inlineStr"><x:is><x:t xml:space="preserve">대기 중인 충돌 파일 저장이 취소되었습니다.</x:t></x:is></x:c><x:c r="D232" t="inlineStr"><x:is><x:t xml:space="preserve">The pending conflict save was canceled.</x:t></x:is></x:c></x:row><x:row r="233"><x:c r="A233"><x:v>1302</x:v></x:c><x:c r="B233" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictStageNoLongerConflicted</x:t></x:is></x:c><x:c r="C233" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일은 더 이상 충돌 상태가 아닙니다. 상태를 새로 고치세요.</x:t></x:is></x:c><x:c r="D233" t="inlineStr"><x:is><x:t xml:space="preserve">{0} is no longer conflicted. Refresh the repository state.</x:t></x:is></x:c></x:row><x:row r="234"><x:c r="A234"><x:v>1303</x:v></x:c><x:c r="B234" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictStageFileChanged</x:t></x:is></x:c><x:c r="C234" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일이 열린 뒤 변경되었습니다. 다시 불러온 후 저장하세요.</x:t></x:is></x:c><x:c r="D234" t="inlineStr"><x:is><x:t xml:space="preserve">{0} changed after it was opened. Reload it before saving.</x:t></x:is></x:c></x:row><x:row r="235"><x:c r="A235"><x:v>1304</x:v></x:c><x:c r="B235" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictStageRefreshFailed</x:t></x:is></x:c><x:c r="C235" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 파일은 저장하고 스테이징했지만 화면을 새로 고치지 못했습니다. {1}</x:t></x:is></x:c><x:c r="D235" t="inlineStr"><x:is><x:t xml:space="preserve">Saved and staged {0}, but could not refresh the screen. {1}</x:t></x:is></x:c></x:row><x:row r="236"><x:c r="A236"><x:v>1500</x:v></x:c><x:c r="B236" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueRepositoryUnavailable</x:t></x:is></x:c><x:c r="C236" t="inlineStr"><x:is><x:t xml:space="preserve">원격 작업을 실행할 저장소를 불러오지 못했습니다.</x:t></x:is></x:c><x:c r="D236" t="inlineStr"><x:is><x:t xml:space="preserve">The requested repository could not be loaded for the remote operation.</x:t></x:is></x:c></x:row><x:row r="237"><x:c r="A237"><x:v>1501</x:v></x:c><x:c r="B237" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueRepositoryChanged</x:t></x:is></x:c><x:c r="C237" t="inlineStr"><x:is><x:t xml:space="preserve">원격 작업을 시작하기 전에 저장소가 변경되었습니다.</x:t></x:is></x:c><x:c r="D237" t="inlineStr"><x:is><x:t xml:space="preserve">The requested repository changed before the remote operation started.</x:t></x:is></x:c></x:row><x:row r="238"><x:c r="A238"><x:v>1502</x:v></x:c><x:c r="B238" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueFetchRemoteChanged</x:t></x:is></x:c><x:c r="C238" t="inlineStr"><x:is><x:t xml:space="preserve">원격 작업을 시작하기 전에 선택한 Fetch 원격이 변경되었습니다.</x:t></x:is></x:c><x:c r="D238" t="inlineStr"><x:is><x:t xml:space="preserve">The selected Fetch remote changed before the operation started.</x:t></x:is></x:c></x:row><x:row r="239"><x:c r="A239"><x:v>1503</x:v></x:c><x:c r="B239" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueFetchRemoteUnavailable</x:t></x:is></x:c><x:c r="C239" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 Fetch 원격을 더 이상 사용할 수 없습니다.</x:t></x:is></x:c><x:c r="D239" t="inlineStr"><x:is><x:t xml:space="preserve">The selected Fetch remote is no longer available.</x:t></x:is></x:c></x:row><x:row r="240"><x:c r="A240"><x:v>1504</x:v></x:c><x:c r="B240" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueFetchAllUnavailable</x:t></x:is></x:c><x:c r="C240" t="inlineStr"><x:is><x:t xml:space="preserve">모든 원격 가져오기에 사용할 원격이 없습니다.</x:t></x:is></x:c><x:c r="D240" t="inlineStr"><x:is><x:t xml:space="preserve">No remote is available for Fetch all.</x:t></x:is></x:c></x:row><x:row r="241"><x:c r="A241"><x:v>1505</x:v></x:c><x:c r="B241" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteQueueBranchChanged</x:t></x:is></x:c><x:c r="C241" t="inlineStr"><x:is><x:t xml:space="preserve">원격 작업을 시작하기 전에 현재 브랜치가 변경되었습니다.</x:t></x:is></x:c><x:c r="D241" t="inlineStr"><x:is><x:t xml:space="preserve">The current branch changed before the remote operation started.</x:t></x:is></x:c></x:row><x:row r="242"><x:c r="A242"><x:v>1600</x:v></x:c><x:c r="B242" t="inlineStr"><x:is><x:t xml:space="preserve">CurrentRepositoryDetails</x:t></x:is></x:c><x:c r="C242" t="inlineStr"><x:is><x:t xml:space="preserve">현재 저장소: {0} ({1})</x:t></x:is></x:c><x:c r="D242" t="inlineStr"><x:is><x:t xml:space="preserve">Current repository: {0} ({1})</x:t></x:is></x:c></x:row><x:row r="243"><x:c r="A243"><x:v>1601</x:v></x:c><x:c r="B243" t="inlineStr"><x:is><x:t xml:space="preserve">GcmLoginCompleted</x:t></x:is></x:c><x:c r="C243" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 로그인 절차를 마쳤습니다. 계정 목록을 확인하세요.</x:t></x:is></x:c><x:c r="D243" t="inlineStr"><x:is><x:t xml:space="preserve">The GitHub sign-in flow finished. Check the account list.</x:t></x:is></x:c></x:row><x:row r="244"><x:c r="A244"><x:v>1602</x:v></x:c><x:c r="B244" t="inlineStr"><x:is><x:t xml:space="preserve">GcmOperationInProgress</x:t></x:is></x:c><x:c r="C244" t="inlineStr"><x:is><x:t xml:space="preserve">계정 작업을 진행 중입니다…</x:t></x:is></x:c><x:c r="D244" t="inlineStr"><x:is><x:t xml:space="preserve">Working on the account…</x:t></x:is></x:c></x:row><x:row r="245"><x:c r="A245"><x:v>1603</x:v></x:c><x:c r="B245" t="inlineStr"><x:is><x:t xml:space="preserve">GitAuthorEmailMissing</x:t></x:is></x:c><x:c r="C245" t="inlineStr"><x:is><x:t xml:space="preserve">Git 작성자 이메일이 설정되지 않았습니다.</x:t></x:is></x:c><x:c r="D245" t="inlineStr"><x:is><x:t xml:space="preserve">Git author email is not configured.</x:t></x:is></x:c></x:row><x:row r="246"><x:c r="A246"><x:v>1604</x:v></x:c><x:c r="B246" t="inlineStr"><x:is><x:t xml:space="preserve">GitAuthorNameMissing</x:t></x:is></x:c><x:c r="C246" t="inlineStr"><x:is><x:t xml:space="preserve">Git 작성자 이름이 설정되지 않았습니다.</x:t></x:is></x:c><x:c r="D246" t="inlineStr"><x:is><x:t xml:space="preserve">Git author name is not configured.</x:t></x:is></x:c></x:row><x:row r="247"><x:c r="A247"><x:v>1605</x:v></x:c><x:c r="B247" t="inlineStr"><x:is><x:t xml:space="preserve">GitAuthorSummary</x:t></x:is></x:c><x:c r="C247" t="inlineStr"><x:is><x:t xml:space="preserve">커밋 작성자: {0} &lt;{1}&gt;</x:t></x:is></x:c><x:c r="D247" t="inlineStr"><x:is><x:t xml:space="preserve">Commit author: {0} &lt;{1}&gt;</x:t></x:is></x:c></x:row><x:row r="248"><x:c r="A248"><x:v>1606</x:v></x:c><x:c r="B248" t="inlineStr"><x:is><x:t xml:space="preserve">GitExecutablePickerTitle</x:t></x:is></x:c><x:c r="C248" t="inlineStr"><x:is><x:t xml:space="preserve">Git 실행 파일 선택</x:t></x:is></x:c><x:c r="D248" t="inlineStr"><x:is><x:t xml:space="preserve">Select Git executable</x:t></x:is></x:c></x:row><x:row r="249"><x:c r="A249"><x:v>1607</x:v></x:c><x:c r="B249" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountActionCanceled</x:t></x:is></x:c><x:c r="C249" t="inlineStr"><x:is><x:t xml:space="preserve">계정 작업이 취소되었습니다.</x:t></x:is></x:c><x:c r="D249" t="inlineStr"><x:is><x:t xml:space="preserve">Account operation canceled.</x:t></x:is></x:c></x:row><x:row r="250"><x:c r="A250"><x:v>1608</x:v></x:c><x:c r="B250" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountLookupCanceled</x:t></x:is></x:c><x:c r="C250" t="inlineStr"><x:is><x:t xml:space="preserve">계정 조회가 취소되었습니다.</x:t></x:is></x:c><x:c r="D250" t="inlineStr"><x:is><x:t xml:space="preserve">Account lookup canceled.</x:t></x:is></x:c></x:row><x:row r="251"><x:c r="A251"><x:v>1609</x:v></x:c><x:c r="B251" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountScopeHint</x:t></x:is></x:c><x:c r="C251" t="inlineStr"><x:is><x:t xml:space="preserve">계정 선택은 현재 저장소의 해당 GitHub HTTPS 원격에만 적용됩니다.</x:t></x:is></x:c><x:c r="D251" t="inlineStr"><x:is><x:t xml:space="preserve">Account selection applies only to the chosen GitHub HTTPS remote in this repository.</x:t></x:is></x:c></x:row><x:row r="252"><x:c r="A252"><x:v>1610</x:v></x:c><x:c r="B252" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountSelected</x:t></x:is></x:c><x:c r="C252" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격에 {1} 계정을 선택했습니다. 인증은 다음 원격 작업에서 확인됩니다.</x:t></x:is></x:c><x:c r="D252" t="inlineStr"><x:is><x:t xml:space="preserve">Selected {1} for remote {0}. Authentication will be checked on the next remote operation.</x:t></x:is></x:c></x:row><x:row r="253"><x:c r="A253"><x:v>1611</x:v></x:c><x:c r="B253" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountSelectionPreview</x:t></x:is></x:c><x:c r="C253" t="inlineStr"><x:is><x:t xml:space="preserve">이 저장소의 {0} 원격에 {1} 계정을 사용합니다.</x:t></x:is></x:c><x:c r="D253" t="inlineStr"><x:is><x:t xml:space="preserve">Use {1} for remote {0} in this repository.</x:t></x:is></x:c></x:row><x:row r="254"><x:c r="A254"><x:v>1612</x:v></x:c><x:c r="B254" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountsLoading</x:t></x:is></x:c><x:c r="C254" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 계정과 원격 정보를 불러오는 중…</x:t></x:is></x:c><x:c r="D254" t="inlineStr"><x:is><x:t xml:space="preserve">Loading GitHub accounts and remotes…</x:t></x:is></x:c></x:row><x:row r="255"><x:c r="A255"><x:v>1613</x:v></x:c><x:c r="B255" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubInheritedAccount</x:t></x:is></x:c><x:c r="C255" t="inlineStr"><x:is><x:t xml:space="preserve">전역 설정에서 상속한 계정: {0}</x:t></x:is></x:c><x:c r="D255" t="inlineStr"><x:is><x:t xml:space="preserve">Account inherited from global settings: {0}</x:t></x:is></x:c></x:row><x:row r="256"><x:c r="A256"><x:v>1614</x:v></x:c><x:c r="B256" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubNoRemotes</x:t></x:is></x:c><x:c r="C256" t="inlineStr"><x:is><x:t xml:space="preserve">등록된 원격이 없습니다.</x:t></x:is></x:c><x:c r="D256" t="inlineStr"><x:is><x:t xml:space="preserve">No remotes are configured.</x:t></x:is></x:c></x:row><x:row r="257"><x:c r="A257"><x:v>1615</x:v></x:c><x:c r="B257" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubNoSelectedAccount</x:t></x:is></x:c><x:c r="C257" t="inlineStr"><x:is><x:t xml:space="preserve">선택된 인증 계정 없음</x:t></x:is></x:c><x:c r="D257" t="inlineStr"><x:is><x:t xml:space="preserve">No authentication account selected</x:t></x:is></x:c></x:row><x:row r="258"><x:c r="A258"><x:v>1616</x:v></x:c><x:c r="B258" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubSelectedAccount</x:t></x:is></x:c><x:c r="C258" t="inlineStr"><x:is><x:t xml:space="preserve">이 저장소에서 선택한 계정: {0}</x:t></x:is></x:c><x:c r="D258" t="inlineStr"><x:is><x:t xml:space="preserve">Account selected for this repository: {0}</x:t></x:is></x:c></x:row><x:row r="259"><x:c r="A259"><x:v>1617</x:v></x:c><x:c r="B259" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubSharedRemoteUrlUnsupported</x:t></x:is></x:c><x:c r="C259" t="inlineStr"><x:is><x:t xml:space="preserve">여러 원격이 같은 URL을 사용해 계정을 따로 지정할 수 없습니다.</x:t></x:is></x:c><x:c r="D259" t="inlineStr"><x:is><x:t xml:space="preserve">Multiple remotes share this URL, so their accounts cannot be selected separately.</x:t></x:is></x:c></x:row><x:row r="260"><x:c r="A260"><x:v>1618</x:v></x:c><x:c r="B260" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubUserNameRequired</x:t></x:is></x:c><x:c r="C260" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 사용자명을 입력하세요.</x:t></x:is></x:c><x:c r="D260" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a GitHub username.</x:t></x:is></x:c></x:row><x:row r="261"><x:c r="A261"><x:v>1619</x:v></x:c><x:c r="B261" t="inlineStr"><x:is><x:t xml:space="preserve">GitPathSaved</x:t></x:is></x:c><x:c r="C261" t="inlineStr"><x:is><x:t xml:space="preserve">Git 경로를 저장했습니다. 버전: {0}</x:t></x:is></x:c><x:c r="D261" t="inlineStr"><x:is><x:t xml:space="preserve">Git path saved. Version: {0}.</x:t></x:is></x:c></x:row><x:row r="262"><x:c r="A262"><x:v>1620</x:v></x:c><x:c r="B262" t="inlineStr"><x:is><x:t xml:space="preserve">GitPathVerified</x:t></x:is></x:c><x:c r="C262" t="inlineStr"><x:is><x:t xml:space="preserve">Git 실행을 확인했습니다. 버전: {0}</x:t></x:is></x:c><x:c r="D262" t="inlineStr"><x:is><x:t xml:space="preserve">Git verified. Version: {0}.</x:t></x:is></x:c></x:row><x:row r="263"><x:c r="A263"><x:v>1621</x:v></x:c><x:c r="B263" t="inlineStr"><x:is><x:t xml:space="preserve">GitSettingsHint</x:t></x:is></x:c><x:c r="C263" t="inlineStr"><x:is><x:t xml:space="preserve">Git 실행 파일과 작성자 설정을 확인하세요.</x:t></x:is></x:c><x:c r="D263" t="inlineStr"><x:is><x:t xml:space="preserve">Review the Git executable and author settings.</x:t></x:is></x:c></x:row><x:row r="264"><x:c r="A264"><x:v>1622</x:v></x:c><x:c r="B264" t="inlineStr"><x:is><x:t xml:space="preserve">GitSettingsRefreshed</x:t></x:is></x:c><x:c r="C264" t="inlineStr"><x:is><x:t xml:space="preserve">Git 설정을 새로 고쳤습니다.</x:t></x:is></x:c><x:c r="D264" t="inlineStr"><x:is><x:t xml:space="preserve">Git settings refreshed.</x:t></x:is></x:c></x:row><x:row r="265"><x:c r="A265"><x:v>1623</x:v></x:c><x:c r="B265" t="inlineStr"><x:is><x:t xml:space="preserve">NotConfigured</x:t></x:is></x:c><x:c r="C265" t="inlineStr"><x:is><x:t xml:space="preserve">설정되지 않음</x:t></x:is></x:c><x:c r="D265" t="inlineStr"><x:is><x:t xml:space="preserve">Not configured</x:t></x:is></x:c></x:row><x:row r="266"><x:c r="A266"><x:v>1624</x:v></x:c><x:c r="B266" t="inlineStr"><x:is><x:t xml:space="preserve">SelectRepositoryPrompt</x:t></x:is></x:c><x:c r="C266" t="inlineStr"><x:is><x:t xml:space="preserve">저장소를 선택하세요.</x:t></x:is></x:c><x:c r="D266" t="inlineStr"><x:is><x:t xml:space="preserve">Select a repository.</x:t></x:is></x:c></x:row><x:row r="267"><x:c r="A267"><x:v>1625</x:v></x:c><x:c r="B267" t="inlineStr"><x:is><x:t xml:space="preserve">GlobalAuthorSaved</x:t></x:is></x:c><x:c r="C267" t="inlineStr"><x:is><x:t xml:space="preserve">전역 커밋 작성자 설정을 저장했습니다.</x:t></x:is></x:c><x:c r="D267" t="inlineStr"><x:is><x:t xml:space="preserve">Saved global commit author settings.</x:t></x:is></x:c></x:row><x:row r="268"><x:c r="A268"><x:v>1626</x:v></x:c><x:c r="B268" t="inlineStr"><x:is><x:t xml:space="preserve">LocalAuthorSaved</x:t></x:is></x:c><x:c r="C268" t="inlineStr"><x:is><x:t xml:space="preserve">이 저장소의 커밋 작성자 설정을 저장했습니다.</x:t></x:is></x:c><x:c r="D268" t="inlineStr"><x:is><x:t xml:space="preserve">Saved commit author settings for this repository.</x:t></x:is></x:c></x:row><x:row r="269"><x:c r="A269"><x:v>1700</x:v></x:c><x:c r="B269" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardSelectionCount</x:t></x:is></x:c><x:c r="C269" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 {0}개 파일 변경 폐기…</x:t></x:is></x:c><x:c r="D269" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes in {0} selected files…</x:t></x:is></x:c></x:row><x:row r="270"><x:c r="A270"><x:v>1701</x:v></x:c><x:c r="B270" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreMenu</x:t></x:is></x:c><x:c r="C270" t="inlineStr"><x:is><x:t xml:space="preserve">무시</x:t></x:is></x:c><x:c r="D270" t="inlineStr"><x:is><x:t xml:space="preserve">Ignore</x:t></x:is></x:c></x:row><x:row r="271"><x:c r="A271"><x:v>1702</x:v></x:c><x:c r="B271" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreRepository</x:t></x:is></x:c><x:c r="C271" t="inlineStr"><x:is><x:t xml:space="preserve">저장소에서 무시 (.gitignore)</x:t></x:is></x:c><x:c r="D271" t="inlineStr"><x:is><x:t xml:space="preserve">Ignore in repository (.gitignore)</x:t></x:is></x:c></x:row><x:row r="272"><x:c r="A272"><x:v>1703</x:v></x:c><x:c r="B272" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreLocal</x:t></x:is></x:c><x:c r="C272" t="inlineStr"><x:is><x:t xml:space="preserve">이 컴퓨터에서만 무시 (.git/info/exclude)</x:t></x:is></x:c><x:c r="D272" t="inlineStr"><x:is><x:t xml:space="preserve">Ignore on this computer only (.git/info/exclude)</x:t></x:is></x:c></x:row><x:row r="273"><x:c r="A273"><x:v>1704</x:v></x:c><x:c r="B273" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreConfirmTitle</x:t></x:is></x:c><x:c r="C273" t="inlineStr"><x:is><x:t xml:space="preserve">선택 파일 무시</x:t></x:is></x:c><x:c r="D273" t="inlineStr"><x:is><x:t xml:space="preserve">Ignore selected files</x:t></x:is></x:c></x:row><x:row r="274"><x:c r="A274"><x:v>1705</x:v></x:c><x:c r="B274" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreConfirmButton</x:t></x:is></x:c><x:c r="C274" t="inlineStr"><x:is><x:t xml:space="preserve">무시 규칙 추가</x:t></x:is></x:c><x:c r="D274" t="inlineStr"><x:is><x:t xml:space="preserve">Add ignore rules</x:t></x:is></x:c></x:row><x:row r="275"><x:c r="A275"><x:v>1706</x:v></x:c><x:c r="B275" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreConfirmDescription</x:t></x:is></x:c><x:c r="C275" t="inlineStr"><x:is><x:t xml:space="preserve">대상: {1}. 선택한 파일 {0}개의 정확한 경로를 무시 규칙에 추가합니다. 파일은 삭제하거나 스테이징하지 않습니다.</x:t></x:is></x:c><x:c r="D275" t="inlineStr"><x:is><x:t xml:space="preserve">Destination: {1}. Add exact-path ignore rules for {0} selected files. Files will not be deleted or staged.</x:t></x:is></x:c></x:row><x:row r="276"><x:c r="A276"><x:v>1707</x:v></x:c><x:c r="B276" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardBatchImpact</x:t></x:is></x:c><x:c r="C276" t="inlineStr"><x:is><x:t xml:space="preserve">추적 파일 {0}개의 스테이징되지 않은 변경을 복원하고 미추적 파일 {1}개를 삭제합니다. 이름 변경 {2}개는 원래 경로로 복원합니다. 이미 스테이징한 변경은 유지됩니다.</x:t></x:is></x:c><x:c r="D276" t="inlineStr"><x:is><x:t xml:space="preserve">Restore unstaged changes in {0} tracked files and delete {1} untracked files. Restore {2} renames to their original paths. Staged changes remain intact.</x:t></x:is></x:c></x:row><x:row r="277"><x:c r="A277"><x:v>1708</x:v></x:c><x:c r="B277" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardBatchPartialFailure</x:t></x:is></x:c><x:c r="C277" t="inlineStr"><x:is><x:t xml:space="preserve">일부 파일의 변경만 폐기했습니다. 완료 {0}개:
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="16.5"/>
+  <x:cols>
+    <x:col min="2" max="2" width="20.125" customWidth="1"/>
+    <x:col min="3" max="3" width="22.625" customWidth="1"/>
+    <x:col min="4" max="4" width="42.75" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="B2">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="B3">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="B4">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="B5">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="B6">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="B7">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="B8">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="B9">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="C9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="B10">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="B11">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="B12">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="B13">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="B14">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="B15">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="B16">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="B17">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="B18">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="B19">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="B20">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="B21">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="B22">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D22" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="B23">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D23" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="B24">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="C24" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D24" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="B25">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="B26">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="C26" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="B27">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="C27" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="B28">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D28" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="B29">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C32" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D32" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C33" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D33" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="B34">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="C34" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D34" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="B35">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="C35" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D35" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="B36">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="C36" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D36" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="B37">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="C37" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D37" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="B38">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="C38" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D38" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="B39">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="C39" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D39" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="B40">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="C40" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D40" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="B41">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D41" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="B42">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="C42" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D42" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="B43">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="C43" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D43" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="B44">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D44" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="B45">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="C45" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D45" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="B46">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="C46" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D46" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="B47">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="C47" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D47" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="B48">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="C48" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D48" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="B49">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="C49" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D49" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="B50">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="C50" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D50" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="B51">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="C51" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D51" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="B52">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="C52" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D52" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="B53">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="C53" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D53" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="B54">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="C54" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D54" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="B55">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="C55" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D55" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="17.450000762939453" customHeight="1">
+      <x:c r="A56">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="B56">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="C56" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D56" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="B57">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="C57" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D57" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="B58">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="C58" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D58" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="B59">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="C59" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D59" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="B60">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="C60" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D60" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="B61">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="C61" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D61" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="B62">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="C62" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D62" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="B63">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="C63" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D63" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="B64">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="C64" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D64" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="B65">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="C65" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D65" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="B66">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="C66" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D66" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="B67">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="C67" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D67" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="B68">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="C68" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D68" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="B69" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C69" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D69" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="B70" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C70" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D70" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="B71" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C71" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D71" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="B72" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C72" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D72" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="B73" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C73" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D73" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="B74" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C74" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D74" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="B75" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C75" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D75" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="B76" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C76" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D76" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="B77" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C77" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D77" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="B78" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C78" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D78" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="B79" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C79" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D79" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80">
+        <x:v>1078</x:v>
+      </x:c>
+      <x:c r="B80" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C80" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D80" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="B81" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C81" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D81" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="B82" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C82" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D82" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="B83" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C83" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D83" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="B84" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C84" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D84" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="B85" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C85" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D85" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="B86" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C86" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D86" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="B87" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C87" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D87" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="B88" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C88" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D88" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c r="B89" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C89" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D89" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="n">
+        <x:v>1088</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>FinalFileHint</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>선택 결과를 확인·편집한 뒤 저장 및 스테이징을 눌러 완료하세요.</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>Review or edit the result, then save and stage to finish.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91">
+        <x:v>1089</x:v>
+      </x:c>
+      <x:c r="B91" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C91" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D91" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="B92" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C92" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D92" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c r="B93" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C93" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D93" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="B94" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C94" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D94" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="B95" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C95" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D95" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="B96" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C96" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D96" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="B97" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C97" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D97" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98">
+        <x:v>1096</x:v>
+      </x:c>
+      <x:c r="B98" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C98" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D98" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="B99" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C99" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D99" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100">
+        <x:v>1098</x:v>
+      </x:c>
+      <x:c r="B100" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C100" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D100" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101">
+        <x:v>1099</x:v>
+      </x:c>
+      <x:c r="B101" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C101" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D101" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="B102" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C102" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D102" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="B103" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C103" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D103" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="B104" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C104" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D104" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="B105" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C105" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D105" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="B106" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C106" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D106" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="B107" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C107" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D107" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="B108" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C108" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D108" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="B109" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C109" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D109" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="B110" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C110" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D110" t="s">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c r="B111" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C111" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D111" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112">
+        <x:v>1110</x:v>
+      </x:c>
+      <x:c r="B112" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C112" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D112" t="s">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="B113" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C113" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D113" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114">
+        <x:v>1112</x:v>
+      </x:c>
+      <x:c r="B114" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C114" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D114" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115">
+        <x:v>1113</x:v>
+      </x:c>
+      <x:c r="B115" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C115" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D115" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="B116" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C116" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D116" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117">
+        <x:v>1115</x:v>
+      </x:c>
+      <x:c r="B117" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C117" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D117" t="s">
+        <x:v>277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c r="B118" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="C118" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="D118" t="s">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="B119" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C119" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D119" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120">
+        <x:v>1118</x:v>
+      </x:c>
+      <x:c r="B120" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C120" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D120" t="s">
+        <x:v>286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c r="B121" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C121" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D121" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="B122" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C122" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D122" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="B123" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C123" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D123" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c r="B124" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C124" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D124" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="B125" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C125" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D125" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="B126" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C126" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D126" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127">
+        <x:v>1125</x:v>
+      </x:c>
+      <x:c r="B127" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="C127" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D127" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128">
+        <x:v>1126</x:v>
+      </x:c>
+      <x:c r="B128" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C128" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D128" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129">
+        <x:v>1127</x:v>
+      </x:c>
+      <x:c r="B129" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C129" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="D129" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130">
+        <x:v>1128</x:v>
+      </x:c>
+      <x:c r="B130" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="C130" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D130" t="s">
+        <x:v>314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131">
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="B131" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C131" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D131" t="s">
+        <x:v>316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="B132" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="C132" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D132" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="B133" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="C133" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D133" t="s">
+        <x:v>322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134">
+        <x:v>1132</x:v>
+      </x:c>
+      <x:c r="B134" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C134" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D134" t="s">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="B135" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C135" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D135" t="s">
+        <x:v>328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136">
+        <x:v>1134</x:v>
+      </x:c>
+      <x:c r="B136" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C136" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D136" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="B137" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="C137" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="D137" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138">
+        <x:v>1136</x:v>
+      </x:c>
+      <x:c r="B138" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C138" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="D138" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139">
+        <x:v>1137</x:v>
+      </x:c>
+      <x:c r="B139" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C139" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="D139" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140">
+        <x:v>1138</x:v>
+      </x:c>
+      <x:c r="B140" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="C140" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="D140" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c r="B141" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C141" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="D141" t="s">
+        <x:v>344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="B142" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C142" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="D142" t="s">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143">
+        <x:v>1141</x:v>
+      </x:c>
+      <x:c r="B143" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C143" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D143" t="s">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="B144" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C144" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="D144" t="s">
+        <x:v>353</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="B145" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="C145" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D145" t="s">
+        <x:v>356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146">
+        <x:v>1144</x:v>
+      </x:c>
+      <x:c r="B146" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C146" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D146" t="s">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="B147" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="C147" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D147" t="s">
+        <x:v>362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148">
+        <x:v>1146</x:v>
+      </x:c>
+      <x:c r="B148" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="C148" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="D148" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149">
+        <x:v>1147</x:v>
+      </x:c>
+      <x:c r="B149" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C149" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D149" t="s">
+        <x:v>368</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c r="B150" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C150" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D150" t="s">
+        <x:v>371</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="B151" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="C151" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="D151" t="s">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="B152" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="C152" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D152" t="s">
+        <x:v>377</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="B153" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="C153" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D153" t="s">
+        <x:v>380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154">
+        <x:v>1152</x:v>
+      </x:c>
+      <x:c r="B154" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="C154" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D154" t="s">
+        <x:v>383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155">
+        <x:v>1153</x:v>
+      </x:c>
+      <x:c r="B155" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C155" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D155" t="s">
+        <x:v>386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156">
+        <x:v>1154</x:v>
+      </x:c>
+      <x:c r="B156" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="C156" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="D156" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="B157" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C157" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D157" t="s">
+        <x:v>392</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158">
+        <x:v>1156</x:v>
+      </x:c>
+      <x:c r="B158" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="C158" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="D158" t="s">
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="B159" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="C159" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="D159" t="s">
+        <x:v>398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160">
+        <x:v>1158</x:v>
+      </x:c>
+      <x:c r="B160" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C160" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="D160" t="s">
+        <x:v>401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161">
+        <x:v>1159</x:v>
+      </x:c>
+      <x:c r="B161" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C161" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="D161" t="s">
+        <x:v>404</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162">
+        <x:v>1160</x:v>
+      </x:c>
+      <x:c r="B162" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="C162" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="D162" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163">
+        <x:v>1161</x:v>
+      </x:c>
+      <x:c r="B163" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="C163" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="D163" t="s">
+        <x:v>410</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164">
+        <x:v>1162</x:v>
+      </x:c>
+      <x:c r="B164" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C164" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="D164" t="s">
+        <x:v>413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165">
+        <x:v>1163</x:v>
+      </x:c>
+      <x:c r="B165" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C165" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D165" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166">
+        <x:v>1164</x:v>
+      </x:c>
+      <x:c r="B166" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="C166" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="D166" t="s">
+        <x:v>417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167">
+        <x:v>1165</x:v>
+      </x:c>
+      <x:c r="B167" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="C167" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="D167" t="s">
+        <x:v>420</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168">
+        <x:v>1166</x:v>
+      </x:c>
+      <x:c r="B168" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="C168" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D168" t="s">
+        <x:v>423</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169">
+        <x:v>1167</x:v>
+      </x:c>
+      <x:c r="B169" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="C169" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="D169" t="s">
+        <x:v>426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170">
+        <x:v>1168</x:v>
+      </x:c>
+      <x:c r="B170" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C170" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D170" t="s">
+        <x:v>429</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="B171" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="C171" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="D171" t="s">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172">
+        <x:v>1170</x:v>
+      </x:c>
+      <x:c r="B172" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="C172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">추적 파일 {0}개의 스테이징되지 않은 변경을 버립니다. 이름 변경 {1}개는 원래 경로로 되돌립니다. 이미 스테이징한 변경은 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D172" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard unstaged changes in {0} tracked files. Restore {1} renames to their original paths. Staged changes remain intact.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173">
+        <x:v>1171</x:v>
+      </x:c>
+      <x:c r="B173" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="C173" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="D173" t="s">
+        <x:v>436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="B174" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C174" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D174" t="s">
+        <x:v>439</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="B175" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C175" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="D175" t="s">
+        <x:v>442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c r="B176" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="C176" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="D176" t="s">
+        <x:v>445</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177">
+        <x:v>1175</x:v>
+      </x:c>
+      <x:c r="B177" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="C177" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="D177" t="s">
+        <x:v>448</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178">
+        <x:v>1176</x:v>
+      </x:c>
+      <x:c r="B178" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C178" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="D178" t="s">
+        <x:v>451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179">
+        <x:v>1177</x:v>
+      </x:c>
+      <x:c r="B179" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C179" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="D179" t="s">
+        <x:v>454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180">
+        <x:v>1178</x:v>
+      </x:c>
+      <x:c r="B180" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="C180" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="D180" t="s">
+        <x:v>457</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181">
+        <x:v>1179</x:v>
+      </x:c>
+      <x:c r="B181" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="C181" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="D181" t="s">
+        <x:v>460</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182">
+        <x:v>1180</x:v>
+      </x:c>
+      <x:c r="B182" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C182" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="D182" t="s">
+        <x:v>463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183">
+        <x:v>1181</x:v>
+      </x:c>
+      <x:c r="B183" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="C183" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="D183" t="s">
+        <x:v>466</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184">
+        <x:v>1182</x:v>
+      </x:c>
+      <x:c r="B184" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C184" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="D184" t="s">
+        <x:v>469</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185">
+        <x:v>1183</x:v>
+      </x:c>
+      <x:c r="B185" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="C185" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="D185" t="s">
+        <x:v>472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186">
+        <x:v>1184</x:v>
+      </x:c>
+      <x:c r="B186" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="C186" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="D186" t="s">
+        <x:v>475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187">
+        <x:v>1185</x:v>
+      </x:c>
+      <x:c r="B187" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="C187" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="D187" t="s">
+        <x:v>478</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188">
+        <x:v>1186</x:v>
+      </x:c>
+      <x:c r="B188" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="C188" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="D188" t="s">
+        <x:v>481</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189">
+        <x:v>1187</x:v>
+      </x:c>
+      <x:c r="B189" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="C189" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="D189" t="s">
+        <x:v>484</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="B190" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C190" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="D190" t="s">
+        <x:v>487</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191">
+        <x:v>1189</x:v>
+      </x:c>
+      <x:c r="B191" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C191" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="D191" t="s">
+        <x:v>490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192">
+        <x:v>1190</x:v>
+      </x:c>
+      <x:c r="B192" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C192" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="D192" t="s">
+        <x:v>493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193">
+        <x:v>1191</x:v>
+      </x:c>
+      <x:c r="B193" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C193" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="D193" t="s">
+        <x:v>496</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194">
+        <x:v>1192</x:v>
+      </x:c>
+      <x:c r="B194" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C194" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="D194" t="s">
+        <x:v>499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195">
+        <x:v>1193</x:v>
+      </x:c>
+      <x:c r="B195" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C195" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="D195" t="s">
+        <x:v>502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196">
+        <x:v>1194</x:v>
+      </x:c>
+      <x:c r="B196" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C196" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D196" t="s">
+        <x:v>505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197">
+        <x:v>1195</x:v>
+      </x:c>
+      <x:c r="B197" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C197" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="D197" t="s">
+        <x:v>508</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198">
+        <x:v>1196</x:v>
+      </x:c>
+      <x:c r="B198" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C198" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="D198" t="s">
+        <x:v>511</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199">
+        <x:v>1197</x:v>
+      </x:c>
+      <x:c r="B199" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C199" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="D199" t="s">
+        <x:v>514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200">
+        <x:v>1198</x:v>
+      </x:c>
+      <x:c r="B200" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C200" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="D200" t="s">
+        <x:v>517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201">
+        <x:v>1199</x:v>
+      </x:c>
+      <x:c r="B201" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C201" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="D201" t="s">
+        <x:v>520</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="B202" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C202" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="D202" t="s">
+        <x:v>523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="B203" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="C203" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="D203" t="s">
+        <x:v>526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204">
+        <x:v>1202</x:v>
+      </x:c>
+      <x:c r="B204" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C204" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="D204" t="s">
+        <x:v>529</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205">
+        <x:v>1203</x:v>
+      </x:c>
+      <x:c r="B205" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C205" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="D205" t="s">
+        <x:v>532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="B206" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="C206" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="D206" t="s">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207">
+        <x:v>1205</x:v>
+      </x:c>
+      <x:c r="B207" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="C207" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="D207" t="s">
+        <x:v>538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="B208" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="C208" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="D208" t="s">
+        <x:v>541</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209">
+        <x:v>1207</x:v>
+      </x:c>
+      <x:c r="B209" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C209" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="D209" t="s">
+        <x:v>544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="B210" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C210" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="D210" t="s">
+        <x:v>547</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211">
+        <x:v>1209</x:v>
+      </x:c>
+      <x:c r="B211" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="C211" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="D211" t="s">
+        <x:v>550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="B212" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="C212" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="D212" t="s">
+        <x:v>553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="B213" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="C213" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="D213" t="s">
+        <x:v>556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="B214" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C214" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="D214" t="s">
+        <x:v>559</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215">
+        <x:v>1213</x:v>
+      </x:c>
+      <x:c r="B215" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="C215" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="D215" t="s">
+        <x:v>562</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216">
+        <x:v>1214</x:v>
+      </x:c>
+      <x:c r="B216" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="C216" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="D216" t="s">
+        <x:v>565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217">
+        <x:v>1215</x:v>
+      </x:c>
+      <x:c r="B217" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="C217" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="D217" t="s">
+        <x:v>568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="B218" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalSelectedFileUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C218" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 파일 {0}을(를) 현재 작업에 사용할 수 없습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D218" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The selected file is no longer available for this operation: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="B219" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalResolveBeforeDiscard</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C219" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0}의 충돌을 해결한 뒤 변경을 폐기하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D219" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Resolve the conflict in {0} before discarding changes.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="B220" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalDiscardRequiresConfirmation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C220" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경을 폐기하려면 확인이 필요합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D220" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discarding changes requires confirmation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="B221" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalIgnoreRequiresConfirmation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C221" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">파일을 무시하려면 확인이 필요합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D221" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ignoring files requires confirmation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222">
+        <x:v>1404</x:v>
+      </x:c>
+      <x:c r="B222" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalLargeStageRequiresConfirmation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C222" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 큰 파일을 스테이징하려면 확인이 필요합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D222" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Staging large new files requires confirmation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223">
+        <x:v>1405</x:v>
+      </x:c>
+      <x:c r="B223" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalSelectionSetChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C223" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 파일 목록이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D223" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The selected file set changed before the operation started. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224">
+        <x:v>1406</x:v>
+      </x:c>
+      <x:c r="B224" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalSelectedFileChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C224" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D224" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The selected file changed before the operation started: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225">
+        <x:v>1407</x:v>
+      </x:c>
+      <x:c r="B225" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalIndexChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C225" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일의 인덱스 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D225" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The index state changed before the operation started: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226">
+        <x:v>1408</x:v>
+      </x:c>
+      <x:c r="B226" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalWorkingFileChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C226" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일의 작업 트리 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D226" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The working-tree state changed before the operation started: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227">
+        <x:v>1409</x:v>
+      </x:c>
+      <x:c r="B227" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StashTargetsUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C227" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stash에 보관할 변경 목록이 없습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D227" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The stash targets are no longer available. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228">
+        <x:v>1410</x:v>
+      </x:c>
+      <x:c r="B228" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StashTargetsChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C228" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stash 보관 대상이 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D228" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The stash targets changed before the operation started. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229">
+        <x:v>1411</x:v>
+      </x:c>
+      <x:c r="B229" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StashTargetChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C229" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stash 보관 대상 {0}이(가) 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D229" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The stash target changed before the operation started: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230">
+        <x:v>1412</x:v>
+      </x:c>
+      <x:c r="B230" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StashTargetIndexChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C230" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stash 보관 대상 {0}의 인덱스 상태가 작업 시작 전에 변경되었습니다. 새로 고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D230" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The stash target index changed before the operation started: {0}. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="B231" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictStageUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C231" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">충돌 파일 저장을 완료할 화면 연결이 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D231" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The conflict save cannot be completed because its screen connection is unavailable.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232">
+        <x:v>1301</x:v>
+      </x:c>
+      <x:c r="B232" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictStageCanceled</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C232" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">대기 중인 충돌 파일 저장이 취소되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D232" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The pending conflict save was canceled.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233">
+        <x:v>1302</x:v>
+      </x:c>
+      <x:c r="B233" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictStageNoLongerConflicted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C233" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일은 더 이상 충돌 상태가 아닙니다. 상태를 새로 고치세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D233" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} is no longer conflicted. Refresh the repository state.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234">
+        <x:v>1303</x:v>
+      </x:c>
+      <x:c r="B234" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictStageFileChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C234" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일이 열린 뒤 변경되었습니다. 다시 불러온 후 저장하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D234" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} changed after it was opened. Reload it before saving.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="B235" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictStageRefreshFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C235" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 파일은 저장하고 스테이징했지만 화면을 새로 고치지 못했습니다. {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D235" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Saved and staged {0}, but could not refresh the screen. {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="B236" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueRepositoryUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C236" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 작업을 실행할 저장소를 불러오지 못했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D236" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The requested repository could not be loaded for the remote operation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237">
+        <x:v>1501</x:v>
+      </x:c>
+      <x:c r="B237" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueRepositoryChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C237" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 작업을 시작하기 전에 저장소가 변경되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D237" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The requested repository changed before the remote operation started.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="B238" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueFetchRemoteChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C238" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 작업을 시작하기 전에 선택한 Fetch 원격이 변경되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D238" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The selected Fetch remote changed before the operation started.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239">
+        <x:v>1503</x:v>
+      </x:c>
+      <x:c r="B239" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueFetchRemoteUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C239" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 Fetch 원격을 더 이상 사용할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D239" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The selected Fetch remote is no longer available.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240">
+        <x:v>1504</x:v>
+      </x:c>
+      <x:c r="B240" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueFetchAllUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C240" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 원격 가져오기에 사용할 원격이 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D240" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No remote is available for Fetch all.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241">
+        <x:v>1505</x:v>
+      </x:c>
+      <x:c r="B241" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteQueueBranchChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C241" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 작업을 시작하기 전에 현재 브랜치가 변경되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D241" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The current branch changed before the remote operation started.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="B242" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CurrentRepositoryDetails</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C242" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">현재 저장소: {0} ({1})</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D242" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Current repository: {0} ({1})</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="B243" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GcmLoginCompleted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C243" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 로그인 절차를 마쳤습니다. 계정 목록을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D243" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The GitHub sign-in flow finished. Check the account list.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="B244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GcmOperationInProgress</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">계정 작업을 진행 중입니다…</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Working on the account…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245">
+        <x:v>1603</x:v>
+      </x:c>
+      <x:c r="B245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitAuthorEmailMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 작성자 이메일이 설정되지 않았습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git author email is not configured.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246">
+        <x:v>1604</x:v>
+      </x:c>
+      <x:c r="B246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitAuthorNameMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 작성자 이름이 설정되지 않았습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git author name is not configured.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247">
+        <x:v>1605</x:v>
+      </x:c>
+      <x:c r="B247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitAuthorSummary</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">커밋 작성자: {0} &lt;{1}&gt;</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Commit author: {0} &lt;{1}&gt;</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248">
+        <x:v>1606</x:v>
+      </x:c>
+      <x:c r="B248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitExecutablePickerTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 실행 파일 선택</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select Git executable</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249">
+        <x:v>1607</x:v>
+      </x:c>
+      <x:c r="B249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountActionCanceled</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">계정 작업이 취소되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account operation canceled.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250">
+        <x:v>1608</x:v>
+      </x:c>
+      <x:c r="B250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountLookupCanceled</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">계정 조회가 취소되었습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account lookup canceled.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="B251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountScopeHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">계정 선택은 현재 저장소의 해당 GitHub HTTPS 원격에만 적용됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account selection applies only to the chosen GitHub HTTPS remote in this repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252">
+        <x:v>1610</x:v>
+      </x:c>
+      <x:c r="B252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountSelected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격에 {1} 계정을 선택했습니다. 인증은 다음 원격 작업에서 확인됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Selected {1} for remote {0}. Authentication will be checked on the next remote operation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253">
+        <x:v>1611</x:v>
+      </x:c>
+      <x:c r="B253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountSelectionPreview</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 저장소의 {0} 원격에 {1} 계정을 사용합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use {1} for remote {0} in this repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254">
+        <x:v>1612</x:v>
+      </x:c>
+      <x:c r="B254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountsLoading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 계정과 원격 정보를 불러오는 중…</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Loading GitHub accounts and remotes…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255">
+        <x:v>1613</x:v>
+      </x:c>
+      <x:c r="B255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubInheritedAccount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">전역 설정에서 상속한 계정: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account inherited from global settings: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256">
+        <x:v>1614</x:v>
+      </x:c>
+      <x:c r="B256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubNoRemotes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">등록된 원격이 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No remotes are configured.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257">
+        <x:v>1615</x:v>
+      </x:c>
+      <x:c r="B257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubNoSelectedAccount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택된 인증 계정 없음</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No authentication account selected</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="B258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubSelectedAccount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 저장소에서 선택한 계정: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account selected for this repository: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="B259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubSharedRemoteUrlUnsupported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">여러 원격이 같은 URL을 사용해 계정을 따로 지정할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Multiple remotes share this URL, so their accounts cannot be selected separately.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260">
+        <x:v>1618</x:v>
+      </x:c>
+      <x:c r="B260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubUserNameRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 사용자명을 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a GitHub username.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261">
+        <x:v>1619</x:v>
+      </x:c>
+      <x:c r="B261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitPathSaved</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 경로를 저장했습니다. 버전: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git path saved. Version: {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262">
+        <x:v>1620</x:v>
+      </x:c>
+      <x:c r="B262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitPathVerified</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 실행을 확인했습니다. 버전: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git verified. Version: {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263">
+        <x:v>1621</x:v>
+      </x:c>
+      <x:c r="B263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitSettingsHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 실행 파일과 작성자 설정을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Review the Git executable and author settings.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264">
+        <x:v>1622</x:v>
+      </x:c>
+      <x:c r="B264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitSettingsRefreshed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 설정을 새로 고쳤습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git settings refreshed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="B265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NotConfigured</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">설정되지 않음</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Not configured</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266">
+        <x:v>1624</x:v>
+      </x:c>
+      <x:c r="B266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SelectRepositoryPrompt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소를 선택하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select a repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267">
+        <x:v>1625</x:v>
+      </x:c>
+      <x:c r="B267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GlobalAuthorSaved</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">전역 커밋 작성자 설정을 저장했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Saved global commit author settings.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268">
+        <x:v>1626</x:v>
+      </x:c>
+      <x:c r="B268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalAuthorSaved</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 저장소의 커밋 작성자 설정을 저장했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Saved commit author settings for this repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="B269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardSelectionCount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 {0}개 파일 변경 폐기…</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes in {0} selected files…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270">
+        <x:v>1701</x:v>
+      </x:c>
+      <x:c r="B270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">무시</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ignore</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="B271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreRepository</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소에서 무시 (.gitignore)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ignore in repository (.gitignore)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272">
+        <x:v>1703</x:v>
+      </x:c>
+      <x:c r="B272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreLocal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 컴퓨터에서만 무시 (.git/info/exclude)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ignore on this computer only (.git/info/exclude)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273">
+        <x:v>1704</x:v>
+      </x:c>
+      <x:c r="B273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreConfirmTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택 파일 무시</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ignore selected files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="B274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreConfirmButton</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">무시 규칙 추가</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add ignore rules</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275">
+        <x:v>1706</x:v>
+      </x:c>
+      <x:c r="B275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IgnoreConfirmDescription</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">대상: {1}. 선택한 파일 {0}개의 정확한 경로를 무시 규칙에 추가합니다. 파일은 삭제하거나 스테이징하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Destination: {1}. Add exact-path ignore rules for {0} selected files. Files will not be deleted or staged.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276">
+        <x:v>1707</x:v>
+      </x:c>
+      <x:c r="B276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardBatchImpact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">추적 파일 {0}개의 스테이징되지 않은 변경을 복원하고 미추적 파일 {1}개를 삭제합니다. 이름 변경 {2}개는 원래 경로로 복원합니다. 이미 스테이징한 변경은 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Restore unstaged changes in {0} tracked files and delete {1} untracked files. Restore {2} renames to their original paths. Staged changes remain intact.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277">
+        <x:v>1708</x:v>
+      </x:c>
+      <x:c r="B277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardBatchPartialFailure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">일부 파일의 변경만 폐기했습니다. 완료 {0}개:
 {1}
 미완료 {2}개:
 {3}
-오류: {4}</x:t></x:is></x:c><x:c r="D277" t="inlineStr"><x:is><x:t xml:space="preserve">Only some changes were discarded. Completed ({0}):
+오류: {4}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only some changes were discarded. Completed ({0}):
 {1}
 Not completed ({2}):
 {3}
-Error: {4}</x:t></x:is></x:c></x:row><x:row r="278"><x:c r="A278"><x:v>1800</x:v></x:c><x:c r="B278" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubGcmUnavailable</x:t></x:is></x:c><x:c r="C278" t="inlineStr"><x:is><x:t xml:space="preserve">Git Credential Manager를 사용할 수 없습니다.</x:t></x:is></x:c><x:c r="D278" t="inlineStr"><x:is><x:t xml:space="preserve">Git Credential Manager is unavailable.</x:t></x:is></x:c></x:row><x:row r="279"><x:c r="A279"><x:v>1801</x:v></x:c><x:c r="B279" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountListUnavailable</x:t></x:is></x:c><x:c r="C279" t="inlineStr"><x:is><x:t xml:space="preserve">GCM 계정 목록을 읽지 못했습니다. 사용자명을 직접 입력하거나 로그인할 수 있습니다.</x:t></x:is></x:c><x:c r="D279" t="inlineStr"><x:is><x:t xml:space="preserve">Could not read the GCM account list. You can enter a username or sign in.</x:t></x:is></x:c></x:row><x:row r="280"><x:c r="A280"><x:v>1802</x:v></x:c><x:c r="B280" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubLoginFailed</x:t></x:is></x:c><x:c r="C280" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 로그인이 취소됐거나 실패했습니다. GCM 로그인 창에서 다시 시도하세요.</x:t></x:is></x:c><x:c r="D280" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub sign-in was canceled or failed. Try again in the GCM sign-in window.</x:t></x:is></x:c></x:row><x:row r="281"><x:c r="A281"><x:v>1803</x:v></x:c><x:c r="B281" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteNameRequired</x:t></x:is></x:c><x:c r="C281" t="inlineStr"><x:is><x:t xml:space="preserve">원격 이름을 선택하세요.</x:t></x:is></x:c><x:c r="D281" t="inlineStr"><x:is><x:t xml:space="preserve">Select a remote name.</x:t></x:is></x:c></x:row><x:row r="282"><x:c r="A282"><x:v>1804</x:v></x:c><x:c r="B282" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteNotFound</x:t></x:is></x:c><x:c r="C282" t="inlineStr"><x:is><x:t xml:space="preserve">원격을 찾을 수 없습니다: {0}</x:t></x:is></x:c><x:c r="D282" t="inlineStr"><x:is><x:t xml:space="preserve">Remote not found: {0}</x:t></x:is></x:c></x:row><x:row r="283"><x:c r="A283"><x:v>1805</x:v></x:c><x:c r="B283" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteUrlUnreadable</x:t></x:is></x:c><x:c r="C283" t="inlineStr"><x:is><x:t xml:space="preserve">원격 URL을 읽을 수 없습니다.</x:t></x:is></x:c><x:c r="D283" t="inlineStr"><x:is><x:t xml:space="preserve">Could not read the remote URL.</x:t></x:is></x:c></x:row><x:row r="284"><x:c r="A284"><x:v>1806</x:v></x:c><x:c r="B284" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteMultipleUrls</x:t></x:is></x:c><x:c r="C284" t="inlineStr"><x:is><x:t xml:space="preserve">URL이 여러 개인 원격은 계정 선택을 지원하지 않습니다.</x:t></x:is></x:c><x:c r="D284" t="inlineStr"><x:is><x:t xml:space="preserve">Account selection is unavailable for remotes with multiple URLs.</x:t></x:is></x:c></x:row><x:row r="285"><x:c r="A285"><x:v>1807</x:v></x:c><x:c r="B285" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteFetchPushMismatch</x:t></x:is></x:c><x:c r="C285" t="inlineStr"><x:is><x:t xml:space="preserve">가져오기와 푸시 URL이 다른 원격은 계정 선택을 지원하지 않습니다.</x:t></x:is></x:c><x:c r="D285" t="inlineStr"><x:is><x:t xml:space="preserve">Account selection is unavailable when fetch and push URLs differ.</x:t></x:is></x:c></x:row><x:row r="286"><x:c r="A286"><x:v>1808</x:v></x:c><x:c r="B286" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteGcmHelperRequired</x:t></x:is></x:c><x:c r="C286" t="inlineStr"><x:is><x:t xml:space="preserve">이 원격의 credential.helper가 GCM manager가 아닙니다.</x:t></x:is></x:c><x:c r="D286" t="inlineStr"><x:is><x:t xml:space="preserve">This remote does not use GCM manager as its credential.helper.</x:t></x:is></x:c></x:row><x:row r="287"><x:c r="A287"><x:v>1809</x:v></x:c><x:c r="B287" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteDefaultAccountUnreadable</x:t></x:is></x:c><x:c r="C287" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격의 기본 계정 설정을 읽지 못했습니다.</x:t></x:is></x:c><x:c r="D287" t="inlineStr"><x:is><x:t xml:space="preserve">Could not read the default account setting for remote {0}.</x:t></x:is></x:c></x:row><x:row r="288"><x:c r="A288"><x:v>1810</x:v></x:c><x:c r="B288" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteLocalAccountUnreadable</x:t></x:is></x:c><x:c r="C288" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격의 저장소 계정 설정을 읽지 못했습니다.</x:t></x:is></x:c><x:c r="D288" t="inlineStr"><x:is><x:t xml:space="preserve">Could not read the repository account setting for remote {0}.</x:t></x:is></x:c></x:row><x:row r="289"><x:c r="A289"><x:v>1811</x:v></x:c><x:c r="B289" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteHttpsRequired</x:t></x:is></x:c><x:c r="C289" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub HTTPS 원격이 아닙니다. SSH 원격은 SSH 키로 인증합니다.</x:t></x:is></x:c><x:c r="D289" t="inlineStr"><x:is><x:t xml:space="preserve">This is not a GitHub HTTPS remote. SSH remotes use SSH keys for authentication.</x:t></x:is></x:c></x:row><x:row r="290"><x:c r="A290"><x:v>1812</x:v></x:c><x:c r="B290" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteHostUnsupported</x:t></x:is></x:c><x:c r="C290" t="inlineStr"><x:is><x:t xml:space="preserve">github.com HTTPS 원격만 지원합니다.</x:t></x:is></x:c><x:c r="D290" t="inlineStr"><x:is><x:t xml:space="preserve">Only github.com HTTPS remotes are supported.</x:t></x:is></x:c></x:row><x:row r="291"><x:c r="A291"><x:v>1813</x:v></x:c><x:c r="B291" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemotePortUnsupported</x:t></x:is></x:c><x:c r="C291" t="inlineStr"><x:is><x:t xml:space="preserve">표준 HTTPS 포트의 GitHub 원격만 지원합니다.</x:t></x:is></x:c><x:c r="D291" t="inlineStr"><x:is><x:t xml:space="preserve">Only GitHub remotes on the standard HTTPS port are supported.</x:t></x:is></x:c></x:row><x:row r="292"><x:c r="A292"><x:v>1814</x:v></x:c><x:c r="B292" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteUserInfoUnsupported</x:t></x:is></x:c><x:c r="C292" t="inlineStr"><x:is><x:t xml:space="preserve">사용자 정보가 포함된 원격 URL은 지원하지 않습니다.</x:t></x:is></x:c><x:c r="D292" t="inlineStr"><x:is><x:t xml:space="preserve">Remote URLs containing user information are unsupported.</x:t></x:is></x:c></x:row><x:row r="293"><x:c r="A293"><x:v>1815</x:v></x:c><x:c r="B293" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteQueryUnsupported</x:t></x:is></x:c><x:c r="C293" t="inlineStr"><x:is><x:t xml:space="preserve">쿼리 또는 프래그먼트가 있는 원격 URL은 지원하지 않습니다.</x:t></x:is></x:c><x:c r="D293" t="inlineStr"><x:is><x:t xml:space="preserve">Remote URLs containing a query or fragment are unsupported.</x:t></x:is></x:c></x:row><x:row r="294"><x:c r="A294"><x:v>1816</x:v></x:c><x:c r="B294" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemotePathInvalid</x:t></x:is></x:c><x:c r="C294" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 저장소 URL 형식이 올바르지 않습니다.</x:t></x:is></x:c><x:c r="D294" t="inlineStr"><x:is><x:t xml:space="preserve">The GitHub repository URL has an invalid format.</x:t></x:is></x:c></x:row><x:row r="295"><x:c r="A295"><x:v>1817</x:v></x:c><x:c r="B295" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteUrlNeedsReview</x:t></x:is></x:c><x:c r="C295" t="inlineStr"><x:is><x:t xml:space="preserve">원격 URL 확인 필요</x:t></x:is></x:c><x:c r="D295" t="inlineStr"><x:is><x:t xml:space="preserve">Check remote URL</x:t></x:is></x:c></x:row><x:row r="296"><x:c r="A296"><x:v>1818</x:v></x:c><x:c r="B296" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubUserNameInvalid</x:t></x:is></x:c><x:c r="C296" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub 사용자명은 영문자·숫자·하이픈 1~39자로 입력하세요.</x:t></x:is></x:c><x:c r="D296" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a GitHub username of 1–39 letters, digits, or hyphens.</x:t></x:is></x:c></x:row><x:row r="297"><x:c r="A297"><x:v>1819</x:v></x:c><x:c r="B297" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubFetchUrlLabel</x:t></x:is></x:c><x:c r="C297" t="inlineStr"><x:is><x:t xml:space="preserve">가져오기: {0}</x:t></x:is></x:c><x:c r="D297" t="inlineStr"><x:is><x:t xml:space="preserve">Fetch: {0}</x:t></x:is></x:c></x:row><x:row r="298"><x:c r="A298"><x:v>1820</x:v></x:c><x:c r="B298" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubPushUrlLabel</x:t></x:is></x:c><x:c r="C298" t="inlineStr"><x:is><x:t xml:space="preserve">푸시: {0}</x:t></x:is></x:c><x:c r="D298" t="inlineStr"><x:is><x:t xml:space="preserve">Push: {0}</x:t></x:is></x:c></x:row><x:row r="299"><x:c r="A299"><x:v>1821</x:v></x:c><x:c r="B299" t="inlineStr"><x:is><x:t xml:space="preserve">GitSettingsHeading</x:t></x:is></x:c><x:c r="C299" t="inlineStr"><x:is><x:t xml:space="preserve">설정</x:t></x:is></x:c><x:c r="D299" t="inlineStr"><x:is><x:t xml:space="preserve">Settings</x:t></x:is></x:c></x:row><x:row r="300"><x:c r="A300"><x:v>1822</x:v></x:c><x:c r="B300" t="inlineStr"><x:is><x:t xml:space="preserve">GitExecutableHeading</x:t></x:is></x:c><x:c r="C300" t="inlineStr"><x:is><x:t xml:space="preserve">GIT 실행 파일</x:t></x:is></x:c><x:c r="D300" t="inlineStr"><x:is><x:t xml:space="preserve">GIT EXECUTABLE</x:t></x:is></x:c></x:row><x:row r="301"><x:c r="A301"><x:v>1823</x:v></x:c><x:c r="B301" t="inlineStr"><x:is><x:t xml:space="preserve">GitPathHint</x:t></x:is></x:c><x:c r="C301" t="inlineStr"><x:is><x:t xml:space="preserve">경로를 비워 두면 PATH에 등록된 Git을 사용합니다.</x:t></x:is></x:c><x:c r="D301" t="inlineStr"><x:is><x:t xml:space="preserve">Leave the path empty to use Git from PATH.</x:t></x:is></x:c></x:row><x:row r="302"><x:c r="A302"><x:v>1824</x:v></x:c><x:c r="B302" t="inlineStr"><x:is><x:t xml:space="preserve">GitPathPlaceholder</x:t></x:is></x:c><x:c r="C302" t="inlineStr"><x:is><x:t xml:space="preserve">PATH의 git 또는 절대 경로</x:t></x:is></x:c><x:c r="D302" t="inlineStr"><x:is><x:t xml:space="preserve">git from PATH, or an absolute path</x:t></x:is></x:c></x:row><x:row r="303"><x:c r="A303"><x:v>1825</x:v></x:c><x:c r="B303" t="inlineStr"><x:is><x:t xml:space="preserve">BrowseGitLabel</x:t></x:is></x:c><x:c r="C303" t="inlineStr"><x:is><x:t xml:space="preserve">찾아보기</x:t></x:is></x:c><x:c r="D303" t="inlineStr"><x:is><x:t xml:space="preserve">Browse</x:t></x:is></x:c></x:row><x:row r="304"><x:c r="A304"><x:v>1826</x:v></x:c><x:c r="B304" t="inlineStr"><x:is><x:t xml:space="preserve">TestGitLabel</x:t></x:is></x:c><x:c r="C304" t="inlineStr"><x:is><x:t xml:space="preserve">Git 확인</x:t></x:is></x:c><x:c r="D304" t="inlineStr"><x:is><x:t xml:space="preserve">Test Git</x:t></x:is></x:c></x:row><x:row r="305"><x:c r="A305"><x:v>1827</x:v></x:c><x:c r="B305" t="inlineStr"><x:is><x:t xml:space="preserve">SaveGitPathLabel</x:t></x:is></x:c><x:c r="C305" t="inlineStr"><x:is><x:t xml:space="preserve">Git 경로 저장</x:t></x:is></x:c><x:c r="D305" t="inlineStr"><x:is><x:t xml:space="preserve">Save Git path</x:t></x:is></x:c></x:row><x:row r="306"><x:c r="A306"><x:v>1828</x:v></x:c><x:c r="B306" t="inlineStr"><x:is><x:t xml:space="preserve">CommitAuthorHeading</x:t></x:is></x:c><x:c r="C306" t="inlineStr"><x:is><x:t xml:space="preserve">커밋 작성자</x:t></x:is></x:c><x:c r="D306" t="inlineStr"><x:is><x:t xml:space="preserve">COMMIT AUTHOR</x:t></x:is></x:c></x:row><x:row r="307"><x:c r="A307"><x:v>1829</x:v></x:c><x:c r="B307" t="inlineStr"><x:is><x:t xml:space="preserve">LocalAuthorHeading</x:t></x:is></x:c><x:c r="C307" t="inlineStr"><x:is><x:t xml:space="preserve">이 저장소 (로컬)</x:t></x:is></x:c><x:c r="D307" t="inlineStr"><x:is><x:t xml:space="preserve">This repository (local)</x:t></x:is></x:c></x:row><x:row r="308"><x:c r="A308"><x:v>1830</x:v></x:c><x:c r="B308" t="inlineStr"><x:is><x:t xml:space="preserve">SaveLocalAuthorLabel</x:t></x:is></x:c><x:c r="C308" t="inlineStr"><x:is><x:t xml:space="preserve">이 저장소에 저장</x:t></x:is></x:c><x:c r="D308" t="inlineStr"><x:is><x:t xml:space="preserve">Save for this repository</x:t></x:is></x:c></x:row><x:row r="309"><x:c r="A309"><x:v>1831</x:v></x:c><x:c r="B309" t="inlineStr"><x:is><x:t xml:space="preserve">GlobalAuthorHeading</x:t></x:is></x:c><x:c r="C309" t="inlineStr"><x:is><x:t xml:space="preserve">모든 저장소 (전역)</x:t></x:is></x:c><x:c r="D309" t="inlineStr"><x:is><x:t xml:space="preserve">All repositories (global)</x:t></x:is></x:c></x:row><x:row r="310"><x:c r="A310"><x:v>1832</x:v></x:c><x:c r="B310" t="inlineStr"><x:is><x:t xml:space="preserve">SaveGlobalAuthorLabel</x:t></x:is></x:c><x:c r="C310" t="inlineStr"><x:is><x:t xml:space="preserve">전역 설정에 저장</x:t></x:is></x:c><x:c r="D310" t="inlineStr"><x:is><x:t xml:space="preserve">Save globally</x:t></x:is></x:c></x:row><x:row r="311"><x:c r="A311"><x:v>1833</x:v></x:c><x:c r="B311" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountsHeading</x:t></x:is></x:c><x:c r="C311" t="inlineStr"><x:is><x:t xml:space="preserve">계정 및 인증</x:t></x:is></x:c><x:c r="D311" t="inlineStr"><x:is><x:t xml:space="preserve">ACCOUNTS AND AUTHENTICATION</x:t></x:is></x:c></x:row><x:row r="312"><x:c r="A312"><x:v>1834</x:v></x:c><x:c r="B312" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountsDescription</x:t></x:is></x:c><x:c r="C312" t="inlineStr"><x:is><x:t xml:space="preserve">Bough는 HTTPS 인증에 Git 자격 증명 도우미를, SSH 인증에 기존 SSH 설정을 사용합니다. 비밀번호와 토큰은 여기에 저장하지 않습니다.</x:t></x:is></x:c><x:c r="D312" t="inlineStr"><x:is><x:t xml:space="preserve">Bough uses Git credential helpers for HTTPS and your existing SSH setup. Passwords and tokens are not stored here.</x:t></x:is></x:c></x:row><x:row r="313"><x:c r="A313"><x:v>1835</x:v></x:c><x:c r="B313" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountsPurpose</x:t></x:is></x:c><x:c r="C313" t="inlineStr"><x:is><x:t xml:space="preserve">Fetch / Pull / Push 인증에만 적용됩니다. 위의 커밋 작성자와 아바타 설정은 별개입니다.</x:t></x:is></x:c><x:c r="D313" t="inlineStr"><x:is><x:t xml:space="preserve">Fetch / Pull / Push authentication only. Commit author and avatar settings above are separate.</x:t></x:is></x:c></x:row><x:row r="314"><x:c r="A314"><x:v>1836</x:v></x:c><x:c r="B314" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAccountsQueueHint</x:t></x:is></x:c><x:c r="C314" t="inlineStr"><x:is><x:t xml:space="preserve">현재 원격 작업이 끝난 뒤 계정을 선택합니다.</x:t></x:is></x:c><x:c r="D314" t="inlineStr"><x:is><x:t xml:space="preserve">Account selection waits until the current remote operation completes.</x:t></x:is></x:c></x:row><x:row r="315"><x:c r="A315"><x:v>1837</x:v></x:c><x:c r="B315" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubExistingAccountPlaceholder</x:t></x:is></x:c><x:c r="C315" t="inlineStr"><x:is><x:t xml:space="preserve">기존 GCM 계정</x:t></x:is></x:c><x:c r="D315" t="inlineStr"><x:is><x:t xml:space="preserve">Existing GCM account</x:t></x:is></x:c></x:row><x:row r="316"><x:c r="A316"><x:v>1838</x:v></x:c><x:c r="B316" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubRemoteUserNameAutomationName</x:t></x:is></x:c><x:c r="C316" t="inlineStr"><x:is><x:t xml:space="preserve">이 원격의 GitHub 사용자명</x:t></x:is></x:c><x:c r="D316" t="inlineStr"><x:is><x:t xml:space="preserve">GitHub username for this remote</x:t></x:is></x:c></x:row><x:row r="317"><x:c r="A317"><x:v>1839</x:v></x:c><x:c r="B317" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubSelectAccountLabel</x:t></x:is></x:c><x:c r="C317" t="inlineStr"><x:is><x:t xml:space="preserve">이 원격에 사용</x:t></x:is></x:c><x:c r="D317" t="inlineStr"><x:is><x:t xml:space="preserve">Use for this remote</x:t></x:is></x:c></x:row><x:row r="318"><x:c r="A318"><x:v>1840</x:v></x:c><x:c r="B318" t="inlineStr"><x:is><x:t xml:space="preserve">GitHubAddAccountLabel</x:t></x:is></x:c><x:c r="C318" t="inlineStr"><x:is><x:t xml:space="preserve">다른 GitHub 계정 추가…</x:t></x:is></x:c><x:c r="D318" t="inlineStr"><x:is><x:t xml:space="preserve">Add another GitHub account…</x:t></x:is></x:c></x:row><x:row r="319"><x:c r="A319"><x:v>1841</x:v></x:c><x:c r="B319" t="inlineStr"><x:is><x:t xml:space="preserve">CredentialHelperHeading</x:t></x:is></x:c><x:c r="C319" t="inlineStr"><x:is><x:t xml:space="preserve">자격 증명 도우미</x:t></x:is></x:c><x:c r="D319" t="inlineStr"><x:is><x:t xml:space="preserve">Credential helper</x:t></x:is></x:c></x:row><x:row r="320"><x:c r="A320"><x:v>1842</x:v></x:c><x:c r="B320" t="inlineStr"><x:is><x:t xml:space="preserve">RemoteUrlsHeading</x:t></x:is></x:c><x:c r="C320" t="inlineStr"><x:is><x:t xml:space="preserve">원격 URL</x:t></x:is></x:c><x:c r="D320" t="inlineStr"><x:is><x:t xml:space="preserve">Remote URLs</x:t></x:is></x:c></x:row><x:row r="321"><x:c r="A321"><x:v>1843</x:v></x:c><x:c r="B321" t="inlineStr"><x:is><x:t xml:space="preserve">SettingsTitle</x:t></x:is></x:c><x:c r="C321" t="inlineStr"><x:is><x:t xml:space="preserve">설정</x:t></x:is></x:c><x:c r="D321" t="inlineStr"><x:is><x:t xml:space="preserve">Settings</x:t></x:is></x:c></x:row><x:row r="322"><x:c r="A322"><x:v>2906</x:v></x:c><x:c r="B322" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteLocalBranch</x:t></x:is></x:c><x:c r="C322" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 브랜치 삭제...</x:t></x:is></x:c><x:c r="D322" t="inlineStr"><x:is><x:t xml:space="preserve">Delete local branch...</x:t></x:is></x:c></x:row><x:row r="323"><x:c r="A323"><x:v>2907</x:v></x:c><x:c r="B323" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteRemoteBranch</x:t></x:is></x:c><x:c r="C323" t="inlineStr"><x:is><x:t xml:space="preserve">원격 브랜치 삭제...</x:t></x:is></x:c><x:c r="D323" t="inlineStr"><x:is><x:t xml:space="preserve">Delete remote branch...</x:t></x:is></x:c></x:row><x:row r="324"><x:c r="A324"><x:v>2908</x:v></x:c><x:c r="B324" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteLocalBranchTitle</x:t></x:is></x:c><x:c r="C324" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 브랜치 삭제</x:t></x:is></x:c><x:c r="D324" t="inlineStr"><x:is><x:t xml:space="preserve">Delete local branch</x:t></x:is></x:c></x:row><x:row r="325"><x:c r="A325"><x:v>2909</x:v></x:c><x:c r="B325" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteRemoteBranchTitle</x:t></x:is></x:c><x:c r="C325" t="inlineStr"><x:is><x:t xml:space="preserve">원격 브랜치 삭제</x:t></x:is></x:c><x:c r="D325" t="inlineStr"><x:is><x:t xml:space="preserve">Delete remote branch</x:t></x:is></x:c></x:row><x:row r="326"><x:c r="A326"><x:v>2910</x:v></x:c><x:c r="B326" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteLocalBranchConfirm</x:t></x:is></x:c><x:c r="C326" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 브랜치를 삭제하시겠습니까? 병합되지 않은 커밋이 있으면 삭제하지 않습니다.</x:t></x:is></x:c><x:c r="D326" t="inlineStr"><x:is><x:t xml:space="preserve">Delete local branch {0}? Git will keep it if it contains unmerged commits.</x:t></x:is></x:c></x:row><x:row r="327"><x:c r="A327"><x:v>2911</x:v></x:c><x:c r="B327" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteRemoteBranchConfirm</x:t></x:is></x:c><x:c r="C327" t="inlineStr"><x:is><x:t xml:space="preserve">원격 브랜치 {0}을(를) 서버에서 삭제하시겠습니까? 다른 사용자에게도 영향을 주며 앱에서 되돌릴 수 없습니다.</x:t></x:is></x:c><x:c r="D327" t="inlineStr"><x:is><x:t xml:space="preserve">Delete remote branch {0} from the server? This affects other users and cannot be undone from the app.</x:t></x:is></x:c></x:row><x:row r="328"><x:c r="A328"><x:v>2912</x:v></x:c><x:c r="B328" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeleteBranchAction</x:t></x:is></x:c><x:c r="C328" t="inlineStr"><x:is><x:t xml:space="preserve">브랜치 삭제</x:t></x:is></x:c><x:c r="D328" t="inlineStr"><x:is><x:t xml:space="preserve">Delete branch</x:t></x:is></x:c></x:row><x:row r="329"><x:c r="A329"><x:v>2913</x:v></x:c><x:c r="B329" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceDeletingBranch</x:t></x:is></x:c><x:c r="C329" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 브랜치 삭제 중...</x:t></x:is></x:c><x:c r="D329" t="inlineStr"><x:is><x:t xml:space="preserve">Deleting branch {0}...</x:t></x:is></x:c></x:row><x:row r="330"><x:c r="A330"><x:v>2914</x:v></x:c><x:c r="B330" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleted</x:t></x:is></x:c><x:c r="C330" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 로컬 브랜치를 삭제했습니다.</x:t></x:is></x:c><x:c r="D330" t="inlineStr"><x:is><x:t xml:space="preserve">Deleted local branch {0}.</x:t></x:is></x:c></x:row><x:row r="331"><x:c r="A331"><x:v>2915</x:v></x:c><x:c r="B331" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleted</x:t></x:is></x:c><x:c r="C331" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격 브랜치를 삭제했습니다.</x:t></x:is></x:c><x:c r="D331" t="inlineStr"><x:is><x:t xml:space="preserve">Deleted remote branch {0}.</x:t></x:is></x:c></x:row><x:row r="332"><x:c r="A332"><x:v>2916</x:v></x:c><x:c r="B332" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceBranchDeleteRefreshFailed</x:t></x:is></x:c><x:c r="C332" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 참조 목록 새로고침 실패: {1}</x:t></x:is></x:c><x:c r="D332" t="inlineStr"><x:is><x:t xml:space="preserve">{0} Could not refresh references: {1}</x:t></x:is></x:c></x:row><x:row r="333"><x:c r="A333"><x:v>2917</x:v></x:c><x:c r="B333" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleteCurrent</x:t></x:is></x:c><x:c r="C333" t="inlineStr"><x:is><x:t xml:space="preserve">현재 체크아웃된 {0} 브랜치는 삭제할 수 없습니다.</x:t></x:is></x:c><x:c r="D333" t="inlineStr"><x:is><x:t xml:space="preserve">Cannot delete the checked-out branch {0}.</x:t></x:is></x:c></x:row><x:row r="334"><x:c r="A334"><x:v>2918</x:v></x:c><x:c r="B334" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleteMissing</x:t></x:is></x:c><x:c r="C334" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 로컬 브랜치를 찾을 수 없습니다.</x:t></x:is></x:c><x:c r="D334" t="inlineStr"><x:is><x:t xml:space="preserve">Local branch {0} no longer exists.</x:t></x:is></x:c></x:row><x:row r="335"><x:c r="A335"><x:v>2919</x:v></x:c><x:c r="B335" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleteChanged</x:t></x:is></x:c><x:c r="C335" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 브랜치가 확인 이후 변경되었습니다. 새로고친 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D335" t="inlineStr"><x:is><x:t xml:space="preserve">Branch {0} changed after confirmation. Refresh and try again.</x:t></x:is></x:c></x:row><x:row r="336"><x:c r="A336"><x:v>2920</x:v></x:c><x:c r="B336" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleteFailed</x:t></x:is></x:c><x:c r="C336" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 로컬 브랜치를 삭제하지 못했습니다: {1}</x:t></x:is></x:c><x:c r="D336" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete local branch {0}: {1}</x:t></x:is></x:c></x:row><x:row r="337"><x:c r="A337"><x:v>2921</x:v></x:c><x:c r="B337" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceLocalBranchDeleteFailedWithoutOutput</x:t></x:is></x:c><x:c r="C337" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 로컬 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</x:t></x:is></x:c><x:c r="D337" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete local branch {0} (exit code {1}).</x:t></x:is></x:c></x:row><x:row r="338"><x:c r="A338"><x:v>2922</x:v></x:c><x:c r="B338" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleteDefault</x:t></x:is></x:c><x:c r="C338" t="inlineStr"><x:is><x:t xml:space="preserve">{0}은(는) 원격의 기본 브랜치라 삭제할 수 없습니다.</x:t></x:is></x:c><x:c r="D338" t="inlineStr"><x:is><x:t xml:space="preserve">Cannot delete {0} because it is the remote's default branch.</x:t></x:is></x:c></x:row><x:row r="339"><x:c r="A339"><x:v>2923</x:v></x:c><x:c r="B339" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleteMissing</x:t></x:is></x:c><x:c r="C339" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격 브랜치를 찾을 수 없습니다.</x:t></x:is></x:c><x:c r="D339" t="inlineStr"><x:is><x:t xml:space="preserve">Remote branch {0} no longer exists.</x:t></x:is></x:c></x:row><x:row r="340"><x:c r="A340"><x:v>2924</x:v></x:c><x:c r="B340" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleteChanged</x:t></x:is></x:c><x:c r="C340" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격 브랜치가 확인 이후 변경되었습니다. Fetch한 뒤 다시 시도하세요.</x:t></x:is></x:c><x:c r="D340" t="inlineStr"><x:is><x:t xml:space="preserve">Remote branch {0} changed after confirmation. Fetch and try again.</x:t></x:is></x:c></x:row><x:row r="341"><x:c r="A341"><x:v>2925</x:v></x:c><x:c r="B341" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleteFailed</x:t></x:is></x:c><x:c r="C341" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격 브랜치를 삭제하지 못했습니다: {1}</x:t></x:is></x:c><x:c r="D341" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete remote branch {0}: {1}</x:t></x:is></x:c></x:row><x:row r="342"><x:c r="A342"><x:v>2926</x:v></x:c><x:c r="B342" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRemoteBranchDeleteFailedWithoutOutput</x:t></x:is></x:c><x:c r="C342" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 원격 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</x:t></x:is></x:c><x:c r="D342" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete remote branch {0} (exit code {1}).</x:t></x:is></x:c></x:row><x:row r="343"><x:c r="A343" t="n"><x:v>2927</x:v></x:c><x:c r="B343" t="str"><x:v>ConflictBatchCurrentFileLabel</x:v></x:c><x:c r="C343" t="str"><x:v>이 파일의 미해결 구간 {0}개</x:v></x:c><x:c r="D343" t="str"><x:v>{0} unresolved sections in this file</x:v></x:c></x:row><x:row r="344"><x:c r="A344"><x:v>2928</x:v></x:c><x:c r="B344" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictBatchTooltip</x:t></x:is></x:c><x:c r="C344" t="inlineStr"><x:is><x:t xml:space="preserve">이미 선택한 구간은 유지합니다. 최종 파일 미리보기만 바뀌며 저장·스테이징은 별도로 해야 합니다.</x:t></x:is></x:c><x:c r="D344" t="inlineStr"><x:is><x:t xml:space="preserve">Previous choices stay unchanged. This updates only the final-file preview; save and stage separately.</x:t></x:is></x:c></x:row><x:row r="345"><x:c r="A345"><x:v>2929</x:v></x:c><x:c r="B345" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictBatchReplaceEditsTitle</x:t></x:is></x:c><x:c r="C345" t="inlineStr"><x:is><x:t xml:space="preserve">직접 편집한 내용 바꾸기</x:t></x:is></x:c><x:c r="D345" t="inlineStr"><x:is><x:t xml:space="preserve">Replace manual edits</x:t></x:is></x:c></x:row><x:row r="346"><x:c r="A346"><x:v>2930</x:v></x:c><x:c r="B346" t="inlineStr"><x:is><x:t xml:space="preserve">ConflictBatchReplaceEditsMessage</x:t></x:is></x:c><x:c r="C346" t="inlineStr"><x:is><x:t xml:space="preserve">최종 파일을 직접 편집했습니다. 남은 구간에 일괄 선택을 적용하면 직접 편집한 내용이 사라집니다. 계속할까요?</x:t></x:is></x:c><x:c r="D346" t="inlineStr"><x:is><x:t xml:space="preserve">You edited the final file. Applying one choice to the remaining sections will replace those manual edits. Continue?</x:t></x:is></x:c></x:row><x:row r="347"><x:c r="A347" t="n"><x:v>2931</x:v></x:c><x:c r="B347" t="str"><x:v>ConflictBatchApplyButton</x:v></x:c><x:c r="C347" t="str"><x:v>남은 구간 일괄 선택</x:v></x:c><x:c r="D347" t="str"><x:v>Choose remaining sections</x:v></x:c></x:row><x:row r="348"><x:c r="A348"><x:v>2932</x:v></x:c><x:c r="B348" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseTargetChange</x:t></x:is></x:c><x:c r="C348" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 대상 · 적용된 커밋</x:t></x:is></x:c><x:c r="D348" t="inlineStr"><x:is><x:t xml:space="preserve">Rebase target · applied commits</x:t></x:is></x:c></x:row><x:row r="349"><x:c r="A349"><x:v>2933</x:v></x:c><x:c r="B349" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseReplayChange</x:t></x:is></x:c><x:c r="C349" t="inlineStr"><x:is><x:t xml:space="preserve">다시 적용 중인 내 커밋</x:t></x:is></x:c><x:c r="D349" t="inlineStr"><x:is><x:t xml:space="preserve">My commit being replayed</x:t></x:is></x:c></x:row><x:row r="350"><x:c r="A350"><x:v>2934</x:v></x:c><x:c r="B350" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseUseTarget</x:t></x:is></x:c><x:c r="C350" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 대상 사용</x:t></x:is></x:c><x:c r="D350" t="inlineStr"><x:is><x:t xml:space="preserve">Use rebase target</x:t></x:is></x:c></x:row><x:row r="351"><x:c r="A351"><x:v>2935</x:v></x:c><x:c r="B351" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseUseReplay</x:t></x:is></x:c><x:c r="C351" t="inlineStr"><x:is><x:t xml:space="preserve">내 커밋 사용</x:t></x:is></x:c><x:c r="D351" t="inlineStr"><x:is><x:t xml:space="preserve">Use my commit</x:t></x:is></x:c></x:row><x:row r="352"><x:c r="A352"><x:v>2936</x:v></x:c><x:c r="B352" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseTargetSource</x:t></x:is></x:c><x:c r="C352" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 대상 HEAD</x:t></x:is></x:c><x:c r="D352" t="inlineStr"><x:is><x:t xml:space="preserve">Rebase target HEAD</x:t></x:is></x:c></x:row><x:row r="353"><x:c r="A353"><x:v>2937</x:v></x:c><x:c r="B353" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseReplaySource</x:t></x:is></x:c><x:c r="C353" t="inlineStr"><x:is><x:t xml:space="preserve">내 커밋 REBASE_HEAD</x:t></x:is></x:c><x:c r="D353" t="inlineStr"><x:is><x:t xml:space="preserve">My commit REBASE_HEAD</x:t></x:is></x:c></x:row><x:row r="354"><x:c r="A354"><x:v>2938</x:v></x:c><x:c r="B354" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseBothOrderTip</x:t></x:is></x:c><x:c r="C354" t="inlineStr"><x:is><x:t xml:space="preserve">둘 다 사용하면 리베이스 대상 내용을 먼저, 다시 적용 중인 내 커밋 내용을 뒤에 둡니다.</x:t></x:is></x:c><x:c r="D354" t="inlineStr"><x:is><x:t xml:space="preserve">Use both places the rebase target content first, followed by my replayed commit.</x:t></x:is></x:c></x:row><x:row r="355"><x:c r="A355"><x:v>2939</x:v></x:c><x:c r="B355" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseProgressLabel</x:t></x:is></x:c><x:c r="C355" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 진행 중</x:t></x:is></x:c><x:c r="D355" t="inlineStr"><x:is><x:t xml:space="preserve">Rebase in progress</x:t></x:is></x:c></x:row><x:row r="356"><x:c r="A356"><x:v>2940</x:v></x:c><x:c r="B356" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseResolveBeforeContinue</x:t></x:is></x:c><x:c r="C356" t="inlineStr"><x:is><x:t xml:space="preserve">남은 충돌 {0}건을 해결·스테이징하면 계속할 수 있습니다.</x:t></x:is></x:c><x:c r="D356" t="inlineStr"><x:is><x:t xml:space="preserve">Resolve and stage {0} remaining conflicts to continue.</x:t></x:is></x:c></x:row><x:row r="357"><x:c r="A357"><x:v>2941</x:v></x:c><x:c r="B357" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseReadyToContinue</x:t></x:is></x:c><x:c r="C357" t="inlineStr"><x:is><x:t xml:space="preserve">모든 충돌을 스테이징했습니다. 계속을 눌러 리베이스를 진행하세요.</x:t></x:is></x:c><x:c r="D357" t="inlineStr"><x:is><x:t xml:space="preserve">All conflicts are staged. Select Continue rebase to proceed.</x:t></x:is></x:c></x:row><x:row r="358"><x:c r="A358"><x:v>2942</x:v></x:c><x:c r="B358" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseContinueAction</x:t></x:is></x:c><x:c r="C358" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 계속</x:t></x:is></x:c><x:c r="D358" t="inlineStr"><x:is><x:t xml:space="preserve">Continue rebase</x:t></x:is></x:c></x:row><x:row r="359"><x:c r="A359"><x:v>2943</x:v></x:c><x:c r="B359" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseNoLongerInProgress</x:t></x:is></x:c><x:c r="C359" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스가 더 이상 진행 중이지 않습니다.</x:t></x:is></x:c><x:c r="D359" t="inlineStr"><x:is><x:t xml:space="preserve">The rebase is no longer in progress.</x:t></x:is></x:c></x:row><x:row r="360"><x:c r="A360"><x:v>2944</x:v></x:c><x:c r="B360" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseUnresolvedConflicts</x:t></x:is></x:c><x:c r="C360" t="inlineStr"><x:is><x:t xml:space="preserve">미해결 충돌 {0}건이 있어 리베이스를 계속할 수 없습니다.</x:t></x:is></x:c><x:c r="D360" t="inlineStr"><x:is><x:t xml:space="preserve">Cannot continue the rebase while {0} conflicts remain unresolved.</x:t></x:is></x:c></x:row><x:row r="361"><x:c r="A361"><x:v>2945</x:v></x:c><x:c r="B361" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseContinueFailed</x:t></x:is></x:c><x:c r="C361" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스 계속에 실패했습니다(종료 코드 {0}). {1}</x:t></x:is></x:c><x:c r="D361" t="inlineStr"><x:is><x:t xml:space="preserve">Could not continue the rebase (exit code {0}). {1}</x:t></x:is></x:c></x:row><x:row r="362"><x:c r="A362"><x:v>2946</x:v></x:c><x:c r="B362" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseNextConflicts</x:t></x:is></x:c><x:c r="C362" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스에서 새 충돌 {0}건이 발생했습니다. 해결·스테이징한 뒤 계속하세요.</x:t></x:is></x:c><x:c r="D362" t="inlineStr"><x:is><x:t xml:space="preserve">The rebase has {0} new conflicts. Resolve and stage them, then continue.</x:t></x:is></x:c></x:row><x:row r="363"><x:c r="A363"><x:v>2947</x:v></x:c><x:c r="B363" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseContinueCompleted</x:t></x:is></x:c><x:c r="C363" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스를 완료했습니다.</x:t></x:is></x:c><x:c r="D363" t="inlineStr"><x:is><x:t xml:space="preserve">Rebase completed.</x:t></x:is></x:c></x:row><x:row r="364"><x:c r="A364"><x:v>2948</x:v></x:c><x:c r="B364" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseContinueStillInProgress</x:t></x:is></x:c><x:c r="C364" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스가 아직 진행 중입니다. Git 상태를 확인하세요.</x:t></x:is></x:c><x:c r="D364" t="inlineStr"><x:is><x:t xml:space="preserve">The rebase is still in progress. Check the Git state.</x:t></x:is></x:c></x:row><x:row r="365"><x:c r="A365"><x:v>2949</x:v></x:c><x:c r="B365" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseRepositoryChanged</x:t></x:is></x:c><x:c r="C365" t="inlineStr"><x:is><x:t xml:space="preserve">저장소 루트가 바뀌어 리베이스를 계속하지 않았습니다: {0}</x:t></x:is></x:c><x:c r="D365" t="inlineStr"><x:is><x:t xml:space="preserve">The repository root changed, so the rebase was not continued: {0}</x:t></x:is></x:c></x:row><x:row r="366"><x:c r="A366"><x:v>2950</x:v></x:c><x:c r="B366" t="inlineStr"><x:is><x:t xml:space="preserve">RebaseCheckingConflicts</x:t></x:is></x:c><x:c r="C366" t="inlineStr"><x:is><x:t xml:space="preserve">충돌 상태를 확인하는 중입니다.</x:t></x:is></x:c><x:c r="D366" t="inlineStr"><x:is><x:t xml:space="preserve">Checking the conflict state.</x:t></x:is></x:c></x:row><x:row r="367"><x:c r="A367"><x:v>2951</x:v></x:c><x:c r="B367" t="inlineStr"><x:is><x:t xml:space="preserve">DefaultPullStrategyHeading</x:t></x:is></x:c><x:c r="C367" t="inlineStr"><x:is><x:t xml:space="preserve">Bough 기본 Pull 방식</x:t></x:is></x:c><x:c r="D367" t="inlineStr"><x:is><x:t xml:space="preserve">Bough default Pull strategy</x:t></x:is></x:c></x:row><x:row r="368"><x:c r="A368"><x:v>2952</x:v></x:c><x:c r="B368" t="inlineStr"><x:is><x:t xml:space="preserve">DefaultPullStrategyDescription</x:t></x:is></x:c><x:c r="C368" t="inlineStr"><x:is><x:t xml:space="preserve">모든 저장소에서 Bough의 기본 Pull 동작에 적용됩니다. Git CLI의 pull.rebase 및 pull.ff 설정은 변경하지 않습니다.</x:t></x:is></x:c><x:c r="D368" t="inlineStr"><x:is><x:t xml:space="preserve">Applies to Bough's default Pull action for every repository. Git CLI pull.rebase and pull.ff settings are not changed.</x:t></x:is></x:c></x:row><x:row r="369"><x:c r="A369"><x:v>2953</x:v></x:c><x:c r="B369" t="inlineStr"><x:is><x:t xml:space="preserve">PullStrategyFastForwardOnly</x:t></x:is></x:c><x:c r="C369" t="inlineStr"><x:is><x:t xml:space="preserve">빠른 전진만</x:t></x:is></x:c><x:c r="D369" t="inlineStr"><x:is><x:t xml:space="preserve">Fast-forward only</x:t></x:is></x:c></x:row><x:row r="370"><x:c r="A370"><x:v>2954</x:v></x:c><x:c r="B370" t="inlineStr"><x:is><x:t xml:space="preserve">PullStrategyMerge</x:t></x:is></x:c><x:c r="C370" t="inlineStr"><x:is><x:t xml:space="preserve">병합</x:t></x:is></x:c><x:c r="D370" t="inlineStr"><x:is><x:t xml:space="preserve">Merge</x:t></x:is></x:c></x:row><x:row r="371"><x:c r="A371"><x:v>2955</x:v></x:c><x:c r="B371" t="inlineStr"><x:is><x:t xml:space="preserve">PullStrategyRebase</x:t></x:is></x:c><x:c r="C371" t="inlineStr"><x:is><x:t xml:space="preserve">리베이스</x:t></x:is></x:c><x:c r="D371" t="inlineStr"><x:is><x:t xml:space="preserve">Rebase</x:t></x:is></x:c></x:row><x:row r="372"><x:c r="A372"><x:v>2956</x:v></x:c><x:c r="B372" t="inlineStr"><x:is><x:t xml:space="preserve">DefaultPullStrategySaved</x:t></x:is></x:c><x:c r="C372" t="inlineStr"><x:is><x:t xml:space="preserve">Bough 기본 Pull 방식 저장: {0}</x:t></x:is></x:c><x:c r="D372" t="inlineStr"><x:is><x:t xml:space="preserve">Bough default Pull strategy saved: {0}</x:t></x:is></x:c></x:row><x:row r="373"><x:c r="A373"><x:v>2957</x:v></x:c><x:c r="B373" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullConfiguredDefaultTip</x:t></x:is></x:c><x:c r="C373" t="inlineStr"><x:is><x:t xml:space="preserve">기본 Pull: {0}. upstream이 없으면 받을 원격 브랜치를 선택합니다.</x:t></x:is></x:c><x:c r="D373" t="inlineStr"><x:is><x:t xml:space="preserve">Default Pull: {0}. Choose a remote branch if there is no upstream.</x:t></x:is></x:c></x:row><x:row r="374"><x:c r="A374"><x:v>2958</x:v></x:c><x:c r="B374" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullConfiguredDefaultAutomation</x:t></x:is></x:c><x:c r="C374" t="inlineStr"><x:is><x:t xml:space="preserve">Pull (기본 방식: {0})</x:t></x:is></x:c><x:c r="D374" t="inlineStr"><x:is><x:t xml:space="preserve">Pull (default: {0})</x:t></x:is></x:c></x:row><x:row r="375"><x:c r="A375"><x:v>2959</x:v></x:c><x:c r="B375" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullStrategyMenuTip</x:t></x:is></x:c><x:c r="C375" t="inlineStr"><x:is><x:t xml:space="preserve">이번 Pull에 사용할 방식 또는 받을 브랜치를 선택합니다. 기본 방식: {0}</x:t></x:is></x:c><x:c r="D375" t="inlineStr"><x:is><x:t xml:space="preserve">Choose a strategy or source branch for this Pull. Default: {0}</x:t></x:is></x:c></x:row><x:row r="376"><x:c r="A376"><x:v>2960</x:v></x:c><x:c r="B376" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullChooseBranchDefaultTip</x:t></x:is></x:c><x:c r="C376" t="inlineStr"><x:is><x:t xml:space="preserve">받을 원격 브랜치를 고른 뒤 기본 방식({0})으로 Pull을 실행합니다.</x:t></x:is></x:c><x:c r="D376" t="inlineStr"><x:is><x:t xml:space="preserve">Choose a remote branch, then Pull with the default strategy ({0}).</x:t></x:is></x:c></x:row><x:row r="377"><x:c r="A377"><x:v>2961</x:v></x:c><x:c r="B377" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullFastForwardAction</x:t></x:is></x:c><x:c r="C377" t="inlineStr"><x:is><x:t xml:space="preserve">빠른 전진만으로 받기</x:t></x:is></x:c><x:c r="D377" t="inlineStr"><x:is><x:t xml:space="preserve">Pull fast-forward only</x:t></x:is></x:c></x:row><x:row r="378"><x:c r="A378"><x:v>2962</x:v></x:c><x:c r="B378" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullDefaultSuffix</x:t></x:is></x:c><x:c r="C378" t="inlineStr"><x:is><x:t xml:space="preserve"> (기본)</x:t></x:is></x:c><x:c r="D378" t="inlineStr"><x:is><x:t xml:space="preserve"> (default)</x:t></x:is></x:c></x:row><x:row r="379"><x:c r="A379"><x:v>2963</x:v></x:c><x:c r="B379" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullStrategyMenuAutomation</x:t></x:is></x:c><x:c r="C379" t="inlineStr"><x:is><x:t xml:space="preserve">Pull 방식 메뉴 (기본: {0})</x:t></x:is></x:c><x:c r="D379" t="inlineStr"><x:is><x:t xml:space="preserve">Pull strategy menu (default: {0})</x:t></x:is></x:c></x:row><x:row r="380"><x:c r="A380"><x:v>2964</x:v></x:c><x:c r="B380" t="inlineStr"><x:is><x:t xml:space="preserve">RemotePullFastForwardTip</x:t></x:is></x:c><x:c r="C380" t="inlineStr"><x:is><x:t xml:space="preserve">현재 upstream에서 빠른 전진만으로 한 번 Pull합니다. upstream이 없으면 받을 원격 브랜치를 선택합니다.</x:t></x:is></x:c><x:c r="D380" t="inlineStr"><x:is><x:t xml:space="preserve">Pull once from the current upstream using fast-forward only. If there is no upstream, choose a remote branch.</x:t></x:is></x:c></x:row><x:row r="381"><x:c r="A381"><x:v>2965</x:v></x:c><x:c r="B381" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardTrackedSelectionCount</x:t></x:is></x:c><x:c r="C381" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 추적 파일 {0}개의 변경 버리기</x:t></x:is></x:c><x:c r="D381" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes in {0} selected tracked files</x:t></x:is></x:c></x:row><x:row r="382"><x:c r="A382"><x:v>2966</x:v></x:c><x:c r="B382" t="inlineStr"><x:is><x:t xml:space="preserve">DeleteUntrackedSelectionCount</x:t></x:is></x:c><x:c r="C382" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 미추적 파일 {0}개 삭제</x:t></x:is></x:c><x:c r="D382" t="inlineStr"><x:is><x:t xml:space="preserve">Delete {0} selected untracked files</x:t></x:is></x:c></x:row><x:row r="383"><x:c r="A383"><x:v>2967</x:v></x:c><x:c r="B383" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardMixedSelectionCount</x:t></x:is></x:c><x:c r="C383" t="inlineStr"><x:is><x:t xml:space="preserve">변경 버리기 {0}개 · 미추적 파일 삭제 {1}개</x:t></x:is></x:c><x:c r="D383" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes in {0} tracked files · delete {1} untracked files</x:t></x:is></x:c></x:row><x:row r="384"><x:c r="A384"><x:v>2968</x:v></x:c><x:c r="B384" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardTrackedTitle</x:t></x:is></x:c><x:c r="C384" t="inlineStr"><x:is><x:t xml:space="preserve">추적 파일 변경 버리기</x:t></x:is></x:c><x:c r="D384" t="inlineStr"><x:is><x:t xml:space="preserve">Discard tracked file changes</x:t></x:is></x:c></x:row><x:row r="385"><x:c r="A385"><x:v>2969</x:v></x:c><x:c r="B385" t="inlineStr"><x:is><x:t xml:space="preserve">DeleteUntrackedTitle</x:t></x:is></x:c><x:c r="C385" t="inlineStr"><x:is><x:t xml:space="preserve">미추적 파일 삭제</x:t></x:is></x:c><x:c r="D385" t="inlineStr"><x:is><x:t xml:space="preserve">Delete untracked files</x:t></x:is></x:c></x:row><x:row r="386"><x:c r="A386"><x:v>2970</x:v></x:c><x:c r="B386" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardMixedTitle</x:t></x:is></x:c><x:c r="C386" t="inlineStr"><x:is><x:t xml:space="preserve">변경 버리기 및 미추적 파일 삭제</x:t></x:is></x:c><x:c r="D386" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes and delete untracked files</x:t></x:is></x:c></x:row><x:row r="387"><x:c r="A387"><x:v>2971</x:v></x:c><x:c r="B387" t="inlineStr"><x:is><x:t xml:space="preserve">DeleteUntrackedImpact</x:t></x:is></x:c><x:c r="C387" t="inlineStr"><x:is><x:t xml:space="preserve">미추적 파일 {0}개를 디스크에서 영구 삭제합니다.</x:t></x:is></x:c><x:c r="D387" t="inlineStr"><x:is><x:t xml:space="preserve">Permanently delete {0} untracked files from disk.</x:t></x:is></x:c></x:row><x:row r="388"><x:c r="A388"><x:v>2972</x:v></x:c><x:c r="B388" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardConfirmMixed</x:t></x:is></x:c><x:c r="C388" t="inlineStr"><x:is><x:t xml:space="preserve">변경 버리기 및 파일 삭제</x:t></x:is></x:c><x:c r="D388" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes and delete files</x:t></x:is></x:c></x:row><x:row r="389"><x:c r="A389" t="n"><x:v>2973</x:v></x:c><x:c r="B389" t="str"><x:v>StopTrackingSelectionCount</x:v></x:c><x:c r="C389" t="str"><x:v>선택한 추적 파일 {0}개 추적 중지 및 무시</x:v></x:c><x:c r="D389" t="str"><x:v>Stop tracking and ignore {0} selected files</x:v></x:c></x:row><x:row r="390"><x:c r="A390" t="n"><x:v>2974</x:v></x:c><x:c r="B390" t="str"><x:v>StopTrackingTitle</x:v></x:c><x:c r="C390" t="str"><x:v>파일 추적 중지 및 무시</x:v></x:c><x:c r="D390" t="str"><x:v>Stop tracking and ignore files</x:v></x:c></x:row><x:row r="391"><x:c r="A391" t="n"><x:v>2975</x:v></x:c><x:c r="B391" t="str"><x:v>StopTrackingDescription</x:v></x:c><x:c r="C391" t="str"><x:v>선택한 추적 파일 {0}개의 경로를 저장소 루트의 .gitignore에 추가하고 Git 인덱스에서 제거합니다. 작업 파일은 남겨두며 삭제가 스테이징됩니다. .gitignore 변경은 자동으로 스테이징하지 않습니다.</x:v></x:c><x:c r="D391" t="str"><x:v>Add the paths of {0} selected tracked files to the repository root .gitignore and remove them from the Git index. Working files are kept, and their deletion is staged. The .gitignore change is not staged automatically.</x:v></x:c></x:row><x:row r="392"><x:c r="A392" t="n"><x:v>2976</x:v></x:c><x:c r="B392" t="str"><x:v>StopTrackingConfirm</x:v></x:c><x:c r="C392" t="str"><x:v>추적 중지 및 무시</x:v></x:c><x:c r="D392" t="str"><x:v>Stop tracking and ignore</x:v></x:c></x:row><x:row r="393"><x:c r="A393"><x:v>2977</x:v></x:c><x:c r="B393" t="inlineStr"><x:is><x:t xml:space="preserve">LocalStopTrackingRequiresConfirmation</x:t></x:is></x:c><x:c r="C393" t="inlineStr"><x:is><x:t xml:space="preserve">추적 중지를 확인할 창을 열 수 없습니다.</x:t></x:is></x:c><x:c r="D393" t="inlineStr"><x:is><x:t xml:space="preserve">The stop-tracking confirmation window is unavailable.</x:t></x:is></x:c></x:row><x:row r="394"><x:c r="A394"><x:v>2978</x:v></x:c><x:c r="B394" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardTrackedContextMenu</x:t></x:is></x:c><x:c r="C394" t="inlineStr"><x:is><x:t xml:space="preserve">변경 버리기</x:t></x:is></x:c><x:c r="D394" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes</x:t></x:is></x:c></x:row><x:row r="395"><x:c r="A395"><x:v>2979</x:v></x:c><x:c r="B395" t="inlineStr"><x:is><x:t xml:space="preserve">DeleteUntrackedContextMenu</x:t></x:is></x:c><x:c r="C395" t="inlineStr"><x:is><x:t xml:space="preserve">파일 삭제</x:t></x:is></x:c><x:c r="D395" t="inlineStr"><x:is><x:t xml:space="preserve">Delete files</x:t></x:is></x:c></x:row><x:row r="396"><x:c r="A396"><x:v>2980</x:v></x:c><x:c r="B396" t="inlineStr"><x:is><x:t xml:space="preserve">DiscardMixedContextMenu</x:t></x:is></x:c><x:c r="C396" t="inlineStr"><x:is><x:t xml:space="preserve">변경 버리기 및 파일 삭제</x:t></x:is></x:c><x:c r="D396" t="inlineStr"><x:is><x:t xml:space="preserve">Discard changes and delete files</x:t></x:is></x:c></x:row><x:row r="397"><x:c r="A397" t="n"><x:v>2981</x:v></x:c><x:c r="B397" t="str"><x:v>StopTrackingContextMenu</x:v></x:c><x:c r="C397" t="str"><x:v>추적 중지 및 무시…</x:v></x:c><x:c r="D397" t="str"><x:v>Stop tracking and ignore…</x:v></x:c></x:row><x:row r="398"><x:c r="A398"><x:v>2982</x:v></x:c><x:c r="B398" t="inlineStr"><x:is><x:t xml:space="preserve">CloneAction</x:t></x:is></x:c><x:c r="C398" t="inlineStr"><x:is><x:t xml:space="preserve">복제</x:t></x:is></x:c><x:c r="D398" t="inlineStr"><x:is><x:t xml:space="preserve">Clone</x:t></x:is></x:c></x:row><x:row r="399"><x:c r="A399"><x:v>2983</x:v></x:c><x:c r="B399" t="inlineStr"><x:is><x:t xml:space="preserve">CloneTitle</x:t></x:is></x:c><x:c r="C399" t="inlineStr"><x:is><x:t xml:space="preserve">저장소 복제</x:t></x:is></x:c><x:c r="D399" t="inlineStr"><x:is><x:t xml:space="preserve">Clone repository</x:t></x:is></x:c></x:row><x:row r="400"><x:c r="A400"><x:v>2984</x:v></x:c><x:c r="B400" t="inlineStr"><x:is><x:t xml:space="preserve">CloneUrlLabel</x:t></x:is></x:c><x:c r="C400" t="inlineStr"><x:is><x:t xml:space="preserve">원격 URL 또는 로컬 경로</x:t></x:is></x:c><x:c r="D400" t="inlineStr"><x:is><x:t xml:space="preserve">Remote URL or local path</x:t></x:is></x:c></x:row><x:row r="401"><x:c r="A401"><x:v>2985</x:v></x:c><x:c r="B401" t="inlineStr"><x:is><x:t xml:space="preserve">CloneParentLabel</x:t></x:is></x:c><x:c r="C401" t="inlineStr"><x:is><x:t xml:space="preserve">저장할 상위 폴더</x:t></x:is></x:c><x:c r="D401" t="inlineStr"><x:is><x:t xml:space="preserve">Parent folder</x:t></x:is></x:c></x:row><x:row r="402"><x:c r="A402"><x:v>2986</x:v></x:c><x:c r="B402" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFolderLabel</x:t></x:is></x:c><x:c r="C402" t="inlineStr"><x:is><x:t xml:space="preserve">새 폴더 이름</x:t></x:is></x:c><x:c r="D402" t="inlineStr"><x:is><x:t xml:space="preserve">New folder name</x:t></x:is></x:c></x:row><x:row r="403"><x:c r="A403"><x:v>2987</x:v></x:c><x:c r="B403" t="inlineStr"><x:is><x:t xml:space="preserve">CloneBrowseParent</x:t></x:is></x:c><x:c r="C403" t="inlineStr"><x:is><x:t xml:space="preserve">찾아보기</x:t></x:is></x:c><x:c r="D403" t="inlineStr"><x:is><x:t xml:space="preserve">Browse</x:t></x:is></x:c></x:row><x:row r="404"><x:c r="A404"><x:v>2988</x:v></x:c><x:c r="B404" t="inlineStr"><x:is><x:t xml:space="preserve">ClonePickParentTitle</x:t></x:is></x:c><x:c r="C404" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 위치 선택</x:t></x:is></x:c><x:c r="D404" t="inlineStr"><x:is><x:t xml:space="preserve">Choose clone location</x:t></x:is></x:c></x:row><x:row r="405"><x:c r="A405"><x:v>2989</x:v></x:c><x:c r="B405" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationPreview</x:t></x:is></x:c><x:c r="C405" t="inlineStr"><x:is><x:t xml:space="preserve">생성 위치: {0}</x:t></x:is></x:c><x:c r="D405" t="inlineStr"><x:is><x:t xml:space="preserve">Destination: {0}</x:t></x:is></x:c></x:row><x:row r="406"><x:c r="A406"><x:v>2990</x:v></x:c><x:c r="B406" t="inlineStr"><x:is><x:t xml:space="preserve">CloneUrlRequired</x:t></x:is></x:c><x:c r="C406" t="inlineStr"><x:is><x:t xml:space="preserve">원격 주소를 입력하세요.</x:t></x:is></x:c><x:c r="D406" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a remote address.</x:t></x:is></x:c></x:row><x:row r="407"><x:c r="A407"><x:v>2991</x:v></x:c><x:c r="B407" t="inlineStr"><x:is><x:t xml:space="preserve">CloneUrlInvalid</x:t></x:is></x:c><x:c r="C407" t="inlineStr"><x:is><x:t xml:space="preserve">지원하지 않는 원격 주소입니다.</x:t></x:is></x:c><x:c r="D407" t="inlineStr"><x:is><x:t xml:space="preserve">The remote address is not supported.</x:t></x:is></x:c></x:row><x:row r="408"><x:c r="A408"><x:v>2992</x:v></x:c><x:c r="B408" t="inlineStr"><x:is><x:t xml:space="preserve">CloneUrlContainsCredentials</x:t></x:is></x:c><x:c r="C408" t="inlineStr"><x:is><x:t xml:space="preserve">주소에 사용자 이름이나 토큰을 포함할 수 없습니다. Git 인증 도우미를 사용하세요.</x:t></x:is></x:c><x:c r="D408" t="inlineStr"><x:is><x:t xml:space="preserve">Remove credentials from the address and use the Git credential helper.</x:t></x:is></x:c></x:row><x:row r="409"><x:c r="A409"><x:v>2993</x:v></x:c><x:c r="B409" t="inlineStr"><x:is><x:t xml:space="preserve">CloneParentRequired</x:t></x:is></x:c><x:c r="C409" t="inlineStr"><x:is><x:t xml:space="preserve">상위 폴더를 선택하세요.</x:t></x:is></x:c><x:c r="D409" t="inlineStr"><x:is><x:t xml:space="preserve">Choose a parent folder.</x:t></x:is></x:c></x:row><x:row r="410"><x:c r="A410"><x:v>2994</x:v></x:c><x:c r="B410" t="inlineStr"><x:is><x:t xml:space="preserve">CloneParentMissing</x:t></x:is></x:c><x:c r="C410" t="inlineStr"><x:is><x:t xml:space="preserve">상위 폴더가 존재하지 않습니다.</x:t></x:is></x:c><x:c r="D410" t="inlineStr"><x:is><x:t xml:space="preserve">The parent folder does not exist.</x:t></x:is></x:c></x:row><x:row r="411"><x:c r="A411"><x:v>2995</x:v></x:c><x:c r="B411" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFolderRequired</x:t></x:is></x:c><x:c r="C411" t="inlineStr"><x:is><x:t xml:space="preserve">새 폴더 이름을 입력하세요.</x:t></x:is></x:c><x:c r="D411" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a new folder name.</x:t></x:is></x:c></x:row><x:row r="412"><x:c r="A412"><x:v>2996</x:v></x:c><x:c r="B412" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFolderInvalid</x:t></x:is></x:c><x:c r="C412" t="inlineStr"><x:is><x:t xml:space="preserve">사용할 수 없는 폴더 이름입니다.</x:t></x:is></x:c><x:c r="D412" t="inlineStr"><x:is><x:t xml:space="preserve">The folder name is invalid.</x:t></x:is></x:c></x:row><x:row r="413"><x:c r="A413"><x:v>2997</x:v></x:c><x:c r="B413" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationOccupied</x:t></x:is></x:c><x:c r="C413" t="inlineStr"><x:is><x:t xml:space="preserve">생성 위치가 이미 존재합니다: {0}</x:t></x:is></x:c><x:c r="D413" t="inlineStr"><x:is><x:t xml:space="preserve">The destination already exists: {0}</x:t></x:is></x:c></x:row><x:row r="414"><x:c r="A414"><x:v>2998</x:v></x:c><x:c r="B414" t="inlineStr"><x:is><x:t xml:space="preserve">CloneQueued</x:t></x:is></x:c><x:c r="C414" t="inlineStr"><x:is><x:t xml:space="preserve">복제 대기 중입니다.</x:t></x:is></x:c><x:c r="D414" t="inlineStr"><x:is><x:t xml:space="preserve">Waiting to clone.</x:t></x:is></x:c></x:row><x:row r="415"><x:c r="A415"><x:v>2999</x:v></x:c><x:c r="B415" t="inlineStr"><x:is><x:t xml:space="preserve">CloneProgress</x:t></x:is></x:c><x:c r="C415" t="inlineStr"><x:is><x:t xml:space="preserve">Git 진행 단계: {0}%</x:t></x:is></x:c><x:c r="D415" t="inlineStr"><x:is><x:t xml:space="preserve">Git progress step: {0}%</x:t></x:is></x:c></x:row><x:row r="416"><x:c r="A416"><x:v>3000</x:v></x:c><x:c r="B416" t="inlineStr"><x:is><x:t xml:space="preserve">CloneRunning</x:t></x:is></x:c><x:c r="C416" t="inlineStr"><x:is><x:t xml:space="preserve">저장소를 복제하는 중입니다.</x:t></x:is></x:c><x:c r="D416" t="inlineStr"><x:is><x:t xml:space="preserve">Cloning the repository.</x:t></x:is></x:c></x:row><x:row r="417"><x:c r="A417"><x:v>3001</x:v></x:c><x:c r="B417" t="inlineStr"><x:is><x:t xml:space="preserve">CloneSucceeded</x:t></x:is></x:c><x:c r="C417" t="inlineStr"><x:is><x:t xml:space="preserve">복제가 완료됐습니다.</x:t></x:is></x:c><x:c r="D417" t="inlineStr"><x:is><x:t xml:space="preserve">Clone completed.</x:t></x:is></x:c></x:row><x:row r="418"><x:c r="A418"><x:v>3002</x:v></x:c><x:c r="B418" t="inlineStr"><x:is><x:t xml:space="preserve">CloneCancelled</x:t></x:is></x:c><x:c r="C418" t="inlineStr"><x:is><x:t xml:space="preserve">복제가 취소됐습니다.</x:t></x:is></x:c><x:c r="D418" t="inlineStr"><x:is><x:t xml:space="preserve">Clone canceled.</x:t></x:is></x:c></x:row><x:row r="419"><x:c r="A419"><x:v>3003</x:v></x:c><x:c r="B419" t="inlineStr"><x:is><x:t xml:space="preserve">CloneGitFailed</x:t></x:is></x:c><x:c r="C419" t="inlineStr"><x:is><x:t xml:space="preserve">Git 복제 명령이 종료 코드 {0}으로 실패했습니다.</x:t></x:is></x:c><x:c r="D419" t="inlineStr"><x:is><x:t xml:space="preserve">Git clone failed with exit code {0}.</x:t></x:is></x:c></x:row><x:row r="420"><x:c r="A420"><x:v>3004</x:v></x:c><x:c r="B420" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationPreserved</x:t></x:is></x:c><x:c r="C420" t="inlineStr"><x:is><x:t xml:space="preserve">복제 위치가 남아 있습니다: {0}. 기존 폴더일 수도 있으므로 내용을 확인하세요.</x:t></x:is></x:c><x:c r="D420" t="inlineStr"><x:is><x:t xml:space="preserve">The destination still exists at {0}. It may have existed before cloning; review it before reuse.</x:t></x:is></x:c></x:row><x:row r="421"><x:c r="A421"><x:v>3005</x:v></x:c><x:c r="B421" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationAbsent</x:t></x:is></x:c><x:c r="C421" t="inlineStr"><x:is><x:t xml:space="preserve">복제 위치에 폴더가 없습니다.</x:t></x:is></x:c><x:c r="D421" t="inlineStr"><x:is><x:t xml:space="preserve">No destination folder exists.</x:t></x:is></x:c></x:row><x:row r="422"><x:c r="A422"><x:v>3006</x:v></x:c><x:c r="B422" t="inlineStr"><x:is><x:t xml:space="preserve">CloneOpenFailed</x:t></x:is></x:c><x:c r="C422" t="inlineStr"><x:is><x:t xml:space="preserve">복제는 완료됐지만 저장소를 열지 못했습니다: {0}</x:t></x:is></x:c><x:c r="D422" t="inlineStr"><x:is><x:t xml:space="preserve">Clone completed, but the repository could not be opened: {0}</x:t></x:is></x:c></x:row><x:row r="423"><x:c r="A423"><x:v>3007</x:v></x:c><x:c r="B423" t="inlineStr"><x:is><x:t xml:space="preserve">CloneStop</x:t></x:is></x:c><x:c r="C423" t="inlineStr"><x:is><x:t xml:space="preserve">중단</x:t></x:is></x:c><x:c r="D423" t="inlineStr"><x:is><x:t xml:space="preserve">Stop</x:t></x:is></x:c></x:row><x:row r="424"><x:c r="A424"><x:v>3008</x:v></x:c><x:c r="B424" t="inlineStr"><x:is><x:t xml:space="preserve">CloneClose</x:t></x:is></x:c><x:c r="C424" t="inlineStr"><x:is><x:t xml:space="preserve">닫기</x:t></x:is></x:c><x:c r="D424" t="inlineStr"><x:is><x:t xml:space="preserve">Close</x:t></x:is></x:c></x:row><x:row r="425"><x:c r="A425"><x:v>3009</x:v></x:c><x:c r="B425" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationLabel</x:t></x:is></x:c><x:c r="C425" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더</x:t></x:is></x:c><x:c r="D425" t="inlineStr"><x:is><x:t xml:space="preserve">Clone destination folder</x:t></x:is></x:c></x:row><x:row r="426"><x:c r="A426"><x:v>3010</x:v></x:c><x:c r="B426" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationHint</x:t></x:is></x:c><x:c r="C426" t="inlineStr"><x:is><x:t xml:space="preserve">기존 빈 폴더 또는 새 폴더의 절대 경로를 입력하세요.</x:t></x:is></x:c><x:c r="D426" t="inlineStr"><x:is><x:t xml:space="preserve">Enter an absolute path to an existing empty folder or a new folder.</x:t></x:is></x:c></x:row><x:row r="427"><x:c r="A427"><x:v>3011</x:v></x:c><x:c r="B427" t="inlineStr"><x:is><x:t xml:space="preserve">CloneBrowseDestination</x:t></x:is></x:c><x:c r="C427" t="inlineStr"><x:is><x:t xml:space="preserve">찾아보기</x:t></x:is></x:c><x:c r="D427" t="inlineStr"><x:is><x:t xml:space="preserve">Browse</x:t></x:is></x:c></x:row><x:row r="428"><x:c r="A428"><x:v>3012</x:v></x:c><x:c r="B428" t="inlineStr"><x:is><x:t xml:space="preserve">ClonePickDestinationTitle</x:t></x:is></x:c><x:c r="C428" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더 선택</x:t></x:is></x:c><x:c r="D428" t="inlineStr"><x:is><x:t xml:space="preserve">Choose a destination folder</x:t></x:is></x:c></x:row><x:row r="429"><x:c r="A429"><x:v>3013</x:v></x:c><x:c r="B429" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationRequired</x:t></x:is></x:c><x:c r="C429" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더 경로를 입력하세요.</x:t></x:is></x:c><x:c r="D429" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a destination folder path.</x:t></x:is></x:c></x:row><x:row r="430"><x:c r="A430"><x:v>3014</x:v></x:c><x:c r="B430" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationInvalid</x:t></x:is></x:c><x:c r="C430" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더 경로가 올바르지 않습니다.</x:t></x:is></x:c><x:c r="D430" t="inlineStr"><x:is><x:t xml:space="preserve">The destination folder path is invalid.</x:t></x:is></x:c></x:row><x:row r="431"><x:c r="A431"><x:v>3015</x:v></x:c><x:c r="B431" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationAbsoluteRequired</x:t></x:is></x:c><x:c r="C431" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더의 절대 경로를 입력하세요.</x:t></x:is></x:c><x:c r="D431" t="inlineStr"><x:is><x:t xml:space="preserve">Enter an absolute destination folder path.</x:t></x:is></x:c></x:row><x:row r="432"><x:c r="A432"><x:v>3016</x:v></x:c><x:c r="B432" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationRootForbidden</x:t></x:is></x:c><x:c r="C432" t="inlineStr"><x:is><x:t xml:space="preserve">드라이브 또는 파일 시스템의 루트 폴더에는 복제할 수 없습니다.</x:t></x:is></x:c><x:c r="D432" t="inlineStr"><x:is><x:t xml:space="preserve">Cannot clone into a drive or file system root.</x:t></x:is></x:c></x:row><x:row r="433"><x:c r="A433"><x:v>3017</x:v></x:c><x:c r="B433" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationParentMissing</x:t></x:is></x:c><x:c r="C433" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더의 상위 폴더가 존재하지 않습니다.</x:t></x:is></x:c><x:c r="D433" t="inlineStr"><x:is><x:t xml:space="preserve">The parent folder of the destination does not exist.</x:t></x:is></x:c></x:row><x:row r="434"><x:c r="A434"><x:v>3018</x:v></x:c><x:c r="B434" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationFileExists</x:t></x:is></x:c><x:c r="C434" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 위치에 파일이 이미 존재합니다: {0}</x:t></x:is></x:c><x:c r="D434" t="inlineStr"><x:is><x:t xml:space="preserve">A file already exists at the destination: {0}</x:t></x:is></x:c></x:row><x:row r="435"><x:c r="A435"><x:v>3019</x:v></x:c><x:c r="B435" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationNotEmpty</x:t></x:is></x:c><x:c r="C435" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더가 비어 있지 않습니다: {0}</x:t></x:is></x:c><x:c r="D435" t="inlineStr"><x:is><x:t xml:space="preserve">The destination folder is not empty: {0}</x:t></x:is></x:c></x:row><x:row r="436"><x:c r="A436"><x:v>3020</x:v></x:c><x:c r="B436" t="inlineStr"><x:is><x:t xml:space="preserve">RepositoryActionsButtonText</x:t></x:is></x:c><x:c r="C436" t="inlineStr"><x:is><x:t xml:space="preserve">+ 저장소</x:t></x:is></x:c><x:c r="D436" t="inlineStr"><x:is><x:t xml:space="preserve">+ Repository</x:t></x:is></x:c></x:row><x:row r="437"><x:c r="A437"><x:v>3021</x:v></x:c><x:c r="B437" t="inlineStr"><x:is><x:t xml:space="preserve">RepositoryActionsTooltip</x:t></x:is></x:c><x:c r="C437" t="inlineStr"><x:is><x:t xml:space="preserve">기존 저장소를 추가하거나 새 저장소를 복제합니다.</x:t></x:is></x:c><x:c r="D437" t="inlineStr"><x:is><x:t xml:space="preserve">Add an existing repository or clone a new one.</x:t></x:is></x:c></x:row><x:row r="438"><x:c r="A438"><x:v>3022</x:v></x:c><x:c r="B438" t="inlineStr"><x:is><x:t xml:space="preserve">RepositoryAddExistingAction</x:t></x:is></x:c><x:c r="C438" t="inlineStr"><x:is><x:t xml:space="preserve">저장소 열기</x:t></x:is></x:c><x:c r="D438" t="inlineStr"><x:is><x:t xml:space="preserve">Open repository</x:t></x:is></x:c></x:row><x:row r="439"><x:c r="A439"><x:v>2404</x:v></x:c><x:c r="B439" t="inlineStr"><x:is><x:t xml:space="preserve">MainOpenIn</x:t></x:is></x:c><x:c r="C439" t="inlineStr"><x:is><x:t xml:space="preserve">열기</x:t></x:is></x:c><x:c r="D439" t="inlineStr"><x:is><x:t xml:space="preserve">Open</x:t></x:is></x:c></x:row><x:row r="440"><x:c r="A440"><x:v>3023</x:v></x:c><x:c r="B440" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalMenu</x:t></x:is></x:c><x:c r="C440" t="inlineStr"><x:is><x:t xml:space="preserve">태그 삭제</x:t></x:is></x:c><x:c r="D440" t="inlineStr"><x:is><x:t xml:space="preserve">Delete tag</x:t></x:is></x:c></x:row><x:row r="441"><x:c r="A441"><x:v>3024</x:v></x:c><x:c r="B441" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteMenu</x:t></x:is></x:c><x:c r="C441" t="inlineStr"><x:is><x:t xml:space="preserve">원격 태그 삭제</x:t></x:is></x:c><x:c r="D441" t="inlineStr"><x:is><x:t xml:space="preserve">Delete remote tag</x:t></x:is></x:c></x:row><x:row r="442"><x:c r="A442"><x:v>3025</x:v></x:c><x:c r="B442" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalTitle</x:t></x:is></x:c><x:c r="C442" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 삭제</x:t></x:is></x:c><x:c r="D442" t="inlineStr"><x:is><x:t xml:space="preserve">Delete local tag</x:t></x:is></x:c></x:row><x:row r="443"><x:c r="A443"><x:v>3026</x:v></x:c><x:c r="B443" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalConfirm</x:t></x:is></x:c><x:c r="C443" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 '{0}'을 삭제합니다.
+Error: {4}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="B278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubGcmUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git Credential Manager를 사용할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git Credential Manager is unavailable.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279">
+        <x:v>1801</x:v>
+      </x:c>
+      <x:c r="B279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountListUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GCM 계정 목록을 읽지 못했습니다. 사용자명을 직접 입력하거나 로그인할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not read the GCM account list. You can enter a username or sign in.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="B280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubLoginFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 로그인이 취소됐거나 실패했습니다. GCM 로그인 창에서 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub sign-in was canceled or failed. Try again in the GCM sign-in window.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281">
+        <x:v>1803</x:v>
+      </x:c>
+      <x:c r="B281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteNameRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 이름을 선택하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select a remote name.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282">
+        <x:v>1804</x:v>
+      </x:c>
+      <x:c r="B282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteNotFound</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격을 찾을 수 없습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote not found: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283">
+        <x:v>1805</x:v>
+      </x:c>
+      <x:c r="B283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteUrlUnreadable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 URL을 읽을 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not read the remote URL.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284">
+        <x:v>1806</x:v>
+      </x:c>
+      <x:c r="B284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteMultipleUrls</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">URL이 여러 개인 원격은 계정 선택을 지원하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account selection is unavailable for remotes with multiple URLs.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285">
+        <x:v>1807</x:v>
+      </x:c>
+      <x:c r="B285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteFetchPushMismatch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">가져오기와 푸시 URL이 다른 원격은 계정 선택을 지원하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account selection is unavailable when fetch and push URLs differ.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286">
+        <x:v>1808</x:v>
+      </x:c>
+      <x:c r="B286" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteGcmHelperRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C286" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 원격의 credential.helper가 GCM manager가 아닙니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D286" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This remote does not use GCM manager as its credential.helper.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287">
+        <x:v>1809</x:v>
+      </x:c>
+      <x:c r="B287" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteDefaultAccountUnreadable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C287" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격의 기본 계정 설정을 읽지 못했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D287" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not read the default account setting for remote {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288">
+        <x:v>1810</x:v>
+      </x:c>
+      <x:c r="B288" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteLocalAccountUnreadable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C288" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격의 저장소 계정 설정을 읽지 못했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D288" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not read the repository account setting for remote {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289">
+        <x:v>1811</x:v>
+      </x:c>
+      <x:c r="B289" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteHttpsRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C289" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub HTTPS 원격이 아닙니다. SSH 원격은 SSH 키로 인증합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D289" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This is not a GitHub HTTPS remote. SSH remotes use SSH keys for authentication.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290">
+        <x:v>1812</x:v>
+      </x:c>
+      <x:c r="B290" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteHostUnsupported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C290" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">github.com HTTPS 원격만 지원합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D290" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only github.com HTTPS remotes are supported.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291">
+        <x:v>1813</x:v>
+      </x:c>
+      <x:c r="B291" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemotePortUnsupported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C291" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">표준 HTTPS 포트의 GitHub 원격만 지원합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D291" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only GitHub remotes on the standard HTTPS port are supported.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292">
+        <x:v>1814</x:v>
+      </x:c>
+      <x:c r="B292" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteUserInfoUnsupported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C292" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">사용자 정보가 포함된 원격 URL은 지원하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D292" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote URLs containing user information are unsupported.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293">
+        <x:v>1815</x:v>
+      </x:c>
+      <x:c r="B293" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteQueryUnsupported</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C293" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">쿼리 또는 프래그먼트가 있는 원격 URL은 지원하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D293" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote URLs containing a query or fragment are unsupported.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294">
+        <x:v>1816</x:v>
+      </x:c>
+      <x:c r="B294" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemotePathInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C294" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 저장소 URL 형식이 올바르지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D294" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The GitHub repository URL has an invalid format.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295">
+        <x:v>1817</x:v>
+      </x:c>
+      <x:c r="B295" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteUrlNeedsReview</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C295" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 URL 확인 필요</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D295" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Check remote URL</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296">
+        <x:v>1818</x:v>
+      </x:c>
+      <x:c r="B296" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubUserNameInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C296" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub 사용자명은 영문자·숫자·하이픈 1~39자로 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D296" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a GitHub username of 1–39 letters, digits, or hyphens.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297">
+        <x:v>1819</x:v>
+      </x:c>
+      <x:c r="B297" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubFetchUrlLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C297" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">가져오기: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D297" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fetch: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298">
+        <x:v>1820</x:v>
+      </x:c>
+      <x:c r="B298" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubPushUrlLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C298" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">푸시: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D298" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Push: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299">
+        <x:v>1821</x:v>
+      </x:c>
+      <x:c r="B299" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitSettingsHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C299" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">설정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D299" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300">
+        <x:v>1822</x:v>
+      </x:c>
+      <x:c r="B300" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitExecutableHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C300" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GIT 실행 파일</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D300" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GIT EXECUTABLE</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301">
+        <x:v>1823</x:v>
+      </x:c>
+      <x:c r="B301" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitPathHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C301" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">경로를 비워 두면 PATH에 등록된 Git을 사용합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D301" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Leave the path empty to use Git from PATH.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302">
+        <x:v>1824</x:v>
+      </x:c>
+      <x:c r="B302" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitPathPlaceholder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C302" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PATH의 git 또는 절대 경로</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D302" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">git from PATH, or an absolute path</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303">
+        <x:v>1825</x:v>
+      </x:c>
+      <x:c r="B303" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BrowseGitLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C303" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">찾아보기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D303" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Browse</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304">
+        <x:v>1826</x:v>
+      </x:c>
+      <x:c r="B304" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TestGitLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C304" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 확인</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D304" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Test Git</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305">
+        <x:v>1827</x:v>
+      </x:c>
+      <x:c r="B305" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SaveGitPathLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C305" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 경로 저장</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D305" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Save Git path</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306">
+        <x:v>1828</x:v>
+      </x:c>
+      <x:c r="B306" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommitAuthorHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C306" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">커밋 작성자</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D306" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">COMMIT AUTHOR</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307">
+        <x:v>1829</x:v>
+      </x:c>
+      <x:c r="B307" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalAuthorHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C307" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 저장소 (로컬)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D307" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This repository (local)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="B308" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SaveLocalAuthorLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C308" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 저장소에 저장</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D308" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Save for this repository</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309">
+        <x:v>1831</x:v>
+      </x:c>
+      <x:c r="B309" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GlobalAuthorHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C309" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 저장소 (전역)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D309" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All repositories (global)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310">
+        <x:v>1832</x:v>
+      </x:c>
+      <x:c r="B310" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SaveGlobalAuthorLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C310" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">전역 설정에 저장</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D310" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Save globally</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="B311" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountsHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C311" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">계정 및 인증</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D311" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ACCOUNTS AND AUTHENTICATION</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312">
+        <x:v>1834</x:v>
+      </x:c>
+      <x:c r="B312" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountsDescription</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C312" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough는 HTTPS 인증에 Git 자격 증명 도우미를, SSH 인증에 기존 SSH 설정을 사용합니다. 비밀번호와 토큰은 여기에 저장하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D312" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough uses Git credential helpers for HTTPS and your existing SSH setup. Passwords and tokens are not stored here.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313">
+        <x:v>1835</x:v>
+      </x:c>
+      <x:c r="B313" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountsPurpose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C313" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fetch / Pull / Push 인증에만 적용됩니다. 위의 커밋 작성자와 아바타 설정은 별개입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D313" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fetch / Pull / Push authentication only. Commit author and avatar settings above are separate.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="B314" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAccountsQueueHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C314" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">현재 원격 작업이 끝난 뒤 계정을 선택합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D314" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Account selection waits until the current remote operation completes.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315">
+        <x:v>1837</x:v>
+      </x:c>
+      <x:c r="B315" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubExistingAccountPlaceholder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C315" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기존 GCM 계정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D315" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Existing GCM account</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="B316" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubRemoteUserNameAutomationName</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C316" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 원격의 GitHub 사용자명</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D316" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHub username for this remote</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317">
+        <x:v>1839</x:v>
+      </x:c>
+      <x:c r="B317" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubSelectAccountLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C317" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 원격에 사용</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D317" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use for this remote</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318">
+        <x:v>1840</x:v>
+      </x:c>
+      <x:c r="B318" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GitHubAddAccountLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C318" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">다른 GitHub 계정 추가…</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D318" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add another GitHub account…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319">
+        <x:v>1841</x:v>
+      </x:c>
+      <x:c r="B319" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CredentialHelperHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C319" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">자격 증명 도우미</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D319" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Credential helper</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320">
+        <x:v>1842</x:v>
+      </x:c>
+      <x:c r="B320" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemoteUrlsHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C320" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 URL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D320" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote URLs</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321">
+        <x:v>1843</x:v>
+      </x:c>
+      <x:c r="B321" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SettingsTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C321" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">설정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D321" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="B322" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteLocalBranch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C322" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 브랜치 삭제...</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D322" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete local branch...</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323">
+        <x:v>2907</x:v>
+      </x:c>
+      <x:c r="B323" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteRemoteBranch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C323" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 브랜치 삭제...</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D323" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete remote branch...</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="324">
+      <x:c r="A324">
+        <x:v>2908</x:v>
+      </x:c>
+      <x:c r="B324" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteLocalBranchTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C324" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 브랜치 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D324" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete local branch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325">
+        <x:v>2909</x:v>
+      </x:c>
+      <x:c r="B325" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteRemoteBranchTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C325" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 브랜치 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D325" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete remote branch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326">
+        <x:v>2910</x:v>
+      </x:c>
+      <x:c r="B326" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteLocalBranchConfirm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C326" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 브랜치를 삭제하시겠습니까? 병합되지 않은 커밋이 있으면 삭제하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D326" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete local branch {0}? Git will keep it if it contains unmerged commits.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327">
+        <x:v>2911</x:v>
+      </x:c>
+      <x:c r="B327" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteRemoteBranchConfirm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C327" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 브랜치 {0}을(를) 서버에서 삭제하시겠습니까? 다른 사용자에게도 영향을 주며 앱에서 되돌릴 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D327" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete remote branch {0} from the server? This affects other users and cannot be undone from the app.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328">
+        <x:v>2912</x:v>
+      </x:c>
+      <x:c r="B328" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeleteBranchAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C328" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">브랜치 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D328" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete branch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329">
+        <x:v>2913</x:v>
+      </x:c>
+      <x:c r="B329" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceDeletingBranch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C329" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 브랜치 삭제 중...</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D329" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deleting branch {0}...</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330">
+        <x:v>2914</x:v>
+      </x:c>
+      <x:c r="B330" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C330" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 로컬 브랜치를 삭제했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D330" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deleted local branch {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331">
+        <x:v>2915</x:v>
+      </x:c>
+      <x:c r="B331" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C331" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격 브랜치를 삭제했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D331" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deleted remote branch {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332">
+        <x:v>2916</x:v>
+      </x:c>
+      <x:c r="B332" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceBranchDeleteRefreshFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C332" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 참조 목록 새로고침 실패: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D332" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} Could not refresh references: {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333">
+        <x:v>2917</x:v>
+      </x:c>
+      <x:c r="B333" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleteCurrent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C333" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">현재 체크아웃된 {0} 브랜치는 삭제할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D333" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cannot delete the checked-out branch {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334">
+        <x:v>2918</x:v>
+      </x:c>
+      <x:c r="B334" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleteMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C334" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 로컬 브랜치를 찾을 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D334" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Local branch {0} no longer exists.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335">
+        <x:v>2919</x:v>
+      </x:c>
+      <x:c r="B335" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleteChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C335" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 브랜치가 확인 이후 변경되었습니다. 새로고친 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D335" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch {0} changed after confirmation. Refresh and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="B336" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleteFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C336" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 로컬 브랜치를 삭제하지 못했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D336" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete local branch {0}: {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337">
+        <x:v>2921</x:v>
+      </x:c>
+      <x:c r="B337" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceLocalBranchDeleteFailedWithoutOutput</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C337" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 로컬 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D337" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete local branch {0} (exit code {1}).</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338">
+        <x:v>2922</x:v>
+      </x:c>
+      <x:c r="B338" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleteDefault</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C338" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0}은(는) 원격의 기본 브랜치라 삭제할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D338" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cannot delete {0} because it is the remote's default branch.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339">
+        <x:v>2923</x:v>
+      </x:c>
+      <x:c r="B339" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleteMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C339" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격 브랜치를 찾을 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D339" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote branch {0} no longer exists.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340">
+        <x:v>2924</x:v>
+      </x:c>
+      <x:c r="B340" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleteChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C340" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격 브랜치가 확인 이후 변경되었습니다. Fetch한 뒤 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D340" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote branch {0} changed after confirmation. Fetch and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341">
+        <x:v>2925</x:v>
+      </x:c>
+      <x:c r="B341" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleteFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C341" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격 브랜치를 삭제하지 못했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D341" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete remote branch {0}: {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342">
+        <x:v>2926</x:v>
+      </x:c>
+      <x:c r="B342" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRemoteBranchDeleteFailedWithoutOutput</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C342" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 원격 브랜치를 삭제하지 못했습니다(종료 코드 {1}).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D342" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete remote branch {0} (exit code {1}).</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" t="n">
+        <x:v>2927</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>ConflictBatchCurrentFileLabel</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>이 파일의 미해결 구간 {0}개</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>{0} unresolved sections in this file</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344">
+        <x:v>2928</x:v>
+      </x:c>
+      <x:c r="B344" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictBatchTooltip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C344" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이미 선택한 구간은 유지합니다. 최종 파일 미리보기만 바뀌며 저장·스테이징은 별도로 해야 합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D344" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Previous choices stay unchanged. This updates only the final-file preview; save and stage separately.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345">
+        <x:v>2929</x:v>
+      </x:c>
+      <x:c r="B345" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictBatchReplaceEditsTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C345" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">직접 편집한 내용 바꾸기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D345" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Replace manual edits</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346">
+        <x:v>2930</x:v>
+      </x:c>
+      <x:c r="B346" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConflictBatchReplaceEditsMessage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C346" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">최종 파일을 직접 편집했습니다. 남은 구간에 일괄 선택을 적용하면 직접 편집한 내용이 사라집니다. 계속할까요?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D346" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">You edited the final file. Applying one choice to the remaining sections will replace those manual edits. Continue?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" t="n">
+        <x:v>2931</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>ConflictBatchApplyButton</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>남은 구간 일괄 선택</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>Choose remaining sections</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348">
+        <x:v>2932</x:v>
+      </x:c>
+      <x:c r="B348" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseTargetChange</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C348" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 대상 · 적용된 커밋</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D348" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebase target · applied commits</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349">
+        <x:v>2933</x:v>
+      </x:c>
+      <x:c r="B349" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseReplayChange</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C349" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">다시 적용 중인 내 커밋</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D349" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">My commit being replayed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350">
+        <x:v>2934</x:v>
+      </x:c>
+      <x:c r="B350" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseUseTarget</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C350" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 대상 사용</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D350" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use rebase target</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351">
+        <x:v>2935</x:v>
+      </x:c>
+      <x:c r="B351" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseUseReplay</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C351" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">내 커밋 사용</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D351" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use my commit</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352">
+        <x:v>2936</x:v>
+      </x:c>
+      <x:c r="B352" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseTargetSource</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C352" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 대상 HEAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D352" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebase target HEAD</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353">
+        <x:v>2937</x:v>
+      </x:c>
+      <x:c r="B353" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseReplaySource</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C353" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">내 커밋 REBASE_HEAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D353" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">My commit REBASE_HEAD</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354">
+        <x:v>2938</x:v>
+      </x:c>
+      <x:c r="B354" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseBothOrderTip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C354" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">둘 다 사용하면 리베이스 대상 내용을 먼저, 다시 적용 중인 내 커밋 내용을 뒤에 둡니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D354" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use both places the rebase target content first, followed by my replayed commit.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355">
+        <x:v>2939</x:v>
+      </x:c>
+      <x:c r="B355" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseProgressLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C355" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 진행 중</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D355" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebase in progress</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356">
+        <x:v>2940</x:v>
+      </x:c>
+      <x:c r="B356" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseResolveBeforeContinue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C356" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">남은 충돌 {0}건을 해결·스테이징하면 계속할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D356" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Resolve and stage {0} remaining conflicts to continue.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357">
+        <x:v>2941</x:v>
+      </x:c>
+      <x:c r="B357" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseReadyToContinue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C357" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 충돌을 스테이징했습니다. 계속을 눌러 리베이스를 진행하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D357" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All conflicts are staged. Select Continue rebase to proceed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358">
+        <x:v>2942</x:v>
+      </x:c>
+      <x:c r="B358" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseContinueAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C358" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 계속</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D358" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Continue rebase</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359">
+        <x:v>2943</x:v>
+      </x:c>
+      <x:c r="B359" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseNoLongerInProgress</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C359" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스가 더 이상 진행 중이지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D359" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The rebase is no longer in progress.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360">
+        <x:v>2944</x:v>
+      </x:c>
+      <x:c r="B360" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseUnresolvedConflicts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C360" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미해결 충돌 {0}건이 있어 리베이스를 계속할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D360" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cannot continue the rebase while {0} conflicts remain unresolved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361">
+        <x:v>2945</x:v>
+      </x:c>
+      <x:c r="B361" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseContinueFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C361" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스 계속에 실패했습니다(종료 코드 {0}). {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D361" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not continue the rebase (exit code {0}). {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362">
+        <x:v>2946</x:v>
+      </x:c>
+      <x:c r="B362" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseNextConflicts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C362" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스에서 새 충돌 {0}건이 발생했습니다. 해결·스테이징한 뒤 계속하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D362" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The rebase has {0} new conflicts. Resolve and stage them, then continue.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363">
+        <x:v>2947</x:v>
+      </x:c>
+      <x:c r="B363" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseContinueCompleted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C363" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스를 완료했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D363" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebase completed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364">
+        <x:v>2948</x:v>
+      </x:c>
+      <x:c r="B364" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseContinueStillInProgress</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C364" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스가 아직 진행 중입니다. Git 상태를 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D364" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The rebase is still in progress. Check the Git state.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365">
+        <x:v>2949</x:v>
+      </x:c>
+      <x:c r="B365" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseRepositoryChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C365" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소 루트가 바뀌어 리베이스를 계속하지 않았습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D365" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The repository root changed, so the rebase was not continued: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366">
+        <x:v>2950</x:v>
+      </x:c>
+      <x:c r="B366" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RebaseCheckingConflicts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C366" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">충돌 상태를 확인하는 중입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D366" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Checking the conflict state.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367">
+        <x:v>2951</x:v>
+      </x:c>
+      <x:c r="B367" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DefaultPullStrategyHeading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C367" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough 기본 Pull 방식</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D367" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough default Pull strategy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368">
+        <x:v>2952</x:v>
+      </x:c>
+      <x:c r="B368" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DefaultPullStrategyDescription</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C368" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 저장소에서 Bough의 기본 Pull 동작에 적용됩니다. Git CLI의 pull.rebase 및 pull.ff 설정은 변경하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D368" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Applies to Bough's default Pull action for every repository. Git CLI pull.rebase and pull.ff settings are not changed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369">
+        <x:v>2953</x:v>
+      </x:c>
+      <x:c r="B369" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PullStrategyFastForwardOnly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C369" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">빠른 전진만</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D369" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fast-forward only</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370">
+        <x:v>2954</x:v>
+      </x:c>
+      <x:c r="B370" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PullStrategyMerge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C370" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">병합</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D370" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Merge</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371">
+        <x:v>2955</x:v>
+      </x:c>
+      <x:c r="B371" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PullStrategyRebase</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C371" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">리베이스</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D371" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebase</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372">
+        <x:v>2956</x:v>
+      </x:c>
+      <x:c r="B372" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DefaultPullStrategySaved</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C372" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough 기본 Pull 방식 저장: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D372" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bough default Pull strategy saved: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373">
+        <x:v>2957</x:v>
+      </x:c>
+      <x:c r="B373" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullConfiguredDefaultTip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C373" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기본 Pull: {0}. upstream이 없으면 받을 원격 브랜치를 선택합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D373" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Default Pull: {0}. Choose a remote branch if there is no upstream.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374">
+        <x:v>2958</x:v>
+      </x:c>
+      <x:c r="B374" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullConfiguredDefaultAutomation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C374" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull (기본 방식: {0})</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D374" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull (default: {0})</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375">
+        <x:v>2959</x:v>
+      </x:c>
+      <x:c r="B375" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullStrategyMenuTip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C375" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이번 Pull에 사용할 방식 또는 받을 브랜치를 선택합니다. 기본 방식: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D375" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose a strategy or source branch for this Pull. Default: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376">
+        <x:v>2960</x:v>
+      </x:c>
+      <x:c r="B376" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullChooseBranchDefaultTip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C376" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">받을 원격 브랜치를 고른 뒤 기본 방식({0})으로 Pull을 실행합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D376" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose a remote branch, then Pull with the default strategy ({0}).</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377">
+        <x:v>2961</x:v>
+      </x:c>
+      <x:c r="B377" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullFastForwardAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C377" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">빠른 전진만으로 받기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D377" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull fast-forward only</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378">
+        <x:v>2962</x:v>
+      </x:c>
+      <x:c r="B378" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullDefaultSuffix</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C378" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"> (기본)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D378" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"> (default)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379">
+        <x:v>2963</x:v>
+      </x:c>
+      <x:c r="B379" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullStrategyMenuAutomation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C379" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull 방식 메뉴 (기본: {0})</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D379" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull strategy menu (default: {0})</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380">
+        <x:v>2964</x:v>
+      </x:c>
+      <x:c r="B380" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RemotePullFastForwardTip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C380" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">현재 upstream에서 빠른 전진만으로 한 번 Pull합니다. upstream이 없으면 받을 원격 브랜치를 선택합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D380" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pull once from the current upstream using fast-forward only. If there is no upstream, choose a remote branch.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381">
+        <x:v>2965</x:v>
+      </x:c>
+      <x:c r="B381" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardTrackedSelectionCount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C381" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 추적 파일 {0}개의 변경 버리기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D381" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes in {0} selected tracked files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382">
+        <x:v>2966</x:v>
+      </x:c>
+      <x:c r="B382" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DeleteUntrackedSelectionCount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C382" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 미추적 파일 {0}개 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D382" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete {0} selected untracked files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383">
+        <x:v>2967</x:v>
+      </x:c>
+      <x:c r="B383" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardMixedSelectionCount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C383" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경 버리기 {0}개 · 미추적 파일 삭제 {1}개</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D383" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes in {0} tracked files · delete {1} untracked files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384">
+        <x:v>2968</x:v>
+      </x:c>
+      <x:c r="B384" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardTrackedTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C384" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">추적 파일 변경 버리기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D384" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard tracked file changes</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385">
+        <x:v>2969</x:v>
+      </x:c>
+      <x:c r="B385" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DeleteUntrackedTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C385" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미추적 파일 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D385" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete untracked files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386">
+        <x:v>2970</x:v>
+      </x:c>
+      <x:c r="B386" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardMixedTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C386" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경 버리기 및 미추적 파일 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D386" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes and delete untracked files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387">
+        <x:v>2971</x:v>
+      </x:c>
+      <x:c r="B387" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DeleteUntrackedImpact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C387" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미추적 파일 {0}개를 디스크에서 영구 삭제합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D387" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Permanently delete {0} untracked files from disk.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388">
+        <x:v>2972</x:v>
+      </x:c>
+      <x:c r="B388" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardConfirmMixed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C388" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경 버리기 및 파일 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D388" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes and delete files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="n">
+        <x:v>2973</x:v>
+      </x:c>
+      <x:c r="B389" t="str">
+        <x:v>StopTrackingSelectionCount</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>선택한 추적 파일 {0}개 추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>Stop tracking and ignore {0} selected files</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="n">
+        <x:v>2974</x:v>
+      </x:c>
+      <x:c r="B390" t="str">
+        <x:v>StopTrackingTitle</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>파일 추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>Stop tracking and ignore files</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="n">
+        <x:v>2975</x:v>
+      </x:c>
+      <x:c r="B391" t="str">
+        <x:v>StopTrackingDescription</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>선택한 추적 파일 {0}개의 경로를 저장소 루트의 .gitignore에 추가하고 Git 인덱스에서 제거합니다. 작업 파일은 남겨두며 삭제가 스테이징됩니다. .gitignore 변경은 자동으로 스테이징하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>Add the paths of {0} selected tracked files to the repository root .gitignore and remove them from the Git index. Working files are kept, and their deletion is staged. The .gitignore change is not staged automatically.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="n">
+        <x:v>2976</x:v>
+      </x:c>
+      <x:c r="B392" t="str">
+        <x:v>StopTrackingConfirm</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>추적 중지 및 무시</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>Stop tracking and ignore</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393">
+        <x:v>2977</x:v>
+      </x:c>
+      <x:c r="B393" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LocalStopTrackingRequiresConfirmation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C393" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">추적 중지를 확인할 창을 열 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D393" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The stop-tracking confirmation window is unavailable.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394">
+        <x:v>2978</x:v>
+      </x:c>
+      <x:c r="B394" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardTrackedContextMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C394" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경 버리기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D394" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395">
+        <x:v>2979</x:v>
+      </x:c>
+      <x:c r="B395" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DeleteUntrackedContextMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C395" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">파일 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D395" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396">
+        <x:v>2980</x:v>
+      </x:c>
+      <x:c r="B396" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DiscardMixedContextMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C396" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">변경 버리기 및 파일 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D396" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Discard changes and delete files</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" t="n">
+        <x:v>2981</x:v>
+      </x:c>
+      <x:c r="B397" t="str">
+        <x:v>StopTrackingContextMenu</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>추적 중지 및 무시…</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>Stop tracking and ignore…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398">
+        <x:v>2982</x:v>
+      </x:c>
+      <x:c r="B398" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C398" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D398" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399">
+        <x:v>2983</x:v>
+      </x:c>
+      <x:c r="B399" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C399" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소 복제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D399" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone repository</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400">
+        <x:v>2984</x:v>
+      </x:c>
+      <x:c r="B400" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneUrlLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C400" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 URL 또는 로컬 경로</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D400" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote URL or local path</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401">
+        <x:v>2985</x:v>
+      </x:c>
+      <x:c r="B401" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneParentLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C401" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장할 상위 폴더</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D401" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Parent folder</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402">
+        <x:v>2986</x:v>
+      </x:c>
+      <x:c r="B402" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFolderLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C402" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 폴더 이름</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D402" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">New folder name</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403">
+        <x:v>2987</x:v>
+      </x:c>
+      <x:c r="B403" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneBrowseParent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C403" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">찾아보기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D403" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Browse</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404">
+        <x:v>2988</x:v>
+      </x:c>
+      <x:c r="B404" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ClonePickParentTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C404" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 위치 선택</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D404" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose clone location</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405">
+        <x:v>2989</x:v>
+      </x:c>
+      <x:c r="B405" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationPreview</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C405" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 위치: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D405" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Destination: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406">
+        <x:v>2990</x:v>
+      </x:c>
+      <x:c r="B406" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneUrlRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C406" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 주소를 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D406" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a remote address.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407">
+        <x:v>2991</x:v>
+      </x:c>
+      <x:c r="B407" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneUrlInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C407" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">지원하지 않는 원격 주소입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D407" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The remote address is not supported.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="408">
+      <x:c r="A408">
+        <x:v>2992</x:v>
+      </x:c>
+      <x:c r="B408" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneUrlContainsCredentials</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C408" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">주소에 사용자 이름이나 토큰을 포함할 수 없습니다. Git 인증 도우미를 사용하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D408" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remove credentials from the address and use the Git credential helper.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="409">
+      <x:c r="A409">
+        <x:v>2993</x:v>
+      </x:c>
+      <x:c r="B409" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneParentRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C409" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">상위 폴더를 선택하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D409" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose a parent folder.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="410">
+      <x:c r="A410">
+        <x:v>2994</x:v>
+      </x:c>
+      <x:c r="B410" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneParentMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C410" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">상위 폴더가 존재하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D410" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The parent folder does not exist.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="411">
+      <x:c r="A411">
+        <x:v>2995</x:v>
+      </x:c>
+      <x:c r="B411" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFolderRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C411" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 폴더 이름을 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D411" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a new folder name.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="412">
+      <x:c r="A412">
+        <x:v>2996</x:v>
+      </x:c>
+      <x:c r="B412" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFolderInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C412" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">사용할 수 없는 폴더 이름입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D412" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The folder name is invalid.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="413">
+      <x:c r="A413">
+        <x:v>2997</x:v>
+      </x:c>
+      <x:c r="B413" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationOccupied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C413" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 위치가 이미 존재합니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D413" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination already exists: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="414">
+      <x:c r="A414">
+        <x:v>2998</x:v>
+      </x:c>
+      <x:c r="B414" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneQueued</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C414" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 대기 중입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D414" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting to clone.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="415">
+      <x:c r="A415">
+        <x:v>2999</x:v>
+      </x:c>
+      <x:c r="B415" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneProgress</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C415" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 진행 단계: {0}%</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D415" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git progress step: {0}%</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="416">
+      <x:c r="A416">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="B416" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneRunning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C416" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소를 복제하는 중입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D416" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cloning the repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="417">
+      <x:c r="A417">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="B417" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneSucceeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C417" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제가 완료됐습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D417" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone completed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="418">
+      <x:c r="A418">
+        <x:v>3002</x:v>
+      </x:c>
+      <x:c r="B418" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneCancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C418" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제가 취소됐습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D418" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone canceled.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="419">
+      <x:c r="A419">
+        <x:v>3003</x:v>
+      </x:c>
+      <x:c r="B419" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneGitFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C419" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 복제 명령이 종료 코드 {0}으로 실패했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D419" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git clone failed with exit code {0}.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="420">
+      <x:c r="A420">
+        <x:v>3004</x:v>
+      </x:c>
+      <x:c r="B420" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationPreserved</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C420" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 위치가 남아 있습니다: {0}. 기존 폴더일 수도 있으므로 내용을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D420" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination still exists at {0}. It may have existed before cloning; review it before reuse.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="421">
+      <x:c r="A421">
+        <x:v>3005</x:v>
+      </x:c>
+      <x:c r="B421" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationAbsent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C421" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 위치에 폴더가 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D421" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No destination folder exists.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="422">
+      <x:c r="A422">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="B422" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneOpenFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C422" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제는 완료됐지만 저장소를 열지 못했습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D422" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone completed, but the repository could not be opened: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="423">
+      <x:c r="A423">
+        <x:v>3007</x:v>
+      </x:c>
+      <x:c r="B423" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneStop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C423" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">중단</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D423" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stop</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="424">
+      <x:c r="A424">
+        <x:v>3008</x:v>
+      </x:c>
+      <x:c r="B424" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneClose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C424" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">닫기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D424" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Close</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="425">
+      <x:c r="A425">
+        <x:v>3009</x:v>
+      </x:c>
+      <x:c r="B425" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationLabel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C425" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D425" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone destination folder</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426">
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="B426" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C426" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기존 빈 폴더 또는 새 폴더의 절대 경로를 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D426" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter an absolute path to an existing empty folder or a new folder.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427">
+        <x:v>3011</x:v>
+      </x:c>
+      <x:c r="B427" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneBrowseDestination</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C427" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">찾아보기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D427" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Browse</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428">
+        <x:v>3012</x:v>
+      </x:c>
+      <x:c r="B428" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ClonePickDestinationTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C428" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더 선택</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D428" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose a destination folder</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429">
+        <x:v>3013</x:v>
+      </x:c>
+      <x:c r="B429" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C429" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더 경로를 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D429" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a destination folder path.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430">
+        <x:v>3014</x:v>
+      </x:c>
+      <x:c r="B430" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C430" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더 경로가 올바르지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D430" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination folder path is invalid.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431">
+        <x:v>3015</x:v>
+      </x:c>
+      <x:c r="B431" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationAbsoluteRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C431" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더의 절대 경로를 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D431" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter an absolute destination folder path.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432">
+        <x:v>3016</x:v>
+      </x:c>
+      <x:c r="B432" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationRootForbidden</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C432" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">드라이브 또는 파일 시스템의 루트 폴더에는 복제할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D432" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cannot clone into a drive or file system root.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433">
+        <x:v>3017</x:v>
+      </x:c>
+      <x:c r="B433" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationParentMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C433" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더의 상위 폴더가 존재하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D433" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The parent folder of the destination does not exist.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434">
+        <x:v>3018</x:v>
+      </x:c>
+      <x:c r="B434" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationFileExists</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C434" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 위치에 파일이 이미 존재합니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D434" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">A file already exists at the destination: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435">
+        <x:v>3019</x:v>
+      </x:c>
+      <x:c r="B435" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationNotEmpty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C435" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더가 비어 있지 않습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D435" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination folder is not empty: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436">
+        <x:v>3020</x:v>
+      </x:c>
+      <x:c r="B436" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RepositoryActionsButtonText</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C436" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">+ 저장소</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D436" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">+ Repository</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437">
+        <x:v>3021</x:v>
+      </x:c>
+      <x:c r="B437" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RepositoryActionsTooltip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C437" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기존 저장소를 추가하거나 새 저장소를 복제합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D437" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add an existing repository or clone a new one.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="438">
+      <x:c r="A438">
+        <x:v>3022</x:v>
+      </x:c>
+      <x:c r="B438" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RepositoryAddExistingAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C438" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소 열기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D438" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Open repository</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="B439" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MainOpenIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C439" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">열기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D439" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Open</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440">
+        <x:v>3023</x:v>
+      </x:c>
+      <x:c r="B440" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C440" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D440" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441">
+        <x:v>3024</x:v>
+      </x:c>
+      <x:c r="B441" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C441" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 태그 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D441" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete remote tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442">
+        <x:v>3025</x:v>
+      </x:c>
+      <x:c r="B442" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C442" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D442" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete local tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443">
+        <x:v>3026</x:v>
+      </x:c>
+      <x:c r="B443" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalConfirm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C443" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 '{0}'을 삭제합니다.
 태그 객체: {1}
-
-로컬 태그 참조만 삭제합니다. 원격 태그, 같은 이름의 브랜치, 작업 파일과 커밋은 유지됩니다.</x:t></x:is></x:c><x:c r="D443" t="inlineStr"><x:is><x:t xml:space="preserve">Delete local tag '{0}'.
+로컬 태그 참조만 삭제합니다. 원격 태그, 같은 이름의 브랜치, 작업 파일과 커밋은 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D443" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete local tag '{0}'.
 Tag object: {1}
-
-Only the local tag reference is deleted. Remote tags, branches with the same name, working files and commits are preserved.</x:t></x:is></x:c></x:row><x:row r="444"><x:c r="A444"><x:v>3027</x:v></x:c><x:c r="B444" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteTitle</x:t></x:is></x:c><x:c r="C444" t="inlineStr"><x:is><x:t xml:space="preserve">원격 태그 삭제</x:t></x:is></x:c><x:c r="D444" t="inlineStr"><x:is><x:t xml:space="preserve">Delete remote tag</x:t></x:is></x:c></x:row><x:row r="445"><x:c r="A445"><x:v>3028</x:v></x:c><x:c r="B445" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteConfirm</x:t></x:is></x:c><x:c r="C445" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제합니다.
+Only the local tag reference is deleted. Remote tags, branches with the same name, working files and commits are preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444">
+        <x:v>3027</x:v>
+      </x:c>
+      <x:c r="B444" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C444" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 태그 삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D444" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete remote tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445">
+        <x:v>3028</x:v>
+      </x:c>
+      <x:c r="B445" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteConfirm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C445" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제합니다.
 태그 객체: {2}
-
-서버의 태그를 삭제하며 다른 사용자에게 영향을 줍니다. 로컬 태그와 같은 이름의 브랜치는 유지됩니다.</x:t></x:is></x:c><x:c r="D445" t="inlineStr"><x:is><x:t xml:space="preserve">Delete tag '{1}' from remote '{0}'.
+서버의 태그를 삭제하며 다른 사용자에게 영향을 줍니다. 로컬 태그와 같은 이름의 브랜치는 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D445" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete tag '{1}' from remote '{0}'.
 Tag object: {2}
-
-This deletes the tag on the server and affects other users. The local tag and branches with the same name are preserved.</x:t></x:is></x:c></x:row><x:row r="446"><x:c r="A446"><x:v>3029</x:v></x:c><x:c r="B446" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteAction</x:t></x:is></x:c><x:c r="C446" t="inlineStr"><x:is><x:t xml:space="preserve">삭제</x:t></x:is></x:c><x:c r="D446" t="inlineStr"><x:is><x:t xml:space="preserve">Delete</x:t></x:is></x:c></x:row><x:row r="447"><x:c r="A447"><x:v>3030</x:v></x:c><x:c r="B447" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteSelectRemoteTitle</x:t></x:is></x:c><x:c r="C447" t="inlineStr"><x:is><x:t xml:space="preserve">태그를 삭제할 원격 선택</x:t></x:is></x:c><x:c r="D447" t="inlineStr"><x:is><x:t xml:space="preserve">Select remote for tag deletion</x:t></x:is></x:c></x:row><x:row r="448"><x:c r="A448"><x:v>3031</x:v></x:c><x:c r="B448" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemotePrompt</x:t></x:is></x:c><x:c r="C448" t="inlineStr"><x:is><x:t xml:space="preserve">태그 '{0}'을 조회할 등록된 원격을 선택하세요. 다음 확인 창에서 서버 삭제 대상을 확인합니다.</x:t></x:is></x:c><x:c r="D448" t="inlineStr"><x:is><x:t xml:space="preserve">Select a registered remote to inspect tag '{0}'. Confirm the server deletion target in the next dialog.</x:t></x:is></x:c></x:row><x:row r="449"><x:c r="A449"><x:v>3032</x:v></x:c><x:c r="B449" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteInspectRemoteAction</x:t></x:is></x:c><x:c r="C449" t="inlineStr"><x:is><x:t xml:space="preserve">대상 확인</x:t></x:is></x:c><x:c r="D449" t="inlineStr"><x:is><x:t xml:space="preserve">Inspect target</x:t></x:is></x:c></x:row><x:row r="450"><x:c r="A450"><x:v>3033</x:v></x:c><x:c r="B450" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalSucceeded</x:t></x:is></x:c><x:c r="C450" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 '{0}'을 삭제했습니다.</x:t></x:is></x:c><x:c r="D450" t="inlineStr"><x:is><x:t xml:space="preserve">Deleted local tag '{0}'.</x:t></x:is></x:c></x:row><x:row r="451"><x:c r="A451"><x:v>3034</x:v></x:c><x:c r="B451" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteSucceeded</x:t></x:is></x:c><x:c r="C451" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제했습니다. 로컬 태그는 유지했습니다.</x:t></x:is></x:c><x:c r="D451" t="inlineStr"><x:is><x:t xml:space="preserve">Deleted tag '{1}' from remote '{0}'. The local tag was preserved.</x:t></x:is></x:c></x:row><x:row r="452"><x:c r="A452"><x:v>3035</x:v></x:c><x:c r="B452" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRefreshFailed</x:t></x:is></x:c><x:c r="C452" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 참조 갱신에 실패했습니다: {1}</x:t></x:is></x:c><x:c r="D452" t="inlineStr"><x:is><x:t xml:space="preserve">{0} Reference refresh failed: {1}</x:t></x:is></x:c></x:row><x:row r="453"><x:c r="A453"><x:v>3036</x:v></x:c><x:c r="B453" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteInvalidName</x:t></x:is></x:c><x:c r="C453" t="inlineStr"><x:is><x:t xml:space="preserve">삭제할 태그 이름이 유효하지 않습니다: {0}</x:t></x:is></x:c><x:c r="D453" t="inlineStr"><x:is><x:t xml:space="preserve">The tag name is not valid for deletion: {0}</x:t></x:is></x:c></x:row><x:row r="454"><x:c r="A454"><x:v>3037</x:v></x:c><x:c r="B454" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteInvalidObjectId</x:t></x:is></x:c><x:c r="C454" t="inlineStr"><x:is><x:t xml:space="preserve">태그 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 참조 목록을 새로 고친 뒤 다시 확인하세요.</x:t></x:is></x:c><x:c r="D454" t="inlineStr"><x:is><x:t xml:space="preserve">The confirmed object OID for tag '{0}' is invalid. Refresh references and confirm again.</x:t></x:is></x:c></x:row><x:row r="455"><x:c r="A455"><x:v>3038</x:v></x:c><x:c r="B455" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalMissing</x:t></x:is></x:c><x:c r="C455" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 '{0}'이 더 이상 존재하지 않습니다.</x:t></x:is></x:c><x:c r="D455" t="inlineStr"><x:is><x:t xml:space="preserve">Local tag '{0}' no longer exists.</x:t></x:is></x:c></x:row><x:row r="456"><x:c r="A456"><x:v>3039</x:v></x:c><x:c r="B456" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalChanged</x:t></x:is></x:c><x:c r="C456" t="inlineStr"><x:is><x:t xml:space="preserve">확인 이후 로컬 태그 '{0}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</x:t></x:is></x:c><x:c r="D456" t="inlineStr"><x:is><x:t xml:space="preserve">Local tag '{0}' changed after confirmation and was not deleted. Confirm again.</x:t></x:is></x:c></x:row><x:row r="457"><x:c r="A457"><x:v>3040</x:v></x:c><x:c r="B457" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteLocalFailed</x:t></x:is></x:c><x:c r="C457" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 '{0}'을 삭제하지 못했습니다: {1}</x:t></x:is></x:c><x:c r="D457" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete local tag '{0}': {1}</x:t></x:is></x:c></x:row><x:row r="458"><x:c r="A458"><x:v>3041</x:v></x:c><x:c r="B458" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteRequired</x:t></x:is></x:c><x:c r="C458" t="inlineStr"><x:is><x:t xml:space="preserve">원격 태그를 삭제하려면 등록된 원격이 필요합니다.</x:t></x:is></x:c><x:c r="D458" t="inlineStr"><x:is><x:t xml:space="preserve">A registered remote is required to delete a remote tag.</x:t></x:is></x:c></x:row><x:row r="459"><x:c r="A459"><x:v>3042</x:v></x:c><x:c r="B459" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteUnavailable</x:t></x:is></x:c><x:c r="C459" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 Push 주소를 확인할 수 없습니다.</x:t></x:is></x:c><x:c r="D459" t="inlineStr"><x:is><x:t xml:space="preserve">Could not resolve the push URL for remote '{0}'.</x:t></x:is></x:c></x:row><x:row r="460"><x:c r="A460"><x:v>3043</x:v></x:c><x:c r="B460" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteMultiplePushUrls</x:t></x:is></x:c><x:c r="C460" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'에 Push 주소가 여러 개라 태그 삭제를 지원하지 않습니다.</x:t></x:is></x:c><x:c r="D460" t="inlineStr"><x:is><x:t xml:space="preserve">Tag deletion is not supported for remote '{0}' because it has multiple push URLs.</x:t></x:is></x:c></x:row><x:row r="461"><x:c r="A461"><x:v>3044</x:v></x:c><x:c r="B461" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteTagMissing</x:t></x:is></x:c><x:c r="C461" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'에 태그 '{1}'이 없습니다.</x:t></x:is></x:c><x:c r="D461" t="inlineStr"><x:is><x:t xml:space="preserve">Remote '{0}' has no tag '{1}'.</x:t></x:is></x:c></x:row><x:row r="462"><x:c r="A462"><x:v>3045</x:v></x:c><x:c r="B462" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteLookupFailed</x:t></x:is></x:c><x:c r="C462" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하지 못했습니다: {2}</x:t></x:is></x:c><x:c r="D462" t="inlineStr"><x:is><x:t xml:space="preserve">Could not inspect tag '{1}' on remote '{0}': {2}</x:t></x:is></x:c></x:row><x:row r="463"><x:c r="A463"><x:v>3046</x:v></x:c><x:c r="B463" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteChanged</x:t></x:is></x:c><x:c r="C463" t="inlineStr"><x:is><x:t xml:space="preserve">확인 이후 원격 '{0}'의 태그 '{1}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</x:t></x:is></x:c><x:c r="D463" t="inlineStr"><x:is><x:t xml:space="preserve">Tag '{1}' on remote '{0}' changed after confirmation and was not deleted. Confirm again.</x:t></x:is></x:c></x:row><x:row r="464"><x:c r="A464"><x:v>3047</x:v></x:c><x:c r="B464" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteUrlChanged</x:t></x:is></x:c><x:c r="C464" t="inlineStr"><x:is><x:t xml:space="preserve">확인 이후 원격 '{0}'의 Push 주소가 변경되어 삭제하지 않았습니다.</x:t></x:is></x:c><x:c r="D464" t="inlineStr"><x:is><x:t xml:space="preserve">The push URL for remote '{0}' changed after confirmation. Nothing was deleted.</x:t></x:is></x:c></x:row><x:row r="465"><x:c r="A465"><x:v>3048</x:v></x:c><x:c r="B465" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRemoteFailed</x:t></x:is></x:c><x:c r="C465" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제하지 못했습니다: {2}</x:t></x:is></x:c><x:c r="D465" t="inlineStr"><x:is><x:t xml:space="preserve">Could not delete tag '{1}' on remote '{0}': {2}</x:t></x:is></x:c></x:row><x:row r="466"><x:c r="A466"><x:v>3049</x:v></x:c><x:c r="B466" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteRepositoryChanged</x:t></x:is></x:c><x:c r="C466" t="inlineStr"><x:is><x:t xml:space="preserve">태그 삭제를 확인한 저장소와 요청한 저장소가 다릅니다.</x:t></x:is></x:c><x:c r="D466" t="inlineStr"><x:is><x:t xml:space="preserve">The requested repository differs from the repository confirmed for tag deletion.</x:t></x:is></x:c></x:row><x:row r="467"><x:c r="A467"><x:v>3050</x:v></x:c><x:c r="B467" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameBranchMenu</x:t></x:is></x:c><x:c r="C467" t="inlineStr"><x:is><x:t xml:space="preserve">브랜치 이름 변경</x:t></x:is></x:c><x:c r="D467" t="inlineStr"><x:is><x:t xml:space="preserve">Rename branch</x:t></x:is></x:c></x:row><x:row r="468"><x:c r="A468"><x:v>3051</x:v></x:c><x:c r="B468" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameTagMenu</x:t></x:is></x:c><x:c r="C468" t="inlineStr"><x:is><x:t xml:space="preserve">태그 이름 변경</x:t></x:is></x:c><x:c r="D468" t="inlineStr"><x:is><x:t xml:space="preserve">Rename tag</x:t></x:is></x:c></x:row><x:row r="469"><x:c r="A469"><x:v>3052</x:v></x:c><x:c r="B469" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameOriginalName</x:t></x:is></x:c><x:c r="C469" t="inlineStr"><x:is><x:t xml:space="preserve">기존 이름</x:t></x:is></x:c><x:c r="D469" t="inlineStr"><x:is><x:t xml:space="preserve">Current name</x:t></x:is></x:c></x:row><x:row r="470"><x:c r="A470"><x:v>3053</x:v></x:c><x:c r="B470" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameNewName</x:t></x:is></x:c><x:c r="C470" t="inlineStr"><x:is><x:t xml:space="preserve">새 이름</x:t></x:is></x:c><x:c r="D470" t="inlineStr"><x:is><x:t xml:space="preserve">New name</x:t></x:is></x:c></x:row><x:row r="471"><x:c r="A471"><x:v>3054</x:v></x:c><x:c r="B471" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameLocalOnly</x:t></x:is></x:c><x:c r="C471" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 참조만 변경합니다. 원격 브랜치와 태그는 변경하지 않습니다.</x:t></x:is></x:c><x:c r="D471" t="inlineStr"><x:is><x:t xml:space="preserve">Only the local reference is renamed. Remote branches and tags are not changed.</x:t></x:is></x:c></x:row><x:row r="472"><x:c r="A472"><x:v>3055</x:v></x:c><x:c r="B472" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameTagObjectsHint</x:t></x:is></x:c><x:c r="C472" t="inlineStr"><x:is><x:t xml:space="preserve">태그 참조 이름만 변경합니다. 객체 내부의 기존 이름·주석·서명은 유지됩니다.</x:t></x:is></x:c><x:c r="D472" t="inlineStr"><x:is><x:t xml:space="preserve">Only the tag reference name changes. The original name, annotation and signature inside the tag object are preserved.</x:t></x:is></x:c></x:row><x:row r="473"><x:c r="A473"><x:v>3056</x:v></x:c><x:c r="B473" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameAction</x:t></x:is></x:c><x:c r="C473" t="inlineStr"><x:is><x:t xml:space="preserve">이름 변경</x:t></x:is></x:c><x:c r="D473" t="inlineStr"><x:is><x:t xml:space="preserve">Rename</x:t></x:is></x:c></x:row><x:row r="474"><x:c r="A474"><x:v>3057</x:v></x:c><x:c r="B474" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameBranchSucceeded</x:t></x:is></x:c><x:c r="C474" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 브랜치 '{0}'의 이름을 '{1}'로 변경했습니다.</x:t></x:is></x:c><x:c r="D474" t="inlineStr"><x:is><x:t xml:space="preserve">Renamed local branch '{0}' to '{1}'.</x:t></x:is></x:c></x:row><x:row r="475"><x:c r="A475"><x:v>3058</x:v></x:c><x:c r="B475" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameTagSucceeded</x:t></x:is></x:c><x:c r="C475" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그 '{0}'의 참조 이름을 '{1}'로 변경했습니다. 태그 객체는 유지했습니다.</x:t></x:is></x:c><x:c r="D475" t="inlineStr"><x:is><x:t xml:space="preserve">Renamed local tag reference '{0}' to '{1}'. The tag object was preserved.</x:t></x:is></x:c></x:row><x:row r="476"><x:c r="A476"><x:v>3059</x:v></x:c><x:c r="B476" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameUnchanged</x:t></x:is></x:c><x:c r="C476" t="inlineStr"><x:is><x:t xml:space="preserve">'{0}'은 기존 이름과 같아 변경하지 않았습니다.</x:t></x:is></x:c><x:c r="D476" t="inlineStr"><x:is><x:t xml:space="preserve">'{0}' is the current name. Nothing was changed.</x:t></x:is></x:c></x:row><x:row r="477"><x:c r="A477"><x:v>3060</x:v></x:c><x:c r="B477" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameRepositoryChanged</x:t></x:is></x:c><x:c r="C477" t="inlineStr"><x:is><x:t xml:space="preserve">이름 변경을 확인한 저장소와 실행할 저장소가 다릅니다.</x:t></x:is></x:c><x:c r="D477" t="inlineStr"><x:is><x:t xml:space="preserve">The execution repository differs from the repository confirmed for renaming.</x:t></x:is></x:c></x:row><x:row r="478"><x:c r="A478"><x:v>3061</x:v></x:c><x:c r="B478" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameSourceInvalid</x:t></x:is></x:c><x:c r="C478" t="inlineStr"><x:is><x:t xml:space="preserve">이름 변경 대상 로컬 참조가 유효하지 않습니다: {0}</x:t></x:is></x:c><x:c r="D478" t="inlineStr"><x:is><x:t xml:space="preserve">The local reference to rename is invalid: {0}</x:t></x:is></x:c></x:row><x:row r="479"><x:c r="A479"><x:v>3062</x:v></x:c><x:c r="B479" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameSourceMissing</x:t></x:is></x:c><x:c r="C479" t="inlineStr"><x:is><x:t xml:space="preserve">이름 변경 대상 참조 '{0}'이 더 이상 존재하지 않습니다.</x:t></x:is></x:c><x:c r="D479" t="inlineStr"><x:is><x:t xml:space="preserve">Reference '{0}' no longer exists and cannot be renamed.</x:t></x:is></x:c></x:row><x:row r="480"><x:c r="A480"><x:v>3063</x:v></x:c><x:c r="B480" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameSourceChanged</x:t></x:is></x:c><x:c r="C480" t="inlineStr"><x:is><x:t xml:space="preserve">확인 이후 참조 '{0}'이 변경되어 이름을 바꾸지 않았습니다. 다시 확인하세요.</x:t></x:is></x:c><x:c r="D480" t="inlineStr"><x:is><x:t xml:space="preserve">Reference '{0}' changed after confirmation and was not renamed. Confirm again.</x:t></x:is></x:c></x:row><x:row r="481"><x:c r="A481"><x:v>3064</x:v></x:c><x:c r="B481" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameInvalidObjectId</x:t></x:is></x:c><x:c r="C481" t="inlineStr"><x:is><x:t xml:space="preserve">참조 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 목록을 새로 고친 뒤 다시 확인하세요.</x:t></x:is></x:c><x:c r="D481" t="inlineStr"><x:is><x:t xml:space="preserve">The confirmed object OID for reference '{0}' is invalid. Refresh references and confirm again.</x:t></x:is></x:c></x:row><x:row r="482"><x:c r="A482"><x:v>3065</x:v></x:c><x:c r="B482" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameNameRequired</x:t></x:is></x:c><x:c r="C482" t="inlineStr"><x:is><x:t xml:space="preserve">새 이름을 입력하세요.</x:t></x:is></x:c><x:c r="D482" t="inlineStr"><x:is><x:t xml:space="preserve">Enter a new name.</x:t></x:is></x:c></x:row><x:row r="483"><x:c r="A483"><x:v>3066</x:v></x:c><x:c r="B483" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameNameInvalid</x:t></x:is></x:c><x:c r="C483" t="inlineStr"><x:is><x:t xml:space="preserve">새 이름이 유효하지 않습니다: {0}</x:t></x:is></x:c><x:c r="D483" t="inlineStr"><x:is><x:t xml:space="preserve">The new name is invalid: {0}</x:t></x:is></x:c></x:row><x:row r="484"><x:c r="A484"><x:v>3067</x:v></x:c><x:c r="B484" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameDestinationExists</x:t></x:is></x:c><x:c r="C484" t="inlineStr"><x:is><x:t xml:space="preserve">목적지 참조 '{0}'이 이미 존재합니다. 덮어쓰지 않습니다.</x:t></x:is></x:c><x:c r="D484" t="inlineStr"><x:is><x:t xml:space="preserve">Destination reference '{0}' already exists. It will not be overwritten.</x:t></x:is></x:c></x:row><x:row r="485"><x:c r="A485"><x:v>3068</x:v></x:c><x:c r="B485" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameLookupFailed</x:t></x:is></x:c><x:c r="C485" t="inlineStr"><x:is><x:t xml:space="preserve">참조 '{0}'을 확인하지 못했습니다: {1}</x:t></x:is></x:c><x:c r="D485" t="inlineStr"><x:is><x:t xml:space="preserve">Could not inspect reference '{0}': {1}</x:t></x:is></x:c></x:row><x:row r="486"><x:c r="A486"><x:v>3069</x:v></x:c><x:c r="B486" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameFailed</x:t></x:is></x:c><x:c r="C486" t="inlineStr"><x:is><x:t xml:space="preserve">참조 '{0}'을 '{1}'로 변경하지 못했습니다: {2}</x:t></x:is></x:c><x:c r="D486" t="inlineStr"><x:is><x:t xml:space="preserve">Could not rename reference '{0}' to '{1}': {2}</x:t></x:is></x:c></x:row><x:row r="487"><x:c r="A487"><x:v>3070</x:v></x:c><x:c r="B487" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameRefreshFailed</x:t></x:is></x:c><x:c r="C487" t="inlineStr"><x:is><x:t xml:space="preserve">{0} 상태 갱신에 실패했습니다: {1}</x:t></x:is></x:c><x:c r="D487" t="inlineStr"><x:is><x:t xml:space="preserve">{0} State refresh failed: {1}</x:t></x:is></x:c></x:row><x:row r="488"><x:c r="A488"><x:v>3071</x:v></x:c><x:c r="B488" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameStateReadFailed</x:t></x:is></x:c><x:c r="C488" t="inlineStr"><x:is><x:t xml:space="preserve">'{0}'에서 '{1}'로 이름 변경은 반영되었지만 저장소 상태를 읽지 못했습니다. 새로 고침하세요.</x:t></x:is></x:c><x:c r="D488" t="inlineStr"><x:is><x:t xml:space="preserve">The rename from '{0}' to '{1}' was applied, but repository state could not be read. Refresh the repository.</x:t></x:is></x:c></x:row><x:row r="489"><x:c r="A489"><x:v>3072</x:v></x:c><x:c r="B489" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameQueueProgress</x:t></x:is></x:c><x:c r="C489" t="inlineStr"><x:is><x:t xml:space="preserve">'{0}'으로 이름 변경 중 · 대기 {1}건</x:t></x:is></x:c><x:c r="D489" t="inlineStr"><x:is><x:t xml:space="preserve">Renaming to '{0}' · {1} queued</x:t></x:is></x:c></x:row><x:row r="490"><x:c r="A490"><x:v>3073</x:v></x:c><x:c r="B490" t="inlineStr"><x:is><x:t xml:space="preserve">ReferenceRenameQueueClosing</x:t></x:is></x:c><x:c r="C490" t="inlineStr"><x:is><x:t xml:space="preserve">'{0}'으로 이름 변경 결과를 기다린 뒤 닫습니다.</x:t></x:is></x:c><x:c r="D490" t="inlineStr"><x:is><x:t xml:space="preserve">Waiting for rename to '{0}' to finish before closing.</x:t></x:is></x:c></x:row><x:row r="491"><x:c r="A491"><x:v>3074</x:v></x:c><x:c r="B491" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogLocalScope</x:t></x:is></x:c><x:c r="C491" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 태그</x:t></x:is></x:c><x:c r="D491" t="inlineStr"><x:is><x:t xml:space="preserve">Local tag</x:t></x:is></x:c></x:row><x:row r="492"><x:c r="A492"><x:v>3075</x:v></x:c><x:c r="B492" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogRemoteScope</x:t></x:is></x:c><x:c r="C492" t="inlineStr"><x:is><x:t xml:space="preserve">원격 태그</x:t></x:is></x:c><x:c r="D492" t="inlineStr"><x:is><x:t xml:space="preserve">Remote tag</x:t></x:is></x:c></x:row><x:row r="493"><x:c r="A493"><x:v>3076</x:v></x:c><x:c r="B493" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogRemoteHint</x:t></x:is></x:c><x:c r="C493" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 원격 서버의 태그만 삭제합니다. 다른 사용자에게 영향을 주며 로컬 태그와 브랜치는 유지됩니다.</x:t></x:is></x:c><x:c r="D493" t="inlineStr"><x:is><x:t xml:space="preserve">Only the tag on the selected remote server is deleted. This affects other users. Local tags and branches are preserved.</x:t></x:is></x:c></x:row><x:row r="494"><x:c r="A494"><x:v>3077</x:v></x:c><x:c r="B494" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogLoading</x:t></x:is></x:c><x:c r="C494" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하는 중입니다.</x:t></x:is></x:c><x:c r="D494" t="inlineStr"><x:is><x:t xml:space="preserve">Inspecting tag '{1}' on remote '{0}'.</x:t></x:is></x:c></x:row><x:row r="495"><x:c r="A495"><x:v>3078</x:v></x:c><x:c r="B495" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogConfirmRemote</x:t></x:is></x:c><x:c r="C495" t="inlineStr"><x:is><x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 서버에서 삭제하는 영향을 확인했습니다.</x:t></x:is></x:c><x:c r="D495" t="inlineStr"><x:is><x:t xml:space="preserve">I confirm the impact of deleting tag '{1}' from remote '{0}' on the server.</x:t></x:is></x:c></x:row><x:row r="496"><x:c r="A496"><x:v>3079</x:v></x:c><x:c r="B496" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogDeleting</x:t></x:is></x:c><x:c r="C496" t="inlineStr"><x:is><x:t xml:space="preserve">태그 삭제 결과를 기다리는 중입니다.</x:t></x:is></x:c><x:c r="D496" t="inlineStr"><x:is><x:t xml:space="preserve">Waiting for the tag deletion result.</x:t></x:is></x:c></x:row><x:row r="497"><x:c r="A497"><x:v>3080</x:v></x:c><x:c r="B497" t="inlineStr"><x:is><x:t xml:space="preserve">TagDeleteDialogReload</x:t></x:is></x:c><x:c r="C497" t="inlineStr"><x:is><x:t xml:space="preserve">대상 다시 조회</x:t></x:is></x:c><x:c r="D497" t="inlineStr"><x:is><x:t xml:space="preserve">Reload target</x:t></x:is></x:c></x:row><x:row r="498"><x:c r="A498"><x:v>3081</x:v></x:c><x:c r="B498" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureAuthentication</x:t></x:is></x:c><x:c r="C498" t="inlineStr"><x:is><x:t xml:space="preserve">Git 인증에 실패했습니다(종료 코드 {0}). 로그인 상태와 인증 도우미 또는 SSH 키를 확인하세요.</x:t></x:is></x:c><x:c r="D498" t="inlineStr"><x:is><x:t xml:space="preserve">Git authentication failed (exit code {0}). Check your sign-in, credential helper, or SSH key.</x:t></x:is></x:c></x:row><x:row r="499"><x:c r="A499"><x:v>3082</x:v></x:c><x:c r="B499" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureRemoteAccessDenied</x:t></x:is></x:c><x:c r="C499" t="inlineStr"><x:is><x:t xml:space="preserve">원격 저장소 접근이 거부되었습니다(종료 코드 {0}). 계정의 저장소 접근 권한을 확인하세요.</x:t></x:is></x:c><x:c r="D499" t="inlineStr"><x:is><x:t xml:space="preserve">Access to the remote repository was denied (exit code {0}). Check the account permissions for this repository.</x:t></x:is></x:c></x:row><x:row r="500"><x:c r="A500"><x:v>3083</x:v></x:c><x:c r="B500" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureRepositoryUnavailable</x:t></x:is></x:c><x:c r="C500" t="inlineStr"><x:is><x:t xml:space="preserve">저장소를 찾거나 읽을 수 없습니다(종료 코드 {0}). 주소 또는 경로, 저장소 존재 여부와 접근 권한을 확인하세요.</x:t></x:is></x:c><x:c r="D500" t="inlineStr"><x:is><x:t xml:space="preserve">The repository could not be found or read (exit code {0}). Check the address or path, repository existence, and access permissions.</x:t></x:is></x:c></x:row><x:row r="501"><x:c r="A501"><x:v>3084</x:v></x:c><x:c r="B501" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureConnection</x:t></x:is></x:c><x:c r="C501" t="inlineStr"><x:is><x:t xml:space="preserve">원격 연결에 실패했습니다(종료 코드 {0}). 네트워크, DNS, 프록시와 서버 인증서를 확인하세요.</x:t></x:is></x:c><x:c r="D501" t="inlineStr"><x:is><x:t xml:space="preserve">The remote connection failed (exit code {0}). Check the network, DNS, proxy, and server certificate.</x:t></x:is></x:c></x:row><x:row r="502"><x:c r="A502"><x:v>3085</x:v></x:c><x:c r="B502" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureDiskFull</x:t></x:is></x:c><x:c r="C502" t="inlineStr"><x:is><x:t xml:space="preserve">Git이 저장 공간 또는 할당량 부족을 보고했습니다(종료 코드 {0}). 로컬 또는 원격의 저장 공간을 확인하세요.</x:t></x:is></x:c><x:c r="D502" t="inlineStr"><x:is><x:t xml:space="preserve">Git reported insufficient storage space or quota (exit code {0}). Check local or remote storage space.</x:t></x:is></x:c></x:row><x:row r="503"><x:c r="A503"><x:v>3086</x:v></x:c><x:c r="B503" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureFileAccess</x:t></x:is></x:c><x:c r="C503" t="inlineStr"><x:is><x:t xml:space="preserve">로컬 파일을 만들거나 쓸 수 없습니다(종료 코드 {0}). 목적지 폴더의 쓰기 권한과 파일 잠금을 확인하세요.</x:t></x:is></x:c><x:c r="D503" t="inlineStr"><x:is><x:t xml:space="preserve">Local files could not be created or written (exit code {0}). Check destination write permissions and file locks.</x:t></x:is></x:c></x:row><x:row r="504"><x:c r="A504"><x:v>3087</x:v></x:c><x:c r="B504" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureDestinationConflict</x:t></x:is></x:c><x:c r="C504" t="inlineStr"><x:is><x:t xml:space="preserve">실행 시 목적지에 이미 내용이 있어 복제할 수 없습니다(종료 코드 {0}). 비어 있는 폴더 또는 새 경로를 선택하세요.</x:t></x:is></x:c><x:c r="D504" t="inlineStr"><x:is><x:t xml:space="preserve">The destination already contained data when cloning ran (exit code {0}). Choose an empty folder or a new path.</x:t></x:is></x:c></x:row><x:row r="505"><x:c r="A505"><x:v>3088</x:v></x:c><x:c r="B505" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureUnknown</x:t></x:is></x:c><x:c r="C505" t="inlineStr"><x:is><x:t xml:space="preserve">Git 복제에 실패했습니다(종료 코드 {0}). 주소, 인증, 연결과 목적지 권한을 확인하세요.</x:t></x:is></x:c><x:c r="D505" t="inlineStr"><x:is><x:t xml:space="preserve">Git clone failed (exit code {0}). Check the address, authentication, connection, and destination permissions.</x:t></x:is></x:c></x:row><x:row r="506"><x:c r="A506"><x:v>3089</x:v></x:c><x:c r="B506" t="inlineStr"><x:is><x:t xml:space="preserve">CloneFailureUnexpected</x:t></x:is></x:c><x:c r="C506" t="inlineStr"><x:is><x:t xml:space="preserve">복제 요청을 처리하지 못했습니다. 주소, 인증, 연결과 목적지 권한을 확인하세요.</x:t></x:is></x:c><x:c r="D506" t="inlineStr"><x:is><x:t xml:space="preserve">The clone request could not be completed. Check the address, authentication, connection, and destination permissions.</x:t></x:is></x:c></x:row><x:row r="507"><x:c r="A507"><x:v>3090</x:v></x:c><x:c r="B507" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationMissingAfterAttempt</x:t></x:is></x:c><x:c r="C507" t="inlineStr"><x:is><x:t xml:space="preserve">목적지 폴더가 없습니다: {0}. 같은 경로로 다시 시도할 수 있습니다.</x:t></x:is></x:c><x:c r="D507" t="inlineStr"><x:is><x:t xml:space="preserve">The destination folder does not exist: {0}. You can retry using this path.</x:t></x:is></x:c></x:row><x:row r="508"><x:c r="A508"><x:v>3091</x:v></x:c><x:c r="B508" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationEmptyAfterAttempt</x:t></x:is></x:c><x:c r="C508" t="inlineStr"><x:is><x:t xml:space="preserve">복제할 폴더가 비어 있습니다: {0}. 실패 원인을 해결한 뒤 다시 시도할 수 있습니다.</x:t></x:is></x:c><x:c r="D508" t="inlineStr"><x:is><x:t xml:space="preserve">The destination folder is empty: {0}. You can retry after resolving the clone error.</x:t></x:is></x:c></x:row><x:row r="509"><x:c r="A509"><x:v>3092</x:v></x:c><x:c r="B509" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationContentsAfterAttempt</x:t></x:is></x:c><x:c r="C509" t="inlineStr"><x:is><x:t xml:space="preserve">복제 위치에 내용이 남아 있습니다: {0}. 다시 시도하기 전에 확인하세요.</x:t></x:is></x:c><x:c r="D509" t="inlineStr"><x:is><x:t xml:space="preserve">Files remain at the destination: {0}. Review them before trying again.</x:t></x:is></x:c></x:row><x:row r="510"><x:c r="A510"><x:v>3093</x:v></x:c><x:c r="B510" t="inlineStr"><x:is><x:t xml:space="preserve">CloneDestinationInspectionFailed</x:t></x:is></x:c><x:c r="C510" t="inlineStr"><x:is><x:t xml:space="preserve">복제 위치의 상태를 확인할 수 없습니다: {0}. 폴더와 접근 권한을 확인하세요.</x:t></x:is></x:c><x:c r="D510" t="inlineStr"><x:is><x:t xml:space="preserve">Could not read the destination state: {0}. Check the folder and access permissions.</x:t></x:is></x:c></x:row><x:row r="511"><x:c r="A511" t="n"><x:v>3094</x:v></x:c><x:c r="B511" t="str"><x:v>AppLanguageHeading</x:v></x:c><x:c r="C511" t="str"><x:v>언어</x:v></x:c><x:c r="D511" t="str"><x:v>Language</x:v></x:c></x:row><x:row r="512"><x:c r="A512" t="n"><x:v>3095</x:v></x:c><x:c r="B512" t="str"><x:v>AppLanguageDescription</x:v></x:c><x:c r="C512" t="str"><x:v>앱에서 사용할 언어를 선택합니다. 변경 사항은 즉시 적용됩니다.</x:v></x:c><x:c r="D512" t="str"><x:v>Choose the app language. Changes apply immediately.</x:v></x:c></x:row><x:row r="513"><x:c r="A513" t="n"><x:v>3096</x:v></x:c><x:c r="B513" t="str"><x:v>AppLanguageKorean</x:v></x:c><x:c r="C513" t="str"><x:v>한국어</x:v></x:c><x:c r="D513" t="str"><x:v>Korean</x:v></x:c></x:row><x:row r="514"><x:c r="A514" t="n"><x:v>3097</x:v></x:c><x:c r="B514" t="str"><x:v>AppLanguageEnglish</x:v></x:c><x:c r="C514" t="str"><x:v>영어</x:v></x:c><x:c r="D514" t="str"><x:v>English</x:v></x:c></x:row><x:row r="515"><x:c r="A515" t="n"><x:v>3098</x:v></x:c><x:c r="B515" t="str"><x:v>AppLanguageSaved</x:v></x:c><x:c r="C515" t="str"><x:v>언어를 변경했습니다.</x:v></x:c><x:c r="D515" t="str"><x:v>Language changed.</x:v></x:c></x:row><x:row r="516"><x:c r="A516" t="n"><x:v>3099</x:v></x:c><x:c r="B516" t="str"><x:v>WorkingStopTrackingPartialFailure</x:v></x:c><x:c r="C516" t="str"><x:v>.gitignore에 무시 규칙을 추가했지만 추적 중지 중 오류가 발생했습니다. 스테이징 상태를 확인하세요.
-{0}</x:v></x:c><x:c r="D516" t="str"><x:v>Ignore rules were added to .gitignore, but stopping tracking encountered an error. Review the staged changes.
-{0}</x:v></x:c></x:row><x:row r="517"><x:c r="A517" t="n"><x:v>3100</x:v></x:c><x:c r="B517" t="str"><x:v>RemotePullFastForwardUnavailable</x:v></x:c><x:c r="C517" t="str"><x:v>빠른 전진으로 통합할 수 없습니다. Pull 메뉴에서 병합 또는 재배치를 선택하세요.</x:v></x:c><x:c r="D517" t="str"><x:v>Fast-forward is not possible. Choose merge or rebase from the Pull menu.</x:v></x:c></x:row><x:row r="518"><x:c r="A518" t="n"><x:v>3101</x:v></x:c><x:c r="B518" t="str"><x:v>RemotePullFetchFailedSummary</x:v></x:c><x:c r="C518" t="str"><x:v>원격 변경을 가져오지 못했습니다. 자세한 내용을 확인하세요.</x:v></x:c><x:c r="D518" t="str"><x:v>Could not fetch remote changes. See details.</x:v></x:c></x:row><x:row r="519"><x:c r="A519" t="n"><x:v>3102</x:v></x:c><x:c r="B519" t="str"><x:v>RemotePullApplyFailedSummary</x:v></x:c><x:c r="C519" t="str"><x:v>가져온 변경을 현재 브랜치에 반영하지 못했습니다. 자세한 내용을 확인하세요.</x:v></x:c><x:c r="D519" t="str"><x:v>Could not apply incoming changes to the current branch. See details.</x:v></x:c></x:row><x:row r="520"><x:c r="A520" t="n"><x:v>3103</x:v></x:c><x:c r="B520" t="str"><x:v>RemotePushFailedSummary</x:v></x:c><x:c r="C520" t="str"><x:v>원격에 변경을 보내지 못했습니다. 자세한 내용을 확인하세요.</x:v></x:c><x:c r="D520" t="str"><x:v>Could not push changes. See details.</x:v></x:c></x:row><x:row r="521"><x:c r="A521" t="n"><x:v>3104</x:v></x:c><x:c r="B521" t="str"><x:v>RemoteFetchFailedSummary</x:v></x:c><x:c r="C521" t="str"><x:v>{0} 가져오기에 실패했습니다. 자세한 내용을 확인하세요.</x:v></x:c><x:c r="D521" t="str"><x:v>Fetch failed for {0}. See details.</x:v></x:c></x:row><x:row r="522"><x:c r="A522" t="n"><x:v>3105</x:v></x:c><x:c r="B522" t="str"><x:v>RemoteOperationDetails</x:v></x:c><x:c r="C522" t="str"><x:v>자세히</x:v></x:c><x:c r="D522" t="str"><x:v>Details</x:v></x:c></x:row><x:row r="523"><x:c r="A523" t="n"><x:v>3106</x:v></x:c><x:c r="B523" t="str"><x:v>ConflictSelectionSummary</x:v></x:c><x:c r="C523" t="str"><x:v>{0}/{1}개 구간 선택</x:v></x:c><x:c r="D523" t="str"><x:v>{0}/{1} sections chosen</x:v></x:c></x:row><x:row r="524"><x:c r="A524" t="n"><x:v>3107</x:v></x:c><x:c r="B524" t="str"><x:v>WorkingMergeMessageReadFailed</x:v></x:c><x:c r="C524" t="str"><x:v>병합 커밋 메시지를 읽지 못했습니다: {0}
-{1}</x:v></x:c><x:c r="D524" t="str"><x:v>Could not read the merge commit message: {0}
-{1}</x:v></x:c></x:row><row r="525" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A525"><v>3124</v></c><c r="B525" t="inlineStr"><is><t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">HistoryLoadingChanges</t></is></c><c r="C525" t="inlineStr"><is><t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">변경 파일을 불러오는 중입니다.</t></is></c><c r="D525" t="inlineStr"><is><t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Loading changed files.</t></is></c></row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+This deletes the tag on the server and affects other users. The local tag and branches with the same name are preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446">
+        <x:v>3029</x:v>
+      </x:c>
+      <x:c r="B446" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C446" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">삭제</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D446" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="B447" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteSelectRemoteTitle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C447" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그를 삭제할 원격 선택</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D447" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select remote for tag deletion</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448">
+        <x:v>3031</x:v>
+      </x:c>
+      <x:c r="B448" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemotePrompt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C448" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 '{0}'을 조회할 등록된 원격을 선택하세요. 다음 확인 창에서 서버 삭제 대상을 확인합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D448" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select a registered remote to inspect tag '{0}'. Confirm the server deletion target in the next dialog.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449">
+        <x:v>3032</x:v>
+      </x:c>
+      <x:c r="B449" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteInspectRemoteAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C449" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">대상 확인</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D449" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inspect target</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450">
+        <x:v>3033</x:v>
+      </x:c>
+      <x:c r="B450" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalSucceeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C450" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 '{0}'을 삭제했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D450" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deleted local tag '{0}'.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451">
+        <x:v>3034</x:v>
+      </x:c>
+      <x:c r="B451" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteSucceeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C451" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제했습니다. 로컬 태그는 유지했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D451" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deleted tag '{1}' from remote '{0}'. The local tag was preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452">
+        <x:v>3035</x:v>
+      </x:c>
+      <x:c r="B452" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRefreshFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C452" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 참조 갱신에 실패했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D452" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} Reference refresh failed: {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453">
+        <x:v>3036</x:v>
+      </x:c>
+      <x:c r="B453" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteInvalidName</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C453" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">삭제할 태그 이름이 유효하지 않습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D453" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The tag name is not valid for deletion: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454">
+        <x:v>3037</x:v>
+      </x:c>
+      <x:c r="B454" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteInvalidObjectId</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C454" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 참조 목록을 새로 고친 뒤 다시 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D454" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The confirmed object OID for tag '{0}' is invalid. Refresh references and confirm again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455">
+        <x:v>3038</x:v>
+      </x:c>
+      <x:c r="B455" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C455" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 '{0}'이 더 이상 존재하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D455" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Local tag '{0}' no longer exists.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456">
+        <x:v>3039</x:v>
+      </x:c>
+      <x:c r="B456" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C456" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">확인 이후 로컬 태그 '{0}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D456" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Local tag '{0}' changed after confirmation and was not deleted. Confirm again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457">
+        <x:v>3040</x:v>
+      </x:c>
+      <x:c r="B457" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteLocalFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C457" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 '{0}'을 삭제하지 못했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D457" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete local tag '{0}': {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458">
+        <x:v>3041</x:v>
+      </x:c>
+      <x:c r="B458" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C458" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 태그를 삭제하려면 등록된 원격이 필요합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D458" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">A registered remote is required to delete a remote tag.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459">
+        <x:v>3042</x:v>
+      </x:c>
+      <x:c r="B459" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C459" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 Push 주소를 확인할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D459" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not resolve the push URL for remote '{0}'.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460">
+        <x:v>3043</x:v>
+      </x:c>
+      <x:c r="B460" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteMultiplePushUrls</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C460" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'에 Push 주소가 여러 개라 태그 삭제를 지원하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D460" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tag deletion is not supported for remote '{0}' because it has multiple push URLs.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461">
+        <x:v>3044</x:v>
+      </x:c>
+      <x:c r="B461" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteTagMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C461" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'에 태그 '{1}'이 없습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D461" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote '{0}' has no tag '{1}'.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462">
+        <x:v>3045</x:v>
+      </x:c>
+      <x:c r="B462" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteLookupFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C462" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하지 못했습니다: {2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D462" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not inspect tag '{1}' on remote '{0}': {2}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463">
+        <x:v>3046</x:v>
+      </x:c>
+      <x:c r="B463" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C463" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">확인 이후 원격 '{0}'의 태그 '{1}'이 변경되어 삭제하지 않았습니다. 다시 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D463" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tag '{1}' on remote '{0}' changed after confirmation and was not deleted. Confirm again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464">
+        <x:v>3047</x:v>
+      </x:c>
+      <x:c r="B464" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteUrlChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C464" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">확인 이후 원격 '{0}'의 Push 주소가 변경되어 삭제하지 않았습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D464" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The push URL for remote '{0}' changed after confirmation. Nothing was deleted.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465">
+        <x:v>3048</x:v>
+      </x:c>
+      <x:c r="B465" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRemoteFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C465" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 삭제하지 못했습니다: {2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D465" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not delete tag '{1}' on remote '{0}': {2}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466">
+        <x:v>3049</x:v>
+      </x:c>
+      <x:c r="B466" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteRepositoryChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C466" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 삭제를 확인한 저장소와 요청한 저장소가 다릅니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D466" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The requested repository differs from the repository confirmed for tag deletion.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467">
+        <x:v>3050</x:v>
+      </x:c>
+      <x:c r="B467" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameBranchMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C467" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">브랜치 이름 변경</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D467" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rename branch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468">
+        <x:v>3051</x:v>
+      </x:c>
+      <x:c r="B468" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameTagMenu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C468" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 이름 변경</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D468" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rename tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469">
+        <x:v>3052</x:v>
+      </x:c>
+      <x:c r="B469" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameOriginalName</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C469" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기존 이름</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D469" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Current name</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470">
+        <x:v>3053</x:v>
+      </x:c>
+      <x:c r="B470" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameNewName</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C470" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 이름</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D470" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">New name</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471">
+        <x:v>3054</x:v>
+      </x:c>
+      <x:c r="B471" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameLocalOnly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C471" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 참조만 변경합니다. 원격 브랜치와 태그는 변경하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D471" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only the local reference is renamed. Remote branches and tags are not changed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472">
+        <x:v>3055</x:v>
+      </x:c>
+      <x:c r="B472" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameTagObjectsHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C472" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 참조 이름만 변경합니다. 객체 내부의 기존 이름·주석·서명은 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D472" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only the tag reference name changes. The original name, annotation and signature inside the tag object are preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473">
+        <x:v>3056</x:v>
+      </x:c>
+      <x:c r="B473" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameAction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C473" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이름 변경</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D473" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rename</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474">
+        <x:v>3057</x:v>
+      </x:c>
+      <x:c r="B474" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameBranchSucceeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C474" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 브랜치 '{0}'의 이름을 '{1}'로 변경했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D474" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Renamed local branch '{0}' to '{1}'.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475">
+        <x:v>3058</x:v>
+      </x:c>
+      <x:c r="B475" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameTagSucceeded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C475" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그 '{0}'의 참조 이름을 '{1}'로 변경했습니다. 태그 객체는 유지했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D475" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Renamed local tag reference '{0}' to '{1}'. The tag object was preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476">
+        <x:v>3059</x:v>
+      </x:c>
+      <x:c r="B476" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameUnchanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C476" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">'{0}'은 기존 이름과 같아 변경하지 않았습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D476" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">'{0}' is the current name. Nothing was changed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477">
+        <x:v>3060</x:v>
+      </x:c>
+      <x:c r="B477" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameRepositoryChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C477" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이름 변경을 확인한 저장소와 실행할 저장소가 다릅니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D477" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The execution repository differs from the repository confirmed for renaming.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478">
+        <x:v>3061</x:v>
+      </x:c>
+      <x:c r="B478" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameSourceInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C478" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이름 변경 대상 로컬 참조가 유효하지 않습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D478" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The local reference to rename is invalid: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479">
+        <x:v>3062</x:v>
+      </x:c>
+      <x:c r="B479" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameSourceMissing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C479" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이름 변경 대상 참조 '{0}'이 더 이상 존재하지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D479" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reference '{0}' no longer exists and cannot be renamed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480">
+        <x:v>3063</x:v>
+      </x:c>
+      <x:c r="B480" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameSourceChanged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C480" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">확인 이후 참조 '{0}'이 변경되어 이름을 바꾸지 않았습니다. 다시 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D480" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reference '{0}' changed after confirmation and was not renamed. Confirm again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481">
+        <x:v>3064</x:v>
+      </x:c>
+      <x:c r="B481" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameInvalidObjectId</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C481" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참조 '{0}'의 확인한 객체 OID가 유효하지 않습니다. 목록을 새로 고친 뒤 다시 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D481" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The confirmed object OID for reference '{0}' is invalid. Refresh references and confirm again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482">
+        <x:v>3065</x:v>
+      </x:c>
+      <x:c r="B482" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameNameRequired</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C482" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 이름을 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D482" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter a new name.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483">
+        <x:v>3066</x:v>
+      </x:c>
+      <x:c r="B483" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameNameInvalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C483" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">새 이름이 유효하지 않습니다: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D483" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The new name is invalid: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484">
+        <x:v>3067</x:v>
+      </x:c>
+      <x:c r="B484" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameDestinationExists</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C484" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">목적지 참조 '{0}'이 이미 존재합니다. 덮어쓰지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D484" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Destination reference '{0}' already exists. It will not be overwritten.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485">
+        <x:v>3068</x:v>
+      </x:c>
+      <x:c r="B485" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameLookupFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C485" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참조 '{0}'을 확인하지 못했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D485" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not inspect reference '{0}': {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486">
+        <x:v>3069</x:v>
+      </x:c>
+      <x:c r="B486" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C486" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참조 '{0}'을 '{1}'로 변경하지 못했습니다: {2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D486" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not rename reference '{0}' to '{1}': {2}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487">
+        <x:v>3070</x:v>
+      </x:c>
+      <x:c r="B487" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameRefreshFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C487" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} 상태 갱신에 실패했습니다: {1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D487" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0} State refresh failed: {1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488">
+        <x:v>3071</x:v>
+      </x:c>
+      <x:c r="B488" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameStateReadFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C488" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">'{0}'에서 '{1}'로 이름 변경은 반영되었지만 저장소 상태를 읽지 못했습니다. 새로 고침하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D488" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The rename from '{0}' to '{1}' was applied, but repository state could not be read. Refresh the repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489">
+        <x:v>3072</x:v>
+      </x:c>
+      <x:c r="B489" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameQueueProgress</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C489" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">'{0}'으로 이름 변경 중 · 대기 {1}건</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D489" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Renaming to '{0}' · {1} queued</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490">
+        <x:v>3073</x:v>
+      </x:c>
+      <x:c r="B490" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReferenceRenameQueueClosing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C490" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">'{0}'으로 이름 변경 결과를 기다린 뒤 닫습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D490" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting for rename to '{0}' to finish before closing.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491">
+        <x:v>3074</x:v>
+      </x:c>
+      <x:c r="B491" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogLocalScope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C491" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 태그</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D491" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Local tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492">
+        <x:v>3075</x:v>
+      </x:c>
+      <x:c r="B492" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogRemoteScope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C492" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 태그</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D492" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remote tag</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="B493" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogRemoteHint</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C493" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택한 원격 서버의 태그만 삭제합니다. 다른 사용자에게 영향을 주며 로컬 태그와 브랜치는 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D493" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only the tag on the selected remote server is deleted. This affects other users. Local tags and branches are preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494">
+        <x:v>3077</x:v>
+      </x:c>
+      <x:c r="B494" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogLoading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C494" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 조회하는 중입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D494" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Inspecting tag '{1}' on remote '{0}'.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495">
+        <x:v>3078</x:v>
+      </x:c>
+      <x:c r="B495" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogConfirmRemote</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C495" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 '{0}'의 태그 '{1}'을 서버에서 삭제하는 영향을 확인했습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D495" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">I confirm the impact of deleting tag '{1}' from remote '{0}' on the server.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496">
+        <x:v>3079</x:v>
+      </x:c>
+      <x:c r="B496" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogDeleting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C496" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">태그 삭제 결과를 기다리는 중입니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D496" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting for the tag deletion result.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497">
+        <x:v>3080</x:v>
+      </x:c>
+      <x:c r="B497" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TagDeleteDialogReload</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C497" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">대상 다시 조회</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D497" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reload target</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498">
+        <x:v>3081</x:v>
+      </x:c>
+      <x:c r="B498" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureAuthentication</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C498" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 인증에 실패했습니다(종료 코드 {0}). 로그인 상태와 인증 도우미 또는 SSH 키를 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D498" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git authentication failed (exit code {0}). Check your sign-in, credential helper, or SSH key.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499">
+        <x:v>3082</x:v>
+      </x:c>
+      <x:c r="B499" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureRemoteAccessDenied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C499" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 저장소 접근이 거부되었습니다(종료 코드 {0}). 계정의 저장소 접근 권한을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D499" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Access to the remote repository was denied (exit code {0}). Check the account permissions for this repository.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500">
+        <x:v>3083</x:v>
+      </x:c>
+      <x:c r="B500" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureRepositoryUnavailable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C500" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장소를 찾거나 읽을 수 없습니다(종료 코드 {0}). 주소 또는 경로, 저장소 존재 여부와 접근 권한을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D500" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The repository could not be found or read (exit code {0}). Check the address or path, repository existence, and access permissions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501">
+        <x:v>3084</x:v>
+      </x:c>
+      <x:c r="B501" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureConnection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C501" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">원격 연결에 실패했습니다(종료 코드 {0}). 네트워크, DNS, 프록시와 서버 인증서를 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D501" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The remote connection failed (exit code {0}). Check the network, DNS, proxy, and server certificate.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502">
+        <x:v>3085</x:v>
+      </x:c>
+      <x:c r="B502" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureDiskFull</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C502" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git이 저장 공간 또는 할당량 부족을 보고했습니다(종료 코드 {0}). 로컬 또는 원격의 저장 공간을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D502" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git reported insufficient storage space or quota (exit code {0}). Check local or remote storage space.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503">
+        <x:v>3086</x:v>
+      </x:c>
+      <x:c r="B503" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureFileAccess</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C503" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로컬 파일을 만들거나 쓸 수 없습니다(종료 코드 {0}). 목적지 폴더의 쓰기 권한과 파일 잠금을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D503" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Local files could not be created or written (exit code {0}). Check destination write permissions and file locks.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504">
+        <x:v>3087</x:v>
+      </x:c>
+      <x:c r="B504" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureDestinationConflict</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C504" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">실행 시 목적지에 이미 내용이 있어 복제할 수 없습니다(종료 코드 {0}). 비어 있는 폴더 또는 새 경로를 선택하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D504" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination already contained data when cloning ran (exit code {0}). Choose an empty folder or a new path.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505">
+        <x:v>3088</x:v>
+      </x:c>
+      <x:c r="B505" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureUnknown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C505" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git 복제에 실패했습니다(종료 코드 {0}). 주소, 인증, 연결과 목적지 권한을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D505" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Git clone failed (exit code {0}). Check the address, authentication, connection, and destination permissions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="506">
+      <x:c r="A506">
+        <x:v>3089</x:v>
+      </x:c>
+      <x:c r="B506" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneFailureUnexpected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C506" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 요청을 처리하지 못했습니다. 주소, 인증, 연결과 목적지 권한을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D506" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The clone request could not be completed. Check the address, authentication, connection, and destination permissions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507">
+        <x:v>3090</x:v>
+      </x:c>
+      <x:c r="B507" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationMissingAfterAttempt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C507" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">목적지 폴더가 없습니다: {0}. 같은 경로로 다시 시도할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D507" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination folder does not exist: {0}. You can retry using this path.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508">
+        <x:v>3091</x:v>
+      </x:c>
+      <x:c r="B508" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationEmptyAfterAttempt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C508" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제할 폴더가 비어 있습니다: {0}. 실패 원인을 해결한 뒤 다시 시도할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D508" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The destination folder is empty: {0}. You can retry after resolving the clone error.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509">
+        <x:v>3092</x:v>
+      </x:c>
+      <x:c r="B509" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationContentsAfterAttempt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C509" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 위치에 내용이 남아 있습니다: {0}. 다시 시도하기 전에 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D509" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Files remain at the destination: {0}. Review them before trying again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510">
+        <x:v>3093</x:v>
+      </x:c>
+      <x:c r="B510" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CloneDestinationInspectionFailed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C510" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">복제 위치의 상태를 확인할 수 없습니다: {0}. 폴더와 접근 권한을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D510" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not read the destination state: {0}. Check the folder and access permissions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" t="n">
+        <x:v>3094</x:v>
+      </x:c>
+      <x:c r="B511" t="str">
+        <x:v>AppLanguageHeading</x:v>
+      </x:c>
+      <x:c r="C511" t="str">
+        <x:v>언어</x:v>
+      </x:c>
+      <x:c r="D511" t="str">
+        <x:v>Language</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" t="n">
+        <x:v>3095</x:v>
+      </x:c>
+      <x:c r="B512" t="str">
+        <x:v>AppLanguageDescription</x:v>
+      </x:c>
+      <x:c r="C512" t="str">
+        <x:v>앱에서 사용할 언어를 선택합니다. 변경 사항은 즉시 적용됩니다.</x:v>
+      </x:c>
+      <x:c r="D512" t="str">
+        <x:v>Choose the app language. Changes apply immediately.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" t="n">
+        <x:v>3096</x:v>
+      </x:c>
+      <x:c r="B513" t="str">
+        <x:v>AppLanguageKorean</x:v>
+      </x:c>
+      <x:c r="C513" t="str">
+        <x:v>한국어</x:v>
+      </x:c>
+      <x:c r="D513" t="str">
+        <x:v>Korean</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514">
+      <x:c r="A514" t="n">
+        <x:v>3097</x:v>
+      </x:c>
+      <x:c r="B514" t="str">
+        <x:v>AppLanguageEnglish</x:v>
+      </x:c>
+      <x:c r="C514" t="str">
+        <x:v>영어</x:v>
+      </x:c>
+      <x:c r="D514" t="str">
+        <x:v>English</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515">
+      <x:c r="A515" t="n">
+        <x:v>3098</x:v>
+      </x:c>
+      <x:c r="B515" t="str">
+        <x:v>AppLanguageSaved</x:v>
+      </x:c>
+      <x:c r="C515" t="str">
+        <x:v>언어를 변경했습니다.</x:v>
+      </x:c>
+      <x:c r="D515" t="str">
+        <x:v>Language changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" t="n">
+        <x:v>3099</x:v>
+      </x:c>
+      <x:c r="B516" t="str">
+        <x:v>WorkingStopTrackingPartialFailure</x:v>
+      </x:c>
+      <x:c r="C516" t="str">
+        <x:v>.gitignore에 무시 규칙을 추가했지만 추적 중지 중 오류가 발생했습니다. 스테이징 상태를 확인하세요.
+{0}</x:v>
+      </x:c>
+      <x:c r="D516" t="str">
+        <x:v>Ignore rules were added to .gitignore, but stopping tracking encountered an error. Review the staged changes.
+{0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="B517" t="str">
+        <x:v>RemotePullFastForwardUnavailable</x:v>
+      </x:c>
+      <x:c r="C517" t="str">
+        <x:v>빠른 전진으로 통합할 수 없습니다. Pull 메뉴에서 병합 또는 재배치를 선택하세요.</x:v>
+      </x:c>
+      <x:c r="D517" t="str">
+        <x:v>Fast-forward is not possible. Choose merge or rebase from the Pull menu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" t="n">
+        <x:v>3101</x:v>
+      </x:c>
+      <x:c r="B518" t="str">
+        <x:v>RemotePullFetchFailedSummary</x:v>
+      </x:c>
+      <x:c r="C518" t="str">
+        <x:v>원격 변경을 가져오지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D518" t="str">
+        <x:v>Could not fetch remote changes. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" t="n">
+        <x:v>3102</x:v>
+      </x:c>
+      <x:c r="B519" t="str">
+        <x:v>RemotePullApplyFailedSummary</x:v>
+      </x:c>
+      <x:c r="C519" t="str">
+        <x:v>가져온 변경을 현재 브랜치에 반영하지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D519" t="str">
+        <x:v>Could not apply incoming changes to the current branch. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="B520" t="str">
+        <x:v>RemotePushFailedSummary</x:v>
+      </x:c>
+      <x:c r="C520" t="str">
+        <x:v>원격에 변경을 보내지 못했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D520" t="str">
+        <x:v>Could not push changes. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" t="n">
+        <x:v>3104</x:v>
+      </x:c>
+      <x:c r="B521" t="str">
+        <x:v>RemoteFetchFailedSummary</x:v>
+      </x:c>
+      <x:c r="C521" t="str">
+        <x:v>{0} 가져오기에 실패했습니다. 자세한 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D521" t="str">
+        <x:v>Fetch failed for {0}. See details.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" t="n">
+        <x:v>3105</x:v>
+      </x:c>
+      <x:c r="B522" t="str">
+        <x:v>RemoteOperationDetails</x:v>
+      </x:c>
+      <x:c r="C522" t="str">
+        <x:v>자세히</x:v>
+      </x:c>
+      <x:c r="D522" t="str">
+        <x:v>Details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" t="n">
+        <x:v>3106</x:v>
+      </x:c>
+      <x:c r="B523" t="str">
+        <x:v>ConflictSelectionSummary</x:v>
+      </x:c>
+      <x:c r="C523" t="str">
+        <x:v>{0}/{1}개 구간 선택</x:v>
+      </x:c>
+      <x:c r="D523" t="str">
+        <x:v>{0}/{1} sections chosen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" t="n">
+        <x:v>3107</x:v>
+      </x:c>
+      <x:c r="B524" t="str">
+        <x:v>WorkingMergeMessageReadFailed</x:v>
+      </x:c>
+      <x:c r="C524" t="str">
+        <x:v>병합 커밋 메시지를 읽지 못했습니다: {0}
+{1}</x:v>
+      </x:c>
+      <x:c r="D524" t="str">
+        <x:v>Could not read the merge commit message: {0}
+{1}</x:v>
+      </x:c>
+    </x:row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="525" spans="1:4">
+      <c r="A525">
+        <v>3124</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryLoadingChanges</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경 파일을 불러오는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loading changed files.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="526" spans="1:4">
+      <c r="A526">
+        <v>3125</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StashSavedRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보관은 완료됐지만 화면 갱신에 실패했습니다. 보관을 다시 실행하지 말고 갱신을 재시도하세요.</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The stash was saved, but refreshing failed. Retry the refresh instead of saving the stash again.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="527" spans="1:4">
+      <c r="A527">
+        <v>3126</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StashSaveRefreshRetry</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">갱신 재시도</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retry refresh</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="528" spans="1:4">
+      <c r="A528">
+        <v>3127</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StashSaveRefreshInProgress</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보관 결과를 다시 읽는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refreshing the saved stash results.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="529" spans="1:4">
+      <c r="A529">
+        <v>3128</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StashSaveCompletionResultMissing</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보관 완료 결과를 확인할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The stash completion result is unavailable.</t>
+        </is>
+      </c>
+    </row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -11147,6 +11147,66 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="530" spans="1:4">
+      <c r="A530">
+        <v>3129</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryNavigationFound</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 {0}(으)로 이동했습니다.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moved to commit {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="531" spans="1:4">
+      <c r="A531">
+        <v>3130</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryNavigationNotFoundInScope</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 조회 범위({1})에서 커밋 {0}을 찾지 못했습니다.</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commit {0} was not found in the current history scope ({1}).</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="532" spans="1:4">
+      <c r="A532">
+        <v>3131</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryNavigationFailed</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 {0} 이동에 필요한 이력을 읽지 못했습니다. {1}</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not read history to navigate to commit {0}. {1}</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -11207,6 +11207,46 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="533" spans="1:4">
+      <c r="A533">
+        <v>3132</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitFileTemporarySnapshotFailed</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 {0}의 커밋 스냅샷을 임시 읽기 전용 파일로 준비하지 못했습니다.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not prepare the commit snapshot of {0} as a temporary read-only file.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="534" spans="1:4">
+      <c r="A534">
+        <v>3133</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistorySnapshotOpenFailed</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 {0}의 스냅샷을 기본 연결 프로그램으로 열지 못했습니다. 파일 연결과 프로그램 설정을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not open the snapshot of {0} with its default application. Check the file association and application settings.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -11247,6 +11247,128 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="535" spans="1:4">
+      <c r="A535">
+        <v>3134</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MutationCompletedReadFailed</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 변경은 완료됐습니다. 최신 상태를 확인하려면 새로 고침하세요.
+{0}</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Git change completed. Refresh to read the updated state.
+{0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="539" spans="1:4">
+      <c r="A539">
+        <v>3138</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LocalCommitSucceededRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋은 완료됐지만 후속 조회 또는 화면 갱신에 실패했습니다. 새로 고침으로 조회만 다시 시도하세요. {0}</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The commit succeeded, but a follow-up read or screen refresh failed. Use Refresh to retry reads only. {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="540" spans="1:4">
+      <c r="A540">
+        <v>3139</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LocalCommittedWithoutHash</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋이 완료됐습니다.</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The commit succeeded.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="541" spans="1:4">
+      <c r="A541">
+        <v>3140</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StashSavedWithoutDetails</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보관 명령이 완료됐습니다.</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The stash save command succeeded.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="542" spans="1:4">
+      <c r="A542">
+        <v>3141</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DiscardResolutionSwitchFileMessage</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 파일의 저장하지 않은 편집을 버리고 {0} 파일로 이동할까요?</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discard the unsaved edits in the current file and open {0}?</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="543" spans="1:4">
+      <c r="A543">
+        <v>3142</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryActionStateReadFailed</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 변경은 완료됐지만 저장소 상태를 읽지 못했습니다. 새로 고침이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Git change completed, but the repository state could not be read. Refresh is required.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -11369,6 +11369,814 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="544" spans="1:4">
+      <c r="A544">
+        <v>3143</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertCommit</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 커밋 되돌리기…</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert this commit…</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="545" spans="1:4">
+      <c r="A545">
+        <v>3144</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertTitle</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 되돌리기</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert commit</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="546" spans="1:4">
+      <c r="A546">
+        <v>3145</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertTargetDescription</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장소: {0}
+현재 브랜치: {1}
+현재 HEAD: {2}
+대상 커밋: {3}
+{4}</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository: {0}
+Current branch: {1}
+Current HEAD: {2}
+Target commit: {3}
+{4}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="547" spans="1:4">
+      <c r="A547">
+        <v>3146</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertImpact</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="548" spans="1:4">
+      <c r="A548">
+        <v>3147</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertParentLabel</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병합 기준 부모</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mainline parent</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="549" spans="1:4">
+      <c r="A549">
+        <v>3148</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertParentChoice</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}번 부모 · {1} · {2}</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parent {0} · {1} · {2}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="550" spans="1:4">
+      <c r="A550">
+        <v>3149</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertMergeWarning</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="551" spans="1:4">
+      <c r="A551">
+        <v>3150</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertAction</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되돌리기</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="552" spans="1:4">
+      <c r="A552">
+        <v>3151</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertSucceeded</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="553" spans="1:4">
+      <c r="A553">
+        <v>3152</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertPaused</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="554" spans="1:4">
+      <c r="A554">
+        <v>3153</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="555" spans="1:4">
+      <c r="A555">
+        <v>3154</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertDetailsFailed</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not read the selected commit's parents and message.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="556" spans="1:4">
+      <c r="A556">
+        <v>3155</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertStateInvalid</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="557" spans="1:4">
+      <c r="A557">
+        <v>3156</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertTargetChanged</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="558" spans="1:4">
+      <c r="A558">
+        <v>3157</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertParentRequired</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Select a valid mainline parent for the merge commit.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="559" spans="1:4">
+      <c r="A559">
+        <v>3158</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertUnresolvedConflicts</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="560" spans="1:4">
+      <c r="A560">
+        <v>3159</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertAlreadyInProgress</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="561" spans="1:4">
+      <c r="A561">
+        <v>3160</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertOtherOperation</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="562" spans="1:4">
+      <c r="A562">
+        <v>3161</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertCleanRequired</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="563" spans="1:4">
+      <c r="A563">
+        <v>3162</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertDetachedHead</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="564" spans="1:4">
+      <c r="A564">
+        <v>3163</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertNoLongerInProgress</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The confirmed revert is no longer in progress.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="565" spans="1:4">
+      <c r="A565">
+        <v>3164</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertStateChanged</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="566" spans="1:4">
+      <c r="A566">
+        <v>3165</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertFailed</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="567" spans="1:4">
+      <c r="A567">
+        <v>3166</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertRepositoryChanged</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The execution repository differs from the confirmed repository.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="568" spans="1:4">
+      <c r="A568">
+        <v>3167</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CommitRevertUnstagedChanges</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="569" spans="1:4">
+      <c r="A569">
+        <v>3168</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertProgressLabel</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소 진행 중</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert in progress</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="570" spans="1:4">
+      <c r="A570">
+        <v>3169</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertCheckingConflicts</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking the conflict state.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="571" spans="1:4">
+      <c r="A571">
+        <v>3170</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertResolveBeforeContinue</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="572" spans="1:4">
+      <c r="A572">
+        <v>3171</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertReadyToContinue</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="573" spans="1:4">
+      <c r="A573">
+        <v>3172</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertContinueAction</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계속</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continue</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="574" spans="1:4">
+      <c r="A574">
+        <v>3173</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertAbortAction</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중단</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abort</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="575" spans="1:4">
+      <c r="A575">
+        <v>3174</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertAbortTitle</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행 중인 커밋 취소 중단</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abort the pending revert</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="576" spans="1:4">
+      <c r="A576">
+        <v>3175</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertAbortMessage</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="577" spans="1:4">
+      <c r="A577">
+        <v>3176</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RevertIncomingChange</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되돌리기 변경</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert changes</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="578" spans="1:4">
+      <c r="A578">
+        <v>3177</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RevertUseIncomingChange</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되돌리기 변경 사용</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use revert changes</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="579" spans="1:4">
+      <c r="A579">
+        <v>3178</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RevertIncomingIndexSource</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revert changes (index stage 3)</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="580" spans="1:4">
+      <c r="A580">
+        <v>3179</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="581" spans="1:4">
+      <c r="A581">
+        <v>3180</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertCompleted</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소가 완료됐습니다.</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The revert completed.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="582" spans="1:4">
+      <c r="A582">
+        <v>3181</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertPaused</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="583" spans="1:4">
+      <c r="A583">
+        <v>3182</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainRevertAborted</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pending revert was aborted.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12177,6 +12177,26 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="584" spans="1:4">
+      <c r="A584">
+        <v>3183</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HistoryRevertAborted</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pending revert was aborted.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12197,6 +12197,26 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="585" spans="1:4">
+      <c r="A585">
+        <v>3184</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LocalMutationErrorWithOperation</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: {1}</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: {1}</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12217,6 +12217,26 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="586" spans="1:4">
+      <c r="A586">
+        <v>3185</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12237,6 +12237,146 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="587" spans="1:4">
+      <c r="A587">
+        <v>3186</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageAction</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apply, save and stage remaining sections in all files</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="588" spans="1:4">
+      <c r="A588">
+        <v>3187</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchAllFilesScope</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} conflicted files · existing choices are preserved</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="589" spans="1:4">
+      <c r="A589">
+        <v>3188</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageTooltip</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="590" spans="1:4">
+      <c r="A590">
+        <v>3189</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageSummary</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="591" spans="1:4">
+      <c r="A591">
+        <v>3190</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageManualExcluded</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="592" spans="1:4">
+      <c r="A592">
+        <v>3191</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageFileResult</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: {1}</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="593" spans="1:4">
+      <c r="A593">
+        <v>3192</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConflictBatchStageRefreshFailed</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12377,6 +12377,866 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="594" spans="1:4">
+      <c r="A594">
+        <v>3193</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateHeading</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 업데이트</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Application update</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="595" spans="1:4">
+      <c r="A595">
+        <v>3194</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateDescription</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="596" spans="1:4">
+      <c r="A596">
+        <v>3195</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCurrentVersionLabel</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 버전</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current version</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="597" spans="1:4">
+      <c r="A597">
+        <v>3196</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateLatestVersionLabel</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최신 정식 버전</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latest official version</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="598" spans="1:4">
+      <c r="A598">
+        <v>3197</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateVersionUnknown</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인되지 않음</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not available</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="599" spans="1:4">
+      <c r="A599">
+        <v>3198</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateNotChecked</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Click Check for updates to look for the latest official release.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="600" spans="1:4">
+      <c r="A600">
+        <v>3199</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCheckAction</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 확인</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check for updates</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="601" spans="1:4">
+      <c r="A601">
+        <v>3200</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateChecking</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking the latest official release.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="602" spans="1:4">
+      <c r="A602">
+        <v>3201</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateNoOfficialRelease</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시된 정식 릴리스가 없습니다.</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No official release has been published.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="603" spans="1:4">
+      <c r="A603">
+        <v>3202</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateUpToDate</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No newer official release is available.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="604" spans="1:4">
+      <c r="A604">
+        <v>3203</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateAvailable</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official version {0} is available.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="605" spans="1:4">
+      <c r="A605">
+        <v>3204</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCheckFailed</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not check for updates: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="606" spans="1:4">
+      <c r="A606">
+        <v>3205</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateRestartAction</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 후 재시작</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Update and restart</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="607" spans="1:4">
+      <c r="A607">
+        <v>3206</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateDownloadingKnown</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드 중: {0} / {1} MiB</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downloading: {0} / {1} MiB</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="608" spans="1:4">
+      <c r="A608">
+        <v>3207</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateDownloadingUnknown</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드 중: {0} MiB</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downloading: {0} MiB</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="609" spans="1:4">
+      <c r="A609">
+        <v>3208</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCancelAction</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="610" spans="1:4">
+      <c r="A610">
+        <v>3209</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCancelled</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update was cancelled. The current application was not changed.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="611" spans="1:4">
+      <c r="A611">
+        <v>3210</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateDownloadFailed</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update download or verification failed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="612" spans="1:4">
+      <c r="A612">
+        <v>3211</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateReady</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version {0} has been downloaded and verified.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="613" spans="1:4">
+      <c r="A613">
+        <v>3212</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateRestartPreparing</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preparing to close the application normally and restart after updating.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="614" spans="1:4">
+      <c r="A614">
+        <v>3213</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateRestartCancelled</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="615" spans="1:4">
+      <c r="A615">
+        <v>3214</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateRestartFailed</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not prepare the update and restart: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="616" spans="1:4">
+      <c r="A616">
+        <v>3215</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateRestartScheduled</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="617" spans="1:4">
+      <c r="A617">
+        <v>3216</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateReleaseAction</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정식 릴리스 페이지 열기</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open official release page</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="618" spans="1:4">
+      <c r="A618">
+        <v>3217</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateInstallUnsupported</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="619" spans="1:4">
+      <c r="A619">
+        <v>3218</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreDeploymentRequired</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="620" spans="1:4">
+      <c r="A620">
+        <v>3219</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="621" spans="1:4">
+      <c r="A621">
+        <v>3220</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreQueryFailed</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="622" spans="1:4">
+      <c r="A622">
+        <v>3221</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreQueryUnavailable</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="623" spans="1:4">
+      <c r="A623">
+        <v>3222</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreReleaseInvalid</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="624" spans="1:4">
+      <c r="A624">
+        <v>3223</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreAssetUnavailable</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="625" spans="1:4">
+      <c r="A625">
+        <v>3224</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreDigestMissing</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="626" spans="1:4">
+      <c r="A626">
+        <v>3225</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="627" spans="1:4">
+      <c r="A627">
+        <v>3226</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="628" spans="1:4">
+      <c r="A628">
+        <v>3227</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreDigestMismatch</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="629" spans="1:4">
+      <c r="A629">
+        <v>3228</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCorePrepareFailed</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="630" spans="1:4">
+      <c r="A630">
+        <v>3229</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreGitBusy</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="631" spans="1:4">
+      <c r="A631">
+        <v>3230</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreCloseUnavailable</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="632" spans="1:4">
+      <c r="A632">
+        <v>3231</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreReplaceFailed</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="633" spans="1:4">
+      <c r="A633">
+        <v>3232</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateCoreRollbackFailed</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="634" spans="1:4">
+      <c r="A634">
+        <v>3233</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateDownloadRequestFailed</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="635" spans="1:4">
+      <c r="A635">
+        <v>3234</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateLaunchFailed</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="636" spans="1:4">
+      <c r="A636">
+        <v>3235</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AppUpdateReleaseOpenFailed</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Could not open the official release page. Please try again shortly.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -13237,6 +13237,306 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="637" spans="1:4">
+      <c r="A637">
+        <v>3236</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchHeading</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 변경 자동 확인</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote checks</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="638" spans="1:4">
+      <c r="A638">
+        <v>3237</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchDescription</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="639" spans="1:4">
+      <c r="A639">
+        <v>3238</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchEnabledLabel</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주기적으로 원격 변경 확인</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check for remote changes periodically</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="640" spans="1:4">
+      <c r="A640">
+        <v>3239</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchIntervalLabel</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 주기</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check interval</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="641" spans="1:4">
+      <c r="A641">
+        <v>3240</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetch1Minute</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1분</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 minute</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="642" spans="1:4">
+      <c r="A642">
+        <v>3241</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetch5Minutes</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5분</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="643" spans="1:4">
+      <c r="A643">
+        <v>3242</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetch10Minutes</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10분</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="644" spans="1:4">
+      <c r="A644">
+        <v>3243</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetch30Minutes</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30분</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="645" spans="1:4">
+      <c r="A645">
+        <v>3244</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchSettingsSaved</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote check settings saved.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="646" spans="1:4">
+      <c r="A646">
+        <v>3245</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AutoFetchOperationName</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 자동 확인</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote check</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="647" spans="1:4">
+      <c r="A647">
+        <v>3246</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemoteIncomingCommits</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">받을 새 커밋 {0}개</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0} new commits to pull</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="648" spans="1:4">
+      <c r="A648">
+        <v>3247</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemoteAutoFetchFailed</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="649" spans="1:4">
+      <c r="A649">
+        <v>3248</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="650" spans="1:4">
+      <c r="A650">
+        <v>3249</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemoteAutoFetchRequestFailed</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="651" spans="1:4">
+      <c r="A651">
+        <v>3250</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RemoteAutoFetchTimedOut</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="588">
   <x:si>
     <x:t xml:space="preserve">Id</x:t>
   </x:si>
@@ -1728,6 +1728,51 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">String</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmoduleOpenNotRegistered</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서브모듈 경로가 현재 상위 저장소에 등록되어 있지 않습니다: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The submodule path is not registered in the current parent repository: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmoduleOpenConfigUnavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상위 저장소의 서브모듈 경로 설정을 읽을 수 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The parent repository's submodule path configuration could not be read.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmoduleOpenDirectoryUnavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서브모듈 폴더가 없거나 접근할 수 없습니다: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The submodule folder is missing or unavailable: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmoduleOpenUninitialized</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서브모듈이 초기화되지 않아 저장소를 열 수 없습니다: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The submodule repository cannot be opened because it is not initialized: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmoduleOpenRepositoryUnavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선택한 경로에서 실제 하위 Git 저장소를 열 수 없습니다: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>An actual child Git repository could not be opened at the selected path: {0}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13537,6 +13582,76 @@
         </is>
       </c>
     </row>
+    <x:row r="652">
+      <x:c r="A652">
+        <x:v>3251</x:v>
+      </x:c>
+      <x:c r="B652" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="C652" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D652" t="s">
+        <x:v>575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653">
+      <x:c r="A653">
+        <x:v>3252</x:v>
+      </x:c>
+      <x:c r="B653" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="C653" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="D653" t="s">
+        <x:v>578</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654">
+      <x:c r="A654">
+        <x:v>3253</x:v>
+      </x:c>
+      <x:c r="B654" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="C654" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="D654" t="s">
+        <x:v>581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655">
+      <x:c r="A655">
+        <x:v>3254</x:v>
+      </x:c>
+      <x:c r="B655" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="C655" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="D655" t="s">
+        <x:v>584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656">
+      <x:c r="A656">
+        <x:v>3255</x:v>
+      </x:c>
+      <x:c r="B656" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="C656" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="D656" t="s">
+        <x:v>587</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="588">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="629">
   <x:si>
     <x:t xml:space="preserve">Id</x:t>
   </x:si>
@@ -1773,6 +1773,135 @@
   </x:si>
   <x:si>
     <x:t>An actual child Git repository could not be opened at the selected path: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushAction</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Push</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushTitle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 Push</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Push tag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushConfirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그: {0}
+객체: {1}
+원격: {2}
+선택한 태그 하나만 전송합니다. 기존 원격 태그는 덮어쓰지 않습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag: {0}
+Object: {1}
+Remote: {2}
+Only this tag will be sent. Existing remote tags will not be overwritten.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushProgress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 {0} → {1} 전송 중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pushing tag {0} to {1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushSucceeded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 {0}을(를) {1}에 전송했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag {0} was pushed to {1}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushAlreadyPresent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {1}에 태그 {0}의 같은 객체가 이미 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remote {1} already has the same object for tag {0}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushRemoteConflict</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {1}의 태그 {0}이(가) 다른 객체를 가리킵니다. 덮어쓰지 않았습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag {0} on remote {1} points to a different object. It was not overwritten.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 {0}을(를) 원격 {1}에 전송하지 못했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag {0} could not be pushed to remote {1}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushLookupFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {1}의 태그 {0}을(를) 확인하지 못했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag {0} could not be checked on remote {1}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushLocalChanged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로컬 태그 {0}이(가) 변경되었거나 없어졌습니다. 태그를 다시 선택해 주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Local tag {0} has changed or no longer exists. Select the tag again.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushLocalReadFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로컬 태그 {0}을(를) 읽지 못했습니다: {1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Local tag {0} could not be read: {1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushUrlChanged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {0}의 Push 주소가 변경되어 전송하지 않았습니다. 대상을 다시 확인해 주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The push URL for remote {0} changed. Nothing was sent. Confirm the target again.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushRemoteUnavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>등록된 원격 {0}의 Push 주소를 읽을 수 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The push URL for registered remote {0} could not be read.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushMultiplePushUrls</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {0}에 Push 주소가 여러 개 있어 태그를 전송할 수 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remote {0} has multiple push URLs, so the tag cannot be pushed.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2041,7 +2170,7 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="629">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="650">
   <x:si>
     <x:t xml:space="preserve">Id</x:t>
   </x:si>
@@ -1902,6 +1902,71 @@
   </x:si>
   <x:si>
     <x:t>Remote {0} has multiple push URLs, so the tag cannot be pushed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RemoteTagPushCandidatesChecking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보낼 태그가 있는지 확인하는 중입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Checking for tags to push.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RemoteTagPushCandidatesCheckFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보낼 태그를 확인하지 못했습니다: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Could not check tags to push: {0}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushCandidatesLoading</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {0}에 보낼 태그를 확인하는 중입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Checking which tags can be pushed to remote {0}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushCandidatesEmpty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {0}에 보낼 새 로컬 태그가 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>There are no new local tags to push to remote {0}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushCandidatesLookupFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원격 {0}에서 태그 전송 후보를 조회하지 못했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tag push candidates could not be read from remote {0}.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushCandidatesSuperseded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 후보 조회가 다른 요청으로 대체되었습니다. 다시 조회해 주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Another request replaced this tag candidate lookup. Reload the candidates.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TagPushCandidatesRefreshFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{0}
+태그 후보를 다시 조회해야 합니다: {1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{0}
+The tag candidates need to be refreshed: {1}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2170,7 +2235,7 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="650">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="656">
   <x:si>
     <x:t xml:space="preserve">Id</x:t>
   </x:si>
@@ -1967,6 +1967,24 @@
   <x:si>
     <x:t>{0}
 The tag candidates need to be refreshed: {1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MainStatusDetailsTitle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작업 상태 자세히</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Operation details</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MainStatusCopyFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상태 메시지를 복사하지 못했습니다. 텍스트를 선택해 복사하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Could not copy the status message. Select the text and copy it.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2235,7 +2253,7 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2235,7 +2235,7 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="678"><c r="A678" t="n"><v>3277</v></c><c r="B678" t="str"><v>WorktreeStatusSubmodule</v></c><c r="C678" t="str"><v>서브모듈</v></c><c r="D678" t="str"><v>Submodule</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="679"><c r="A679" t="n"><v>3278</v></c><c r="B679" t="str"><v>WorktreeStatusSubmodulePreview</v></c><c r="C679" t="str"><v>서브모듈 변경 · 내부 파일 변경은 서브모듈 저장소에서 확인하세요.</v></c><c r="D679" t="str"><v>Submodule changes · Open the submodule repository to inspect changes to its files.</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="680"><c r="A680" t="n"><v>3279</v></c><c r="B680" t="str"><v>WorkingSubmoduleDiscardUnsupported</v></c><c r="C680" t="str"><v>이 서브모듈 상태는 상위 저장소에서 되돌릴 수 없습니다. 서브모듈 저장소를 열어 처리하세요: {0}</v></c><c r="D680" t="str"><v>This submodule state cannot be restored from the parent repository. Open the submodule repository to handle it: {0}</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="681"><c r="A681" t="n"><v>3280</v></c><c r="B681" t="str"><v>WorkingSubmoduleOperationInProgress</v></c><c r="C681" t="str"><v>서브모듈에 진행 중인 Git 작업이 있어 커밋 위치를 되돌리지 않았습니다. 서브모듈 저장소에서 작업을 먼저 완료하거나 중단하세요: {0}</v></c><c r="D681" t="str"><v>The submodule has a Git operation in progress. Complete or abort it in the submodule repository before restoring its commit: {0}</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="682"><c r="A682" t="n"><v>3281</v></c><c r="B682" t="str"><v>WorkingSubmoduleDirty</v></c><c r="C682" t="str"><v>서브모듈 내부에 미커밋 변경이나 미추적 파일이 있어 커밋 위치를 되돌리지 않았습니다. 서브모듈 저장소를 열어 먼저 처리하세요: {0}</v></c><c r="D682" t="str"><v>The submodule has uncommitted changes or untracked files. Handle them in the submodule repository before restoring its commit: {0}</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="683"><c r="A683" t="n"><v>3282</v></c><c r="B683" t="str"><v>WorkingSubmoduleCommitUnavailable</v></c><c r="C683" t="str"><v>복원할 커밋을 서브모듈에서 읽을 수 없습니다. 서브모듈 저장소에서 상태를 확인하고 필요한 커밋을 가져온 뒤 다시 시도하세요: {0} · {1}</v></c><c r="D683" t="str"><v>The target commit cannot be read in the submodule. Check the submodule repository and fetch the commit if needed, then try again: {0} · {1}</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="684"><c r="A684" t="n"><v>3283</v></c><c r="B684" t="str"><v>DiscardSubmoduleTitle</v></c><c r="C684" t="str"><v>서브모듈 커밋 위치 되돌리기</v></c><c r="D684" t="str"><v>Restore submodule commit</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="685"><c r="A685" t="n"><v>3284</v></c><c r="B685" t="str"><v>DiscardSubmoduleImpact</v></c><c r="C685" t="str"><v>서브모듈 {0}개의 체크아웃을 상위 저장소의 스테이징된 커밋으로 되돌립니다. 서브모듈은 분리된 HEAD 상태가 되며 브랜치와 커밋 기록은 유지됩니다. 내부의 미커밋 변경은 폐기하지 않습니다.</v></c><c r="D685" t="str"><v>Restore the checkout of {0} submodules to the commits recorded in the parent index. The submodules will have detached HEADs; branches and commit history are preserved. Uncommitted changes inside them will not be discarded.</v></c></row><row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="686"><c r="A686" t="n"><v>3285</v></c><c r="B686" t="str"><v>DiscardSubmoduleConfirm</v></c><c r="C686" t="str"><v>커밋 위치 되돌리기</v></c><c r="D686" t="str"><v>Restore commit</v></c></row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2253,7 +2253,11 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row><x:row r="680" spans="1:4"><x:c r="A680"><x:v>3279</x:v></x:c><x:c r="B680" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathLabel</x:t></x:is></x:c><x:c r="C680" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 경로 (선택)</x:t></x:is></x:c><x:c r="D680" t="inlineStr"><x:is><x:t xml:space="preserve">Folder path (optional)</x:t></x:is></x:c></x:row><x:row r="681" spans="1:4"><x:c r="A681"><x:v>3280</x:v></x:c><x:c r="B681" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathHint</x:t></x:is></x:c><x:c r="C681" t="inlineStr"><x:is><x:t xml:space="preserve">비워두면 선택한 파일만 무시합니다. 폴더를 입력하면 해당 폴더와 하위의 미추적 항목 및 앞으로 추가할 파일을 무시합니다. 예: Design/Deliverables/</x:t></x:is></x:c><x:c r="D681" t="inlineStr"><x:is><x:t xml:space="preserve">Leave empty to ignore only the selected files. Enter a folder to ignore its untracked contents and future files. Example: Design/Deliverables/</x:t></x:is></x:c></x:row><x:row r="682" spans="1:4"><x:c r="A682"><x:v>3281</x:v></x:c><x:c r="B682" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryConfirmDescription</x:t></x:is></x:c><x:c r="C682" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 전체: {0}
+적용 위치: {1}
+하위 미추적 항목과 앞으로 추가할 파일을 무시합니다. 이미 추적 중인 파일은 유지됩니다.</x:t></x:is></x:c><x:c r="D682" t="inlineStr"><x:is><x:t xml:space="preserve">Entire folder: {0}
+Ignore location: {1}
+Untracked contents and future files will be ignored. Already tracked files are unchanged.</x:t></x:is></x:c></x:row><x:row r="683" spans="1:4"><x:c r="A683"><x:v>3282</x:v></x:c><x:c r="B683" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPreparing</x:t></x:is></x:c><x:c r="C683" t="inlineStr"><x:is><x:t xml:space="preserve">무시할 범위와 규칙을 준비하고 있습니다.</x:t></x:is></x:c><x:c r="D683" t="inlineStr"><x:is><x:t xml:space="preserve">Preparing the ignore scope and rule.</x:t></x:is></x:c></x:row><x:row r="684" spans="1:4"><x:c r="A684"><x:v>3283</x:v></x:c><x:c r="B684" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryUnavailable</x:t></x:is></x:c><x:c r="C684" t="inlineStr"><x:is><x:t xml:space="preserve">폴더를 사용할 수 없습니다. 저장소 안에 있는 실제 폴더 경로를 입력하세요: {0}</x:t></x:is></x:c><x:c r="D684" t="inlineStr"><x:is><x:t xml:space="preserve">The folder is unavailable. Enter an existing folder path inside the repository: {0}</x:t></x:is></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2253,7 +2253,7 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row><x:row r="680" spans="1:4"><x:c r="A680"><x:v>3279</x:v></x:c><x:c r="B680" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathLabel</x:t></x:is></x:c><x:c r="C680" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 경로 (선택)</x:t></x:is></x:c><x:c r="D680" t="inlineStr"><x:is><x:t xml:space="preserve">Folder path (optional)</x:t></x:is></x:c></x:row><x:row r="681" spans="1:4"><x:c r="A681"><x:v>3280</x:v></x:c><x:c r="B681" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathHint</x:t></x:is></x:c><x:c r="C681" t="inlineStr"><x:is><x:t xml:space="preserve">비워두면 선택한 파일만 무시합니다. 폴더를 입력하면 해당 폴더와 하위의 미추적 항목 및 앞으로 추가할 파일을 무시합니다. 예: Design/Deliverables/</x:t></x:is></x:c><x:c r="D681" t="inlineStr"><x:is><x:t xml:space="preserve">Leave empty to ignore only the selected files. Enter a folder to ignore its untracked contents and future files. Example: Design/Deliverables/</x:t></x:is></x:c></x:row><x:row r="682" spans="1:4"><x:c r="A682"><x:v>3281</x:v></x:c><x:c r="B682" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryConfirmDescription</x:t></x:is></x:c><x:c r="C682" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 전체: {0}
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row><x:row r="680" spans="1:4"><x:c r="A680"><x:v>3279</x:v></x:c><x:c r="B680" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathLabel</x:t></x:is></x:c><x:c r="C680" t="inlineStr"><x:is><x:t xml:space="preserve">무시할 경로</x:t></x:is></x:c><x:c r="D680" t="inlineStr"><x:is><x:t xml:space="preserve">Path to ignore</x:t></x:is></x:c></x:row><x:row r="681" spans="1:4"><x:c r="A681"><x:v>3280</x:v></x:c><x:c r="B681" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathHint</x:t></x:is></x:c><x:c r="C681" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 파일 경로를 폴더 경로로 바꾸면 폴더 전체를 무시합니다. 비워두면 선택한 파일들을 그대로 무시합니다.</x:t></x:is></x:c><x:c r="D681" t="inlineStr"><x:is><x:t xml:space="preserve">Change the selected file path to a folder path to ignore the entire folder. Leave empty to ignore the selected files.</x:t></x:is></x:c></x:row><x:row r="682" spans="1:4"><x:c r="A682"><x:v>3281</x:v></x:c><x:c r="B682" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryConfirmDescription</x:t></x:is></x:c><x:c r="C682" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 전체: {0}
 적용 위치: {1}
 하위 미추적 항목과 앞으로 추가할 파일을 무시합니다. 이미 추적 중인 파일은 유지됩니다.</x:t></x:is></x:c><x:c r="D682" t="inlineStr"><x:is><x:t xml:space="preserve">Entire folder: {0}
 Ignore location: {1}

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2253,11 +2253,15 @@
 Current branch: {1}
 Current HEAD: {2}
 Target commit: {3}
-{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row><x:row r="680" spans="1:4"><x:c r="A680"><x:v>3279</x:v></x:c><x:c r="B680" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathLabel</x:t></x:is></x:c><x:c r="C680" t="inlineStr"><x:is><x:t xml:space="preserve">무시할 경로</x:t></x:is></x:c><x:c r="D680" t="inlineStr"><x:is><x:t xml:space="preserve">Path to ignore</x:t></x:is></x:c></x:row><x:row r="681" spans="1:4"><x:c r="A681"><x:v>3280</x:v></x:c><x:c r="B681" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathHint</x:t></x:is></x:c><x:c r="C681" t="inlineStr"><x:is><x:t xml:space="preserve">선택한 파일 경로를 폴더 경로로 바꾸면 폴더 전체를 무시합니다. 비워두면 선택한 파일들을 그대로 무시합니다.</x:t></x:is></x:c><x:c r="D681" t="inlineStr"><x:is><x:t xml:space="preserve">Change the selected file path to a folder path to ignore the entire folder. Leave empty to ignore the selected files.</x:t></x:is></x:c></x:row><x:row r="682" spans="1:4"><x:c r="A682"><x:v>3281</x:v></x:c><x:c r="B682" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryConfirmDescription</x:t></x:is></x:c><x:c r="C682" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 전체: {0}
+{4}</t></is></c></row><row r="547" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A547"><v>3146</v></c><c r="B547" t="inlineStr"><is><t xml:space="preserve">HistoryRevertImpact</t></is></c><c r="C547" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 변경을 취소하는 새 커밋을 만듭니다. 기존 커밋과 원격 참조는 유지합니다.</t></is></c><c r="D547" t="inlineStr"><is><t xml:space="preserve">Create a new commit that reverses the selected commit's changes. Existing commits and remote references are preserved.</t></is></c></row><row r="548" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A548"><v>3147</v></c><c r="B548" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentLabel</t></is></c><c r="C548" t="inlineStr"><is><t xml:space="preserve">병합 기준 부모</t></is></c><c r="D548" t="inlineStr"><is><t xml:space="preserve">Mainline parent</t></is></c></row><row r="549" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A549"><v>3148</v></c><c r="B549" t="inlineStr"><is><t xml:space="preserve">HistoryRevertParentChoice</t></is></c><c r="C549" t="inlineStr"><is><t xml:space="preserve">{0}번 부모 · {1} · {2}</t></is></c><c r="D549" t="inlineStr"><is><t xml:space="preserve">Parent {0} · {1} · {2}</t></is></c></row><row r="550" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A550"><v>3149</v></c><c r="B550" t="inlineStr"><is><t xml:space="preserve">HistoryRevertMergeWarning</t></is></c><c r="C550" t="inlineStr"><is><t xml:space="preserve">선택한 부모를 기준으로 병합 변경을 취소합니다. 이후 병합에서 가져오는 변경에도 영향을 줄 수 있습니다.</t></is></c><c r="D550" t="inlineStr"><is><t xml:space="preserve">Reverse the merge changes relative to the chosen parent. This can also affect changes introduced by later merges.</t></is></c></row><row r="551" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A551"><v>3150</v></c><c r="B551" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAction</t></is></c><c r="C551" t="inlineStr"><is><t xml:space="preserve">되돌리기</t></is></c><c r="D551" t="inlineStr"><is><t xml:space="preserve">Revert</t></is></c></row><row r="552" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A552"><v>3151</v></c><c r="B552" t="inlineStr"><is><t xml:space="preserve">HistoryRevertSucceeded</t></is></c><c r="C552" t="inlineStr"><is><t xml:space="preserve">커밋 {0}의 변경을 취소하는 새 커밋을 만들었습니다.</t></is></c><c r="D552" t="inlineStr"><is><t xml:space="preserve">Created a new commit that reverses the changes from {0}.</t></is></c></row><row r="553" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A553"><v>3152</v></c><c r="B553" t="inlineStr"><is><t xml:space="preserve">HistoryRevertPaused</t></is></c><c r="C553" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결·저장·스테이징한 뒤 계속하거나 표시된 오류를 확인하세요.</t></is></c><c r="D553" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve, save, and stage conflicts before continuing, or review the reported error.</t></is></c></row><row r="554" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A554"><v>3153</v></c><c r="B554" t="inlineStr"><is><t xml:space="preserve">CommitRevertRefreshFailed</t></is></c><c r="C554" t="inlineStr"><is><t xml:space="preserve">커밋 취소 이후 상태를 갱신하지 못했습니다. 새로 고침으로 조회를 다시 시도하세요. {0}</t></is></c><c r="D554" t="inlineStr"><is><t xml:space="preserve">Could not refresh the state after the revert operation. Use Refresh to retry the read. {0}</t></is></c></row><row r="555" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A555"><v>3154</v></c><c r="B555" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetailsFailed</t></is></c><c r="C555" t="inlineStr"><is><t xml:space="preserve">선택 커밋의 부모와 메시지를 읽지 못했습니다.</t></is></c><c r="D555" t="inlineStr"><is><t xml:space="preserve">Could not read the selected commit's parents and message.</t></is></c></row><row r="556" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A556"><v>3155</v></c><c r="B556" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateInvalid</t></is></c><c r="C556" t="inlineStr"><is><t xml:space="preserve">Git 작업 상태를 확인하지 못했습니다. 새로 고침한 뒤 다시 시도하세요.</t></is></c><c r="D556" t="inlineStr"><is><t xml:space="preserve">Could not determine the Git operation state. Refresh before trying again.</t></is></c></row><row r="557" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A557"><v>3156</v></c><c r="B557" t="inlineStr"><is><t xml:space="preserve">CommitRevertTargetChanged</t></is></c><c r="C557" t="inlineStr"><is><t xml:space="preserve">확인 후 현재 브랜치 또는 HEAD가 바뀌었습니다. 다시 확인하세요.</t></is></c><c r="D557" t="inlineStr"><is><t xml:space="preserve">The current branch or HEAD changed after confirmation. Review it again.</t></is></c></row><row r="558" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A558"><v>3157</v></c><c r="B558" t="inlineStr"><is><t xml:space="preserve">CommitRevertParentRequired</t></is></c><c r="C558" t="inlineStr"><is><t xml:space="preserve">병합 커밋의 유효한 기준 부모를 선택해야 합니다.</t></is></c><c r="D558" t="inlineStr"><is><t xml:space="preserve">Select a valid mainline parent for the merge commit.</t></is></c></row><row r="559" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A559"><v>3158</v></c><c r="B559" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnresolvedConflicts</t></is></c><c r="C559" t="inlineStr"><is><t xml:space="preserve">미해결 충돌 {0}개가 남아 있어 되돌리기를 계속할 수 없습니다.</t></is></c><c r="D559" t="inlineStr"><is><t xml:space="preserve">Cannot continue the revert while {0} conflicts remain unresolved.</t></is></c></row><row r="560" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A560"><v>3159</v></c><c r="B560" t="inlineStr"><is><t xml:space="preserve">CommitRevertAlreadyInProgress</t></is></c><c r="C560" t="inlineStr"><is><t xml:space="preserve">이미 되돌리기가 진행 중입니다. 기존 작업을 계속하거나 중단하세요.</t></is></c><c r="D560" t="inlineStr"><is><t xml:space="preserve">A revert is already in progress. Continue or abort the existing operation.</t></is></c></row><row r="561" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A561"><v>3160</v></c><c r="B561" t="inlineStr"><is><t xml:space="preserve">CommitRevertOtherOperation</t></is></c><c r="C561" t="inlineStr"><is><t xml:space="preserve">다른 Git 작업이 진행 중이어서 되돌리기를 시작할 수 없습니다.</t></is></c><c r="D561" t="inlineStr"><is><t xml:space="preserve">Cannot start a revert while another Git operation is in progress.</t></is></c></row><row r="562" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A562"><v>3161</v></c><c r="B562" t="inlineStr"><is><t xml:space="preserve">CommitRevertCleanRequired</t></is></c><c r="C562" t="inlineStr"><is><t xml:space="preserve">작업 트리 또는 인덱스에 변경이 있습니다. 먼저 직접 정리하세요. 파일을 자동으로 버리거나 보관하지 않습니다.</t></is></c><c r="D562" t="inlineStr"><is><t xml:space="preserve">The working tree or index has changes. Resolve them first. Files are not discarded or stashed automatically.</t></is></c></row><row r="563" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A563"><v>3162</v></c><c r="B563" t="inlineStr"><is><t xml:space="preserve">CommitRevertDetachedHead</t></is></c><c r="C563" t="inlineStr"><is><t xml:space="preserve">로컬 브랜치에서만 되돌리기를 시작할 수 있습니다. 현재 HEAD는 분리된 상태입니다.</t></is></c><c r="D563" t="inlineStr"><is><t xml:space="preserve">Start a revert on a local branch. HEAD is currently detached.</t></is></c></row><row r="564" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A564"><v>3163</v></c><c r="B564" t="inlineStr"><is><t xml:space="preserve">CommitRevertNoLongerInProgress</t></is></c><c r="C564" t="inlineStr"><is><t xml:space="preserve">확인한 되돌리기가 더 이상 진행 중이 아닙니다.</t></is></c><c r="D564" t="inlineStr"><is><t xml:space="preserve">The confirmed revert is no longer in progress.</t></is></c></row><row r="565" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A565"><v>3164</v></c><c r="B565" t="inlineStr"><is><t xml:space="preserve">CommitRevertStateChanged</t></is></c><c r="C565" t="inlineStr"><is><t xml:space="preserve">확인 후 되돌리기 대상 또는 작업 상태가 바뀌었습니다. 최신 상태를 다시 확인하세요.</t></is></c><c r="D565" t="inlineStr"><is><t xml:space="preserve">The revert target or working state changed after confirmation. Review the latest state.</t></is></c></row><row r="566" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A566"><v>3165</v></c><c r="B566" t="inlineStr"><is><t xml:space="preserve">CommitRevertFailed</t></is></c><c r="C566" t="inlineStr"><is><t xml:space="preserve">Git 되돌리기 명령이 완료되지 않았습니다(종료 코드 {0}). 진행 상태를 확인하세요.</t></is></c><c r="D566" t="inlineStr"><is><t xml:space="preserve">The Git revert command did not complete (exit code {0}). Check the operation state.</t></is></c></row><row r="567" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A567"><v>3166</v></c><c r="B567" t="inlineStr"><is><t xml:space="preserve">CommitRevertRepositoryChanged</t></is></c><c r="C567" t="inlineStr"><is><t xml:space="preserve">확인한 저장소와 실행 대상 저장소가 다릅니다.</t></is></c><c r="D567" t="inlineStr"><is><t xml:space="preserve">The execution repository differs from the confirmed repository.</t></is></c></row><row r="568" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A568"><v>3167</v></c><c r="B568" t="inlineStr"><is><t xml:space="preserve">CommitRevertUnstagedChanges</t></is></c><c r="C568" t="inlineStr"><is><t xml:space="preserve">작업 트리의 변경을 스테이징한 뒤 되돌리기를 계속하세요. 새 파일이나 관련 없는 변경도 먼저 확인해야 합니다.</t></is></c><c r="D568" t="inlineStr"><is><t xml:space="preserve">Stage the intended working changes before continuing the revert. Review new files and unrelated edits first.</t></is></c></row><row r="569" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A569"><v>3168</v></c><c r="B569" t="inlineStr"><is><t xml:space="preserve">MainRevertProgressLabel</t></is></c><c r="C569" t="inlineStr"><is><t xml:space="preserve">커밋 취소 진행 중</t></is></c><c r="D569" t="inlineStr"><is><t xml:space="preserve">Revert in progress</t></is></c></row><row r="570" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A570"><v>3169</v></c><c r="B570" t="inlineStr"><is><t xml:space="preserve">MainRevertCheckingConflicts</t></is></c><c r="C570" t="inlineStr"><is><t xml:space="preserve">충돌 상태를 확인하는 중입니다.</t></is></c><c r="D570" t="inlineStr"><is><t xml:space="preserve">Checking the conflict state.</t></is></c></row><row r="571" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A571"><v>3170</v></c><c r="B571" t="inlineStr"><is><t xml:space="preserve">MainRevertResolveBeforeContinue</t></is></c><c r="C571" t="inlineStr"><is><t xml:space="preserve">충돌 {0}개를 해결하고 저장·스테이징한 뒤 계속하세요.</t></is></c><c r="D571" t="inlineStr"><is><t xml:space="preserve">Resolve, save, and stage {0} conflicts before continuing.</t></is></c></row><row r="572" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A572"><v>3171</v></c><c r="B572" t="inlineStr"><is><t xml:space="preserve">MainRevertReadyToContinue</t></is></c><c r="C572" t="inlineStr"><is><t xml:space="preserve">충돌 해결 내용을 저장·스테이징했다면 커밋 취소를 계속하세요.</t></is></c><c r="D572" t="inlineStr"><is><t xml:space="preserve">Continue the revert after saving and staging your conflict resolutions.</t></is></c></row><row r="573" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A573"><v>3172</v></c><c r="B573" t="inlineStr"><is><t xml:space="preserve">MainRevertContinueAction</t></is></c><c r="C573" t="inlineStr"><is><t xml:space="preserve">계속</t></is></c><c r="D573" t="inlineStr"><is><t xml:space="preserve">Continue</t></is></c></row><row r="574" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A574"><v>3173</v></c><c r="B574" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortAction</t></is></c><c r="C574" t="inlineStr"><is><t xml:space="preserve">중단</t></is></c><c r="D574" t="inlineStr"><is><t xml:space="preserve">Abort</t></is></c></row><row r="575" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A575"><v>3174</v></c><c r="B575" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortTitle</t></is></c><c r="C575" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소 중단</t></is></c><c r="D575" t="inlineStr"><is><t xml:space="preserve">Abort the pending revert</t></is></c></row><row r="576" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A576"><v>3175</v></c><c r="B576" t="inlineStr"><is><t xml:space="preserve">MainRevertAbortMessage</t></is></c><c r="C576" t="inlineStr"><is><t xml:space="preserve">커밋 취소를 중단하고 시작 전 상태로 되돌릴까요? 저장하지 않은 충돌 해결 초안, 저장한 해결 내용과 진행 중 편집한 파일의 변경이 사라질 수 있습니다. 저장소: {0}</t></is></c><c r="D576" t="inlineStr"><is><t xml:space="preserve">Abort the revert and return to the state before it started? Unsaved conflict drafts, saved resolutions, and file edits made during the operation may be lost. Repository: {0}</t></is></c></row><row r="577" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A577"><v>3176</v></c><c r="B577" t="inlineStr"><is><t xml:space="preserve">RevertIncomingChange</t></is></c><c r="C577" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경</t></is></c><c r="D577" t="inlineStr"><is><t xml:space="preserve">Revert changes</t></is></c></row><row r="578" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A578"><v>3177</v></c><c r="B578" t="inlineStr"><is><t xml:space="preserve">RevertUseIncomingChange</t></is></c><c r="C578" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 사용</t></is></c><c r="D578" t="inlineStr"><is><t xml:space="preserve">Use revert changes</t></is></c></row><row r="579" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A579"><v>3178</v></c><c r="B579" t="inlineStr"><is><t xml:space="preserve">RevertIncomingIndexSource</t></is></c><c r="C579" t="inlineStr"><is><t xml:space="preserve">되돌리기 변경 (인덱스 stage 3)</t></is></c><c r="D579" t="inlineStr"><is><t xml:space="preserve">Revert changes (index stage 3)</t></is></c></row><row r="580" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A580"><v>3179</v></c><c r="B580" t="inlineStr"><is><t xml:space="preserve">MainRevertSaveDraftBeforeContinue</t></is></c><c r="C580" t="inlineStr"><is><t xml:space="preserve">현재 충돌 파일의 추가 편집을 저장하거나 명시적으로 버린 뒤 계속하세요.</t></is></c><c r="D580" t="inlineStr"><is><t xml:space="preserve">Save or explicitly discard the additional edits in the current conflict file before continuing.</t></is></c></row><row r="581" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A581"><v>3180</v></c><c r="B581" t="inlineStr"><is><t xml:space="preserve">MainRevertCompleted</t></is></c><c r="C581" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 완료됐습니다.</t></is></c><c r="D581" t="inlineStr"><is><t xml:space="preserve">The revert completed.</t></is></c></row><row r="582" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A582"><v>3181</v></c><c r="B582" t="inlineStr"><is><t xml:space="preserve">MainRevertPaused</t></is></c><c r="C582" t="inlineStr"><is><t xml:space="preserve">커밋 취소가 진행 중입니다. 충돌을 해결하거나 표시된 오류를 확인하세요.</t></is></c><c r="D582" t="inlineStr"><is><t xml:space="preserve">The revert is still in progress. Resolve the conflicts or review the reported error.</t></is></c></row><row r="583" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A583"><v>3182</v></c><c r="B583" t="inlineStr"><is><t xml:space="preserve">MainRevertAborted</t></is></c><c r="C583" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D583" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="584" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A584"><v>3183</v></c><c r="B584" t="inlineStr"><is><t xml:space="preserve">HistoryRevertAborted</t></is></c><c r="C584" t="inlineStr"><is><t xml:space="preserve">진행 중인 커밋 취소를 중단했습니다.</t></is></c><c r="D584" t="inlineStr"><is><t xml:space="preserve">The pending revert was aborted.</t></is></c></row><row r="585" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A585"><v>3184</v></c><c r="B585" t="inlineStr"><is><t xml:space="preserve">LocalMutationErrorWithOperation</t></is></c><c r="C585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D585" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="586" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A586"><v>3185</v></c><c r="B586" t="inlineStr"><is><t xml:space="preserve">RemotePullLocalChangesWouldBeOverwritten</t></is></c><c r="C586" t="inlineStr"><is><t xml:space="preserve">로컬 변경을 덮어쓸 수 있어 병합이 시작되지 않았습니다. 변경을 커밋하거나 Stash에 보관한 뒤 다시 Pull하세요.</t></is></c><c r="D586" t="inlineStr"><is><t xml:space="preserve">The merge did not start because it would overwrite local changes. Commit or stash your changes, then pull again.</t></is></c></row><row r="587" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A587"><v>3186</v></c><c r="B587" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageAction</t></is></c><c r="C587" t="inlineStr"><is><t xml:space="preserve">모든 파일의 남은 구간 적용·저장·스테이징</t></is></c><c r="D587" t="inlineStr"><is><t xml:space="preserve">Apply, save and stage remaining sections in all files</t></is></c></row><row r="588" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A588"><v>3187</v></c><c r="B588" t="inlineStr"><is><t xml:space="preserve">ConflictBatchAllFilesScope</t></is></c><c r="C588" t="inlineStr"><is><t xml:space="preserve">충돌 파일 {0}개 · 기존 선택 보존</t></is></c><c r="D588" t="inlineStr"><is><t xml:space="preserve">{0} conflicted files · existing choices are preserved</t></is></c></row><row r="589" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A589"><v>3188</v></c><c r="B589" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageTooltip</t></is></c><c r="C589" t="inlineStr"><is><t xml:space="preserve">모든 충돌 파일의 아직 선택하지 않은 구간에만 같은 선택을 적용하고 파일을 저장·스테이징합니다. 이미 고른 구간은 보존합니다. 분리할 수 없는 수동 편집 파일은 제외하며, 병합 커밋·리베이스·Revert 계속은 자동 실행하지 않습니다.</t></is></c><c r="D589" t="inlineStr"><is><t xml:space="preserve">Apply the same choice only to unselected sections in all conflicted files, then save and stage the files. Existing choices are preserved. Files with inseparable manual edits are excluded. Merge commits, rebase continue and revert continue are not run automatically.</t></is></c></row><row r="590" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A590"><v>3189</v></c><c r="B590" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageSummary</t></is></c><c r="C590" t="inlineStr"><is><t xml:space="preserve">저장·스테이징 {0}개 · 실패 {1}개 · 제외 {2}개</t></is></c><c r="D590" t="inlineStr"><is><t xml:space="preserve">Saved and staged: {0} · Failed: {1} · Excluded: {2}</t></is></c></row><row r="591" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A591"><v>3190</v></c><c r="B591" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageManualExcluded</t></is></c><c r="C591" t="inlineStr"><is><t xml:space="preserve">수동 편집을 보존하기 위해 제외했습니다. 이 파일은 파일별 저장·스테이징을 사용하세요.</t></is></c><c r="D591" t="inlineStr"><is><t xml:space="preserve">Excluded to preserve manual edits. Use the individual save and stage action for this file.</t></is></c></row><row r="592" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A592"><v>3191</v></c><c r="B592" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageFileResult</t></is></c><c r="C592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c><c r="D592" t="inlineStr"><is><t xml:space="preserve">{0}: {1}</t></is></c></row><row r="593" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A593"><v>3192</v></c><c r="B593" t="inlineStr"><is><t xml:space="preserve">ConflictBatchStageRefreshFailed</t></is></c><c r="C593" t="inlineStr"><is><t xml:space="preserve">파일별 저장 결과는 유지됩니다. 완료 상태를 다시 읽지 못했습니다: {0}</t></is></c><c r="D593" t="inlineStr"><is><t xml:space="preserve">Per-file save results are preserved. The completion state could not be refreshed: {0}</t></is></c></row><row r="594" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A594"><v>3193</v></c><c r="B594" t="inlineStr"><is><t xml:space="preserve">AppUpdateHeading</t></is></c><c r="C594" t="inlineStr"><is><t xml:space="preserve">앱 업데이트</t></is></c><c r="D594" t="inlineStr"><is><t xml:space="preserve">Application update</t></is></c></row><row r="595" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A595"><v>3194</v></c><c r="B595" t="inlineStr"><is><t xml:space="preserve">AppUpdateDescription</t></is></c><c r="C595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">GitHub에 게시된 Bough 정식 릴리스만 확인합니다. 자동으로 조회하거나 설치하지 않습니다.</x:t></x:is></c><c r="D595" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Checks only official Bough releases published on GitHub. Updates are not checked or installed automatically.</x:t></x:is></c></row><row r="596" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A596"><v>3195</v></c><c r="B596" t="inlineStr"><is><t xml:space="preserve">AppUpdateCurrentVersionLabel</t></is></c><c r="C596" t="inlineStr"><is><t xml:space="preserve">현재 버전</t></is></c><c r="D596" t="inlineStr"><is><t xml:space="preserve">Current version</t></is></c></row><row r="597" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A597"><v>3196</v></c><c r="B597" t="inlineStr"><is><t xml:space="preserve">AppUpdateLatestVersionLabel</t></is></c><c r="C597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">최신 정식 버전</x:t></x:is></c><c r="D597" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Latest official version</x:t></x:is></c></row><row r="598" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A598"><v>3197</v></c><c r="B598" t="inlineStr"><is><t xml:space="preserve">AppUpdateVersionUnknown</t></is></c><c r="C598" t="inlineStr"><is><t xml:space="preserve">확인되지 않음</t></is></c><c r="D598" t="inlineStr"><is><t xml:space="preserve">Not available</t></is></c></row><row r="599" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A599"><v>3198</v></c><c r="B599" t="inlineStr"><is><t xml:space="preserve">AppUpdateNotChecked</t></is></c><c r="C599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">업데이트 확인을 눌러 최신 정식 릴리스를 조회하세요.</x:t></x:is></c><c r="D599" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Click Check for updates to look for the latest official release.</x:t></x:is></c></row><row r="600" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A600"><v>3199</v></c><c r="B600" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckAction</t></is></c><c r="C600" t="inlineStr"><is><t xml:space="preserve">업데이트 확인</t></is></c><c r="D600" t="inlineStr"><is><t xml:space="preserve">Check for updates</t></is></c></row><row r="601" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A601"><v>3200</v></c><c r="B601" t="inlineStr"><is><t xml:space="preserve">AppUpdateChecking</t></is></c><c r="C601" t="inlineStr"><is><t xml:space="preserve">최신 정식 릴리스를 확인하고 있습니다.</t></is></c><c r="D601" t="inlineStr"><is><t xml:space="preserve">Checking the latest official release.</t></is></c></row><row r="602" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A602"><v>3201</v></c><c r="B602" t="inlineStr"><is><t xml:space="preserve">AppUpdateNoOfficialRelease</t></is></c><c r="C602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">게시된 정식 릴리스가 없습니다.</x:t></x:is></c><c r="D602" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">No official release has been published.</x:t></x:is></c></row><row r="603" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A603"><v>3202</v></c><c r="B603" t="inlineStr"><is><t xml:space="preserve">AppUpdateUpToDate</t></is></c><c r="C603" t="inlineStr"><is><t xml:space="preserve">현재 버전보다 새로운 정식 릴리스가 없습니다.</t></is></c><c r="D603" t="inlineStr"><is><t xml:space="preserve">No newer official release is available.</t></is></c></row><row r="604" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A604"><v>3203</v></c><c r="B604" t="inlineStr"><is><t xml:space="preserve">AppUpdateAvailable</t></is></c><c r="C604" t="inlineStr"><is><t xml:space="preserve">새 정식 버전 {0}을 사용할 수 있습니다.</t></is></c><c r="D604" t="inlineStr"><is><t xml:space="preserve">Official version {0} is available.</t></is></c></row><row r="605" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A605"><v>3204</v></c><c r="B605" t="inlineStr"><is><t xml:space="preserve">AppUpdateCheckFailed</t></is></c><c r="C605" t="inlineStr"><is><t xml:space="preserve">업데이트 확인에 실패했습니다: {0}</t></is></c><c r="D605" t="inlineStr"><is><t xml:space="preserve">Could not check for updates: {0}</t></is></c></row><row r="606" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A606"><v>3205</v></c><c r="B606" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartAction</t></is></c><c r="C606" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작</t></is></c><c r="D606" t="inlineStr"><is><t xml:space="preserve">Update and restart</t></is></c></row><row r="607" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A607"><v>3206</v></c><c r="B607" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingKnown</t></is></c><c r="C607" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} / {1} MiB</t></is></c><c r="D607" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} / {1} MiB</t></is></c></row><row r="608" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A608"><v>3207</v></c><c r="B608" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadingUnknown</t></is></c><c r="C608" t="inlineStr"><is><t xml:space="preserve">다운로드 중: {0} MiB</t></is></c><c r="D608" t="inlineStr"><is><t xml:space="preserve">Downloading: {0} MiB</t></is></c></row><row r="609" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A609"><v>3208</v></c><c r="B609" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelAction</t></is></c><c r="C609" t="inlineStr"><is><t xml:space="preserve">취소</t></is></c><c r="D609" t="inlineStr"><is><t xml:space="preserve">Cancel</t></is></c></row><row r="610" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A610"><v>3209</v></c><c r="B610" t="inlineStr"><is><t xml:space="preserve">AppUpdateCancelled</t></is></c><c r="C610" t="inlineStr"><is><t xml:space="preserve">업데이트 작업을 취소했습니다. 현재 앱은 변경되지 않았습니다.</t></is></c><c r="D610" t="inlineStr"><is><t xml:space="preserve">The update was cancelled. The current application was not changed.</t></is></c></row><row r="611" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A611"><v>3210</v></c><c r="B611" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadFailed</t></is></c><c r="C611" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 또는 확인에 실패했습니다: {0}</t></is></c><c r="D611" t="inlineStr"><is><t xml:space="preserve">The update download or verification failed: {0}</t></is></c></row><row r="612" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A612"><v>3211</v></c><c r="B612" t="inlineStr"><is><t xml:space="preserve">AppUpdateReady</t></is></c><c r="C612" t="inlineStr"><is><t xml:space="preserve">버전 {0}의 다운로드와 확인이 완료되었습니다.</t></is></c><c r="D612" t="inlineStr"><is><t xml:space="preserve">Version {0} has been downloaded and verified.</t></is></c></row><row r="613" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A613"><v>3212</v></c><c r="B613" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartPreparing</t></is></c><c r="C613" t="inlineStr"><is><t xml:space="preserve">앱의 정상 종료와 업데이트 후 재시작을 준비하고 있습니다.</t></is></c><c r="D613" t="inlineStr"><is><t xml:space="preserve">Preparing to close the application normally and restart after updating.</t></is></c></row><row r="614" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A614"><v>3213</v></c><c r="B614" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartCancelled</t></is></c><c r="C614" t="inlineStr"><is><t xml:space="preserve">앱 종료가 취소되어 업데이트를 적용하지 않았습니다.</t></is></c><c r="D614" t="inlineStr"><is><t xml:space="preserve">Application shutdown was cancelled. The update was not applied.</t></is></c></row><row r="615" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A615"><v>3214</v></c><c r="B615" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartFailed</t></is></c><c r="C615" t="inlineStr"><is><t xml:space="preserve">업데이트 후 재시작을 준비하지 못했습니다: {0}</t></is></c><c r="D615" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update and restart: {0}</t></is></c></row><row r="616" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A616"><v>3215</v></c><c r="B616" t="inlineStr"><is><t xml:space="preserve">AppUpdateRestartScheduled</t></is></c><c r="C616" t="inlineStr"><is><t xml:space="preserve">앱이 정상 종료된 뒤 업데이트를 적용하고 다시 실행합니다.</t></is></c><c r="D616" t="inlineStr"><is><t xml:space="preserve">The update will be applied and the application restarted after normal shutdown.</t></is></c></row><row r="617" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A617"><v>3216</v></c><c r="B617" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseAction</t></is></c><c r="C617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">정식 릴리스 페이지 열기</x:t></x:is></c><c r="D617" t="inlineStr"><x:is><x:t d6p1:space="preserve" xmlns:d6p1="http://www.w3.org/XML/1998/namespace">Open official release page</x:t></x:is></c></row><row r="618" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A618"><v>3217</v></c><c r="B618" t="inlineStr"><is><t xml:space="preserve">AppUpdateInstallUnsupported</t></is></c><c r="C618" t="inlineStr"><is><t xml:space="preserve">현재 실행 환경에서는 자동 업데이트를 적용할 수 없습니다. 정식 릴리스 페이지를 확인하세요.</t></is></c><c r="D618" t="inlineStr"><is><t xml:space="preserve">Automatic updating is not supported in this running environment. See the official release page.</t></is></c></row><row r="619" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A619"><v>3218</v></c><c r="B619" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDeploymentRequired</t></is></c><c r="C619" t="inlineStr"><is><t xml:space="preserve">자동 업데이트는 배포된 Windows x64 단일 실행 파일에서만 사용할 수 있습니다. 릴리스 페이지에서 새 버전을 다운로드하세요.</t></is></c><c r="D619" t="inlineStr"><is><t xml:space="preserve">Automatic updates are available only in the published Windows x64 single executable. Download the new version from the release page.</t></is></c></row><row r="620" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A620"><v>3219</v></c><c r="B620" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCurrentVersionInvalid</t></is></c><c r="C620" t="inlineStr"><is><t xml:space="preserve">현재 앱의 배포 버전을 확인할 수 없습니다. 릴리스 페이지에서 새 버전을 확인하세요.</t></is></c><c r="D620" t="inlineStr"><is><t xml:space="preserve">The current application version could not be identified. Check the release page for a new version.</t></is></c></row><row r="621" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A621"><v>3220</v></c><c r="B621" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryFailed</t></is></c><c r="C621" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 조회 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 확인하세요.</t></is></c><c r="D621" t="inlineStr"><is><t xml:space="preserve">The stable release request failed (HTTP {0}). Try again later.</t></is></c></row><row r="622" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A622"><v>3221</v></c><c r="B622" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreQueryUnavailable</t></is></c><c r="C622" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 정보를 가져오지 못했습니다. 네트워크 연결을 확인하세요.</t></is></c><c r="D622" t="inlineStr"><is><t xml:space="preserve">Could not retrieve the stable release information. Check your network connection.</t></is></c></row><row r="623" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A623"><v>3222</v></c><c r="B623" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReleaseInvalid</t></is></c><c r="C623" t="inlineStr"><is><t xml:space="preserve">공식 정식 릴리스 정보를 확인할 수 없어 자동 업데이트를 중단했습니다.</t></is></c><c r="D623" t="inlineStr"><is><t xml:space="preserve">Automatic updating was stopped because the official stable release information could not be verified.</t></is></c></row><row r="624" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A624"><v>3223</v></c><c r="B624" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreAssetUnavailable</t></is></c><c r="C624" t="inlineStr"><is><t xml:space="preserve">이 정식 릴리스에서 Windows x64 단일 실행 파일을 찾을 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D624" t="inlineStr"><is><t xml:space="preserve">The Windows x64 single executable is unavailable in this stable release. Check the release page.</t></is></c></row><row r="625" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A625"><v>3224</v></c><c r="B625" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMissing</t></is></c><c r="C625" t="inlineStr"><is><t xml:space="preserve">공식 SHA-256 정보가 없어 자동으로 교체할 수 없습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D625" t="inlineStr"><is><t xml:space="preserve">Automatic replacement is unavailable because the official SHA-256 digest is missing. Check the release page.</t></is></c></row><row r="626" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A626"><v>3225</v></c><c r="B626" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadIncomplete</t></is></c><c r="C626" t="inlineStr"><is><t xml:space="preserve">업데이트 파일이 완전히 다운로드되지 않았습니다. 현재 실행 파일은 변경하지 않았습니다.</t></is></c><c r="D626" t="inlineStr"><is><t xml:space="preserve">The update file was not downloaded completely. The current executable has not been changed.</t></is></c></row><row r="627" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A627"><v>3226</v></c><c r="B627" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDownloadUnavailable</t></is></c><c r="C627" t="inlineStr"><is><t xml:space="preserve">업데이트를 다운로드하지 못했습니다. 네트워크 연결과 임시 폴더의 접근 권한·여유 공간을 확인하세요.</t></is></c><c r="D627" t="inlineStr"><is><t xml:space="preserve">Could not download the update. Check your connection, temporary folder permissions, and available disk space.</t></is></c></row><row r="628" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A628"><v>3227</v></c><c r="B628" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreDigestMismatch</t></is></c><c r="C628" t="inlineStr"><is><t xml:space="preserve">다운로드한 파일의 SHA-256이 공식 정보와 일치하지 않습니다. 자동 교체하지 않습니다. 릴리스 페이지를 확인하세요.</t></is></c><c r="D628" t="inlineStr"><is><t xml:space="preserve">The downloaded file's SHA-256 does not match the official digest. It will not be installed automatically. Check the release page.</t></is></c></row><row r="629" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A629"><v>3228</v></c><c r="B629" t="inlineStr"><is><t xml:space="preserve">AppUpdateCorePrepareFailed</t></is></c><c r="C629" t="inlineStr"><is><t xml:space="preserve">업데이트 재시작을 준비하지 못했습니다. 현재 앱과 실행 파일은 유지됩니다.</t></is></c><c r="D629" t="inlineStr"><is><t xml:space="preserve">Could not prepare the update restart. The current application and executable are retained.</t></is></c></row><row r="630" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A630"><v>3229</v></c><c r="B630" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreGitBusy</t></is></c><c r="C630" t="inlineStr"><is><t xml:space="preserve">앱 작업이나 Git 실행·대기 작업이 남아 있습니다. 작업이 끝난 뒤 업데이트 후 재시작을 다시 선택하세요.</t></is></c><c r="D630" t="inlineStr"><is><t xml:space="preserve">Application work or running or queued Git operations remain. Select update and restart again after they finish.</t></is></c></row><row r="631" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A631"><v>3230</v></c><c r="B631" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreCloseUnavailable</t></is></c><c r="C631" t="inlineStr"><is><t xml:space="preserve">현재 메인 창에 정상 종료를 요청할 수 없습니다. 앱을 다시 연 뒤 업데이트를 시도하세요.</t></is></c><c r="D631" t="inlineStr"><is><t xml:space="preserve">A normal shutdown cannot be requested from the current main window. Reopen the application before trying to update.</t></is></c></row><row r="632" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A632"><v>3231</v></c><c r="B632" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreReplaceFailed</t></is></c><c r="C632" t="inlineStr"><is><t xml:space="preserve">업데이트 파일을 교체하지 못해 기존 앱을 다시 열었습니다. 실행 파일의 접근 권한과 다른 실행 중인 Bough를 확인하세요.</t></is></c><c r="D632" t="inlineStr"><is><t xml:space="preserve">The update could not replace the executable, so the previous application was reopened. Check file permissions and other running instances of Bough.</t></is></c></row><row r="633" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A633"><v>3232</v></c><c r="B633" t="inlineStr"><is><t xml:space="preserve">AppUpdateCoreRollbackFailed</t></is></c><c r="C633" t="inlineStr"><is><t xml:space="preserve">업데이트 실패 후 기존 실행 파일 복원을 완료하지 못했습니다. 설치 폴더에 보존된 백업과 접근 권한을 확인하세요.</t></is></c><c r="D633" t="inlineStr"><is><t xml:space="preserve">Restoring the previous executable after the update failure could not be completed. Check the preserved backup and permissions in the installation folder.</t></is></c></row><row r="634" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A634"><v>3233</v></c><c r="B634" t="inlineStr"><is><t xml:space="preserve">AppUpdateDownloadRequestFailed</t></is></c><c r="C634" t="inlineStr"><is><t xml:space="preserve">업데이트 다운로드 요청이 실패했습니다(HTTP {0}). 잠시 후 다시 시도하세요.</t></is></c><c r="D634" t="inlineStr"><is><t xml:space="preserve">The update download request failed (HTTP {0}). Try again later.</t></is></c></row><row r="635" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A635"><v>3234</v></c><c r="B635" t="inlineStr"><is><t xml:space="preserve">AppUpdateLaunchFailed</t></is></c><c r="C635" t="inlineStr"><is><t xml:space="preserve">새 버전을 실행하지 못해 기존 실행 파일을 복원했습니다. 기존 앱을 계속 사용할 수 있습니다.</t></is></c><c r="D635" t="inlineStr"><is><t xml:space="preserve">The new version could not be started, so the previous executable was restored. You can continue using the previous application.</t></is></c></row><row r="636" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A636"><v>3235</v></c><c r="B636" t="inlineStr"><is><t xml:space="preserve">AppUpdateReleaseOpenFailed</t></is></c><c r="C636" t="inlineStr"><is><t xml:space="preserve">정식 릴리스 페이지를 열지 못했습니다. 잠시 후 다시 시도하세요.</t></is></c><c r="D636" t="inlineStr"><is><t xml:space="preserve">Could not open the official release page. Please try again shortly.</t></is></c></row><row r="637" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A637"><v>3236</v></c><c r="B637" t="inlineStr"><is><t xml:space="preserve">AutoFetchHeading</t></is></c><c r="C637" t="inlineStr"><is><t xml:space="preserve">원격 변경 자동 확인</t></is></c><c r="D637" t="inlineStr"><is><t xml:space="preserve">Automatic remote checks</t></is></c></row><row r="638" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A638"><v>3237</v></c><c r="B638" t="inlineStr"><is><t xml:space="preserve">AutoFetchDescription</t></is></c><c r="C638" t="inlineStr"><is><t xml:space="preserve">현재 열린 저장소의 원격 변경을 주기적으로 가져와 받을 새 커밋을 알려줍니다. Pull과 작업 파일 변경은 자동 실행하지 않습니다.</t></is></c><c r="D638" t="inlineStr"><is><t xml:space="preserve">Fetch remote changes periodically for the open repository and show new incoming commits. Pull and working file changes are not performed automatically.</t></is></c></row><row r="639" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A639"><v>3238</v></c><c r="B639" t="inlineStr"><is><t xml:space="preserve">AutoFetchEnabledLabel</t></is></c><c r="C639" t="inlineStr"><is><t xml:space="preserve">주기적으로 원격 변경 확인</t></is></c><c r="D639" t="inlineStr"><is><t xml:space="preserve">Check for remote changes periodically</t></is></c></row><row r="640" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A640"><v>3239</v></c><c r="B640" t="inlineStr"><is><t xml:space="preserve">AutoFetchIntervalLabel</t></is></c><c r="C640" t="inlineStr"><is><t xml:space="preserve">확인 주기</t></is></c><c r="D640" t="inlineStr"><is><t xml:space="preserve">Check interval</t></is></c></row><row r="641" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A641"><v>3240</v></c><c r="B641" t="inlineStr"><is><t xml:space="preserve">AutoFetch1Minute</t></is></c><c r="C641" t="inlineStr"><is><t xml:space="preserve">1분</t></is></c><c r="D641" t="inlineStr"><is><t xml:space="preserve">1 minute</t></is></c></row><row r="642" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A642"><v>3241</v></c><c r="B642" t="inlineStr"><is><t xml:space="preserve">AutoFetch5Minutes</t></is></c><c r="C642" t="inlineStr"><is><t xml:space="preserve">5분</t></is></c><c r="D642" t="inlineStr"><is><t xml:space="preserve">5 minutes</t></is></c></row><row r="643" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A643"><v>3242</v></c><c r="B643" t="inlineStr"><is><t xml:space="preserve">AutoFetch10Minutes</t></is></c><c r="C643" t="inlineStr"><is><t xml:space="preserve">10분</t></is></c><c r="D643" t="inlineStr"><is><t xml:space="preserve">10 minutes</t></is></c></row><row r="644" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A644"><v>3243</v></c><c r="B644" t="inlineStr"><is><t xml:space="preserve">AutoFetch30Minutes</t></is></c><c r="C644" t="inlineStr"><is><t xml:space="preserve">30분</t></is></c><c r="D644" t="inlineStr"><is><t xml:space="preserve">30 minutes</t></is></c></row><row r="645" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A645"><v>3244</v></c><c r="B645" t="inlineStr"><is><t xml:space="preserve">AutoFetchSettingsSaved</t></is></c><c r="C645" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 설정을 저장했습니다.</t></is></c><c r="D645" t="inlineStr"><is><t xml:space="preserve">Automatic remote check settings saved.</t></is></c></row><row r="646" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A646"><v>3245</v></c><c r="B646" t="inlineStr"><is><t xml:space="preserve">AutoFetchOperationName</t></is></c><c r="C646" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인</t></is></c><c r="D646" t="inlineStr"><is><t xml:space="preserve">Automatic remote check</t></is></c></row><row r="647" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A647"><v>3246</v></c><c r="B647" t="inlineStr"><is><t xml:space="preserve">RemoteIncomingCommits</t></is></c><c r="C647" t="inlineStr"><is><t xml:space="preserve">받을 새 커밋 {0}개</t></is></c><c r="D647" t="inlineStr"><is><t xml:space="preserve">{0} new commits to pull</t></is></c></row><row r="648" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A648"><v>3247</v></c><c r="B648" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchFailed</t></is></c><c r="C648" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인에 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D648" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed. Use Fetch to try again.</t></is></c></row><row r="649" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A649"><v>3248</v></c><c r="B649" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchConfigurationUnavailable</t></is></c><c r="C649" t="inlineStr"><is><t xml:space="preserve">이 원격 또는 사용자 지정 SSH 설정은 자동 확인할 수 없습니다. Fetch로 직접 확인하세요.</t></is></c><c r="D649" t="inlineStr"><is><t xml:space="preserve">This remote or custom SSH configuration cannot be checked automatically. Use Fetch manually.</t></is></c></row><row r="650" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A650"><v>3249</v></c><c r="B650" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchRequestFailed</t></is></c><c r="C650" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인이 종료 코드 {0}으로 실패했습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D650" t="inlineStr"><is><t xml:space="preserve">Automatic remote check failed with exit code {0}. Use Fetch to try again.</t></is></c></row><row r="651" spans="1:4" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><c r="A651"><v>3250</v></c><c r="B651" t="inlineStr"><is><t xml:space="preserve">RemoteAutoFetchTimedOut</t></is></c><c r="C651" t="inlineStr"><is><t xml:space="preserve">원격 자동 확인 시간이 초과됐습니다. Fetch로 다시 확인하세요.</t></is></c><c r="D651" t="inlineStr"><is><t xml:space="preserve">Automatic remote check timed out. Use Fetch to try again.</t></is></c></row><x:row r="652"><x:c r="A652"><x:v>3251</x:v></x:c><x:c r="B652" t="s"><x:v>573</x:v></x:c><x:c r="C652" t="s"><x:v>574</x:v></x:c><x:c r="D652" t="s"><x:v>575</x:v></x:c></x:row><x:row r="653"><x:c r="A653"><x:v>3252</x:v></x:c><x:c r="B653" t="s"><x:v>576</x:v></x:c><x:c r="C653" t="s"><x:v>577</x:v></x:c><x:c r="D653" t="s"><x:v>578</x:v></x:c></x:row><x:row r="654"><x:c r="A654"><x:v>3253</x:v></x:c><x:c r="B654" t="s"><x:v>579</x:v></x:c><x:c r="C654" t="s"><x:v>580</x:v></x:c><x:c r="D654" t="s"><x:v>581</x:v></x:c></x:row><x:row r="655"><x:c r="A655"><x:v>3254</x:v></x:c><x:c r="B655" t="s"><x:v>582</x:v></x:c><x:c r="C655" t="s"><x:v>583</x:v></x:c><x:c r="D655" t="s"><x:v>584</x:v></x:c></x:row><x:row r="656"><x:c r="A656"><x:v>3255</x:v></x:c><x:c r="B656" t="s"><x:v>585</x:v></x:c><x:c r="C656" t="s"><x:v>586</x:v></x:c><x:c r="D656" t="s"><x:v>587</x:v></x:c></x:row><x:row r="657"><x:c r="A657"><x:v>3256</x:v></x:c><x:c r="B657" t="s"><x:v>588</x:v></x:c><x:c r="C657" t="s"><x:v>589</x:v></x:c><x:c r="D657" t="s"><x:v>589</x:v></x:c></x:row><x:row r="658"><x:c r="A658"><x:v>3257</x:v></x:c><x:c r="B658" t="s"><x:v>590</x:v></x:c><x:c r="C658" t="s"><x:v>591</x:v></x:c><x:c r="D658" t="s"><x:v>592</x:v></x:c></x:row><x:row r="659"><x:c r="A659"><x:v>3258</x:v></x:c><x:c r="B659" t="s"><x:v>593</x:v></x:c><x:c r="C659" t="s"><x:v>594</x:v></x:c><x:c r="D659" t="s"><x:v>595</x:v></x:c></x:row><x:row r="660"><x:c r="A660"><x:v>3259</x:v></x:c><x:c r="B660" t="s"><x:v>596</x:v></x:c><x:c r="C660" t="s"><x:v>597</x:v></x:c><x:c r="D660" t="s"><x:v>598</x:v></x:c></x:row><x:row r="661"><x:c r="A661"><x:v>3260</x:v></x:c><x:c r="B661" t="s"><x:v>599</x:v></x:c><x:c r="C661" t="s"><x:v>600</x:v></x:c><x:c r="D661" t="s"><x:v>601</x:v></x:c></x:row><x:row r="662"><x:c r="A662"><x:v>3261</x:v></x:c><x:c r="B662" t="s"><x:v>602</x:v></x:c><x:c r="C662" t="s"><x:v>603</x:v></x:c><x:c r="D662" t="s"><x:v>604</x:v></x:c></x:row><x:row r="663"><x:c r="A663"><x:v>3262</x:v></x:c><x:c r="B663" t="s"><x:v>605</x:v></x:c><x:c r="C663" t="s"><x:v>606</x:v></x:c><x:c r="D663" t="s"><x:v>607</x:v></x:c></x:row><x:row r="664"><x:c r="A664"><x:v>3263</x:v></x:c><x:c r="B664" t="s"><x:v>608</x:v></x:c><x:c r="C664" t="s"><x:v>609</x:v></x:c><x:c r="D664" t="s"><x:v>610</x:v></x:c></x:row><x:row r="665"><x:c r="A665"><x:v>3264</x:v></x:c><x:c r="B665" t="s"><x:v>611</x:v></x:c><x:c r="C665" t="s"><x:v>612</x:v></x:c><x:c r="D665" t="s"><x:v>613</x:v></x:c></x:row><x:row r="666"><x:c r="A666"><x:v>3265</x:v></x:c><x:c r="B666" t="s"><x:v>614</x:v></x:c><x:c r="C666" t="s"><x:v>615</x:v></x:c><x:c r="D666" t="s"><x:v>616</x:v></x:c></x:row><x:row r="667"><x:c r="A667"><x:v>3266</x:v></x:c><x:c r="B667" t="s"><x:v>617</x:v></x:c><x:c r="C667" t="s"><x:v>618</x:v></x:c><x:c r="D667" t="s"><x:v>619</x:v></x:c></x:row><x:row r="668"><x:c r="A668"><x:v>3267</x:v></x:c><x:c r="B668" t="s"><x:v>620</x:v></x:c><x:c r="C668" t="s"><x:v>621</x:v></x:c><x:c r="D668" t="s"><x:v>622</x:v></x:c></x:row><x:row r="669"><x:c r="A669"><x:v>3268</x:v></x:c><x:c r="B669" t="s"><x:v>623</x:v></x:c><x:c r="C669" t="s"><x:v>624</x:v></x:c><x:c r="D669" t="s"><x:v>625</x:v></x:c></x:row><x:row r="670"><x:c r="A670"><x:v>3269</x:v></x:c><x:c r="B670" t="s"><x:v>626</x:v></x:c><x:c r="C670" t="s"><x:v>627</x:v></x:c><x:c r="D670" t="s"><x:v>628</x:v></x:c></x:row><x:row r="671"><x:c r="A671"><x:v>3270</x:v></x:c><x:c r="B671" t="s"><x:v>629</x:v></x:c><x:c r="C671" t="s"><x:v>630</x:v></x:c><x:c r="D671" t="s"><x:v>631</x:v></x:c></x:row><x:row r="672"><x:c r="A672"><x:v>3271</x:v></x:c><x:c r="B672" t="s"><x:v>632</x:v></x:c><x:c r="C672" t="s"><x:v>633</x:v></x:c><x:c r="D672" t="s"><x:v>634</x:v></x:c></x:row><x:row r="673"><x:c r="A673"><x:v>3272</x:v></x:c><x:c r="B673" t="s"><x:v>635</x:v></x:c><x:c r="C673" t="s"><x:v>636</x:v></x:c><x:c r="D673" t="s"><x:v>637</x:v></x:c></x:row><x:row r="674"><x:c r="A674"><x:v>3273</x:v></x:c><x:c r="B674" t="s"><x:v>638</x:v></x:c><x:c r="C674" t="s"><x:v>639</x:v></x:c><x:c r="D674" t="s"><x:v>640</x:v></x:c></x:row><x:row r="675"><x:c r="A675"><x:v>3274</x:v></x:c><x:c r="B675" t="s"><x:v>641</x:v></x:c><x:c r="C675" t="s"><x:v>642</x:v></x:c><x:c r="D675" t="s"><x:v>643</x:v></x:c></x:row><x:row r="676"><x:c r="A676"><x:v>3275</x:v></x:c><x:c r="B676" t="s"><x:v>644</x:v></x:c><x:c r="C676" t="s"><x:v>645</x:v></x:c><x:c r="D676" t="s"><x:v>646</x:v></x:c></x:row><x:row r="677"><x:c r="A677"><x:v>3276</x:v></x:c><x:c r="B677" t="s"><x:v>647</x:v></x:c><x:c r="C677" t="s"><x:v>648</x:v></x:c><x:c r="D677" t="s"><x:v>649</x:v></x:c></x:row><x:row r="678"><x:c r="A678"><x:v>3277</x:v></x:c><x:c r="B678" t="s"><x:v>650</x:v></x:c><x:c r="C678" t="s"><x:v>651</x:v></x:c><x:c r="D678" t="s"><x:v>652</x:v></x:c></x:row><x:row r="679"><x:c r="A679"><x:v>3278</x:v></x:c><x:c r="B679" t="s"><x:v>653</x:v></x:c><x:c r="C679" t="s"><x:v>654</x:v></x:c><x:c r="D679" t="s"><x:v>655</x:v></x:c></x:row><x:row r="680" spans="1:4"><x:c r="A680"><x:v>3279</x:v></x:c><x:c r="B680" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathLabel</x:t></x:is></x:c><x:c r="C680" t="inlineStr"><x:is><x:t xml:space="preserve">무시 패턴</x:t></x:is></x:c><x:c r="D680" t="inlineStr"><x:is><x:t xml:space="preserve">Ignore pattern</x:t></x:is></x:c></x:row><x:row r="681" spans="1:4"><x:c r="A681"><x:v>3280</x:v></x:c><x:c r="B681" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPathHint</x:t></x:is></x:c><x:c r="C681" t="inlineStr"><x:is><x:t xml:space="preserve">Git 무시 패턴을 한 줄로 입력하세요(*, **, ?, [] 등). 비워두면 선택 파일을 무시합니다. 맨 앞 !는 재포함, #은 주석입니다.</x:t></x:is></x:c><x:c r="D681" t="inlineStr"><x:is><x:t xml:space="preserve">Enter one Git ignore pattern (*, **, ?, [] etc.). Leave empty to ignore the selected files. A leading ! re-includes; a leading # is a comment.</x:t></x:is></x:c></x:row><x:row r="682" spans="1:4"><x:c r="A682"><x:v>3281</x:v></x:c><x:c r="B682" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryConfirmDescription</x:t></x:is></x:c><x:c r="C682" t="inlineStr"><x:is><x:t xml:space="preserve">폴더 전체: {0}
 적용 위치: {1}
 하위 미추적 항목과 앞으로 추가할 파일을 무시합니다. 이미 추적 중인 파일은 유지됩니다.</x:t></x:is></x:c><x:c r="D682" t="inlineStr"><x:is><x:t xml:space="preserve">Entire folder: {0}
 Ignore location: {1}
-Untracked contents and future files will be ignored. Already tracked files are unchanged.</x:t></x:is></x:c></x:row><x:row r="683" spans="1:4"><x:c r="A683"><x:v>3282</x:v></x:c><x:c r="B683" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPreparing</x:t></x:is></x:c><x:c r="C683" t="inlineStr"><x:is><x:t xml:space="preserve">무시할 범위와 규칙을 준비하고 있습니다.</x:t></x:is></x:c><x:c r="D683" t="inlineStr"><x:is><x:t xml:space="preserve">Preparing the ignore scope and rule.</x:t></x:is></x:c></x:row><x:row r="684" spans="1:4"><x:c r="A684"><x:v>3283</x:v></x:c><x:c r="B684" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryUnavailable</x:t></x:is></x:c><x:c r="C684" t="inlineStr"><x:is><x:t xml:space="preserve">폴더를 사용할 수 없습니다. 저장소 안에 있는 실제 폴더 경로를 입력하세요: {0}</x:t></x:is></x:c><x:c r="D684" t="inlineStr"><x:is><x:t xml:space="preserve">The folder is unavailable. Enter an existing folder path inside the repository: {0}</x:t></x:is></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
+Untracked contents and future files will be ignored. Already tracked files are unchanged.</x:t></x:is></x:c></x:row><x:row r="683" spans="1:4"><x:c r="A683"><x:v>3282</x:v></x:c><x:c r="B683" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryPreparing</x:t></x:is></x:c><x:c r="C683" t="inlineStr"><x:is><x:t xml:space="preserve">무시할 범위와 규칙을 준비하고 있습니다.</x:t></x:is></x:c><x:c r="D683" t="inlineStr"><x:is><x:t xml:space="preserve">Preparing the ignore scope and rule.</x:t></x:is></x:c></x:row><x:row r="684" spans="1:4"><x:c r="A684"><x:v>3283</x:v></x:c><x:c r="B684" t="inlineStr"><x:is><x:t xml:space="preserve">IgnoreDirectoryUnavailable</x:t></x:is></x:c><x:c r="C684" t="inlineStr"><x:is><x:t xml:space="preserve">폴더를 사용할 수 없습니다. 저장소 안에 있는 실제 폴더 경로를 입력하세요: {0}</x:t></x:is></x:c><x:c r="D684" t="inlineStr"><x:is><x:t xml:space="preserve">The folder is unavailable. Enter an existing folder path inside the repository: {0}</x:t></x:is></x:c></x:row><x:row r="685" spans="1:4"><x:c r="A685"><x:v>3284</x:v></x:c><x:c r="B685" t="inlineStr"><x:is><x:t xml:space="preserve">IgnorePatternConfirmDescription</x:t></x:is></x:c><x:c r="C685" t="inlineStr"><x:is><x:t xml:space="preserve">기록할 Git 무시 패턴: {0}
+적용 위치: {1}
+Git이 입력한 패턴을 그대로 해석합니다.</x:t></x:is></x:c><x:c r="D685" t="inlineStr"><x:is><x:t xml:space="preserve">Git ignore pattern to write: {0}
+Write to: {1}
+Git interprets the pattern as entered.</x:t></x:is></x:c></x:row><x:row r="686" spans="1:4"><x:c r="A686"><x:v>3285</x:v></x:c><x:c r="B686" t="inlineStr"><x:is><x:t xml:space="preserve">IgnorePatternInvalid</x:t></x:is></x:c><x:c r="C686" t="inlineStr"><x:is><x:t xml:space="preserve">무시 패턴은 비어 있지 않은 한 줄이어야 하며 제어 문자를 포함할 수 없습니다.</x:t></x:is></x:c><x:c r="D686" t="inlineStr"><x:is><x:t xml:space="preserve">Enter one nonempty ignore pattern without line breaks or control characters.</x:t></x:is></x:c></x:row></x:sheetData><x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3" /></x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
